--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -5674,14 +5674,14 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>6.7614</v>
+        <v>6.7571</v>
       </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="6" t="n">
         <v>6.7621</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>6.7565</v>
+        <v>6.756</v>
       </c>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
@@ -5712,13 +5712,13 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>21.96</v>
+        <v>22.27</v>
       </c>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
+      <c r="H8" s="6" t="n">
+        <v>0.31</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3642,1749 +3642,4299 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>101450</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>106650</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>104050</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>186900</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>195800</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>191350</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>94200</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>98900</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>96550</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>191000</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>200500</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>195750</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>116650</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>122450</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>119550</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>214300</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>223900</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>219100</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>211600</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>219900</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>215750</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>-600</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="F101" s="6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>102407</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>106587</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>104497</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>-76.5</v>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>155318</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>155318</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>155318</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>-2320</v>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>7646</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>7646</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>7646</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H106" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>33050</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>33050</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>33050</v>
+      </c>
+      <c r="F107" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>170885</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>170885</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>170885</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>89058</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>89058</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>89058</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>-666</v>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>7494</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>7494</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>7494</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>7062</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>7062</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>7062</v>
+      </c>
+      <c r="F111" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H111" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H112" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E113" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F113" s="6" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="E115" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="F115" s="6" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>118000</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H117" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>339000</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>344500</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H118" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>139000</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>146000</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>142500</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>162000</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>171000</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>166500</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>1070000</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>1105000</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>2430</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>2550</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>2490</v>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>22400</v>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>25550</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>23975</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>26600</v>
+      </c>
+      <c r="D125" s="4" t="n">
+        <v>30750</v>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>28675</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H125" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>16600</v>
+      </c>
+      <c r="D126" s="4" t="n">
+        <v>18300</v>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>17450</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D127" s="4" t="n">
+        <v>11800</v>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>11300</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>17800</v>
+      </c>
+      <c r="D128" s="4" t="n">
+        <v>19300</v>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>18550</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E129" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D130" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E130" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>315000</v>
+      </c>
+      <c r="D131" s="4" t="n">
+        <v>330000</v>
+      </c>
+      <c r="E131" s="4" t="n">
+        <v>322500</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>-5500</v>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H131" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>108000</v>
+      </c>
+      <c r="D132" s="4" t="n">
+        <v>114000</v>
+      </c>
+      <c r="E132" s="4" t="n">
+        <v>111000</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>39000</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E133" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>2420</v>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>2530</v>
+      </c>
+      <c r="E134" s="4" t="n">
+        <v>2475</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>2450</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>2560</v>
+      </c>
+      <c r="E135" s="4" t="n">
+        <v>2505</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H135" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="D136" s="4" t="n">
+        <v>295</v>
+      </c>
+      <c r="E136" s="4" t="n">
+        <v>265</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>288000</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>295000</v>
+      </c>
+      <c r="E137" s="4" t="n">
+        <v>291500</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H137" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="E138" s="6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D139" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E139" s="6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>154000</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>168000</v>
+      </c>
+      <c r="E140" s="4" t="n">
+        <v>161000</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>148000</v>
+      </c>
+      <c r="D141" s="4" t="n">
+        <v>162000</v>
+      </c>
+      <c r="E141" s="4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H141" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>7590</v>
+      </c>
+      <c r="D142" s="4" t="n">
+        <v>7790</v>
+      </c>
+      <c r="E142" s="4" t="n">
+        <v>7690</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>33400</v>
+      </c>
+      <c r="D143" s="4" t="n">
+        <v>33820</v>
+      </c>
+      <c r="E143" s="4" t="n">
+        <v>33610</v>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>166000</v>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>175000</v>
+      </c>
+      <c r="E144" s="4" t="n">
+        <v>170500</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="E145" s="6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="D146" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="E146" s="6" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D147" s="4" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="E147" s="4" t="n">
+        <v>1135000</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H147" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>385000</v>
+      </c>
+      <c r="D148" s="4" t="n">
+        <v>410000</v>
+      </c>
+      <c r="E148" s="4" t="n">
+        <v>397500</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D149" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E149" s="6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>34500</v>
+      </c>
+      <c r="D150" s="4" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E150" s="4" t="n">
+        <v>36750</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>88000</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>90500</v>
+      </c>
+      <c r="E151" s="4" t="n">
+        <v>89250</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>-750</v>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>215000</v>
+      </c>
+      <c r="D152" s="4" t="n">
+        <v>232000</v>
+      </c>
+      <c r="E152" s="4" t="n">
+        <v>223500</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>59570</v>
+      </c>
+      <c r="D153" s="4" t="n">
+        <v>60570</v>
+      </c>
+      <c r="E153" s="4" t="n">
+        <v>60070</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>64500</v>
+      </c>
+      <c r="D154" s="4" t="n">
+        <v>69500</v>
+      </c>
+      <c r="E154" s="4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D155" s="6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E155" s="6" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>25737</v>
+      </c>
+      <c r="D156" s="4" t="n">
+        <v>25737</v>
+      </c>
+      <c r="E156" s="4" t="n">
+        <v>25737</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>-925</v>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D157" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E157" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>382000</v>
+      </c>
+      <c r="D158" s="4" t="n">
+        <v>385000</v>
+      </c>
+      <c r="E158" s="4" t="n">
+        <v>383500</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D159" s="4" t="n">
+        <v>101600</v>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>99800</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H159" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D160" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D161" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E161" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>8108</v>
+      </c>
+      <c r="D162" s="4" t="n">
+        <v>8598</v>
+      </c>
+      <c r="E162" s="4" t="n">
+        <v>8353</v>
+      </c>
+      <c r="F162" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>2470</v>
+      </c>
+      <c r="D163" s="4" t="n">
+        <v>2470</v>
+      </c>
+      <c r="E163" s="4" t="n">
+        <v>2470</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H163" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
-      <c r="H90" s="9" t="n"/>
-    </row>
-    <row r="91">
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B165" s="9" t="n"/>
+      <c r="C165" s="9" t="n"/>
+      <c r="D165" s="9" t="n"/>
+      <c r="E165" s="9" t="n"/>
+      <c r="F165" s="9" t="n"/>
+      <c r="G165" s="9" t="n"/>
+      <c r="H165" s="9" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C91" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$91),"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$91),"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$91),"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$91)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="2" t="inlineStr">
+      <c r="C166" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$166),"")</f>
+        <v/>
+      </c>
+      <c r="D166" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$166),"")</f>
+        <v/>
+      </c>
+      <c r="E166" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$166),"")</f>
+        <v/>
+      </c>
+      <c r="F166" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$166)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C92" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$92),"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$92),"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$92),"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$92)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="2" t="inlineStr">
+      <c r="C167" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$167),"")</f>
+        <v/>
+      </c>
+      <c r="D167" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$167),"")</f>
+        <v/>
+      </c>
+      <c r="E167" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$167),"")</f>
+        <v/>
+      </c>
+      <c r="F167" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$167)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C93" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$93),"")</f>
-        <v/>
-      </c>
-      <c r="D93" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$93),"")</f>
-        <v/>
-      </c>
-      <c r="E93" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$93),"")</f>
-        <v/>
-      </c>
-      <c r="F93" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$93)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="2" t="inlineStr">
+      <c r="C168" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$168),"")</f>
+        <v/>
+      </c>
+      <c r="D168" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$168),"")</f>
+        <v/>
+      </c>
+      <c r="E168" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$168),"")</f>
+        <v/>
+      </c>
+      <c r="F168" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$168)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C94" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$94),"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$94),"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$94),"")</f>
-        <v/>
-      </c>
-      <c r="F94" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$94)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="2" t="inlineStr">
+      <c r="C169" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$169),"")</f>
+        <v/>
+      </c>
+      <c r="D169" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$169),"")</f>
+        <v/>
+      </c>
+      <c r="E169" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$169),"")</f>
+        <v/>
+      </c>
+      <c r="F169" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$169)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C95" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$95),"")</f>
-        <v/>
-      </c>
-      <c r="D95" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$95),"")</f>
-        <v/>
-      </c>
-      <c r="E95" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$95),"")</f>
-        <v/>
-      </c>
-      <c r="F95" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$95)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="2" t="inlineStr">
+      <c r="C170" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$170),"")</f>
+        <v/>
+      </c>
+      <c r="D170" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$170),"")</f>
+        <v/>
+      </c>
+      <c r="E170" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$170),"")</f>
+        <v/>
+      </c>
+      <c r="F170" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$170)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C96" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$96),"")</f>
-        <v/>
-      </c>
-      <c r="D96" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$96),"")</f>
-        <v/>
-      </c>
-      <c r="E96" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$96),"")</f>
-        <v/>
-      </c>
-      <c r="F96" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$96)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C171" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$171),"")</f>
+        <v/>
+      </c>
+      <c r="D171" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$171),"")</f>
+        <v/>
+      </c>
+      <c r="E171" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$171),"")</f>
+        <v/>
+      </c>
+      <c r="F171" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$171)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C97" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$97),"")</f>
-        <v/>
-      </c>
-      <c r="D97" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$97),"")</f>
-        <v/>
-      </c>
-      <c r="E97" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$97),"")</f>
-        <v/>
-      </c>
-      <c r="F97" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$97)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="2" t="inlineStr">
+      <c r="C172" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$172),"")</f>
+        <v/>
+      </c>
+      <c r="D172" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$172),"")</f>
+        <v/>
+      </c>
+      <c r="E172" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$172),"")</f>
+        <v/>
+      </c>
+      <c r="F172" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$172)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C98" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$98),"")</f>
-        <v/>
-      </c>
-      <c r="D98" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$98),"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$98),"")</f>
-        <v/>
-      </c>
-      <c r="F98" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$98)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C173" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$173),"")</f>
+        <v/>
+      </c>
+      <c r="D173" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$173),"")</f>
+        <v/>
+      </c>
+      <c r="E173" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$173),"")</f>
+        <v/>
+      </c>
+      <c r="F173" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$173)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C99" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$99),"")</f>
-        <v/>
-      </c>
-      <c r="D99" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$99),"")</f>
-        <v/>
-      </c>
-      <c r="E99" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$99),"")</f>
-        <v/>
-      </c>
-      <c r="F99" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$99)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="2" t="inlineStr">
+      <c r="C174" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$174),"")</f>
+        <v/>
+      </c>
+      <c r="D174" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$174),"")</f>
+        <v/>
+      </c>
+      <c r="E174" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$174),"")</f>
+        <v/>
+      </c>
+      <c r="F174" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$174)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C100" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$100),"")</f>
-        <v/>
-      </c>
-      <c r="D100" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$100),"")</f>
-        <v/>
-      </c>
-      <c r="E100" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$100),"")</f>
-        <v/>
-      </c>
-      <c r="F100" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$100)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="2" t="inlineStr">
+      <c r="C175" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$175),"")</f>
+        <v/>
+      </c>
+      <c r="D175" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$175),"")</f>
+        <v/>
+      </c>
+      <c r="E175" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$175),"")</f>
+        <v/>
+      </c>
+      <c r="F175" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$175)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C101" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$101),"")</f>
-        <v/>
-      </c>
-      <c r="D101" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$101),"")</f>
-        <v/>
-      </c>
-      <c r="E101" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$101),"")</f>
-        <v/>
-      </c>
-      <c r="F101" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$101)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="2" t="inlineStr">
+      <c r="C176" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$176),"")</f>
+        <v/>
+      </c>
+      <c r="D176" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$176),"")</f>
+        <v/>
+      </c>
+      <c r="E176" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$176),"")</f>
+        <v/>
+      </c>
+      <c r="F176" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$176)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C102" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$102),"")</f>
-        <v/>
-      </c>
-      <c r="D102" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$102),"")</f>
-        <v/>
-      </c>
-      <c r="E102" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$102),"")</f>
-        <v/>
-      </c>
-      <c r="F102" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$102)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C177" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$177),"")</f>
+        <v/>
+      </c>
+      <c r="D177" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$177),"")</f>
+        <v/>
+      </c>
+      <c r="E177" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$177),"")</f>
+        <v/>
+      </c>
+      <c r="F177" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$177)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C103" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$103),"")</f>
-        <v/>
-      </c>
-      <c r="D103" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$103),"")</f>
-        <v/>
-      </c>
-      <c r="E103" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$103),"")</f>
-        <v/>
-      </c>
-      <c r="F103" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$103)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="2" t="inlineStr">
+      <c r="C178" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$178),"")</f>
+        <v/>
+      </c>
+      <c r="D178" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$178),"")</f>
+        <v/>
+      </c>
+      <c r="E178" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$178),"")</f>
+        <v/>
+      </c>
+      <c r="F178" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$178)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C104" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$104),"")</f>
-        <v/>
-      </c>
-      <c r="D104" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$104),"")</f>
-        <v/>
-      </c>
-      <c r="E104" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$104),"")</f>
-        <v/>
-      </c>
-      <c r="F104" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$104)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="2" t="inlineStr">
+      <c r="C179" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$179),"")</f>
+        <v/>
+      </c>
+      <c r="D179" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$179),"")</f>
+        <v/>
+      </c>
+      <c r="E179" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$179),"")</f>
+        <v/>
+      </c>
+      <c r="F179" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$179)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C105" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$105),"")</f>
-        <v/>
-      </c>
-      <c r="D105" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$105),"")</f>
-        <v/>
-      </c>
-      <c r="E105" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$105),"")</f>
-        <v/>
-      </c>
-      <c r="F105" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$105)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="B106" s="2" t="inlineStr">
+      <c r="C180" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$180),"")</f>
+        <v/>
+      </c>
+      <c r="D180" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$180),"")</f>
+        <v/>
+      </c>
+      <c r="E180" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$180),"")</f>
+        <v/>
+      </c>
+      <c r="F180" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$180)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C106" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$106),"")</f>
-        <v/>
-      </c>
-      <c r="D106" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$106),"")</f>
-        <v/>
-      </c>
-      <c r="E106" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$106),"")</f>
-        <v/>
-      </c>
-      <c r="F106" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$106)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="2" t="inlineStr">
+      <c r="C181" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$181),"")</f>
+        <v/>
+      </c>
+      <c r="D181" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$181),"")</f>
+        <v/>
+      </c>
+      <c r="E181" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$181),"")</f>
+        <v/>
+      </c>
+      <c r="F181" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$181)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C107" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$107),"")</f>
-        <v/>
-      </c>
-      <c r="D107" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$107),"")</f>
-        <v/>
-      </c>
-      <c r="E107" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$107),"")</f>
-        <v/>
-      </c>
-      <c r="F107" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$107)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="B108" s="2" t="inlineStr">
+      <c r="C182" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$182),"")</f>
+        <v/>
+      </c>
+      <c r="D182" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$182),"")</f>
+        <v/>
+      </c>
+      <c r="E182" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$182),"")</f>
+        <v/>
+      </c>
+      <c r="F182" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$182)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C108" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$108),"")</f>
-        <v/>
-      </c>
-      <c r="D108" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$108),"")</f>
-        <v/>
-      </c>
-      <c r="E108" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$108),"")</f>
-        <v/>
-      </c>
-      <c r="F108" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$108)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="B109" s="2" t="inlineStr">
+      <c r="C183" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$183),"")</f>
+        <v/>
+      </c>
+      <c r="D183" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$183),"")</f>
+        <v/>
+      </c>
+      <c r="E183" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$183),"")</f>
+        <v/>
+      </c>
+      <c r="F183" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$183)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C109" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$109),"")</f>
-        <v/>
-      </c>
-      <c r="D109" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$109),"")</f>
-        <v/>
-      </c>
-      <c r="E109" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$109),"")</f>
-        <v/>
-      </c>
-      <c r="F109" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$109)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110">
-      <c r="B110" s="2" t="inlineStr">
+      <c r="C184" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$184),"")</f>
+        <v/>
+      </c>
+      <c r="D184" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$184),"")</f>
+        <v/>
+      </c>
+      <c r="E184" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$184),"")</f>
+        <v/>
+      </c>
+      <c r="F184" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$184)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C110" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$110),"")</f>
-        <v/>
-      </c>
-      <c r="D110" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$110),"")</f>
-        <v/>
-      </c>
-      <c r="E110" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$110),"")</f>
-        <v/>
-      </c>
-      <c r="F110" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$110)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="B111" s="2" t="inlineStr">
+      <c r="C185" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$185),"")</f>
+        <v/>
+      </c>
+      <c r="D185" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$185),"")</f>
+        <v/>
+      </c>
+      <c r="E185" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$185),"")</f>
+        <v/>
+      </c>
+      <c r="F185" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$185)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C111" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$111),"")</f>
-        <v/>
-      </c>
-      <c r="D111" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$111),"")</f>
-        <v/>
-      </c>
-      <c r="E111" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$111),"")</f>
-        <v/>
-      </c>
-      <c r="F111" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$111)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="B112" s="2" t="inlineStr">
+      <c r="C186" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$186),"")</f>
+        <v/>
+      </c>
+      <c r="D186" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$186),"")</f>
+        <v/>
+      </c>
+      <c r="E186" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$186),"")</f>
+        <v/>
+      </c>
+      <c r="F186" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$186)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C112" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$112),"")</f>
-        <v/>
-      </c>
-      <c r="D112" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$112),"")</f>
-        <v/>
-      </c>
-      <c r="E112" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$112),"")</f>
-        <v/>
-      </c>
-      <c r="F112" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$112)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="B113" s="2" t="inlineStr">
+      <c r="C187" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$187),"")</f>
+        <v/>
+      </c>
+      <c r="D187" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$187),"")</f>
+        <v/>
+      </c>
+      <c r="E187" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$187),"")</f>
+        <v/>
+      </c>
+      <c r="F187" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$187)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C113" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$113),"")</f>
-        <v/>
-      </c>
-      <c r="D113" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$113),"")</f>
-        <v/>
-      </c>
-      <c r="E113" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$113),"")</f>
-        <v/>
-      </c>
-      <c r="F113" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$113)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="2" t="inlineStr">
+      <c r="C188" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$188),"")</f>
+        <v/>
+      </c>
+      <c r="D188" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$188),"")</f>
+        <v/>
+      </c>
+      <c r="E188" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$188),"")</f>
+        <v/>
+      </c>
+      <c r="F188" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$188)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C114" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$114),"")</f>
-        <v/>
-      </c>
-      <c r="D114" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$114),"")</f>
-        <v/>
-      </c>
-      <c r="E114" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$114),"")</f>
-        <v/>
-      </c>
-      <c r="F114" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$114)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="2" t="inlineStr">
+      <c r="C189" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$189),"")</f>
+        <v/>
+      </c>
+      <c r="D189" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$189),"")</f>
+        <v/>
+      </c>
+      <c r="E189" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$189),"")</f>
+        <v/>
+      </c>
+      <c r="F189" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$189)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C115" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$115),"")</f>
-        <v/>
-      </c>
-      <c r="D115" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$115),"")</f>
-        <v/>
-      </c>
-      <c r="E115" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$115),"")</f>
-        <v/>
-      </c>
-      <c r="F115" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$115)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="2" t="inlineStr">
+      <c r="C190" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$190),"")</f>
+        <v/>
+      </c>
+      <c r="D190" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$190),"")</f>
+        <v/>
+      </c>
+      <c r="E190" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$190),"")</f>
+        <v/>
+      </c>
+      <c r="F190" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$190)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C116" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$116),"")</f>
-        <v/>
-      </c>
-      <c r="D116" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$116),"")</f>
-        <v/>
-      </c>
-      <c r="E116" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$116),"")</f>
-        <v/>
-      </c>
-      <c r="F116" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$116)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" s="2" t="inlineStr">
+      <c r="C191" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$191),"")</f>
+        <v/>
+      </c>
+      <c r="D191" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$191),"")</f>
+        <v/>
+      </c>
+      <c r="E191" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$191),"")</f>
+        <v/>
+      </c>
+      <c r="F191" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$191)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C117" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$117),"")</f>
-        <v/>
-      </c>
-      <c r="D117" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$117),"")</f>
-        <v/>
-      </c>
-      <c r="E117" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$117),"")</f>
-        <v/>
-      </c>
-      <c r="F117" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$117)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" s="2" t="inlineStr">
+      <c r="C192" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$192),"")</f>
+        <v/>
+      </c>
+      <c r="D192" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$192),"")</f>
+        <v/>
+      </c>
+      <c r="E192" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$192),"")</f>
+        <v/>
+      </c>
+      <c r="F192" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$192)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C118" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$118),"")</f>
-        <v/>
-      </c>
-      <c r="D118" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$118),"")</f>
-        <v/>
-      </c>
-      <c r="E118" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$118),"")</f>
-        <v/>
-      </c>
-      <c r="F118" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$118)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="B119" s="2" t="inlineStr">
+      <c r="C193" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$193),"")</f>
+        <v/>
+      </c>
+      <c r="D193" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$193),"")</f>
+        <v/>
+      </c>
+      <c r="E193" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$193),"")</f>
+        <v/>
+      </c>
+      <c r="F193" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$193)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C119" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$119),"")</f>
-        <v/>
-      </c>
-      <c r="D119" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$119),"")</f>
-        <v/>
-      </c>
-      <c r="E119" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$119),"")</f>
-        <v/>
-      </c>
-      <c r="F119" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$119)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" s="2" t="inlineStr">
+      <c r="C194" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$194),"")</f>
+        <v/>
+      </c>
+      <c r="D194" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$194),"")</f>
+        <v/>
+      </c>
+      <c r="E194" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$194),"")</f>
+        <v/>
+      </c>
+      <c r="F194" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$194)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C120" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$120),"")</f>
-        <v/>
-      </c>
-      <c r="D120" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$120),"")</f>
-        <v/>
-      </c>
-      <c r="E120" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$120),"")</f>
-        <v/>
-      </c>
-      <c r="F120" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$120)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="B121" s="2" t="inlineStr">
+      <c r="C195" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$195),"")</f>
+        <v/>
+      </c>
+      <c r="D195" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$195),"")</f>
+        <v/>
+      </c>
+      <c r="E195" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$195),"")</f>
+        <v/>
+      </c>
+      <c r="F195" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$195)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C121" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$121),"")</f>
-        <v/>
-      </c>
-      <c r="D121" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$121),"")</f>
-        <v/>
-      </c>
-      <c r="E121" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$121),"")</f>
-        <v/>
-      </c>
-      <c r="F121" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$121)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="B122" s="2" t="inlineStr">
+      <c r="C196" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$196),"")</f>
+        <v/>
+      </c>
+      <c r="D196" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$196),"")</f>
+        <v/>
+      </c>
+      <c r="E196" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$196),"")</f>
+        <v/>
+      </c>
+      <c r="F196" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$196)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C122" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$122),"")</f>
-        <v/>
-      </c>
-      <c r="D122" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$122),"")</f>
-        <v/>
-      </c>
-      <c r="E122" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$122),"")</f>
-        <v/>
-      </c>
-      <c r="F122" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$122)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="2" t="inlineStr">
+      <c r="C197" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$197),"")</f>
+        <v/>
+      </c>
+      <c r="D197" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$197),"")</f>
+        <v/>
+      </c>
+      <c r="E197" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$197),"")</f>
+        <v/>
+      </c>
+      <c r="F197" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$197)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C123" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$123),"")</f>
-        <v/>
-      </c>
-      <c r="D123" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$123),"")</f>
-        <v/>
-      </c>
-      <c r="E123" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$123),"")</f>
-        <v/>
-      </c>
-      <c r="F123" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$123)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="B124" s="2" t="inlineStr">
+      <c r="C198" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$198),"")</f>
+        <v/>
+      </c>
+      <c r="D198" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$198),"")</f>
+        <v/>
+      </c>
+      <c r="E198" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$198),"")</f>
+        <v/>
+      </c>
+      <c r="F198" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$198)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C124" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$124),"")</f>
-        <v/>
-      </c>
-      <c r="D124" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$124),"")</f>
-        <v/>
-      </c>
-      <c r="E124" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$124),"")</f>
-        <v/>
-      </c>
-      <c r="F124" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$124)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="B125" s="2" t="inlineStr">
+      <c r="C199" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$199),"")</f>
+        <v/>
+      </c>
+      <c r="D199" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$199),"")</f>
+        <v/>
+      </c>
+      <c r="E199" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$199),"")</f>
+        <v/>
+      </c>
+      <c r="F199" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$199)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C125" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$125),"")</f>
-        <v/>
-      </c>
-      <c r="D125" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$125),"")</f>
-        <v/>
-      </c>
-      <c r="E125" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$125),"")</f>
-        <v/>
-      </c>
-      <c r="F125" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$125)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126">
-      <c r="B126" s="2" t="inlineStr">
+      <c r="C200" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$200),"")</f>
+        <v/>
+      </c>
+      <c r="D200" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$200),"")</f>
+        <v/>
+      </c>
+      <c r="E200" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$200),"")</f>
+        <v/>
+      </c>
+      <c r="F200" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$200)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C126" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$126),"")</f>
-        <v/>
-      </c>
-      <c r="D126" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$126),"")</f>
-        <v/>
-      </c>
-      <c r="E126" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$126),"")</f>
-        <v/>
-      </c>
-      <c r="F126" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$126)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C201" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$201),"")</f>
+        <v/>
+      </c>
+      <c r="D201" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$201),"")</f>
+        <v/>
+      </c>
+      <c r="E201" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$201),"")</f>
+        <v/>
+      </c>
+      <c r="F201" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$201)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C127" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$127),"")</f>
-        <v/>
-      </c>
-      <c r="D127" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$127),"")</f>
-        <v/>
-      </c>
-      <c r="E127" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$127),"")</f>
-        <v/>
-      </c>
-      <c r="F127" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$127)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128">
-      <c r="B128" s="2" t="inlineStr">
+      <c r="C202" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$202),"")</f>
+        <v/>
+      </c>
+      <c r="D202" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$202),"")</f>
+        <v/>
+      </c>
+      <c r="E202" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$202),"")</f>
+        <v/>
+      </c>
+      <c r="F202" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$202)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C128" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$128),"")</f>
-        <v/>
-      </c>
-      <c r="D128" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$128),"")</f>
-        <v/>
-      </c>
-      <c r="E128" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$128),"")</f>
-        <v/>
-      </c>
-      <c r="F128" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$128)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="B129" s="2" t="inlineStr">
+      <c r="C203" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$203),"")</f>
+        <v/>
+      </c>
+      <c r="D203" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$203),"")</f>
+        <v/>
+      </c>
+      <c r="E203" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$203),"")</f>
+        <v/>
+      </c>
+      <c r="F203" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$203)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C129" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$129),"")</f>
-        <v/>
-      </c>
-      <c r="D129" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$129),"")</f>
-        <v/>
-      </c>
-      <c r="E129" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$129),"")</f>
-        <v/>
-      </c>
-      <c r="F129" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$129)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130">
-      <c r="B130" s="2" t="inlineStr">
+      <c r="C204" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$204),"")</f>
+        <v/>
+      </c>
+      <c r="D204" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$204),"")</f>
+        <v/>
+      </c>
+      <c r="E204" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$204),"")</f>
+        <v/>
+      </c>
+      <c r="F204" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$204)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C130" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$130),"")</f>
-        <v/>
-      </c>
-      <c r="D130" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$130),"")</f>
-        <v/>
-      </c>
-      <c r="E130" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$130),"")</f>
-        <v/>
-      </c>
-      <c r="F130" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$130)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" s="2" t="inlineStr">
+      <c r="C205" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$205),"")</f>
+        <v/>
+      </c>
+      <c r="D205" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$205),"")</f>
+        <v/>
+      </c>
+      <c r="E205" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$205),"")</f>
+        <v/>
+      </c>
+      <c r="F205" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$205)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C131" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$131),"")</f>
-        <v/>
-      </c>
-      <c r="D131" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$131),"")</f>
-        <v/>
-      </c>
-      <c r="E131" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$131),"")</f>
-        <v/>
-      </c>
-      <c r="F131" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$131)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="B132" s="2" t="inlineStr">
+      <c r="C206" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$206),"")</f>
+        <v/>
+      </c>
+      <c r="D206" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$206),"")</f>
+        <v/>
+      </c>
+      <c r="E206" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$206),"")</f>
+        <v/>
+      </c>
+      <c r="F206" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$206)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C132" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$132),"")</f>
-        <v/>
-      </c>
-      <c r="D132" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$132),"")</f>
-        <v/>
-      </c>
-      <c r="E132" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$132),"")</f>
-        <v/>
-      </c>
-      <c r="F132" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$132)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="B133" s="2" t="inlineStr">
+      <c r="C207" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$207),"")</f>
+        <v/>
+      </c>
+      <c r="D207" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$207),"")</f>
+        <v/>
+      </c>
+      <c r="E207" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$207),"")</f>
+        <v/>
+      </c>
+      <c r="F207" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$207)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C133" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$133),"")</f>
-        <v/>
-      </c>
-      <c r="D133" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$133),"")</f>
-        <v/>
-      </c>
-      <c r="E133" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$133),"")</f>
-        <v/>
-      </c>
-      <c r="F133" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$133)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="B134" s="2" t="inlineStr">
+      <c r="C208" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$208),"")</f>
+        <v/>
+      </c>
+      <c r="D208" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$208),"")</f>
+        <v/>
+      </c>
+      <c r="E208" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$208),"")</f>
+        <v/>
+      </c>
+      <c r="F208" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$208)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C134" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$134),"")</f>
-        <v/>
-      </c>
-      <c r="D134" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$134),"")</f>
-        <v/>
-      </c>
-      <c r="E134" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$134),"")</f>
-        <v/>
-      </c>
-      <c r="F134" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$134)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="B135" s="2" t="inlineStr">
+      <c r="C209" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$209),"")</f>
+        <v/>
+      </c>
+      <c r="D209" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$209),"")</f>
+        <v/>
+      </c>
+      <c r="E209" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$209),"")</f>
+        <v/>
+      </c>
+      <c r="F209" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$209)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C135" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$135),"")</f>
-        <v/>
-      </c>
-      <c r="D135" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$135),"")</f>
-        <v/>
-      </c>
-      <c r="E135" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$135),"")</f>
-        <v/>
-      </c>
-      <c r="F135" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$135)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="B136" s="2" t="inlineStr">
+      <c r="C210" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$210),"")</f>
+        <v/>
+      </c>
+      <c r="D210" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$210),"")</f>
+        <v/>
+      </c>
+      <c r="E210" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$210),"")</f>
+        <v/>
+      </c>
+      <c r="F210" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$210)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C136" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$136),"")</f>
-        <v/>
-      </c>
-      <c r="D136" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$136),"")</f>
-        <v/>
-      </c>
-      <c r="E136" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$136),"")</f>
-        <v/>
-      </c>
-      <c r="F136" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$136)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137">
-      <c r="B137" s="2" t="inlineStr">
+      <c r="C211" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$211),"")</f>
+        <v/>
+      </c>
+      <c r="D211" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$211),"")</f>
+        <v/>
+      </c>
+      <c r="E211" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$211),"")</f>
+        <v/>
+      </c>
+      <c r="F211" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$211)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C137" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$137),"")</f>
-        <v/>
-      </c>
-      <c r="D137" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$137),"")</f>
-        <v/>
-      </c>
-      <c r="E137" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$137),"")</f>
-        <v/>
-      </c>
-      <c r="F137" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$137)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="B138" s="2" t="inlineStr">
+      <c r="C212" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$212),"")</f>
+        <v/>
+      </c>
+      <c r="D212" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$212),"")</f>
+        <v/>
+      </c>
+      <c r="E212" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$212),"")</f>
+        <v/>
+      </c>
+      <c r="F212" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$212)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C138" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$138),"")</f>
-        <v/>
-      </c>
-      <c r="D138" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$138),"")</f>
-        <v/>
-      </c>
-      <c r="E138" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$138),"")</f>
-        <v/>
-      </c>
-      <c r="F138" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$138)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139">
-      <c r="B139" s="2" t="inlineStr">
+      <c r="C213" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$213),"")</f>
+        <v/>
+      </c>
+      <c r="D213" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$213),"")</f>
+        <v/>
+      </c>
+      <c r="E213" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$213),"")</f>
+        <v/>
+      </c>
+      <c r="F213" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$213)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C139" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$139),"")</f>
-        <v/>
-      </c>
-      <c r="D139" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$139),"")</f>
-        <v/>
-      </c>
-      <c r="E139" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$139),"")</f>
-        <v/>
-      </c>
-      <c r="F139" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$139)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="B140" s="2" t="inlineStr">
+      <c r="C214" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$214),"")</f>
+        <v/>
+      </c>
+      <c r="D214" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$214),"")</f>
+        <v/>
+      </c>
+      <c r="E214" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$214),"")</f>
+        <v/>
+      </c>
+      <c r="F214" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$214)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C140" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$140),"")</f>
-        <v/>
-      </c>
-      <c r="D140" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$140),"")</f>
-        <v/>
-      </c>
-      <c r="E140" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$140),"")</f>
-        <v/>
-      </c>
-      <c r="F140" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$140)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" s="2" t="inlineStr">
+      <c r="C215" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$215),"")</f>
+        <v/>
+      </c>
+      <c r="D215" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$215),"")</f>
+        <v/>
+      </c>
+      <c r="E215" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$215),"")</f>
+        <v/>
+      </c>
+      <c r="F215" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$215)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C141" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$141),"")</f>
-        <v/>
-      </c>
-      <c r="D141" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$141),"")</f>
-        <v/>
-      </c>
-      <c r="E141" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$141),"")</f>
-        <v/>
-      </c>
-      <c r="F141" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$141)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="B142" s="2" t="inlineStr">
+      <c r="C216" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$216),"")</f>
+        <v/>
+      </c>
+      <c r="D216" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$216),"")</f>
+        <v/>
+      </c>
+      <c r="E216" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$216),"")</f>
+        <v/>
+      </c>
+      <c r="F216" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$216)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C142" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$142),"")</f>
-        <v/>
-      </c>
-      <c r="D142" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$142),"")</f>
-        <v/>
-      </c>
-      <c r="E142" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$142),"")</f>
-        <v/>
-      </c>
-      <c r="F142" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$142)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143">
-      <c r="B143" s="2" t="inlineStr">
+      <c r="C217" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$217),"")</f>
+        <v/>
+      </c>
+      <c r="D217" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$217),"")</f>
+        <v/>
+      </c>
+      <c r="E217" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$217),"")</f>
+        <v/>
+      </c>
+      <c r="F217" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$217)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C143" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$143),"")</f>
-        <v/>
-      </c>
-      <c r="D143" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$143),"")</f>
-        <v/>
-      </c>
-      <c r="E143" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$143),"")</f>
-        <v/>
-      </c>
-      <c r="F143" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$143)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="B144" s="2" t="inlineStr">
+      <c r="C218" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$218),"")</f>
+        <v/>
+      </c>
+      <c r="D218" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$218),"")</f>
+        <v/>
+      </c>
+      <c r="E218" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$218),"")</f>
+        <v/>
+      </c>
+      <c r="F218" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$218)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C144" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$144),"")</f>
-        <v/>
-      </c>
-      <c r="D144" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$144),"")</f>
-        <v/>
-      </c>
-      <c r="E144" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$144),"")</f>
-        <v/>
-      </c>
-      <c r="F144" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$144)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="B145" s="2" t="inlineStr">
+      <c r="C219" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$219),"")</f>
+        <v/>
+      </c>
+      <c r="D219" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$219),"")</f>
+        <v/>
+      </c>
+      <c r="E219" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$219),"")</f>
+        <v/>
+      </c>
+      <c r="F219" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$219)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C145" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$145),"")</f>
-        <v/>
-      </c>
-      <c r="D145" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$145),"")</f>
-        <v/>
-      </c>
-      <c r="E145" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$145),"")</f>
-        <v/>
-      </c>
-      <c r="F145" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$145)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="B146" s="2" t="inlineStr">
+      <c r="C220" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$220),"")</f>
+        <v/>
+      </c>
+      <c r="D220" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$220),"")</f>
+        <v/>
+      </c>
+      <c r="E220" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$220),"")</f>
+        <v/>
+      </c>
+      <c r="F220" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$220)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C146" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$146),"")</f>
-        <v/>
-      </c>
-      <c r="D146" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$146),"")</f>
-        <v/>
-      </c>
-      <c r="E146" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$146),"")</f>
-        <v/>
-      </c>
-      <c r="F146" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$146)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" s="2" t="inlineStr">
+      <c r="C221" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$221),"")</f>
+        <v/>
+      </c>
+      <c r="D221" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$221),"")</f>
+        <v/>
+      </c>
+      <c r="E221" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$221),"")</f>
+        <v/>
+      </c>
+      <c r="F221" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$221)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C147" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$147),"")</f>
-        <v/>
-      </c>
-      <c r="D147" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$147),"")</f>
-        <v/>
-      </c>
-      <c r="E147" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$147),"")</f>
-        <v/>
-      </c>
-      <c r="F147" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$147)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="B148" s="2" t="inlineStr">
+      <c r="C222" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$222),"")</f>
+        <v/>
+      </c>
+      <c r="D222" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$222),"")</f>
+        <v/>
+      </c>
+      <c r="E222" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$222),"")</f>
+        <v/>
+      </c>
+      <c r="F222" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$222)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C148" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$148),"")</f>
-        <v/>
-      </c>
-      <c r="D148" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$148),"")</f>
-        <v/>
-      </c>
-      <c r="E148" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$148),"")</f>
-        <v/>
-      </c>
-      <c r="F148" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$148)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" s="2" t="inlineStr">
+      <c r="C223" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$223),"")</f>
+        <v/>
+      </c>
+      <c r="D223" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$223),"")</f>
+        <v/>
+      </c>
+      <c r="E223" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$223),"")</f>
+        <v/>
+      </c>
+      <c r="F223" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$223)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C149" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$149),"")</f>
-        <v/>
-      </c>
-      <c r="D149" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$149),"")</f>
-        <v/>
-      </c>
-      <c r="E149" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$149),"")</f>
-        <v/>
-      </c>
-      <c r="F149" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$149)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="B150" s="2" t="inlineStr">
+      <c r="C224" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$224),"")</f>
+        <v/>
+      </c>
+      <c r="D224" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$224),"")</f>
+        <v/>
+      </c>
+      <c r="E224" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$224),"")</f>
+        <v/>
+      </c>
+      <c r="F224" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$224)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C150" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$150),"")</f>
-        <v/>
-      </c>
-      <c r="D150" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$150),"")</f>
-        <v/>
-      </c>
-      <c r="E150" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$150),"")</f>
-        <v/>
-      </c>
-      <c r="F150" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$150)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="B151" s="2" t="inlineStr">
+      <c r="C225" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$225),"")</f>
+        <v/>
+      </c>
+      <c r="D225" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$225),"")</f>
+        <v/>
+      </c>
+      <c r="E225" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$225),"")</f>
+        <v/>
+      </c>
+      <c r="F225" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$225)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C151" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$151),"")</f>
-        <v/>
-      </c>
-      <c r="D151" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$151),"")</f>
-        <v/>
-      </c>
-      <c r="E151" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$151),"")</f>
-        <v/>
-      </c>
-      <c r="F151" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$151)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="B152" s="2" t="inlineStr">
+      <c r="C226" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$226),"")</f>
+        <v/>
+      </c>
+      <c r="D226" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$226),"")</f>
+        <v/>
+      </c>
+      <c r="E226" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$226),"")</f>
+        <v/>
+      </c>
+      <c r="F226" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$226)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C152" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$152),"")</f>
-        <v/>
-      </c>
-      <c r="D152" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$152),"")</f>
-        <v/>
-      </c>
-      <c r="E152" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$152),"")</f>
-        <v/>
-      </c>
-      <c r="F152" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$152)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="B153" s="2" t="inlineStr">
+      <c r="C227" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$227),"")</f>
+        <v/>
+      </c>
+      <c r="D227" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$227),"")</f>
+        <v/>
+      </c>
+      <c r="E227" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$227),"")</f>
+        <v/>
+      </c>
+      <c r="F227" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$227)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C153" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$153),"")</f>
-        <v/>
-      </c>
-      <c r="D153" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$153),"")</f>
-        <v/>
-      </c>
-      <c r="E153" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$153),"")</f>
-        <v/>
-      </c>
-      <c r="F153" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$153)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="B154" s="2" t="inlineStr">
+      <c r="C228" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$228),"")</f>
+        <v/>
+      </c>
+      <c r="D228" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$228),"")</f>
+        <v/>
+      </c>
+      <c r="E228" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$228),"")</f>
+        <v/>
+      </c>
+      <c r="F228" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$228)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C154" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$154),"")</f>
-        <v/>
-      </c>
-      <c r="D154" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$154),"")</f>
-        <v/>
-      </c>
-      <c r="E154" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$154),"")</f>
-        <v/>
-      </c>
-      <c r="F154" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$154)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="B155" s="2" t="inlineStr">
+      <c r="C229" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$229),"")</f>
+        <v/>
+      </c>
+      <c r="D229" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$229),"")</f>
+        <v/>
+      </c>
+      <c r="E229" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$229),"")</f>
+        <v/>
+      </c>
+      <c r="F229" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$229)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C155" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$155),"")</f>
-        <v/>
-      </c>
-      <c r="D155" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$155),"")</f>
-        <v/>
-      </c>
-      <c r="E155" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$155),"")</f>
-        <v/>
-      </c>
-      <c r="F155" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$155)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="B156" s="2" t="inlineStr">
+      <c r="C230" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$230),"")</f>
+        <v/>
+      </c>
+      <c r="D230" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$230),"")</f>
+        <v/>
+      </c>
+      <c r="E230" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$230),"")</f>
+        <v/>
+      </c>
+      <c r="F230" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$230)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C156" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$156),"")</f>
-        <v/>
-      </c>
-      <c r="D156" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$156),"")</f>
-        <v/>
-      </c>
-      <c r="E156" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$156),"")</f>
-        <v/>
-      </c>
-      <c r="F156" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$156)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="B157" s="2" t="inlineStr">
+      <c r="C231" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$231),"")</f>
+        <v/>
+      </c>
+      <c r="D231" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$231),"")</f>
+        <v/>
+      </c>
+      <c r="E231" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$231),"")</f>
+        <v/>
+      </c>
+      <c r="F231" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$231)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C157" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$157),"")</f>
-        <v/>
-      </c>
-      <c r="D157" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$157),"")</f>
-        <v/>
-      </c>
-      <c r="E157" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$157),"")</f>
-        <v/>
-      </c>
-      <c r="F157" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$157)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="158">
-      <c r="B158" s="2" t="inlineStr">
+      <c r="C232" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$232),"")</f>
+        <v/>
+      </c>
+      <c r="D232" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$232),"")</f>
+        <v/>
+      </c>
+      <c r="E232" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$232),"")</f>
+        <v/>
+      </c>
+      <c r="F232" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$232)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C158" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$158),"")</f>
-        <v/>
-      </c>
-      <c r="D158" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$158),"")</f>
-        <v/>
-      </c>
-      <c r="E158" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$158),"")</f>
-        <v/>
-      </c>
-      <c r="F158" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$158)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="2" t="inlineStr">
+      <c r="C233" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$233),"")</f>
+        <v/>
+      </c>
+      <c r="D233" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$233),"")</f>
+        <v/>
+      </c>
+      <c r="E233" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$233),"")</f>
+        <v/>
+      </c>
+      <c r="F233" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$233)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C159" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$159),"")</f>
-        <v/>
-      </c>
-      <c r="D159" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$159),"")</f>
-        <v/>
-      </c>
-      <c r="E159" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$159),"")</f>
-        <v/>
-      </c>
-      <c r="F159" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$159)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="160">
-      <c r="B160" s="2" t="inlineStr">
+      <c r="C234" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$234),"")</f>
+        <v/>
+      </c>
+      <c r="D234" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$234),"")</f>
+        <v/>
+      </c>
+      <c r="E234" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$234),"")</f>
+        <v/>
+      </c>
+      <c r="F234" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$234)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C160" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$160),"")</f>
-        <v/>
-      </c>
-      <c r="D160" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$160),"")</f>
-        <v/>
-      </c>
-      <c r="E160" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$160),"")</f>
-        <v/>
-      </c>
-      <c r="F160" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$160)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161">
-      <c r="B161" s="2" t="inlineStr">
+      <c r="C235" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$235),"")</f>
+        <v/>
+      </c>
+      <c r="D235" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$235),"")</f>
+        <v/>
+      </c>
+      <c r="E235" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$235),"")</f>
+        <v/>
+      </c>
+      <c r="F235" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$235)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C161" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$161),"")</f>
-        <v/>
-      </c>
-      <c r="D161" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$161),"")</f>
-        <v/>
-      </c>
-      <c r="E161" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$161),"")</f>
-        <v/>
-      </c>
-      <c r="F161" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$161)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="B162" s="2" t="inlineStr">
+      <c r="C236" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$236),"")</f>
+        <v/>
+      </c>
+      <c r="D236" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$236),"")</f>
+        <v/>
+      </c>
+      <c r="E236" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$236),"")</f>
+        <v/>
+      </c>
+      <c r="F236" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$236)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C162" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$162),"")</f>
-        <v/>
-      </c>
-      <c r="D162" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$162),"")</f>
-        <v/>
-      </c>
-      <c r="E162" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$162),"")</f>
-        <v/>
-      </c>
-      <c r="F162" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$162)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163">
-      <c r="B163" s="2" t="inlineStr">
+      <c r="C237" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$237),"")</f>
+        <v/>
+      </c>
+      <c r="D237" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$237),"")</f>
+        <v/>
+      </c>
+      <c r="E237" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$237),"")</f>
+        <v/>
+      </c>
+      <c r="F237" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$237)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="B238" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C163" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$163),"")</f>
-        <v/>
-      </c>
-      <c r="D163" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$163),"")</f>
-        <v/>
-      </c>
-      <c r="E163" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$163),"")</f>
-        <v/>
-      </c>
-      <c r="F163" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$163)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164">
-      <c r="B164" s="2" t="inlineStr">
+      <c r="C238" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$238),"")</f>
+        <v/>
+      </c>
+      <c r="D238" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$238),"")</f>
+        <v/>
+      </c>
+      <c r="E238" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$238),"")</f>
+        <v/>
+      </c>
+      <c r="F238" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$238)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C164" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$164),"")</f>
-        <v/>
-      </c>
-      <c r="D164" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$164),"")</f>
-        <v/>
-      </c>
-      <c r="E164" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$164),"")</f>
-        <v/>
-      </c>
-      <c r="F164" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$164)*(F$2:F$88),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="165">
-      <c r="B165" s="2" t="inlineStr">
+      <c r="C239" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$239),"")</f>
+        <v/>
+      </c>
+      <c r="D239" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$239),"")</f>
+        <v/>
+      </c>
+      <c r="E239" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$239),"")</f>
+        <v/>
+      </c>
+      <c r="F239" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$239)*(F$2:F$163),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C165" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$165),"")</f>
-        <v/>
-      </c>
-      <c r="D165" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$165),"")</f>
-        <v/>
-      </c>
-      <c r="E165" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$88,A$2:A$88,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$88,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$88,$B$165),"")</f>
-        <v/>
-      </c>
-      <c r="F165" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$88)=YEAR(TODAY()))*(MONTH(A$2:A$88)=MONTH(TODAY()))*(B$2:B$88=$B$165)*(F$2:F$88),"")</f>
+      <c r="C240" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$240),"")</f>
+        <v/>
+      </c>
+      <c r="D240" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$240),"")</f>
+        <v/>
+      </c>
+      <c r="E240" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$240),"")</f>
+        <v/>
+      </c>
+      <c r="F240" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$240)*(F$2:F$163),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H88"/>
+  <autoFilter ref="A1:H163"/>
   <mergeCells count="1">
-    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A165:H165"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5396,7 +7946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5767,134 +8317,355 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>131640</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>133550</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>133980</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>131780</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>-1850</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>172320</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>176780</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>174440</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>174440</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>-5600</v>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>6.7568</v>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>6.7614</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>6.7565</v>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/16</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D12" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$12),"")</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$12),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$12),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$12),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$9)=YEAR(TODAY()))*(MONTH(A$2:A$9)=MONTH(TODAY()))*(C$2:C$9=$C$12)*(H$2:H$9),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" s="2" t="inlineStr">
+      <c r="D17" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
+        <v/>
+      </c>
+      <c r="E17" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$17)*(H$2:H$14),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D13" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$13),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$9)=YEAR(TODAY()))*(MONTH(A$2:A$9)=MONTH(TODAY()))*(C$2:C$9=$C$13)*(H$2:H$9),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D18" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$18)*(H$2:H$14),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D14" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$14),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$14),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$14),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$14),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$9)=YEAR(TODAY()))*(MONTH(A$2:A$9)=MONTH(TODAY()))*(C$2:C$9=$C$14)*(H$2:H$9),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15" s="2" t="inlineStr">
+      <c r="D19" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$19)*(H$2:H$14),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D20" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
+        <v/>
+      </c>
+      <c r="E20" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$20)*(H$2:H$14),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D15" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$15),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$15),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$15),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$9,A$2:A$9,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$9,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$9,$C$15),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$9)=YEAR(TODAY()))*(MONTH(A$2:A$9)=MONTH(TODAY()))*(C$2:C$9=$C$15)*(H$2:H$9),"")</f>
+      <c r="D21" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
+        <v/>
+      </c>
+      <c r="E21" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$21)*(H$2:H$14),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J9"/>
+  <autoFilter ref="A1:J14"/>
   <mergeCells count="1">
-    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A16:J16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -3654,16 +3654,16 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>101450</v>
+        <v>101150</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>106650</v>
+        <v>106350</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>104050</v>
+        <v>103750</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
@@ -3688,16 +3688,16 @@
         </is>
       </c>
       <c r="C90" s="3" t="n">
-        <v>186900</v>
+        <v>186300</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>195800</v>
+        <v>194800</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>191350</v>
+        <v>190550</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>-400</v>
+        <v>-800</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
@@ -3722,16 +3722,16 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>94200</v>
+        <v>94000</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>98900</v>
+        <v>98700</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>96550</v>
+        <v>96350</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>191000</v>
+        <v>190700</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>200500</v>
+        <v>200200</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>195750</v>
+        <v>195450</v>
       </c>
       <c r="F92" s="4" t="n">
         <v>-300</v>
@@ -3790,13 +3790,13 @@
         </is>
       </c>
       <c r="C93" s="3" t="n">
-        <v>116650</v>
+        <v>116550</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>122450</v>
+        <v>122250</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>119550</v>
+        <v>119400</v>
       </c>
       <c r="F93" s="4" t="n">
         <v>-150</v>
@@ -3824,16 +3824,16 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>214300</v>
+        <v>214000</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>223900</v>
+        <v>223600</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>219100</v>
+        <v>218800</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -3858,16 +3858,16 @@
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>85</v>
+        <v>85.5</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E95" s="6" t="n">
-        <v>85.5</v>
+        <v>86.25</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
@@ -3926,16 +3926,16 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>211600</v>
+        <v>211100</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>219900</v>
+        <v>219400</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>215750</v>
+        <v>215250</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>-600</v>
+        <v>-500</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
@@ -4070,8 +4070,8 @@
       <c r="E101" s="6" t="n">
         <v>75.72</v>
       </c>
-      <c r="F101" s="6" t="n">
-        <v>-0.13</v>
+      <c r="F101" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
@@ -4104,8 +4104,8 @@
       <c r="E102" s="6" t="n">
         <v>75.83</v>
       </c>
-      <c r="F102" s="6" t="n">
-        <v>-0.16</v>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
@@ -4138,8 +4138,8 @@
       <c r="E103" s="6" t="n">
         <v>75.83</v>
       </c>
-      <c r="F103" s="6" t="n">
-        <v>-0.16</v>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
@@ -4164,16 +4164,16 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>102407</v>
+        <v>102322</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>106587</v>
+        <v>106498</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>104497</v>
+        <v>104410</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>-76.5</v>
+        <v>-87</v>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
@@ -4198,16 +4198,16 @@
         </is>
       </c>
       <c r="C105" s="3" t="n">
-        <v>155318</v>
+        <v>154204</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>155318</v>
+        <v>154204</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>155318</v>
+        <v>154204</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>-2320</v>
+        <v>-1114</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
@@ -4232,16 +4232,16 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>7646</v>
+        <v>7651</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>7646</v>
+        <v>7651</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>7646</v>
+        <v>7651</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
@@ -4266,16 +4266,16 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>33050</v>
+        <v>33051</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>33050</v>
+        <v>33051</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>33050</v>
+        <v>33051</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
@@ -4300,16 +4300,16 @@
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>170885</v>
+        <v>168094</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>170885</v>
+        <v>168094</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>170885</v>
+        <v>168094</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>264</v>
+        <v>-2791</v>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
@@ -4334,16 +4334,16 @@
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>89058</v>
+        <v>88576</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>89058</v>
+        <v>88576</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>89058</v>
+        <v>88576</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>-666</v>
+        <v>-482</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>7494</v>
+        <v>7489</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>7494</v>
+        <v>7489</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>7494</v>
+        <v>7489</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>58</v>
+        <v>-5</v>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
@@ -4410,8 +4410,8 @@
       <c r="E111" s="4" t="n">
         <v>7062</v>
       </c>
-      <c r="F111" s="6" t="n">
-        <v>1</v>
+      <c r="F111" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
@@ -4444,8 +4444,8 @@
       <c r="E112" s="6" t="n">
         <v>82.53</v>
       </c>
-      <c r="F112" s="6" t="n">
-        <v>-0.78</v>
+      <c r="F112" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
@@ -4478,8 +4478,8 @@
       <c r="E113" s="6" t="n">
         <v>76.5</v>
       </c>
-      <c r="F113" s="6" t="n">
-        <v>-0.26</v>
+      <c r="F113" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
@@ -4512,8 +4512,8 @@
       <c r="E114" s="6" t="n">
         <v>80.13</v>
       </c>
-      <c r="F114" s="6" t="n">
-        <v>-0.92</v>
+      <c r="F114" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
@@ -4546,8 +4546,8 @@
       <c r="E115" s="6" t="n">
         <v>76.11</v>
       </c>
-      <c r="F115" s="6" t="n">
-        <v>-0.31</v>
+      <c r="F115" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
@@ -4640,16 +4640,16 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>339000</v>
+        <v>335000</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>350000</v>
+        <v>348000</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>344500</v>
+        <v>341500</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>-1000</v>
+        <v>-3000</v>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
@@ -4708,16 +4708,16 @@
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>139000</v>
+        <v>138000</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>146000</v>
+        <v>145000</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>142500</v>
+        <v>141500</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>-1500</v>
+        <v>-1000</v>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
@@ -4745,13 +4745,13 @@
         <v>162000</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>171000</v>
+        <v>168000</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>166500</v>
+        <v>165000</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
@@ -4810,16 +4810,16 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>2430</v>
+        <v>2425</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>2550</v>
+        <v>2535</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
@@ -4844,16 +4844,16 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>22400</v>
+        <v>22050</v>
       </c>
       <c r="D124" s="4" t="n">
         <v>25550</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>23975</v>
+        <v>23800</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>325</v>
+        <v>-175</v>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
@@ -4878,16 +4878,16 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>26600</v>
+        <v>26200</v>
       </c>
       <c r="D125" s="4" t="n">
         <v>30750</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>28675</v>
+        <v>28475</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>425</v>
+        <v>-200</v>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
@@ -4912,16 +4912,16 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>16600</v>
+        <v>16500</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>18300</v>
+        <v>18000</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>17450</v>
+        <v>17250</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
@@ -4946,16 +4946,16 @@
         </is>
       </c>
       <c r="C127" s="3" t="n">
-        <v>10800</v>
+        <v>10500</v>
       </c>
       <c r="D127" s="4" t="n">
         <v>11800</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>11300</v>
+        <v>11150</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
@@ -4983,13 +4983,13 @@
         <v>17800</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>19300</v>
+        <v>19000</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>18550</v>
+        <v>18400</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
@@ -5082,16 +5082,16 @@
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>315000</v>
+        <v>310000</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>330000</v>
+        <v>325000</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>322500</v>
+        <v>317500</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>-5500</v>
+        <v>-5000</v>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
@@ -5116,16 +5116,16 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>108000</v>
+        <v>106000</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>114000</v>
+        <v>112000</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>111000</v>
+        <v>109000</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>-1500</v>
+        <v>-2000</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
@@ -5218,16 +5218,16 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>2450</v>
+        <v>2445</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>2560</v>
+        <v>2545</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>2505</v>
+        <v>2495</v>
       </c>
       <c r="F135" s="6" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
@@ -5255,13 +5255,13 @@
         <v>235</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>265</v>
-      </c>
-      <c r="F136" s="4" t="n">
-        <v>0</v>
+        <v>263</v>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>-2</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -5320,16 +5320,16 @@
         </is>
       </c>
       <c r="C138" s="7" t="n">
-        <v>18.25</v>
+        <v>18.05</v>
       </c>
       <c r="D138" s="6" t="n">
         <v>21.15</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>-0.125</v>
+        <v>-0.1</v>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
@@ -5354,16 +5354,16 @@
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="D139" s="6" t="n">
         <v>21.1</v>
       </c>
       <c r="E139" s="6" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="F139" s="6" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -5388,16 +5388,16 @@
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>154000</v>
+        <v>153000</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>168000</v>
+        <v>167000</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>161000</v>
+        <v>160000</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>-1500</v>
+        <v>-1000</v>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
@@ -5422,16 +5422,16 @@
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>148000</v>
+        <v>146000</v>
       </c>
       <c r="D141" s="4" t="n">
         <v>162000</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>155000</v>
+        <v>154000</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>-1500</v>
+        <v>-1000</v>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
@@ -5498,8 +5498,8 @@
       <c r="E143" s="4" t="n">
         <v>33610</v>
       </c>
-      <c r="F143" s="6" t="n">
-        <v>10</v>
+      <c r="F143" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
@@ -5527,13 +5527,13 @@
         <v>166000</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>175000</v>
+        <v>172000</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>170500</v>
+        <v>169000</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
@@ -5561,13 +5561,13 @@
         <v>20.15</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>22.25</v>
+        <v>22.05</v>
       </c>
       <c r="E145" s="6" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F145" s="4" t="n">
-        <v>0</v>
+        <v>21.1</v>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
@@ -5595,13 +5595,13 @@
         <v>20.35</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="F146" s="4" t="n">
-        <v>0</v>
+        <v>21.23</v>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
@@ -5660,16 +5660,16 @@
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>385000</v>
+        <v>384000</v>
       </c>
       <c r="D148" s="4" t="n">
         <v>410000</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>397500</v>
+        <v>397000</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>-1000</v>
+        <v>-500</v>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
@@ -5762,16 +5762,16 @@
         </is>
       </c>
       <c r="C151" s="3" t="n">
-        <v>88000</v>
+        <v>87500</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>90500</v>
+        <v>90000</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>89250</v>
+        <v>88750</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>-750</v>
+        <v>-500</v>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
@@ -5796,16 +5796,16 @@
         </is>
       </c>
       <c r="C152" s="3" t="n">
-        <v>215000</v>
+        <v>210000</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>232000</v>
+        <v>230000</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>223500</v>
+        <v>220000</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>-4000</v>
+        <v>-3500</v>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
@@ -5830,16 +5830,16 @@
         </is>
       </c>
       <c r="C153" s="3" t="n">
-        <v>59570</v>
+        <v>59410</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>60570</v>
+        <v>60210</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>60070</v>
+        <v>59810</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
@@ -6000,16 +6000,16 @@
         </is>
       </c>
       <c r="C158" s="3" t="n">
-        <v>382000</v>
+        <v>381000</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>385000</v>
+        <v>384000</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>383500</v>
+        <v>382500</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
@@ -6037,13 +6037,13 @@
         <v>98000</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>101600</v>
+        <v>101200</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>99800</v>
+        <v>99600</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
@@ -6136,16 +6136,16 @@
         </is>
       </c>
       <c r="C162" s="3" t="n">
-        <v>8108</v>
+        <v>8104</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>8598</v>
+        <v>8431</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>8353</v>
+        <v>8267.5</v>
       </c>
       <c r="F162" s="6" t="n">
-        <v>9.5</v>
+        <v>-85.5</v>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
@@ -8376,19 +8376,19 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>172320</v>
+        <v>168420</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>176780</v>
+        <v>175200</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>174440</v>
+        <v>169980</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>174440</v>
+        <v>169980</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5600</v>
+        <v>-5780</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
@@ -8418,14 +8418,14 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>6.7568</v>
+        <v>6.757</v>
       </c>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="6" t="n">
-        <v>6.7614</v>
+        <v>6.7565</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>6.7565</v>
+        <v>6.7564</v>
       </c>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
@@ -8461,8 +8461,8 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
+      <c r="H13" s="6" t="n">
+        <v>-0.22</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$163</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6192,1749 +6192,4299 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>100950</v>
+      </c>
+      <c r="D164" s="4" t="n">
+        <v>106150</v>
+      </c>
+      <c r="E164" s="4" t="n">
+        <v>103550</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="165">
-      <c r="A165" s="8" t="inlineStr">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>186300</v>
+      </c>
+      <c r="D165" s="4" t="n">
+        <v>194800</v>
+      </c>
+      <c r="E165" s="4" t="n">
+        <v>190550</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>93800</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>98500</v>
+      </c>
+      <c r="E166" s="4" t="n">
+        <v>96150</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H166" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>190800</v>
+      </c>
+      <c r="D167" s="4" t="n">
+        <v>200300</v>
+      </c>
+      <c r="E167" s="4" t="n">
+        <v>195550</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H167" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>116350</v>
+      </c>
+      <c r="D168" s="4" t="n">
+        <v>122050</v>
+      </c>
+      <c r="E168" s="4" t="n">
+        <v>119200</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H168" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>214000</v>
+      </c>
+      <c r="D169" s="4" t="n">
+        <v>223600</v>
+      </c>
+      <c r="E169" s="4" t="n">
+        <v>218800</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H169" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="E170" s="6" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F170" s="6" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H170" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D171" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E171" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>211100</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>219400</v>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>215250</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="D173" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E173" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H173" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="D174" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="E174" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="E175" s="6" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H175" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="D176" s="6" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="E176" s="6" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="D177" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="E177" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H177" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="E178" s="6" t="n">
+        <v>75.83</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H178" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>102301</v>
+      </c>
+      <c r="D179" s="4" t="n">
+        <v>106476</v>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>104388.5</v>
+      </c>
+      <c r="F179" s="6" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H179" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>154696</v>
+      </c>
+      <c r="D180" s="4" t="n">
+        <v>154696</v>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>154696</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>492</v>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>7655</v>
+      </c>
+      <c r="D181" s="4" t="n">
+        <v>7655</v>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>7655</v>
+      </c>
+      <c r="F181" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>33042</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>33042</v>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>33042</v>
+      </c>
+      <c r="F182" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>168483</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>168483</v>
+      </c>
+      <c r="E183" s="4" t="n">
+        <v>168483</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>389</v>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H183" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>88315</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>88315</v>
+      </c>
+      <c r="E184" s="4" t="n">
+        <v>88315</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>-261</v>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>7489</v>
+      </c>
+      <c r="D185" s="4" t="n">
+        <v>7489</v>
+      </c>
+      <c r="E185" s="4" t="n">
+        <v>7489</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H185" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>7062</v>
+      </c>
+      <c r="D186" s="4" t="n">
+        <v>7062</v>
+      </c>
+      <c r="E186" s="4" t="n">
+        <v>7062</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H186" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="E187" s="6" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D188" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E188" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F188" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="D189" s="6" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="E189" s="6" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C190" s="7" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="D190" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="E190" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="F190" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E191" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F191" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D192" s="4" t="n">
+        <v>118000</v>
+      </c>
+      <c r="E192" s="4" t="n">
+        <v>114000</v>
+      </c>
+      <c r="F192" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>332000</v>
+      </c>
+      <c r="D193" s="4" t="n">
+        <v>345000</v>
+      </c>
+      <c r="E193" s="4" t="n">
+        <v>338500</v>
+      </c>
+      <c r="F193" s="4" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D194" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E194" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F194" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>138500</v>
+      </c>
+      <c r="D195" s="4" t="n">
+        <v>145500</v>
+      </c>
+      <c r="E195" s="4" t="n">
+        <v>142000</v>
+      </c>
+      <c r="F195" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>162000</v>
+      </c>
+      <c r="D196" s="4" t="n">
+        <v>169000</v>
+      </c>
+      <c r="E196" s="4" t="n">
+        <v>165500</v>
+      </c>
+      <c r="F196" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>1070000</v>
+      </c>
+      <c r="D197" s="4" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="E197" s="4" t="n">
+        <v>1105000</v>
+      </c>
+      <c r="F197" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>2425</v>
+      </c>
+      <c r="D198" s="4" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E198" s="4" t="n">
+        <v>2481</v>
+      </c>
+      <c r="F198" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>22050</v>
+      </c>
+      <c r="D199" s="4" t="n">
+        <v>25550</v>
+      </c>
+      <c r="E199" s="4" t="n">
+        <v>23800</v>
+      </c>
+      <c r="F199" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>26200</v>
+      </c>
+      <c r="D200" s="4" t="n">
+        <v>30750</v>
+      </c>
+      <c r="E200" s="4" t="n">
+        <v>28475</v>
+      </c>
+      <c r="F200" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H200" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="D201" s="4" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E201" s="4" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F201" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D202" s="4" t="n">
+        <v>11800</v>
+      </c>
+      <c r="E202" s="4" t="n">
+        <v>11150</v>
+      </c>
+      <c r="F202" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>17800</v>
+      </c>
+      <c r="D203" s="4" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E203" s="4" t="n">
+        <v>18400</v>
+      </c>
+      <c r="F203" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H203" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E204" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F204" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D205" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E205" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F205" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H205" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>305000</v>
+      </c>
+      <c r="D206" s="4" t="n">
+        <v>320000</v>
+      </c>
+      <c r="E206" s="4" t="n">
+        <v>312500</v>
+      </c>
+      <c r="F206" s="4" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H206" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>106000</v>
+      </c>
+      <c r="D207" s="4" t="n">
+        <v>112000</v>
+      </c>
+      <c r="E207" s="4" t="n">
+        <v>109000</v>
+      </c>
+      <c r="F207" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>39000</v>
+      </c>
+      <c r="D208" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E208" s="4" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F208" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>2420</v>
+      </c>
+      <c r="D209" s="4" t="n">
+        <v>2530</v>
+      </c>
+      <c r="E209" s="4" t="n">
+        <v>2475</v>
+      </c>
+      <c r="F209" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H209" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>2445</v>
+      </c>
+      <c r="D210" s="4" t="n">
+        <v>2547</v>
+      </c>
+      <c r="E210" s="4" t="n">
+        <v>2496</v>
+      </c>
+      <c r="F210" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="D211" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="E211" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="F211" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H211" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>288000</v>
+      </c>
+      <c r="D212" s="4" t="n">
+        <v>295000</v>
+      </c>
+      <c r="E212" s="4" t="n">
+        <v>291500</v>
+      </c>
+      <c r="F212" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E213" s="6" t="n">
+        <v>19.65</v>
+      </c>
+      <c r="F213" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="D214" s="6" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="E214" s="6" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="F214" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>154000</v>
+      </c>
+      <c r="D215" s="4" t="n">
+        <v>167000</v>
+      </c>
+      <c r="E215" s="4" t="n">
+        <v>160500</v>
+      </c>
+      <c r="F215" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H215" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>146500</v>
+      </c>
+      <c r="D216" s="4" t="n">
+        <v>162500</v>
+      </c>
+      <c r="E216" s="4" t="n">
+        <v>154500</v>
+      </c>
+      <c r="F216" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H216" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>7590</v>
+      </c>
+      <c r="D217" s="4" t="n">
+        <v>7790</v>
+      </c>
+      <c r="E217" s="4" t="n">
+        <v>7690</v>
+      </c>
+      <c r="F217" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H217" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>33400</v>
+      </c>
+      <c r="D218" s="4" t="n">
+        <v>33820</v>
+      </c>
+      <c r="E218" s="4" t="n">
+        <v>33610</v>
+      </c>
+      <c r="F218" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>166000</v>
+      </c>
+      <c r="D219" s="4" t="n">
+        <v>173000</v>
+      </c>
+      <c r="E219" s="4" t="n">
+        <v>169500</v>
+      </c>
+      <c r="F219" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H219" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C220" s="7" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="E220" s="6" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="F220" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H220" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C221" s="7" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="D221" s="6" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E221" s="6" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="F221" s="6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H221" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D222" s="4" t="n">
+        <v>1170000</v>
+      </c>
+      <c r="E222" s="4" t="n">
+        <v>1135000</v>
+      </c>
+      <c r="F222" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H222" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>382000</v>
+      </c>
+      <c r="D223" s="4" t="n">
+        <v>405000</v>
+      </c>
+      <c r="E223" s="4" t="n">
+        <v>393500</v>
+      </c>
+      <c r="F223" s="4" t="n">
+        <v>-3500</v>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H223" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C224" s="7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D224" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E224" s="6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F224" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H224" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>34500</v>
+      </c>
+      <c r="D225" s="4" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E225" s="4" t="n">
+        <v>36750</v>
+      </c>
+      <c r="F225" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H225" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>87000</v>
+      </c>
+      <c r="D226" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>88500</v>
+      </c>
+      <c r="F226" s="4" t="n">
+        <v>-250</v>
+      </c>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D227" s="4" t="n">
+        <v>225000</v>
+      </c>
+      <c r="E227" s="4" t="n">
+        <v>217500</v>
+      </c>
+      <c r="F227" s="4" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>59730</v>
+      </c>
+      <c r="D228" s="4" t="n">
+        <v>60330</v>
+      </c>
+      <c r="E228" s="4" t="n">
+        <v>60030</v>
+      </c>
+      <c r="F228" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="G228" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H228" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>64500</v>
+      </c>
+      <c r="D229" s="4" t="n">
+        <v>69500</v>
+      </c>
+      <c r="E229" s="4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="F229" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H229" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C230" s="7" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="D230" s="6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E230" s="6" t="n">
+        <v>25.13</v>
+      </c>
+      <c r="F230" s="6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H230" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>26783</v>
+      </c>
+      <c r="D231" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="E231" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="F231" s="4" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H231" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D232" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E232" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F232" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H232" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>380000</v>
+      </c>
+      <c r="D233" s="4" t="n">
+        <v>383000</v>
+      </c>
+      <c r="E233" s="4" t="n">
+        <v>381500</v>
+      </c>
+      <c r="F233" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H233" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D234" s="4" t="n">
+        <v>101200</v>
+      </c>
+      <c r="E234" s="4" t="n">
+        <v>99600</v>
+      </c>
+      <c r="F234" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H234" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D235" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="E235" s="4" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F235" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H235" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D236" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E236" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H236" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>8109</v>
+      </c>
+      <c r="D237" s="4" t="n">
+        <v>8490</v>
+      </c>
+      <c r="E237" s="4" t="n">
+        <v>8299.5</v>
+      </c>
+      <c r="F237" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H237" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>2470</v>
+      </c>
+      <c r="D238" s="4" t="n">
+        <v>2470</v>
+      </c>
+      <c r="E238" s="4" t="n">
+        <v>2470</v>
+      </c>
+      <c r="F238" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="G238" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H238" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B165" s="9" t="n"/>
-      <c r="C165" s="9" t="n"/>
-      <c r="D165" s="9" t="n"/>
-      <c r="E165" s="9" t="n"/>
-      <c r="F165" s="9" t="n"/>
-      <c r="G165" s="9" t="n"/>
-      <c r="H165" s="9" t="n"/>
-    </row>
-    <row r="166">
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B240" s="9" t="n"/>
+      <c r="C240" s="9" t="n"/>
+      <c r="D240" s="9" t="n"/>
+      <c r="E240" s="9" t="n"/>
+      <c r="F240" s="9" t="n"/>
+      <c r="G240" s="9" t="n"/>
+      <c r="H240" s="9" t="n"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C166" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$166),"")</f>
-        <v/>
-      </c>
-      <c r="D166" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$166),"")</f>
-        <v/>
-      </c>
-      <c r="E166" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$166),"")</f>
-        <v/>
-      </c>
-      <c r="F166" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$166)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="167">
-      <c r="B167" s="2" t="inlineStr">
+      <c r="C241" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$241),"")</f>
+        <v/>
+      </c>
+      <c r="D241" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$241),"")</f>
+        <v/>
+      </c>
+      <c r="E241" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$241),"")</f>
+        <v/>
+      </c>
+      <c r="F241" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$241)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C167" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$167),"")</f>
-        <v/>
-      </c>
-      <c r="D167" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$167),"")</f>
-        <v/>
-      </c>
-      <c r="E167" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$167),"")</f>
-        <v/>
-      </c>
-      <c r="F167" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$167)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168">
-      <c r="B168" s="2" t="inlineStr">
+      <c r="C242" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$242),"")</f>
+        <v/>
+      </c>
+      <c r="D242" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$242),"")</f>
+        <v/>
+      </c>
+      <c r="E242" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$242),"")</f>
+        <v/>
+      </c>
+      <c r="F242" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$242)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C168" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$168),"")</f>
-        <v/>
-      </c>
-      <c r="D168" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$168),"")</f>
-        <v/>
-      </c>
-      <c r="E168" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$168),"")</f>
-        <v/>
-      </c>
-      <c r="F168" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$168)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C243" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$243),"")</f>
+        <v/>
+      </c>
+      <c r="D243" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$243),"")</f>
+        <v/>
+      </c>
+      <c r="E243" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$243),"")</f>
+        <v/>
+      </c>
+      <c r="F243" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$243)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C169" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$169),"")</f>
-        <v/>
-      </c>
-      <c r="D169" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$169),"")</f>
-        <v/>
-      </c>
-      <c r="E169" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$169),"")</f>
-        <v/>
-      </c>
-      <c r="F169" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$169)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170">
-      <c r="B170" s="2" t="inlineStr">
+      <c r="C244" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$244),"")</f>
+        <v/>
+      </c>
+      <c r="D244" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$244),"")</f>
+        <v/>
+      </c>
+      <c r="E244" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$244),"")</f>
+        <v/>
+      </c>
+      <c r="F244" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$244)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="B245" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C170" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$170),"")</f>
-        <v/>
-      </c>
-      <c r="D170" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$170),"")</f>
-        <v/>
-      </c>
-      <c r="E170" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$170),"")</f>
-        <v/>
-      </c>
-      <c r="F170" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$170)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C245" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$245),"")</f>
+        <v/>
+      </c>
+      <c r="D245" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$245),"")</f>
+        <v/>
+      </c>
+      <c r="E245" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$245),"")</f>
+        <v/>
+      </c>
+      <c r="F245" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$245)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C171" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$171),"")</f>
-        <v/>
-      </c>
-      <c r="D171" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$171),"")</f>
-        <v/>
-      </c>
-      <c r="E171" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$171),"")</f>
-        <v/>
-      </c>
-      <c r="F171" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$171)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="172">
-      <c r="B172" s="2" t="inlineStr">
+      <c r="C246" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$246),"")</f>
+        <v/>
+      </c>
+      <c r="D246" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$246),"")</f>
+        <v/>
+      </c>
+      <c r="E246" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$246),"")</f>
+        <v/>
+      </c>
+      <c r="F246" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$246)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C172" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$172),"")</f>
-        <v/>
-      </c>
-      <c r="D172" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$172),"")</f>
-        <v/>
-      </c>
-      <c r="E172" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$172),"")</f>
-        <v/>
-      </c>
-      <c r="F172" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$172)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173">
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C247" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$247),"")</f>
+        <v/>
+      </c>
+      <c r="D247" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$247),"")</f>
+        <v/>
+      </c>
+      <c r="E247" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$247),"")</f>
+        <v/>
+      </c>
+      <c r="F247" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$247)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C173" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$173),"")</f>
-        <v/>
-      </c>
-      <c r="D173" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$173),"")</f>
-        <v/>
-      </c>
-      <c r="E173" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$173),"")</f>
-        <v/>
-      </c>
-      <c r="F173" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$173)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="174">
-      <c r="B174" s="2" t="inlineStr">
+      <c r="C248" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$248),"")</f>
+        <v/>
+      </c>
+      <c r="D248" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$248),"")</f>
+        <v/>
+      </c>
+      <c r="E248" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$248),"")</f>
+        <v/>
+      </c>
+      <c r="F248" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$248)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C174" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$174),"")</f>
-        <v/>
-      </c>
-      <c r="D174" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$174),"")</f>
-        <v/>
-      </c>
-      <c r="E174" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$174),"")</f>
-        <v/>
-      </c>
-      <c r="F174" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$174)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175">
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C249" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$249),"")</f>
+        <v/>
+      </c>
+      <c r="D249" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$249),"")</f>
+        <v/>
+      </c>
+      <c r="E249" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$249),"")</f>
+        <v/>
+      </c>
+      <c r="F249" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$249)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C175" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$175),"")</f>
-        <v/>
-      </c>
-      <c r="D175" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$175),"")</f>
-        <v/>
-      </c>
-      <c r="E175" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$175),"")</f>
-        <v/>
-      </c>
-      <c r="F175" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$175)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="B176" s="2" t="inlineStr">
+      <c r="C250" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$250),"")</f>
+        <v/>
+      </c>
+      <c r="D250" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$250),"")</f>
+        <v/>
+      </c>
+      <c r="E250" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$250),"")</f>
+        <v/>
+      </c>
+      <c r="F250" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$250)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C176" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$176),"")</f>
-        <v/>
-      </c>
-      <c r="D176" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$176),"")</f>
-        <v/>
-      </c>
-      <c r="E176" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$176),"")</f>
-        <v/>
-      </c>
-      <c r="F176" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$176)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="177">
-      <c r="B177" s="2" t="inlineStr">
+      <c r="C251" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$251),"")</f>
+        <v/>
+      </c>
+      <c r="D251" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$251),"")</f>
+        <v/>
+      </c>
+      <c r="E251" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$251),"")</f>
+        <v/>
+      </c>
+      <c r="F251" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$251)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C177" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$177),"")</f>
-        <v/>
-      </c>
-      <c r="D177" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$177),"")</f>
-        <v/>
-      </c>
-      <c r="E177" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$177),"")</f>
-        <v/>
-      </c>
-      <c r="F177" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$177)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="178">
-      <c r="B178" s="2" t="inlineStr">
+      <c r="C252" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$252),"")</f>
+        <v/>
+      </c>
+      <c r="D252" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$252),"")</f>
+        <v/>
+      </c>
+      <c r="E252" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$252),"")</f>
+        <v/>
+      </c>
+      <c r="F252" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$252)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C178" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$178),"")</f>
-        <v/>
-      </c>
-      <c r="D178" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$178),"")</f>
-        <v/>
-      </c>
-      <c r="E178" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$178),"")</f>
-        <v/>
-      </c>
-      <c r="F178" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$178)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="B179" s="2" t="inlineStr">
+      <c r="C253" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$253),"")</f>
+        <v/>
+      </c>
+      <c r="D253" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$253),"")</f>
+        <v/>
+      </c>
+      <c r="E253" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$253),"")</f>
+        <v/>
+      </c>
+      <c r="F253" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$253)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C179" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$179),"")</f>
-        <v/>
-      </c>
-      <c r="D179" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$179),"")</f>
-        <v/>
-      </c>
-      <c r="E179" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$179),"")</f>
-        <v/>
-      </c>
-      <c r="F179" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$179)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="B180" s="2" t="inlineStr">
+      <c r="C254" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$254),"")</f>
+        <v/>
+      </c>
+      <c r="D254" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$254),"")</f>
+        <v/>
+      </c>
+      <c r="E254" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$254),"")</f>
+        <v/>
+      </c>
+      <c r="F254" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$254)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C180" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$180),"")</f>
-        <v/>
-      </c>
-      <c r="D180" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$180),"")</f>
-        <v/>
-      </c>
-      <c r="E180" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$180),"")</f>
-        <v/>
-      </c>
-      <c r="F180" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$180)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="B181" s="2" t="inlineStr">
+      <c r="C255" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$255),"")</f>
+        <v/>
+      </c>
+      <c r="D255" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$255),"")</f>
+        <v/>
+      </c>
+      <c r="E255" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$255),"")</f>
+        <v/>
+      </c>
+      <c r="F255" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$255)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C181" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$181),"")</f>
-        <v/>
-      </c>
-      <c r="D181" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$181),"")</f>
-        <v/>
-      </c>
-      <c r="E181" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$181),"")</f>
-        <v/>
-      </c>
-      <c r="F181" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$181)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="B182" s="2" t="inlineStr">
+      <c r="C256" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$256),"")</f>
+        <v/>
+      </c>
+      <c r="D256" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$256),"")</f>
+        <v/>
+      </c>
+      <c r="E256" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$256),"")</f>
+        <v/>
+      </c>
+      <c r="F256" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$256)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C182" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$182),"")</f>
-        <v/>
-      </c>
-      <c r="D182" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$182),"")</f>
-        <v/>
-      </c>
-      <c r="E182" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$182),"")</f>
-        <v/>
-      </c>
-      <c r="F182" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$182)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="B183" s="2" t="inlineStr">
+      <c r="C257" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$257),"")</f>
+        <v/>
+      </c>
+      <c r="D257" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$257),"")</f>
+        <v/>
+      </c>
+      <c r="E257" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$257),"")</f>
+        <v/>
+      </c>
+      <c r="F257" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$257)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C183" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$183),"")</f>
-        <v/>
-      </c>
-      <c r="D183" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$183),"")</f>
-        <v/>
-      </c>
-      <c r="E183" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$183),"")</f>
-        <v/>
-      </c>
-      <c r="F183" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$183)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="B184" s="2" t="inlineStr">
+      <c r="C258" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$258),"")</f>
+        <v/>
+      </c>
+      <c r="D258" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$258),"")</f>
+        <v/>
+      </c>
+      <c r="E258" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$258),"")</f>
+        <v/>
+      </c>
+      <c r="F258" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$258)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="B259" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C184" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$184),"")</f>
-        <v/>
-      </c>
-      <c r="D184" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$184),"")</f>
-        <v/>
-      </c>
-      <c r="E184" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$184),"")</f>
-        <v/>
-      </c>
-      <c r="F184" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$184)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="B185" s="2" t="inlineStr">
+      <c r="C259" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$259),"")</f>
+        <v/>
+      </c>
+      <c r="D259" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$259),"")</f>
+        <v/>
+      </c>
+      <c r="E259" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$259),"")</f>
+        <v/>
+      </c>
+      <c r="F259" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$259)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C185" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$185),"")</f>
-        <v/>
-      </c>
-      <c r="D185" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$185),"")</f>
-        <v/>
-      </c>
-      <c r="E185" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$185),"")</f>
-        <v/>
-      </c>
-      <c r="F185" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$185)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="B186" s="2" t="inlineStr">
+      <c r="C260" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$260),"")</f>
+        <v/>
+      </c>
+      <c r="D260" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$260),"")</f>
+        <v/>
+      </c>
+      <c r="E260" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$260),"")</f>
+        <v/>
+      </c>
+      <c r="F260" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$260)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C186" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$186),"")</f>
-        <v/>
-      </c>
-      <c r="D186" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$186),"")</f>
-        <v/>
-      </c>
-      <c r="E186" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$186),"")</f>
-        <v/>
-      </c>
-      <c r="F186" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$186)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="B187" s="2" t="inlineStr">
+      <c r="C261" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$261),"")</f>
+        <v/>
+      </c>
+      <c r="D261" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$261),"")</f>
+        <v/>
+      </c>
+      <c r="E261" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$261),"")</f>
+        <v/>
+      </c>
+      <c r="F261" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$261)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="B262" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C187" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$187),"")</f>
-        <v/>
-      </c>
-      <c r="D187" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$187),"")</f>
-        <v/>
-      </c>
-      <c r="E187" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$187),"")</f>
-        <v/>
-      </c>
-      <c r="F187" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$187)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="B188" s="2" t="inlineStr">
+      <c r="C262" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$262),"")</f>
+        <v/>
+      </c>
+      <c r="D262" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$262),"")</f>
+        <v/>
+      </c>
+      <c r="E262" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$262),"")</f>
+        <v/>
+      </c>
+      <c r="F262" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$262)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C188" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$188),"")</f>
-        <v/>
-      </c>
-      <c r="D188" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$188),"")</f>
-        <v/>
-      </c>
-      <c r="E188" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$188),"")</f>
-        <v/>
-      </c>
-      <c r="F188" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$188)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" s="2" t="inlineStr">
+      <c r="C263" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$263),"")</f>
+        <v/>
+      </c>
+      <c r="D263" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$263),"")</f>
+        <v/>
+      </c>
+      <c r="E263" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$263),"")</f>
+        <v/>
+      </c>
+      <c r="F263" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$263)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C189" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$189),"")</f>
-        <v/>
-      </c>
-      <c r="D189" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$189),"")</f>
-        <v/>
-      </c>
-      <c r="E189" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$189),"")</f>
-        <v/>
-      </c>
-      <c r="F189" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$189)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="B190" s="2" t="inlineStr">
+      <c r="C264" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$264),"")</f>
+        <v/>
+      </c>
+      <c r="D264" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$264),"")</f>
+        <v/>
+      </c>
+      <c r="E264" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$264),"")</f>
+        <v/>
+      </c>
+      <c r="F264" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$264)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C190" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$190),"")</f>
-        <v/>
-      </c>
-      <c r="D190" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$190),"")</f>
-        <v/>
-      </c>
-      <c r="E190" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$190),"")</f>
-        <v/>
-      </c>
-      <c r="F190" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$190)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="B191" s="2" t="inlineStr">
+      <c r="C265" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$265),"")</f>
+        <v/>
+      </c>
+      <c r="D265" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$265),"")</f>
+        <v/>
+      </c>
+      <c r="E265" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$265),"")</f>
+        <v/>
+      </c>
+      <c r="F265" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$265)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C191" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$191),"")</f>
-        <v/>
-      </c>
-      <c r="D191" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$191),"")</f>
-        <v/>
-      </c>
-      <c r="E191" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$191),"")</f>
-        <v/>
-      </c>
-      <c r="F191" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$191)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="B192" s="2" t="inlineStr">
+      <c r="C266" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$266),"")</f>
+        <v/>
+      </c>
+      <c r="D266" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$266),"")</f>
+        <v/>
+      </c>
+      <c r="E266" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$266),"")</f>
+        <v/>
+      </c>
+      <c r="F266" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$266)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C192" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$192),"")</f>
-        <v/>
-      </c>
-      <c r="D192" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$192),"")</f>
-        <v/>
-      </c>
-      <c r="E192" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$192),"")</f>
-        <v/>
-      </c>
-      <c r="F192" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$192)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="B193" s="2" t="inlineStr">
+      <c r="C267" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$267),"")</f>
+        <v/>
+      </c>
+      <c r="D267" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$267),"")</f>
+        <v/>
+      </c>
+      <c r="E267" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$267),"")</f>
+        <v/>
+      </c>
+      <c r="F267" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$267)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C193" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$193),"")</f>
-        <v/>
-      </c>
-      <c r="D193" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$193),"")</f>
-        <v/>
-      </c>
-      <c r="E193" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$193),"")</f>
-        <v/>
-      </c>
-      <c r="F193" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$193)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="B194" s="2" t="inlineStr">
+      <c r="C268" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$268),"")</f>
+        <v/>
+      </c>
+      <c r="D268" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$268),"")</f>
+        <v/>
+      </c>
+      <c r="E268" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$268),"")</f>
+        <v/>
+      </c>
+      <c r="F268" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$268)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C194" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$194),"")</f>
-        <v/>
-      </c>
-      <c r="D194" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$194),"")</f>
-        <v/>
-      </c>
-      <c r="E194" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$194),"")</f>
-        <v/>
-      </c>
-      <c r="F194" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$194)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="B195" s="2" t="inlineStr">
+      <c r="C269" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$269),"")</f>
+        <v/>
+      </c>
+      <c r="D269" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$269),"")</f>
+        <v/>
+      </c>
+      <c r="E269" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$269),"")</f>
+        <v/>
+      </c>
+      <c r="F269" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$269)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C195" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$195),"")</f>
-        <v/>
-      </c>
-      <c r="D195" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$195),"")</f>
-        <v/>
-      </c>
-      <c r="E195" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$195),"")</f>
-        <v/>
-      </c>
-      <c r="F195" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$195)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="B196" s="2" t="inlineStr">
+      <c r="C270" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$270),"")</f>
+        <v/>
+      </c>
+      <c r="D270" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$270),"")</f>
+        <v/>
+      </c>
+      <c r="E270" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$270),"")</f>
+        <v/>
+      </c>
+      <c r="F270" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$270)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="B271" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C196" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$196),"")</f>
-        <v/>
-      </c>
-      <c r="D196" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$196),"")</f>
-        <v/>
-      </c>
-      <c r="E196" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$196),"")</f>
-        <v/>
-      </c>
-      <c r="F196" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$196)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="B197" s="2" t="inlineStr">
+      <c r="C271" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$271),"")</f>
+        <v/>
+      </c>
+      <c r="D271" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$271),"")</f>
+        <v/>
+      </c>
+      <c r="E271" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$271),"")</f>
+        <v/>
+      </c>
+      <c r="F271" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$271)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C197" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$197),"")</f>
-        <v/>
-      </c>
-      <c r="D197" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$197),"")</f>
-        <v/>
-      </c>
-      <c r="E197" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$197),"")</f>
-        <v/>
-      </c>
-      <c r="F197" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$197)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="B198" s="2" t="inlineStr">
+      <c r="C272" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$272),"")</f>
+        <v/>
+      </c>
+      <c r="D272" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$272),"")</f>
+        <v/>
+      </c>
+      <c r="E272" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$272),"")</f>
+        <v/>
+      </c>
+      <c r="F272" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$272)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273">
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C198" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$198),"")</f>
-        <v/>
-      </c>
-      <c r="D198" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$198),"")</f>
-        <v/>
-      </c>
-      <c r="E198" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$198),"")</f>
-        <v/>
-      </c>
-      <c r="F198" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$198)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="B199" s="2" t="inlineStr">
+      <c r="C273" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$273),"")</f>
+        <v/>
+      </c>
+      <c r="D273" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$273),"")</f>
+        <v/>
+      </c>
+      <c r="E273" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$273),"")</f>
+        <v/>
+      </c>
+      <c r="F273" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$273)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="B274" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C199" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$199),"")</f>
-        <v/>
-      </c>
-      <c r="D199" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$199),"")</f>
-        <v/>
-      </c>
-      <c r="E199" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$199),"")</f>
-        <v/>
-      </c>
-      <c r="F199" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$199)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="B200" s="2" t="inlineStr">
+      <c r="C274" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$274),"")</f>
+        <v/>
+      </c>
+      <c r="D274" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$274),"")</f>
+        <v/>
+      </c>
+      <c r="E274" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$274),"")</f>
+        <v/>
+      </c>
+      <c r="F274" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$274)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275">
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C200" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$200),"")</f>
-        <v/>
-      </c>
-      <c r="D200" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$200),"")</f>
-        <v/>
-      </c>
-      <c r="E200" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$200),"")</f>
-        <v/>
-      </c>
-      <c r="F200" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$200)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="B201" s="2" t="inlineStr">
+      <c r="C275" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$275),"")</f>
+        <v/>
+      </c>
+      <c r="D275" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$275),"")</f>
+        <v/>
+      </c>
+      <c r="E275" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$275),"")</f>
+        <v/>
+      </c>
+      <c r="F275" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$275)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C201" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$201),"")</f>
-        <v/>
-      </c>
-      <c r="D201" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$201),"")</f>
-        <v/>
-      </c>
-      <c r="E201" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$201),"")</f>
-        <v/>
-      </c>
-      <c r="F201" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$201)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="B202" s="2" t="inlineStr">
+      <c r="C276" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$276),"")</f>
+        <v/>
+      </c>
+      <c r="D276" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$276),"")</f>
+        <v/>
+      </c>
+      <c r="E276" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$276),"")</f>
+        <v/>
+      </c>
+      <c r="F276" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$276)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C202" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$202),"")</f>
-        <v/>
-      </c>
-      <c r="D202" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$202),"")</f>
-        <v/>
-      </c>
-      <c r="E202" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$202),"")</f>
-        <v/>
-      </c>
-      <c r="F202" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$202)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="B203" s="2" t="inlineStr">
+      <c r="C277" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$277),"")</f>
+        <v/>
+      </c>
+      <c r="D277" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$277),"")</f>
+        <v/>
+      </c>
+      <c r="E277" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$277),"")</f>
+        <v/>
+      </c>
+      <c r="F277" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$277)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C203" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$203),"")</f>
-        <v/>
-      </c>
-      <c r="D203" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$203),"")</f>
-        <v/>
-      </c>
-      <c r="E203" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$203),"")</f>
-        <v/>
-      </c>
-      <c r="F203" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$203)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="B204" s="2" t="inlineStr">
+      <c r="C278" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$278),"")</f>
+        <v/>
+      </c>
+      <c r="D278" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$278),"")</f>
+        <v/>
+      </c>
+      <c r="E278" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$278),"")</f>
+        <v/>
+      </c>
+      <c r="F278" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$278)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C204" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$204),"")</f>
-        <v/>
-      </c>
-      <c r="D204" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$204),"")</f>
-        <v/>
-      </c>
-      <c r="E204" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$204),"")</f>
-        <v/>
-      </c>
-      <c r="F204" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$204)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205">
-      <c r="B205" s="2" t="inlineStr">
+      <c r="C279" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$279),"")</f>
+        <v/>
+      </c>
+      <c r="D279" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$279),"")</f>
+        <v/>
+      </c>
+      <c r="E279" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$279),"")</f>
+        <v/>
+      </c>
+      <c r="F279" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$279)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C205" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$205),"")</f>
-        <v/>
-      </c>
-      <c r="D205" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$205),"")</f>
-        <v/>
-      </c>
-      <c r="E205" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$205),"")</f>
-        <v/>
-      </c>
-      <c r="F205" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$205)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="B206" s="2" t="inlineStr">
+      <c r="C280" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$280),"")</f>
+        <v/>
+      </c>
+      <c r="D280" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$280),"")</f>
+        <v/>
+      </c>
+      <c r="E280" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$280),"")</f>
+        <v/>
+      </c>
+      <c r="F280" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$280)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C206" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$206),"")</f>
-        <v/>
-      </c>
-      <c r="D206" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$206),"")</f>
-        <v/>
-      </c>
-      <c r="E206" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$206),"")</f>
-        <v/>
-      </c>
-      <c r="F206" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$206)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207">
-      <c r="B207" s="2" t="inlineStr">
+      <c r="C281" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$281),"")</f>
+        <v/>
+      </c>
+      <c r="D281" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$281),"")</f>
+        <v/>
+      </c>
+      <c r="E281" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$281),"")</f>
+        <v/>
+      </c>
+      <c r="F281" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$281)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C207" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$207),"")</f>
-        <v/>
-      </c>
-      <c r="D207" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$207),"")</f>
-        <v/>
-      </c>
-      <c r="E207" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$207),"")</f>
-        <v/>
-      </c>
-      <c r="F207" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$207)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="B208" s="2" t="inlineStr">
+      <c r="C282" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$282),"")</f>
+        <v/>
+      </c>
+      <c r="D282" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$282),"")</f>
+        <v/>
+      </c>
+      <c r="E282" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$282),"")</f>
+        <v/>
+      </c>
+      <c r="F282" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$282)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C208" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$208),"")</f>
-        <v/>
-      </c>
-      <c r="D208" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$208),"")</f>
-        <v/>
-      </c>
-      <c r="E208" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$208),"")</f>
-        <v/>
-      </c>
-      <c r="F208" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$208)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209">
-      <c r="B209" s="2" t="inlineStr">
+      <c r="C283" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$283),"")</f>
+        <v/>
+      </c>
+      <c r="D283" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$283),"")</f>
+        <v/>
+      </c>
+      <c r="E283" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$283),"")</f>
+        <v/>
+      </c>
+      <c r="F283" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$283)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C209" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$209),"")</f>
-        <v/>
-      </c>
-      <c r="D209" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$209),"")</f>
-        <v/>
-      </c>
-      <c r="E209" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$209),"")</f>
-        <v/>
-      </c>
-      <c r="F209" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$209)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="B210" s="2" t="inlineStr">
+      <c r="C284" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$284),"")</f>
+        <v/>
+      </c>
+      <c r="D284" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$284),"")</f>
+        <v/>
+      </c>
+      <c r="E284" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$284),"")</f>
+        <v/>
+      </c>
+      <c r="F284" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$284)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C210" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$210),"")</f>
-        <v/>
-      </c>
-      <c r="D210" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$210),"")</f>
-        <v/>
-      </c>
-      <c r="E210" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$210),"")</f>
-        <v/>
-      </c>
-      <c r="F210" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$210)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="B211" s="2" t="inlineStr">
+      <c r="C285" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$285),"")</f>
+        <v/>
+      </c>
+      <c r="D285" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$285),"")</f>
+        <v/>
+      </c>
+      <c r="E285" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$285),"")</f>
+        <v/>
+      </c>
+      <c r="F285" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$285)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C211" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$211),"")</f>
-        <v/>
-      </c>
-      <c r="D211" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$211),"")</f>
-        <v/>
-      </c>
-      <c r="E211" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$211),"")</f>
-        <v/>
-      </c>
-      <c r="F211" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$211)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="B212" s="2" t="inlineStr">
+      <c r="C286" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$286),"")</f>
+        <v/>
+      </c>
+      <c r="D286" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$286),"")</f>
+        <v/>
+      </c>
+      <c r="E286" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$286),"")</f>
+        <v/>
+      </c>
+      <c r="F286" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$286)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C212" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$212),"")</f>
-        <v/>
-      </c>
-      <c r="D212" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$212),"")</f>
-        <v/>
-      </c>
-      <c r="E212" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$212),"")</f>
-        <v/>
-      </c>
-      <c r="F212" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$212)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="B213" s="2" t="inlineStr">
+      <c r="C287" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$287),"")</f>
+        <v/>
+      </c>
+      <c r="D287" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$287),"")</f>
+        <v/>
+      </c>
+      <c r="E287" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$287),"")</f>
+        <v/>
+      </c>
+      <c r="F287" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$287)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C213" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$213),"")</f>
-        <v/>
-      </c>
-      <c r="D213" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$213),"")</f>
-        <v/>
-      </c>
-      <c r="E213" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$213),"")</f>
-        <v/>
-      </c>
-      <c r="F213" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$213)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="B214" s="2" t="inlineStr">
+      <c r="C288" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$288),"")</f>
+        <v/>
+      </c>
+      <c r="D288" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$288),"")</f>
+        <v/>
+      </c>
+      <c r="E288" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$288),"")</f>
+        <v/>
+      </c>
+      <c r="F288" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$288)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C214" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$214),"")</f>
-        <v/>
-      </c>
-      <c r="D214" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$214),"")</f>
-        <v/>
-      </c>
-      <c r="E214" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$214),"")</f>
-        <v/>
-      </c>
-      <c r="F214" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$214)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="B215" s="2" t="inlineStr">
+      <c r="C289" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$289),"")</f>
+        <v/>
+      </c>
+      <c r="D289" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$289),"")</f>
+        <v/>
+      </c>
+      <c r="E289" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$289),"")</f>
+        <v/>
+      </c>
+      <c r="F289" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$289)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C215" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$215),"")</f>
-        <v/>
-      </c>
-      <c r="D215" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$215),"")</f>
-        <v/>
-      </c>
-      <c r="E215" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$215),"")</f>
-        <v/>
-      </c>
-      <c r="F215" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$215)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216">
-      <c r="B216" s="2" t="inlineStr">
+      <c r="C290" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$290),"")</f>
+        <v/>
+      </c>
+      <c r="D290" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$290),"")</f>
+        <v/>
+      </c>
+      <c r="E290" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$290),"")</f>
+        <v/>
+      </c>
+      <c r="F290" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$290)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C216" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$216),"")</f>
-        <v/>
-      </c>
-      <c r="D216" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$216),"")</f>
-        <v/>
-      </c>
-      <c r="E216" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$216),"")</f>
-        <v/>
-      </c>
-      <c r="F216" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$216)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217">
-      <c r="B217" s="2" t="inlineStr">
+      <c r="C291" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$291),"")</f>
+        <v/>
+      </c>
+      <c r="D291" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$291),"")</f>
+        <v/>
+      </c>
+      <c r="E291" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$291),"")</f>
+        <v/>
+      </c>
+      <c r="F291" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$291)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="B292" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C217" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$217),"")</f>
-        <v/>
-      </c>
-      <c r="D217" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$217),"")</f>
-        <v/>
-      </c>
-      <c r="E217" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$217),"")</f>
-        <v/>
-      </c>
-      <c r="F217" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$217)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="B218" s="2" t="inlineStr">
+      <c r="C292" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$292),"")</f>
+        <v/>
+      </c>
+      <c r="D292" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$292),"")</f>
+        <v/>
+      </c>
+      <c r="E292" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$292),"")</f>
+        <v/>
+      </c>
+      <c r="F292" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$292)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="B293" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C218" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$218),"")</f>
-        <v/>
-      </c>
-      <c r="D218" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$218),"")</f>
-        <v/>
-      </c>
-      <c r="E218" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$218),"")</f>
-        <v/>
-      </c>
-      <c r="F218" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$218)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="B219" s="2" t="inlineStr">
+      <c r="C293" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$293),"")</f>
+        <v/>
+      </c>
+      <c r="D293" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$293),"")</f>
+        <v/>
+      </c>
+      <c r="E293" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$293),"")</f>
+        <v/>
+      </c>
+      <c r="F293" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$293)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="B294" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C219" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$219),"")</f>
-        <v/>
-      </c>
-      <c r="D219" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$219),"")</f>
-        <v/>
-      </c>
-      <c r="E219" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$219),"")</f>
-        <v/>
-      </c>
-      <c r="F219" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$219)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="B220" s="2" t="inlineStr">
+      <c r="C294" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$294),"")</f>
+        <v/>
+      </c>
+      <c r="D294" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$294),"")</f>
+        <v/>
+      </c>
+      <c r="E294" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$294),"")</f>
+        <v/>
+      </c>
+      <c r="F294" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$294)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="B295" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C220" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$220),"")</f>
-        <v/>
-      </c>
-      <c r="D220" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$220),"")</f>
-        <v/>
-      </c>
-      <c r="E220" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$220),"")</f>
-        <v/>
-      </c>
-      <c r="F220" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$220)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221">
-      <c r="B221" s="2" t="inlineStr">
+      <c r="C295" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$295),"")</f>
+        <v/>
+      </c>
+      <c r="D295" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$295),"")</f>
+        <v/>
+      </c>
+      <c r="E295" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$295),"")</f>
+        <v/>
+      </c>
+      <c r="F295" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$295)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="B296" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C221" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$221),"")</f>
-        <v/>
-      </c>
-      <c r="D221" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$221),"")</f>
-        <v/>
-      </c>
-      <c r="E221" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$221),"")</f>
-        <v/>
-      </c>
-      <c r="F221" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$221)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222">
-      <c r="B222" s="2" t="inlineStr">
+      <c r="C296" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$296),"")</f>
+        <v/>
+      </c>
+      <c r="D296" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$296),"")</f>
+        <v/>
+      </c>
+      <c r="E296" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$296),"")</f>
+        <v/>
+      </c>
+      <c r="F296" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$296)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="B297" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C222" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$222),"")</f>
-        <v/>
-      </c>
-      <c r="D222" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$222),"")</f>
-        <v/>
-      </c>
-      <c r="E222" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$222),"")</f>
-        <v/>
-      </c>
-      <c r="F222" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$222)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="B223" s="2" t="inlineStr">
+      <c r="C297" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$297),"")</f>
+        <v/>
+      </c>
+      <c r="D297" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$297),"")</f>
+        <v/>
+      </c>
+      <c r="E297" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$297),"")</f>
+        <v/>
+      </c>
+      <c r="F297" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$297)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="B298" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C223" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$223),"")</f>
-        <v/>
-      </c>
-      <c r="D223" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$223),"")</f>
-        <v/>
-      </c>
-      <c r="E223" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$223),"")</f>
-        <v/>
-      </c>
-      <c r="F223" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$223)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="224">
-      <c r="B224" s="2" t="inlineStr">
+      <c r="C298" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$298),"")</f>
+        <v/>
+      </c>
+      <c r="D298" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$298),"")</f>
+        <v/>
+      </c>
+      <c r="E298" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$298),"")</f>
+        <v/>
+      </c>
+      <c r="F298" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$298)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C224" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$224),"")</f>
-        <v/>
-      </c>
-      <c r="D224" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$224),"")</f>
-        <v/>
-      </c>
-      <c r="E224" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$224),"")</f>
-        <v/>
-      </c>
-      <c r="F224" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$224)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="225">
-      <c r="B225" s="2" t="inlineStr">
+      <c r="C299" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$299),"")</f>
+        <v/>
+      </c>
+      <c r="D299" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$299),"")</f>
+        <v/>
+      </c>
+      <c r="E299" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$299),"")</f>
+        <v/>
+      </c>
+      <c r="F299" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$299)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="B300" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C225" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$225),"")</f>
-        <v/>
-      </c>
-      <c r="D225" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$225),"")</f>
-        <v/>
-      </c>
-      <c r="E225" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$225),"")</f>
-        <v/>
-      </c>
-      <c r="F225" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$225)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="226">
-      <c r="B226" s="2" t="inlineStr">
+      <c r="C300" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$300),"")</f>
+        <v/>
+      </c>
+      <c r="D300" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$300),"")</f>
+        <v/>
+      </c>
+      <c r="E300" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$300),"")</f>
+        <v/>
+      </c>
+      <c r="F300" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$300)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="B301" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C226" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$226),"")</f>
-        <v/>
-      </c>
-      <c r="D226" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$226),"")</f>
-        <v/>
-      </c>
-      <c r="E226" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$226),"")</f>
-        <v/>
-      </c>
-      <c r="F226" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$226)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="B227" s="2" t="inlineStr">
+      <c r="C301" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$301),"")</f>
+        <v/>
+      </c>
+      <c r="D301" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$301),"")</f>
+        <v/>
+      </c>
+      <c r="E301" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$301),"")</f>
+        <v/>
+      </c>
+      <c r="F301" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$301)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C227" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$227),"")</f>
-        <v/>
-      </c>
-      <c r="D227" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$227),"")</f>
-        <v/>
-      </c>
-      <c r="E227" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$227),"")</f>
-        <v/>
-      </c>
-      <c r="F227" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$227)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228">
-      <c r="B228" s="2" t="inlineStr">
+      <c r="C302" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$302),"")</f>
+        <v/>
+      </c>
+      <c r="D302" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$302),"")</f>
+        <v/>
+      </c>
+      <c r="E302" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$302),"")</f>
+        <v/>
+      </c>
+      <c r="F302" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$302)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="B303" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C228" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$228),"")</f>
-        <v/>
-      </c>
-      <c r="D228" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$228),"")</f>
-        <v/>
-      </c>
-      <c r="E228" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$228),"")</f>
-        <v/>
-      </c>
-      <c r="F228" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$228)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229">
-      <c r="B229" s="2" t="inlineStr">
+      <c r="C303" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$303),"")</f>
+        <v/>
+      </c>
+      <c r="D303" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$303),"")</f>
+        <v/>
+      </c>
+      <c r="E303" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$303),"")</f>
+        <v/>
+      </c>
+      <c r="F303" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$303)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="B304" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C229" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$229),"")</f>
-        <v/>
-      </c>
-      <c r="D229" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$229),"")</f>
-        <v/>
-      </c>
-      <c r="E229" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$229),"")</f>
-        <v/>
-      </c>
-      <c r="F229" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$229)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="B230" s="2" t="inlineStr">
+      <c r="C304" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$304),"")</f>
+        <v/>
+      </c>
+      <c r="D304" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$304),"")</f>
+        <v/>
+      </c>
+      <c r="E304" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$304),"")</f>
+        <v/>
+      </c>
+      <c r="F304" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$304)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="B305" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C230" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$230),"")</f>
-        <v/>
-      </c>
-      <c r="D230" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$230),"")</f>
-        <v/>
-      </c>
-      <c r="E230" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$230),"")</f>
-        <v/>
-      </c>
-      <c r="F230" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$230)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="B231" s="2" t="inlineStr">
+      <c r="C305" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$305),"")</f>
+        <v/>
+      </c>
+      <c r="D305" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$305),"")</f>
+        <v/>
+      </c>
+      <c r="E305" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$305),"")</f>
+        <v/>
+      </c>
+      <c r="F305" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$305)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C231" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$231),"")</f>
-        <v/>
-      </c>
-      <c r="D231" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$231),"")</f>
-        <v/>
-      </c>
-      <c r="E231" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$231),"")</f>
-        <v/>
-      </c>
-      <c r="F231" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$231)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="B232" s="2" t="inlineStr">
+      <c r="C306" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$306),"")</f>
+        <v/>
+      </c>
+      <c r="D306" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$306),"")</f>
+        <v/>
+      </c>
+      <c r="E306" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$306),"")</f>
+        <v/>
+      </c>
+      <c r="F306" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$306)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307">
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C232" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$232),"")</f>
-        <v/>
-      </c>
-      <c r="D232" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$232),"")</f>
-        <v/>
-      </c>
-      <c r="E232" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$232),"")</f>
-        <v/>
-      </c>
-      <c r="F232" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$232)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233">
-      <c r="B233" s="2" t="inlineStr">
+      <c r="C307" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$307),"")</f>
+        <v/>
+      </c>
+      <c r="D307" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$307),"")</f>
+        <v/>
+      </c>
+      <c r="E307" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$307),"")</f>
+        <v/>
+      </c>
+      <c r="F307" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$307)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="B308" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C233" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$233),"")</f>
-        <v/>
-      </c>
-      <c r="D233" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$233),"")</f>
-        <v/>
-      </c>
-      <c r="E233" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$233),"")</f>
-        <v/>
-      </c>
-      <c r="F233" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$233)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234">
-      <c r="B234" s="2" t="inlineStr">
+      <c r="C308" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$308),"")</f>
+        <v/>
+      </c>
+      <c r="D308" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$308),"")</f>
+        <v/>
+      </c>
+      <c r="E308" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$308),"")</f>
+        <v/>
+      </c>
+      <c r="F308" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$308)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C234" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$234),"")</f>
-        <v/>
-      </c>
-      <c r="D234" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$234),"")</f>
-        <v/>
-      </c>
-      <c r="E234" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$234),"")</f>
-        <v/>
-      </c>
-      <c r="F234" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$234)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235">
-      <c r="B235" s="2" t="inlineStr">
+      <c r="C309" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$309),"")</f>
+        <v/>
+      </c>
+      <c r="D309" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$309),"")</f>
+        <v/>
+      </c>
+      <c r="E309" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$309),"")</f>
+        <v/>
+      </c>
+      <c r="F309" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$309)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310">
+      <c r="B310" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C235" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$235),"")</f>
-        <v/>
-      </c>
-      <c r="D235" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$235),"")</f>
-        <v/>
-      </c>
-      <c r="E235" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$235),"")</f>
-        <v/>
-      </c>
-      <c r="F235" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$235)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236">
-      <c r="B236" s="2" t="inlineStr">
+      <c r="C310" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$310),"")</f>
+        <v/>
+      </c>
+      <c r="D310" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$310),"")</f>
+        <v/>
+      </c>
+      <c r="E310" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$310),"")</f>
+        <v/>
+      </c>
+      <c r="F310" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$310)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311">
+      <c r="B311" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C236" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$236),"")</f>
-        <v/>
-      </c>
-      <c r="D236" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$236),"")</f>
-        <v/>
-      </c>
-      <c r="E236" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$236),"")</f>
-        <v/>
-      </c>
-      <c r="F236" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$236)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237">
-      <c r="B237" s="2" t="inlineStr">
+      <c r="C311" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$311),"")</f>
+        <v/>
+      </c>
+      <c r="D311" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$311),"")</f>
+        <v/>
+      </c>
+      <c r="E311" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$311),"")</f>
+        <v/>
+      </c>
+      <c r="F311" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$311)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C237" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$237),"")</f>
-        <v/>
-      </c>
-      <c r="D237" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$237),"")</f>
-        <v/>
-      </c>
-      <c r="E237" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$237),"")</f>
-        <v/>
-      </c>
-      <c r="F237" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$237)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="B238" s="2" t="inlineStr">
+      <c r="C312" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$312),"")</f>
+        <v/>
+      </c>
+      <c r="D312" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$312),"")</f>
+        <v/>
+      </c>
+      <c r="E312" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$312),"")</f>
+        <v/>
+      </c>
+      <c r="F312" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$312)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313">
+      <c r="B313" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C238" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$238),"")</f>
-        <v/>
-      </c>
-      <c r="D238" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$238),"")</f>
-        <v/>
-      </c>
-      <c r="E238" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$238),"")</f>
-        <v/>
-      </c>
-      <c r="F238" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$238)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239">
-      <c r="B239" s="2" t="inlineStr">
+      <c r="C313" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$313),"")</f>
+        <v/>
+      </c>
+      <c r="D313" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$313),"")</f>
+        <v/>
+      </c>
+      <c r="E313" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$313),"")</f>
+        <v/>
+      </c>
+      <c r="F313" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$313)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314">
+      <c r="B314" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C239" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$239),"")</f>
-        <v/>
-      </c>
-      <c r="D239" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$239),"")</f>
-        <v/>
-      </c>
-      <c r="E239" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$239),"")</f>
-        <v/>
-      </c>
-      <c r="F239" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$239)*(F$2:F$163),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="B240" s="2" t="inlineStr">
+      <c r="C314" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$314),"")</f>
+        <v/>
+      </c>
+      <c r="D314" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$314),"")</f>
+        <v/>
+      </c>
+      <c r="E314" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$314),"")</f>
+        <v/>
+      </c>
+      <c r="F314" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$314)*(F$2:F$238),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C240" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$240),"")</f>
-        <v/>
-      </c>
-      <c r="D240" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$240),"")</f>
-        <v/>
-      </c>
-      <c r="E240" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$163,A$2:A$163,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$163,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$163,$B$240),"")</f>
-        <v/>
-      </c>
-      <c r="F240" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$163)=YEAR(TODAY()))*(MONTH(A$2:A$163)=MONTH(TODAY()))*(B$2:B$163=$B$240)*(F$2:F$163),"")</f>
+      <c r="C315" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$315),"")</f>
+        <v/>
+      </c>
+      <c r="D315" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$315),"")</f>
+        <v/>
+      </c>
+      <c r="E315" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$315),"")</f>
+        <v/>
+      </c>
+      <c r="F315" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$315)*(F$2:F$238),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H163"/>
+  <autoFilter ref="A1:H238"/>
   <mergeCells count="1">
-    <mergeCell ref="A165:H165"/>
+    <mergeCell ref="A240:H240"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7946,7 +10496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8511,161 +11061,355 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>131640</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>133550</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>133980</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>131780</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-1850</v>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>165820</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>171800</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>167920</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>-6680</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>6.7632</v>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>6.7572</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>6.7572</v>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D17" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$17),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$17)*(H$2:H$14),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" s="2" t="inlineStr">
+      <c r="D22" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$22)*(H$2:H$19),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D18" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$18),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$18)*(H$2:H$14),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" s="2" t="inlineStr">
+      <c r="D23" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
+        <v/>
+      </c>
+      <c r="E23" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$23)*(H$2:H$19),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D19" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
-        <v/>
-      </c>
-      <c r="E19" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$19),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$19)*(H$2:H$14),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="C20" s="2" t="inlineStr">
+      <c r="D24" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
+        <v/>
+      </c>
+      <c r="E24" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$24)*(H$2:H$19),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>碳酸锂(LC)连续</t>
         </is>
       </c>
-      <c r="D20" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
-        <v/>
-      </c>
-      <c r="E20" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$20),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$20)*(H$2:H$14),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" s="2" t="inlineStr">
+      <c r="D25" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
+        <v/>
+      </c>
+      <c r="E25" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$25)*(H$2:H$19),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D21" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
-        <v/>
-      </c>
-      <c r="E21" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$14,A$2:A$14,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$14,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$14,$C$21),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$14)=YEAR(TODAY()))*(MONTH(A$2:A$14)=MONTH(TODAY()))*(C$2:C$14=$C$21)*(H$2:H$14),"")</f>
+      <c r="D26" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$26)*(H$2:H$19),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J14"/>
+  <autoFilter ref="A1:J19"/>
   <mergeCells count="1">
-    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -11129,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>167920</v>
+        <v>167880</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>-6680</v>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -11129,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>167880</v>
+        <v>168140</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>-6680</v>
@@ -11162,7 +11162,7 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6.7632</v>
+        <v>6.763</v>
       </c>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="6" t="n">

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -6204,16 +6204,16 @@
         </is>
       </c>
       <c r="C164" s="3" t="n">
-        <v>100950</v>
+        <v>100900</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>106150</v>
+        <v>106100</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>103550</v>
-      </c>
-      <c r="F164" s="4" t="n">
-        <v>-200</v>
+        <v>103500</v>
+      </c>
+      <c r="F164" s="6" t="n">
+        <v>-50</v>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
@@ -6238,16 +6238,16 @@
         </is>
       </c>
       <c r="C165" s="3" t="n">
-        <v>186300</v>
+        <v>185500</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>194800</v>
+        <v>193400</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>190550</v>
+        <v>189450</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="C166" s="3" t="n">
-        <v>93800</v>
+        <v>93750</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>98500</v>
+        <v>98450</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>96150</v>
-      </c>
-      <c r="F166" s="4" t="n">
-        <v>-200</v>
+        <v>96100</v>
+      </c>
+      <c r="F166" s="6" t="n">
+        <v>-50</v>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
@@ -6306,16 +6306,16 @@
         </is>
       </c>
       <c r="C167" s="3" t="n">
-        <v>190800</v>
+        <v>190000</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>200300</v>
+        <v>199500</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>195550</v>
+        <v>194750</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>100</v>
+        <v>-800</v>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="C168" s="3" t="n">
-        <v>116350</v>
+        <v>116300</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>122050</v>
+        <v>122000</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>119200</v>
-      </c>
-      <c r="F168" s="4" t="n">
-        <v>-200</v>
+        <v>119150</v>
+      </c>
+      <c r="F168" s="6" t="n">
+        <v>-50</v>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
@@ -6374,16 +6374,16 @@
         </is>
       </c>
       <c r="C169" s="3" t="n">
-        <v>214000</v>
+        <v>213200</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>223600</v>
+        <v>222800</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>218800</v>
+        <v>218000</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
@@ -6408,16 +6408,16 @@
         </is>
       </c>
       <c r="C170" s="7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E170" s="6" t="n">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="F170" s="6" t="n">
-        <v>-0.75</v>
+        <v>1</v>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
@@ -6476,16 +6476,16 @@
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>211100</v>
+        <v>210300</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>219400</v>
+        <v>218600</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>215250</v>
+        <v>214450</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
@@ -6510,16 +6510,16 @@
         </is>
       </c>
       <c r="C173" s="7" t="n">
-        <v>79</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>79</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E173" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="F173" s="4" t="n">
-        <v>0</v>
+        <v>78.98999999999999</v>
+      </c>
+      <c r="F173" s="6" t="n">
+        <v>-0.01</v>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
@@ -6544,16 +6544,16 @@
         </is>
       </c>
       <c r="C174" s="7" t="n">
-        <v>79.05</v>
+        <v>79</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>79.05</v>
+        <v>79</v>
       </c>
       <c r="E174" s="6" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="F174" s="4" t="n">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="F174" s="6" t="n">
+        <v>-0.05</v>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
@@ -6578,16 +6578,16 @@
         </is>
       </c>
       <c r="C175" s="7" t="n">
-        <v>79.05</v>
+        <v>79</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>79.05</v>
+        <v>79</v>
       </c>
       <c r="E175" s="6" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="F175" s="4" t="n">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="F175" s="6" t="n">
+        <v>-0.05</v>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
@@ -6646,16 +6646,16 @@
         </is>
       </c>
       <c r="C177" s="7" t="n">
-        <v>75.83</v>
+        <v>75.73</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>75.83</v>
+        <v>75.73</v>
       </c>
       <c r="E177" s="6" t="n">
-        <v>75.83</v>
-      </c>
-      <c r="F177" s="4" t="n">
-        <v>0</v>
+        <v>75.73</v>
+      </c>
+      <c r="F177" s="6" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
@@ -6680,16 +6680,16 @@
         </is>
       </c>
       <c r="C178" s="7" t="n">
-        <v>75.83</v>
+        <v>75.73</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>75.83</v>
+        <v>75.73</v>
       </c>
       <c r="E178" s="6" t="n">
-        <v>75.83</v>
-      </c>
-      <c r="F178" s="4" t="n">
-        <v>0</v>
+        <v>75.73</v>
+      </c>
+      <c r="F178" s="6" t="n">
+        <v>-0.1</v>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
@@ -6714,16 +6714,16 @@
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>102301</v>
+        <v>101802</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>106476</v>
+        <v>105958</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>104388.5</v>
-      </c>
-      <c r="F179" s="6" t="n">
-        <v>-21.5</v>
+        <v>103880</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>-508.5</v>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>154696</v>
+        <v>152617</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>154696</v>
+        <v>152617</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>154696</v>
+        <v>152617</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>492</v>
+        <v>-2079</v>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
@@ -6782,16 +6782,16 @@
         </is>
       </c>
       <c r="C181" s="3" t="n">
-        <v>7655</v>
+        <v>7658</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>7655</v>
+        <v>7658</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>7655</v>
+        <v>7658</v>
       </c>
       <c r="F181" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
@@ -6816,16 +6816,16 @@
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>33042</v>
+        <v>33000</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>33042</v>
+        <v>33000</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>33042</v>
+        <v>33000</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>-9</v>
+        <v>-42</v>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
@@ -6850,16 +6850,16 @@
         </is>
       </c>
       <c r="C183" s="3" t="n">
-        <v>168483</v>
+        <v>167053</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>168483</v>
+        <v>167053</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>168483</v>
+        <v>167053</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>389</v>
+        <v>-1430</v>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
@@ -6884,16 +6884,16 @@
         </is>
       </c>
       <c r="C184" s="3" t="n">
-        <v>88315</v>
+        <v>88287</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>88315</v>
+        <v>88287</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>88315</v>
-      </c>
-      <c r="F184" s="4" t="n">
-        <v>-261</v>
+        <v>88287</v>
+      </c>
+      <c r="F184" s="6" t="n">
+        <v>-28</v>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
@@ -6918,16 +6918,16 @@
         </is>
       </c>
       <c r="C185" s="3" t="n">
-        <v>7489</v>
+        <v>7458</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>7489</v>
+        <v>7458</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>7489</v>
-      </c>
-      <c r="F185" s="4" t="n">
-        <v>0</v>
+        <v>7458</v>
+      </c>
+      <c r="F185" s="6" t="n">
+        <v>-31</v>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
@@ -6952,16 +6952,16 @@
         </is>
       </c>
       <c r="C186" s="3" t="n">
-        <v>7062</v>
+        <v>6975</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>7062</v>
+        <v>6975</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>7062</v>
-      </c>
-      <c r="F186" s="4" t="n">
-        <v>0</v>
+        <v>6975</v>
+      </c>
+      <c r="F186" s="6" t="n">
+        <v>-87</v>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
@@ -7159,13 +7159,13 @@
         <v>110000</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>118000</v>
+        <v>112000</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>114000</v>
+        <v>111000</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>338500</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
@@ -7258,16 +7258,16 @@
         </is>
       </c>
       <c r="C195" s="3" t="n">
-        <v>138500</v>
+        <v>136000</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>145500</v>
+        <v>144000</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>142000</v>
+        <v>140000</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>500</v>
+        <v>-2000</v>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
@@ -7292,16 +7292,16 @@
         </is>
       </c>
       <c r="C196" s="3" t="n">
-        <v>162000</v>
+        <v>160500</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>169000</v>
+        <v>166000</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>165500</v>
+        <v>163250</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>500</v>
+        <v>-2250</v>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
@@ -7329,13 +7329,13 @@
         <v>1070000</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>1140000</v>
+        <v>1130000</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>1105000</v>
+        <v>1100000</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
@@ -7360,16 +7360,16 @@
         </is>
       </c>
       <c r="C198" s="3" t="n">
-        <v>2425</v>
+        <v>2370</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>2537</v>
+        <v>2500</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>2481</v>
+        <v>2435</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>1</v>
+        <v>-46</v>
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
@@ -7394,16 +7394,16 @@
         </is>
       </c>
       <c r="C199" s="3" t="n">
-        <v>22050</v>
+        <v>21800</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>25550</v>
+        <v>25200</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>23800</v>
+        <v>23500</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
@@ -7428,16 +7428,16 @@
         </is>
       </c>
       <c r="C200" s="3" t="n">
-        <v>26200</v>
+        <v>25850</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>30750</v>
+        <v>30350</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>28475</v>
+        <v>28100</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>0</v>
+        <v>-375</v>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
@@ -7462,16 +7462,16 @@
         </is>
       </c>
       <c r="C201" s="3" t="n">
-        <v>16500</v>
+        <v>16300</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>18000</v>
+        <v>17600</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>17250</v>
+        <v>16950</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
@@ -7499,13 +7499,13 @@
         <v>10500</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>11800</v>
+        <v>11500</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>11150</v>
+        <v>11000</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
@@ -7530,16 +7530,16 @@
         </is>
       </c>
       <c r="C203" s="3" t="n">
-        <v>17800</v>
+        <v>17400</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>19000</v>
+        <v>18800</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>18400</v>
+        <v>18100</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>312500</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
@@ -7700,16 +7700,16 @@
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>39000</v>
+        <v>38500</v>
       </c>
       <c r="D208" s="4" t="n">
         <v>41000</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>40000</v>
+        <v>39750</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>0</v>
+        <v>-250</v>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
@@ -7734,16 +7734,16 @@
         </is>
       </c>
       <c r="C209" s="3" t="n">
-        <v>2420</v>
+        <v>2380</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>2530</v>
+        <v>2450</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>2475</v>
-      </c>
-      <c r="F209" s="4" t="n">
-        <v>125</v>
+        <v>2415</v>
+      </c>
+      <c r="F209" s="6" t="n">
+        <v>-60</v>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
@@ -7768,16 +7768,16 @@
         </is>
       </c>
       <c r="C210" s="3" t="n">
-        <v>2445</v>
+        <v>2390</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>2547</v>
+        <v>2510</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>2496</v>
+        <v>2450</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>1</v>
+        <v>-46</v>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
@@ -7836,16 +7836,16 @@
         </is>
       </c>
       <c r="C212" s="3" t="n">
-        <v>288000</v>
+        <v>285000</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>295000</v>
+        <v>290000</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>291500</v>
+        <v>287500</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
@@ -7870,16 +7870,16 @@
         </is>
       </c>
       <c r="C213" s="7" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="E213" s="6" t="n">
-        <v>19.65</v>
+        <v>19.45</v>
       </c>
       <c r="F213" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
@@ -7904,16 +7904,16 @@
         </is>
       </c>
       <c r="C214" s="7" t="n">
-        <v>17.95</v>
+        <v>17.75</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>21.15</v>
+        <v>20.95</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>19.55</v>
+        <v>19.35</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
@@ -7938,16 +7938,16 @@
         </is>
       </c>
       <c r="C215" s="3" t="n">
-        <v>154000</v>
+        <v>152000</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>167000</v>
+        <v>165000</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>160500</v>
+        <v>158500</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>500</v>
+        <v>-2000</v>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
@@ -7972,16 +7972,16 @@
         </is>
       </c>
       <c r="C216" s="3" t="n">
-        <v>146500</v>
+        <v>145000</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>162500</v>
+        <v>160000</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>154500</v>
+        <v>152500</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>500</v>
+        <v>-2000</v>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
@@ -8040,16 +8040,16 @@
         </is>
       </c>
       <c r="C218" s="3" t="n">
-        <v>33400</v>
+        <v>33370</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>33820</v>
+        <v>33750</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>33610</v>
-      </c>
-      <c r="F218" s="4" t="n">
-        <v>0</v>
+        <v>33560</v>
+      </c>
+      <c r="F218" s="6" t="n">
+        <v>-50</v>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
@@ -8074,16 +8074,16 @@
         </is>
       </c>
       <c r="C219" s="3" t="n">
-        <v>166000</v>
+        <v>164500</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>173000</v>
+        <v>170000</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>169500</v>
+        <v>167250</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>500</v>
+        <v>-2250</v>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
@@ -8108,16 +8108,16 @@
         </is>
       </c>
       <c r="C220" s="7" t="n">
-        <v>20.15</v>
+        <v>19.95</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>22.15</v>
+        <v>21.95</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>21.15</v>
+        <v>20.95</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
@@ -8142,16 +8142,16 @@
         </is>
       </c>
       <c r="C221" s="7" t="n">
-        <v>20.35</v>
+        <v>20.15</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="E221" s="6" t="n">
-        <v>21.28</v>
+        <v>21.08</v>
       </c>
       <c r="F221" s="6" t="n">
-        <v>0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
@@ -8179,13 +8179,13 @@
         <v>1100000</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>1170000</v>
+        <v>1160000</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>1135000</v>
+        <v>1130000</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
@@ -8210,16 +8210,16 @@
         </is>
       </c>
       <c r="C223" s="3" t="n">
-        <v>382000</v>
+        <v>372000</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>405000</v>
+        <v>395000</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>393500</v>
+        <v>383500</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>-3500</v>
+        <v>-10000</v>
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
@@ -8278,16 +8278,16 @@
         </is>
       </c>
       <c r="C225" s="3" t="n">
-        <v>34500</v>
+        <v>32500</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>39000</v>
+        <v>37000</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>36750</v>
+        <v>34750</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>88500</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>-250</v>
+        <v>0</v>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         <v>210000</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>217500</v>
+        <v>215000</v>
       </c>
       <c r="F227" s="4" t="n">
         <v>-2500</v>
@@ -8380,16 +8380,16 @@
         </is>
       </c>
       <c r="C228" s="3" t="n">
-        <v>59730</v>
+        <v>59180</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>60330</v>
+        <v>59780</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>60030</v>
+        <v>59480</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>220</v>
+        <v>-550</v>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
@@ -8448,13 +8448,13 @@
         </is>
       </c>
       <c r="C230" s="7" t="n">
-        <v>24.75</v>
+        <v>24.5</v>
       </c>
       <c r="D230" s="6" t="n">
         <v>25.5</v>
       </c>
       <c r="E230" s="6" t="n">
-        <v>25.13</v>
+        <v>25</v>
       </c>
       <c r="F230" s="6" t="n">
         <v>-0.13</v>
@@ -8559,7 +8559,7 @@
         <v>381500</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
@@ -8587,13 +8587,13 @@
         <v>98000</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>101200</v>
+        <v>101000</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>99600</v>
+        <v>99500</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
@@ -8686,16 +8686,16 @@
         </is>
       </c>
       <c r="C237" s="3" t="n">
-        <v>8109</v>
+        <v>8020</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>8490</v>
+        <v>8319</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>8299.5</v>
-      </c>
-      <c r="F237" s="6" t="n">
-        <v>32</v>
+        <v>8169.5</v>
+      </c>
+      <c r="F237" s="4" t="n">
+        <v>-130</v>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
@@ -8720,16 +8720,16 @@
         </is>
       </c>
       <c r="C238" s="3" t="n">
-        <v>2470</v>
+        <v>2398</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>2470</v>
+        <v>2398</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>2470</v>
-      </c>
-      <c r="F238" s="4" t="n">
-        <v>172</v>
+        <v>2398</v>
+      </c>
+      <c r="F238" s="6" t="n">
+        <v>-72</v>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
@@ -11120,19 +11120,19 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>165820</v>
+        <v>160100</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>171800</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0</v>
+        <v>160500</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>168140</v>
+        <v>160560</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-6680</v>
+        <v>-12400</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -11162,14 +11162,14 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>6.763</v>
+        <v>6.7609</v>
       </c>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="6" t="n">
         <v>6.7572</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>6.7572</v>
+        <v>6.7564</v>
       </c>
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
@@ -11200,13 +11200,13 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>21.02</v>
+        <v>21.1</v>
       </c>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="6" t="n">
-        <v>0.03</v>
+        <v>0.38</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$238</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$313</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H315"/>
+  <dimension ref="A1:H390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8742,1749 +8742,4299 @@
         </is>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>100900</v>
+      </c>
+      <c r="D239" s="4" t="n">
+        <v>106100</v>
+      </c>
+      <c r="E239" s="4" t="n">
+        <v>103500</v>
+      </c>
+      <c r="F239" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H239" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="240">
-      <c r="A240" s="8" t="inlineStr">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>185500</v>
+      </c>
+      <c r="D240" s="4" t="n">
+        <v>193400</v>
+      </c>
+      <c r="E240" s="4" t="n">
+        <v>189450</v>
+      </c>
+      <c r="F240" s="4" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="G240" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H240" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>93750</v>
+      </c>
+      <c r="D241" s="4" t="n">
+        <v>98450</v>
+      </c>
+      <c r="E241" s="4" t="n">
+        <v>96100</v>
+      </c>
+      <c r="F241" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G241" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H241" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D242" s="4" t="n">
+        <v>199500</v>
+      </c>
+      <c r="E242" s="4" t="n">
+        <v>194750</v>
+      </c>
+      <c r="F242" s="4" t="n">
+        <v>-800</v>
+      </c>
+      <c r="G242" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H242" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>116300</v>
+      </c>
+      <c r="D243" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="E243" s="4" t="n">
+        <v>119150</v>
+      </c>
+      <c r="F243" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H243" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>213200</v>
+      </c>
+      <c r="D244" s="4" t="n">
+        <v>222800</v>
+      </c>
+      <c r="E244" s="4" t="n">
+        <v>218000</v>
+      </c>
+      <c r="F244" s="4" t="n">
+        <v>-800</v>
+      </c>
+      <c r="G244" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H244" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C245" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="D245" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E245" s="6" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="F245" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H245" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C246" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D246" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E246" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F246" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H246" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>210300</v>
+      </c>
+      <c r="D247" s="4" t="n">
+        <v>218600</v>
+      </c>
+      <c r="E247" s="4" t="n">
+        <v>214450</v>
+      </c>
+      <c r="F247" s="4" t="n">
+        <v>-800</v>
+      </c>
+      <c r="G247" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H247" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C248" s="7" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="D248" s="6" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="E248" s="6" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="F248" s="6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H248" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C249" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="D249" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E249" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="F249" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C250" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="D250" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="E250" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="F250" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G250" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C251" s="7" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="D251" s="6" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="E251" s="6" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="F251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C252" s="7" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="D252" s="6" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="E252" s="6" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="F252" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G252" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C253" s="7" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="D253" s="6" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="E253" s="6" t="n">
+        <v>75.73</v>
+      </c>
+      <c r="F253" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G253" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H253" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="n">
+        <v>101802</v>
+      </c>
+      <c r="D254" s="4" t="n">
+        <v>105958</v>
+      </c>
+      <c r="E254" s="4" t="n">
+        <v>103880</v>
+      </c>
+      <c r="F254" s="4" t="n">
+        <v>-508.5</v>
+      </c>
+      <c r="G254" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H254" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>152617</v>
+      </c>
+      <c r="D255" s="4" t="n">
+        <v>152617</v>
+      </c>
+      <c r="E255" s="4" t="n">
+        <v>152617</v>
+      </c>
+      <c r="F255" s="4" t="n">
+        <v>-2079</v>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H255" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>7658</v>
+      </c>
+      <c r="D256" s="4" t="n">
+        <v>7658</v>
+      </c>
+      <c r="E256" s="4" t="n">
+        <v>7658</v>
+      </c>
+      <c r="F256" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G256" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H256" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D257" s="4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E257" s="4" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F257" s="6" t="n">
+        <v>-42</v>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H257" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>167053</v>
+      </c>
+      <c r="D258" s="4" t="n">
+        <v>167053</v>
+      </c>
+      <c r="E258" s="4" t="n">
+        <v>167053</v>
+      </c>
+      <c r="F258" s="4" t="n">
+        <v>-1430</v>
+      </c>
+      <c r="G258" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H258" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>88287</v>
+      </c>
+      <c r="D259" s="4" t="n">
+        <v>88287</v>
+      </c>
+      <c r="E259" s="4" t="n">
+        <v>88287</v>
+      </c>
+      <c r="F259" s="6" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G259" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H259" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>7458</v>
+      </c>
+      <c r="D260" s="4" t="n">
+        <v>7458</v>
+      </c>
+      <c r="E260" s="4" t="n">
+        <v>7458</v>
+      </c>
+      <c r="F260" s="6" t="n">
+        <v>-31</v>
+      </c>
+      <c r="G260" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H260" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>6975</v>
+      </c>
+      <c r="D261" s="4" t="n">
+        <v>6975</v>
+      </c>
+      <c r="E261" s="4" t="n">
+        <v>6975</v>
+      </c>
+      <c r="F261" s="6" t="n">
+        <v>-87</v>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H261" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C262" s="7" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="D262" s="6" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="E262" s="6" t="n">
+        <v>82.53</v>
+      </c>
+      <c r="F262" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H262" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C263" s="7" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D263" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E263" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F263" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H263" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C264" s="7" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="D264" s="6" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="E264" s="6" t="n">
+        <v>80.13</v>
+      </c>
+      <c r="F264" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H264" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C265" s="7" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="D265" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="E265" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="F265" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H265" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C266" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D266" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E266" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F266" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H266" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>110000</v>
+      </c>
+      <c r="D267" s="4" t="n">
+        <v>112000</v>
+      </c>
+      <c r="E267" s="4" t="n">
+        <v>111000</v>
+      </c>
+      <c r="F267" s="4" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H267" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>332000</v>
+      </c>
+      <c r="D268" s="4" t="n">
+        <v>345000</v>
+      </c>
+      <c r="E268" s="4" t="n">
+        <v>338500</v>
+      </c>
+      <c r="F268" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H268" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D269" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E269" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F269" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H269" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>136000</v>
+      </c>
+      <c r="D270" s="4" t="n">
+        <v>144000</v>
+      </c>
+      <c r="E270" s="4" t="n">
+        <v>140000</v>
+      </c>
+      <c r="F270" s="4" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G270" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H270" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>160500</v>
+      </c>
+      <c r="D271" s="4" t="n">
+        <v>166000</v>
+      </c>
+      <c r="E271" s="4" t="n">
+        <v>163250</v>
+      </c>
+      <c r="F271" s="4" t="n">
+        <v>-2250</v>
+      </c>
+      <c r="G271" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H271" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>1070000</v>
+      </c>
+      <c r="D272" s="4" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="E272" s="4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="F272" s="4" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H272" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>2370</v>
+      </c>
+      <c r="D273" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E273" s="4" t="n">
+        <v>2435</v>
+      </c>
+      <c r="F273" s="6" t="n">
+        <v>-46</v>
+      </c>
+      <c r="G273" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H273" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>21800</v>
+      </c>
+      <c r="D274" s="4" t="n">
+        <v>25200</v>
+      </c>
+      <c r="E274" s="4" t="n">
+        <v>23500</v>
+      </c>
+      <c r="F274" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G274" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H274" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>25850</v>
+      </c>
+      <c r="D275" s="4" t="n">
+        <v>30350</v>
+      </c>
+      <c r="E275" s="4" t="n">
+        <v>28100</v>
+      </c>
+      <c r="F275" s="4" t="n">
+        <v>-375</v>
+      </c>
+      <c r="G275" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H275" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>16300</v>
+      </c>
+      <c r="D276" s="4" t="n">
+        <v>17600</v>
+      </c>
+      <c r="E276" s="4" t="n">
+        <v>16950</v>
+      </c>
+      <c r="F276" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G276" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>10500</v>
+      </c>
+      <c r="D277" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="E277" s="4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F277" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G277" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H277" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>17400</v>
+      </c>
+      <c r="D278" s="4" t="n">
+        <v>18800</v>
+      </c>
+      <c r="E278" s="4" t="n">
+        <v>18100</v>
+      </c>
+      <c r="F278" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G278" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H278" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C279" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D279" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E279" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F279" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H279" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D280" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E280" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F280" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H280" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C281" s="3" t="n">
+        <v>305000</v>
+      </c>
+      <c r="D281" s="4" t="n">
+        <v>320000</v>
+      </c>
+      <c r="E281" s="4" t="n">
+        <v>312500</v>
+      </c>
+      <c r="F281" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H281" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C282" s="3" t="n">
+        <v>106000</v>
+      </c>
+      <c r="D282" s="4" t="n">
+        <v>112000</v>
+      </c>
+      <c r="E282" s="4" t="n">
+        <v>109000</v>
+      </c>
+      <c r="F282" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H282" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C283" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D283" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E283" s="4" t="n">
+        <v>39750</v>
+      </c>
+      <c r="F283" s="4" t="n">
+        <v>-250</v>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C284" s="3" t="n">
+        <v>2380</v>
+      </c>
+      <c r="D284" s="4" t="n">
+        <v>2450</v>
+      </c>
+      <c r="E284" s="4" t="n">
+        <v>2415</v>
+      </c>
+      <c r="F284" s="6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G284" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H284" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C285" s="3" t="n">
+        <v>2390</v>
+      </c>
+      <c r="D285" s="4" t="n">
+        <v>2510</v>
+      </c>
+      <c r="E285" s="4" t="n">
+        <v>2450</v>
+      </c>
+      <c r="F285" s="6" t="n">
+        <v>-46</v>
+      </c>
+      <c r="G285" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H285" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C286" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="D286" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="E286" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="F286" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H286" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C287" s="3" t="n">
+        <v>285000</v>
+      </c>
+      <c r="D287" s="4" t="n">
+        <v>290000</v>
+      </c>
+      <c r="E287" s="4" t="n">
+        <v>287500</v>
+      </c>
+      <c r="F287" s="4" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="G287" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H287" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C288" s="7" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="D288" s="6" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="E288" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F288" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G288" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H288" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C289" s="7" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D289" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E289" s="6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F289" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G289" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C290" s="3" t="n">
+        <v>152000</v>
+      </c>
+      <c r="D290" s="4" t="n">
+        <v>165000</v>
+      </c>
+      <c r="E290" s="4" t="n">
+        <v>158500</v>
+      </c>
+      <c r="F290" s="4" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G290" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H290" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C291" s="3" t="n">
+        <v>145000</v>
+      </c>
+      <c r="D291" s="4" t="n">
+        <v>160000</v>
+      </c>
+      <c r="E291" s="4" t="n">
+        <v>152500</v>
+      </c>
+      <c r="F291" s="4" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G291" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C292" s="3" t="n">
+        <v>7590</v>
+      </c>
+      <c r="D292" s="4" t="n">
+        <v>7790</v>
+      </c>
+      <c r="E292" s="4" t="n">
+        <v>7690</v>
+      </c>
+      <c r="F292" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H292" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C293" s="3" t="n">
+        <v>33370</v>
+      </c>
+      <c r="D293" s="4" t="n">
+        <v>33750</v>
+      </c>
+      <c r="E293" s="4" t="n">
+        <v>33560</v>
+      </c>
+      <c r="F293" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G293" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H293" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C294" s="3" t="n">
+        <v>164500</v>
+      </c>
+      <c r="D294" s="4" t="n">
+        <v>170000</v>
+      </c>
+      <c r="E294" s="4" t="n">
+        <v>167250</v>
+      </c>
+      <c r="F294" s="4" t="n">
+        <v>-2250</v>
+      </c>
+      <c r="G294" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H294" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C295" s="7" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="D295" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E295" s="6" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="F295" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H295" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C296" s="7" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="D296" s="6" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="E296" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F296" s="6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G296" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H296" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C297" s="3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D297" s="4" t="n">
+        <v>1160000</v>
+      </c>
+      <c r="E297" s="4" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="F297" s="4" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H297" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C298" s="3" t="n">
+        <v>372000</v>
+      </c>
+      <c r="D298" s="4" t="n">
+        <v>395000</v>
+      </c>
+      <c r="E298" s="4" t="n">
+        <v>383500</v>
+      </c>
+      <c r="F298" s="4" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="G298" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H298" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C299" s="7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D299" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E299" s="6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F299" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H299" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C300" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D300" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E300" s="4" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F300" s="4" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G300" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H300" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C301" s="3" t="n">
+        <v>87000</v>
+      </c>
+      <c r="D301" s="4" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E301" s="4" t="n">
+        <v>88500</v>
+      </c>
+      <c r="F301" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H301" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C302" s="3" t="n">
+        <v>210000</v>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E302" s="4" t="n">
+        <v>215000</v>
+      </c>
+      <c r="F302" s="4" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="G302" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H302" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="n">
+        <v>59180</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>59780</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>59480</v>
+      </c>
+      <c r="F303" s="4" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G303" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C304" s="3" t="n">
+        <v>64500</v>
+      </c>
+      <c r="D304" s="4" t="n">
+        <v>69500</v>
+      </c>
+      <c r="E304" s="4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="F304" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H304" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C305" s="7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D305" s="6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E305" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F305" s="6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G305" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H305" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C306" s="3" t="n">
+        <v>26783</v>
+      </c>
+      <c r="D306" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="E306" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="F306" s="4" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G306" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H306" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C307" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D307" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E307" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F307" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H307" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="n">
+        <v>380000</v>
+      </c>
+      <c r="D308" s="4" t="n">
+        <v>383000</v>
+      </c>
+      <c r="E308" s="4" t="n">
+        <v>381500</v>
+      </c>
+      <c r="F308" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H308" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C309" s="3" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D309" s="4" t="n">
+        <v>101000</v>
+      </c>
+      <c r="E309" s="4" t="n">
+        <v>99500</v>
+      </c>
+      <c r="F309" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G309" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H309" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C310" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D310" s="4" t="n">
+        <v>94000</v>
+      </c>
+      <c r="E310" s="4" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F310" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H310" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C311" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D311" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E311" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F311" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H311" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C312" s="3" t="n">
+        <v>8020</v>
+      </c>
+      <c r="D312" s="4" t="n">
+        <v>8319</v>
+      </c>
+      <c r="E312" s="4" t="n">
+        <v>8169.5</v>
+      </c>
+      <c r="F312" s="4" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G312" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H312" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C313" s="3" t="n">
+        <v>2398</v>
+      </c>
+      <c r="D313" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="E313" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F313" s="6" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G313" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H313" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B240" s="9" t="n"/>
-      <c r="C240" s="9" t="n"/>
-      <c r="D240" s="9" t="n"/>
-      <c r="E240" s="9" t="n"/>
-      <c r="F240" s="9" t="n"/>
-      <c r="G240" s="9" t="n"/>
-      <c r="H240" s="9" t="n"/>
-    </row>
-    <row r="241">
-      <c r="B241" s="2" t="inlineStr">
+      <c r="B315" s="9" t="n"/>
+      <c r="C315" s="9" t="n"/>
+      <c r="D315" s="9" t="n"/>
+      <c r="E315" s="9" t="n"/>
+      <c r="F315" s="9" t="n"/>
+      <c r="G315" s="9" t="n"/>
+      <c r="H315" s="9" t="n"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C241" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$241),"")</f>
-        <v/>
-      </c>
-      <c r="D241" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$241),"")</f>
-        <v/>
-      </c>
-      <c r="E241" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$241),"")</f>
-        <v/>
-      </c>
-      <c r="F241" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$241)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242">
-      <c r="B242" s="2" t="inlineStr">
+      <c r="C316" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$316),"")</f>
+        <v/>
+      </c>
+      <c r="D316" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$316),"")</f>
+        <v/>
+      </c>
+      <c r="E316" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$316),"")</f>
+        <v/>
+      </c>
+      <c r="F316" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$316)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C242" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$242),"")</f>
-        <v/>
-      </c>
-      <c r="D242" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$242),"")</f>
-        <v/>
-      </c>
-      <c r="E242" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$242),"")</f>
-        <v/>
-      </c>
-      <c r="F242" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$242)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243">
-      <c r="B243" s="2" t="inlineStr">
+      <c r="C317" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$317),"")</f>
+        <v/>
+      </c>
+      <c r="D317" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$317),"")</f>
+        <v/>
+      </c>
+      <c r="E317" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$317),"")</f>
+        <v/>
+      </c>
+      <c r="F317" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$317)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C243" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$243),"")</f>
-        <v/>
-      </c>
-      <c r="D243" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$243),"")</f>
-        <v/>
-      </c>
-      <c r="E243" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$243),"")</f>
-        <v/>
-      </c>
-      <c r="F243" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$243)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="B244" s="2" t="inlineStr">
+      <c r="C318" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$318),"")</f>
+        <v/>
+      </c>
+      <c r="D318" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$318),"")</f>
+        <v/>
+      </c>
+      <c r="E318" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$318),"")</f>
+        <v/>
+      </c>
+      <c r="F318" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$318)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C244" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$244),"")</f>
-        <v/>
-      </c>
-      <c r="D244" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$244),"")</f>
-        <v/>
-      </c>
-      <c r="E244" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$244),"")</f>
-        <v/>
-      </c>
-      <c r="F244" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$244)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245">
-      <c r="B245" s="2" t="inlineStr">
+      <c r="C319" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$319),"")</f>
+        <v/>
+      </c>
+      <c r="D319" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$319),"")</f>
+        <v/>
+      </c>
+      <c r="E319" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$319),"")</f>
+        <v/>
+      </c>
+      <c r="F319" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$319)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C245" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$245),"")</f>
-        <v/>
-      </c>
-      <c r="D245" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$245),"")</f>
-        <v/>
-      </c>
-      <c r="E245" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$245),"")</f>
-        <v/>
-      </c>
-      <c r="F245" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$245)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246">
-      <c r="B246" s="2" t="inlineStr">
+      <c r="C320" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$320),"")</f>
+        <v/>
+      </c>
+      <c r="D320" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$320),"")</f>
+        <v/>
+      </c>
+      <c r="E320" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$320),"")</f>
+        <v/>
+      </c>
+      <c r="F320" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$320)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C246" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$246),"")</f>
-        <v/>
-      </c>
-      <c r="D246" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$246),"")</f>
-        <v/>
-      </c>
-      <c r="E246" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$246),"")</f>
-        <v/>
-      </c>
-      <c r="F246" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$246)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
-      <c r="B247" s="2" t="inlineStr">
+      <c r="C321" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$321),"")</f>
+        <v/>
+      </c>
+      <c r="D321" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$321),"")</f>
+        <v/>
+      </c>
+      <c r="E321" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$321),"")</f>
+        <v/>
+      </c>
+      <c r="F321" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$321)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C247" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$247),"")</f>
-        <v/>
-      </c>
-      <c r="D247" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$247),"")</f>
-        <v/>
-      </c>
-      <c r="E247" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$247),"")</f>
-        <v/>
-      </c>
-      <c r="F247" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$247)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="B248" s="2" t="inlineStr">
+      <c r="C322" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$322),"")</f>
+        <v/>
+      </c>
+      <c r="D322" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$322),"")</f>
+        <v/>
+      </c>
+      <c r="E322" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$322),"")</f>
+        <v/>
+      </c>
+      <c r="F322" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$322)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="323">
+      <c r="B323" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C248" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$248),"")</f>
-        <v/>
-      </c>
-      <c r="D248" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$248),"")</f>
-        <v/>
-      </c>
-      <c r="E248" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$248),"")</f>
-        <v/>
-      </c>
-      <c r="F248" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$248)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="B249" s="2" t="inlineStr">
+      <c r="C323" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$323),"")</f>
+        <v/>
+      </c>
+      <c r="D323" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$323),"")</f>
+        <v/>
+      </c>
+      <c r="E323" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$323),"")</f>
+        <v/>
+      </c>
+      <c r="F323" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$323)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C249" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$249),"")</f>
-        <v/>
-      </c>
-      <c r="D249" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$249),"")</f>
-        <v/>
-      </c>
-      <c r="E249" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$249),"")</f>
-        <v/>
-      </c>
-      <c r="F249" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$249)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="B250" s="2" t="inlineStr">
+      <c r="C324" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$324),"")</f>
+        <v/>
+      </c>
+      <c r="D324" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$324),"")</f>
+        <v/>
+      </c>
+      <c r="E324" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$324),"")</f>
+        <v/>
+      </c>
+      <c r="F324" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$324)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325">
+      <c r="B325" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C250" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$250),"")</f>
-        <v/>
-      </c>
-      <c r="D250" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$250),"")</f>
-        <v/>
-      </c>
-      <c r="E250" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$250),"")</f>
-        <v/>
-      </c>
-      <c r="F250" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$250)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="251">
-      <c r="B251" s="2" t="inlineStr">
+      <c r="C325" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$325),"")</f>
+        <v/>
+      </c>
+      <c r="D325" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$325),"")</f>
+        <v/>
+      </c>
+      <c r="E325" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$325),"")</f>
+        <v/>
+      </c>
+      <c r="F325" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$325)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326">
+      <c r="B326" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C251" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$251),"")</f>
-        <v/>
-      </c>
-      <c r="D251" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$251),"")</f>
-        <v/>
-      </c>
-      <c r="E251" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$251),"")</f>
-        <v/>
-      </c>
-      <c r="F251" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$251)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="B252" s="2" t="inlineStr">
+      <c r="C326" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$326),"")</f>
+        <v/>
+      </c>
+      <c r="D326" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$326),"")</f>
+        <v/>
+      </c>
+      <c r="E326" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$326),"")</f>
+        <v/>
+      </c>
+      <c r="F326" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$326)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="B327" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C252" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$252),"")</f>
-        <v/>
-      </c>
-      <c r="D252" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$252),"")</f>
-        <v/>
-      </c>
-      <c r="E252" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$252),"")</f>
-        <v/>
-      </c>
-      <c r="F252" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$252)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="B253" s="2" t="inlineStr">
+      <c r="C327" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$327),"")</f>
+        <v/>
+      </c>
+      <c r="D327" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$327),"")</f>
+        <v/>
+      </c>
+      <c r="E327" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$327),"")</f>
+        <v/>
+      </c>
+      <c r="F327" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$327)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="B328" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C253" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$253),"")</f>
-        <v/>
-      </c>
-      <c r="D253" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$253),"")</f>
-        <v/>
-      </c>
-      <c r="E253" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$253),"")</f>
-        <v/>
-      </c>
-      <c r="F253" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$253)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254">
-      <c r="B254" s="2" t="inlineStr">
+      <c r="C328" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$328),"")</f>
+        <v/>
+      </c>
+      <c r="D328" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$328),"")</f>
+        <v/>
+      </c>
+      <c r="E328" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$328),"")</f>
+        <v/>
+      </c>
+      <c r="F328" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$328)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="B329" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C254" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$254),"")</f>
-        <v/>
-      </c>
-      <c r="D254" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$254),"")</f>
-        <v/>
-      </c>
-      <c r="E254" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$254),"")</f>
-        <v/>
-      </c>
-      <c r="F254" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$254)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="B255" s="2" t="inlineStr">
+      <c r="C329" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$329),"")</f>
+        <v/>
+      </c>
+      <c r="D329" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$329),"")</f>
+        <v/>
+      </c>
+      <c r="E329" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$329),"")</f>
+        <v/>
+      </c>
+      <c r="F329" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$329)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330">
+      <c r="B330" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C255" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$255),"")</f>
-        <v/>
-      </c>
-      <c r="D255" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$255),"")</f>
-        <v/>
-      </c>
-      <c r="E255" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$255),"")</f>
-        <v/>
-      </c>
-      <c r="F255" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$255)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="B256" s="2" t="inlineStr">
+      <c r="C330" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$330),"")</f>
+        <v/>
+      </c>
+      <c r="D330" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$330),"")</f>
+        <v/>
+      </c>
+      <c r="E330" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$330),"")</f>
+        <v/>
+      </c>
+      <c r="F330" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$330)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331">
+      <c r="B331" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C256" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$256),"")</f>
-        <v/>
-      </c>
-      <c r="D256" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$256),"")</f>
-        <v/>
-      </c>
-      <c r="E256" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$256),"")</f>
-        <v/>
-      </c>
-      <c r="F256" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$256)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257">
-      <c r="B257" s="2" t="inlineStr">
+      <c r="C331" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$331),"")</f>
+        <v/>
+      </c>
+      <c r="D331" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$331),"")</f>
+        <v/>
+      </c>
+      <c r="E331" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$331),"")</f>
+        <v/>
+      </c>
+      <c r="F331" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$331)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332">
+      <c r="B332" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C257" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$257),"")</f>
-        <v/>
-      </c>
-      <c r="D257" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$257),"")</f>
-        <v/>
-      </c>
-      <c r="E257" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$257),"")</f>
-        <v/>
-      </c>
-      <c r="F257" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$257)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258">
-      <c r="B258" s="2" t="inlineStr">
+      <c r="C332" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$332),"")</f>
+        <v/>
+      </c>
+      <c r="D332" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$332),"")</f>
+        <v/>
+      </c>
+      <c r="E332" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$332),"")</f>
+        <v/>
+      </c>
+      <c r="F332" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$332)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333">
+      <c r="B333" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C258" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$258),"")</f>
-        <v/>
-      </c>
-      <c r="D258" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$258),"")</f>
-        <v/>
-      </c>
-      <c r="E258" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$258),"")</f>
-        <v/>
-      </c>
-      <c r="F258" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$258)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259">
-      <c r="B259" s="2" t="inlineStr">
+      <c r="C333" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$333),"")</f>
+        <v/>
+      </c>
+      <c r="D333" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$333),"")</f>
+        <v/>
+      </c>
+      <c r="E333" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$333),"")</f>
+        <v/>
+      </c>
+      <c r="F333" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$333)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334">
+      <c r="B334" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C259" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$259),"")</f>
-        <v/>
-      </c>
-      <c r="D259" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$259),"")</f>
-        <v/>
-      </c>
-      <c r="E259" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$259),"")</f>
-        <v/>
-      </c>
-      <c r="F259" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$259)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260">
-      <c r="B260" s="2" t="inlineStr">
+      <c r="C334" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$334),"")</f>
+        <v/>
+      </c>
+      <c r="D334" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$334),"")</f>
+        <v/>
+      </c>
+      <c r="E334" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$334),"")</f>
+        <v/>
+      </c>
+      <c r="F334" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$334)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335">
+      <c r="B335" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C260" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$260),"")</f>
-        <v/>
-      </c>
-      <c r="D260" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$260),"")</f>
-        <v/>
-      </c>
-      <c r="E260" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$260),"")</f>
-        <v/>
-      </c>
-      <c r="F260" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$260)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261">
-      <c r="B261" s="2" t="inlineStr">
+      <c r="C335" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$335),"")</f>
+        <v/>
+      </c>
+      <c r="D335" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$335),"")</f>
+        <v/>
+      </c>
+      <c r="E335" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$335),"")</f>
+        <v/>
+      </c>
+      <c r="F335" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$335)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336">
+      <c r="B336" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C261" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$261),"")</f>
-        <v/>
-      </c>
-      <c r="D261" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$261),"")</f>
-        <v/>
-      </c>
-      <c r="E261" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$261),"")</f>
-        <v/>
-      </c>
-      <c r="F261" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$261)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262">
-      <c r="B262" s="2" t="inlineStr">
+      <c r="C336" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$336),"")</f>
+        <v/>
+      </c>
+      <c r="D336" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$336),"")</f>
+        <v/>
+      </c>
+      <c r="E336" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$336),"")</f>
+        <v/>
+      </c>
+      <c r="F336" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$336)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="337">
+      <c r="B337" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C262" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$262),"")</f>
-        <v/>
-      </c>
-      <c r="D262" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$262),"")</f>
-        <v/>
-      </c>
-      <c r="E262" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$262),"")</f>
-        <v/>
-      </c>
-      <c r="F262" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$262)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263">
-      <c r="B263" s="2" t="inlineStr">
+      <c r="C337" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$337),"")</f>
+        <v/>
+      </c>
+      <c r="D337" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$337),"")</f>
+        <v/>
+      </c>
+      <c r="E337" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$337),"")</f>
+        <v/>
+      </c>
+      <c r="F337" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$337)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338">
+      <c r="B338" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C263" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$263),"")</f>
-        <v/>
-      </c>
-      <c r="D263" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$263),"")</f>
-        <v/>
-      </c>
-      <c r="E263" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$263),"")</f>
-        <v/>
-      </c>
-      <c r="F263" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$263)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264">
-      <c r="B264" s="2" t="inlineStr">
+      <c r="C338" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$338),"")</f>
+        <v/>
+      </c>
+      <c r="D338" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$338),"")</f>
+        <v/>
+      </c>
+      <c r="E338" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$338),"")</f>
+        <v/>
+      </c>
+      <c r="F338" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$338)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339">
+      <c r="B339" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C264" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$264),"")</f>
-        <v/>
-      </c>
-      <c r="D264" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$264),"")</f>
-        <v/>
-      </c>
-      <c r="E264" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$264),"")</f>
-        <v/>
-      </c>
-      <c r="F264" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$264)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265">
-      <c r="B265" s="2" t="inlineStr">
+      <c r="C339" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$339),"")</f>
+        <v/>
+      </c>
+      <c r="D339" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$339),"")</f>
+        <v/>
+      </c>
+      <c r="E339" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$339),"")</f>
+        <v/>
+      </c>
+      <c r="F339" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$339)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="B340" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C265" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$265),"")</f>
-        <v/>
-      </c>
-      <c r="D265" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$265),"")</f>
-        <v/>
-      </c>
-      <c r="E265" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$265),"")</f>
-        <v/>
-      </c>
-      <c r="F265" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$265)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266">
-      <c r="B266" s="2" t="inlineStr">
+      <c r="C340" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$340),"")</f>
+        <v/>
+      </c>
+      <c r="D340" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$340),"")</f>
+        <v/>
+      </c>
+      <c r="E340" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$340),"")</f>
+        <v/>
+      </c>
+      <c r="F340" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$340)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="B341" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C266" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$266),"")</f>
-        <v/>
-      </c>
-      <c r="D266" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$266),"")</f>
-        <v/>
-      </c>
-      <c r="E266" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$266),"")</f>
-        <v/>
-      </c>
-      <c r="F266" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$266)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267">
-      <c r="B267" s="2" t="inlineStr">
+      <c r="C341" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$341),"")</f>
+        <v/>
+      </c>
+      <c r="D341" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$341),"")</f>
+        <v/>
+      </c>
+      <c r="E341" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$341),"")</f>
+        <v/>
+      </c>
+      <c r="F341" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$341)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="342">
+      <c r="B342" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C267" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$267),"")</f>
-        <v/>
-      </c>
-      <c r="D267" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$267),"")</f>
-        <v/>
-      </c>
-      <c r="E267" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$267),"")</f>
-        <v/>
-      </c>
-      <c r="F267" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$267)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="B268" s="2" t="inlineStr">
+      <c r="C342" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$342),"")</f>
+        <v/>
+      </c>
+      <c r="D342" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$342),"")</f>
+        <v/>
+      </c>
+      <c r="E342" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$342),"")</f>
+        <v/>
+      </c>
+      <c r="F342" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$342)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="343">
+      <c r="B343" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C268" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$268),"")</f>
-        <v/>
-      </c>
-      <c r="D268" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$268),"")</f>
-        <v/>
-      </c>
-      <c r="E268" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$268),"")</f>
-        <v/>
-      </c>
-      <c r="F268" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$268)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269">
-      <c r="B269" s="2" t="inlineStr">
+      <c r="C343" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$343),"")</f>
+        <v/>
+      </c>
+      <c r="D343" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$343),"")</f>
+        <v/>
+      </c>
+      <c r="E343" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$343),"")</f>
+        <v/>
+      </c>
+      <c r="F343" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$343)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344">
+      <c r="B344" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C269" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$269),"")</f>
-        <v/>
-      </c>
-      <c r="D269" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$269),"")</f>
-        <v/>
-      </c>
-      <c r="E269" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$269),"")</f>
-        <v/>
-      </c>
-      <c r="F269" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$269)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="270">
-      <c r="B270" s="2" t="inlineStr">
+      <c r="C344" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$344),"")</f>
+        <v/>
+      </c>
+      <c r="D344" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$344),"")</f>
+        <v/>
+      </c>
+      <c r="E344" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$344),"")</f>
+        <v/>
+      </c>
+      <c r="F344" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$344)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345">
+      <c r="B345" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C270" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$270),"")</f>
-        <v/>
-      </c>
-      <c r="D270" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$270),"")</f>
-        <v/>
-      </c>
-      <c r="E270" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$270),"")</f>
-        <v/>
-      </c>
-      <c r="F270" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$270)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271">
-      <c r="B271" s="2" t="inlineStr">
+      <c r="C345" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$345),"")</f>
+        <v/>
+      </c>
+      <c r="D345" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$345),"")</f>
+        <v/>
+      </c>
+      <c r="E345" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$345),"")</f>
+        <v/>
+      </c>
+      <c r="F345" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$345)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346">
+      <c r="B346" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C271" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$271),"")</f>
-        <v/>
-      </c>
-      <c r="D271" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$271),"")</f>
-        <v/>
-      </c>
-      <c r="E271" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$271),"")</f>
-        <v/>
-      </c>
-      <c r="F271" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$271)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="272">
-      <c r="B272" s="2" t="inlineStr">
+      <c r="C346" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$346),"")</f>
+        <v/>
+      </c>
+      <c r="D346" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$346),"")</f>
+        <v/>
+      </c>
+      <c r="E346" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$346),"")</f>
+        <v/>
+      </c>
+      <c r="F346" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$346)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347">
+      <c r="B347" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C272" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$272),"")</f>
-        <v/>
-      </c>
-      <c r="D272" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$272),"")</f>
-        <v/>
-      </c>
-      <c r="E272" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$272),"")</f>
-        <v/>
-      </c>
-      <c r="F272" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$272)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273">
-      <c r="B273" s="2" t="inlineStr">
+      <c r="C347" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$347),"")</f>
+        <v/>
+      </c>
+      <c r="D347" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$347),"")</f>
+        <v/>
+      </c>
+      <c r="E347" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$347),"")</f>
+        <v/>
+      </c>
+      <c r="F347" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$347)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348">
+      <c r="B348" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C273" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$273),"")</f>
-        <v/>
-      </c>
-      <c r="D273" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$273),"")</f>
-        <v/>
-      </c>
-      <c r="E273" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$273),"")</f>
-        <v/>
-      </c>
-      <c r="F273" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$273)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="B274" s="2" t="inlineStr">
+      <c r="C348" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$348),"")</f>
+        <v/>
+      </c>
+      <c r="D348" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$348),"")</f>
+        <v/>
+      </c>
+      <c r="E348" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$348),"")</f>
+        <v/>
+      </c>
+      <c r="F348" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$348)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349">
+      <c r="B349" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C274" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$274),"")</f>
-        <v/>
-      </c>
-      <c r="D274" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$274),"")</f>
-        <v/>
-      </c>
-      <c r="E274" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$274),"")</f>
-        <v/>
-      </c>
-      <c r="F274" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$274)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275">
-      <c r="B275" s="2" t="inlineStr">
+      <c r="C349" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$349),"")</f>
+        <v/>
+      </c>
+      <c r="D349" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$349),"")</f>
+        <v/>
+      </c>
+      <c r="E349" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$349),"")</f>
+        <v/>
+      </c>
+      <c r="F349" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$349)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C275" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$275),"")</f>
-        <v/>
-      </c>
-      <c r="D275" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$275),"")</f>
-        <v/>
-      </c>
-      <c r="E275" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$275),"")</f>
-        <v/>
-      </c>
-      <c r="F275" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$275)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276">
-      <c r="B276" s="2" t="inlineStr">
+      <c r="C350" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$350),"")</f>
+        <v/>
+      </c>
+      <c r="D350" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$350),"")</f>
+        <v/>
+      </c>
+      <c r="E350" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$350),"")</f>
+        <v/>
+      </c>
+      <c r="F350" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$350)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C276" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$276),"")</f>
-        <v/>
-      </c>
-      <c r="D276" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$276),"")</f>
-        <v/>
-      </c>
-      <c r="E276" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$276),"")</f>
-        <v/>
-      </c>
-      <c r="F276" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$276)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="277">
-      <c r="B277" s="2" t="inlineStr">
+      <c r="C351" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$351),"")</f>
+        <v/>
+      </c>
+      <c r="D351" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$351),"")</f>
+        <v/>
+      </c>
+      <c r="E351" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$351),"")</f>
+        <v/>
+      </c>
+      <c r="F351" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$351)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C277" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$277),"")</f>
-        <v/>
-      </c>
-      <c r="D277" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$277),"")</f>
-        <v/>
-      </c>
-      <c r="E277" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$277),"")</f>
-        <v/>
-      </c>
-      <c r="F277" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$277)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="278">
-      <c r="B278" s="2" t="inlineStr">
+      <c r="C352" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$352),"")</f>
+        <v/>
+      </c>
+      <c r="D352" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$352),"")</f>
+        <v/>
+      </c>
+      <c r="E352" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$352),"")</f>
+        <v/>
+      </c>
+      <c r="F352" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$352)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C278" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$278),"")</f>
-        <v/>
-      </c>
-      <c r="D278" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$278),"")</f>
-        <v/>
-      </c>
-      <c r="E278" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$278),"")</f>
-        <v/>
-      </c>
-      <c r="F278" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$278)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="279">
-      <c r="B279" s="2" t="inlineStr">
+      <c r="C353" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$353),"")</f>
+        <v/>
+      </c>
+      <c r="D353" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$353),"")</f>
+        <v/>
+      </c>
+      <c r="E353" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$353),"")</f>
+        <v/>
+      </c>
+      <c r="F353" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$353)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C279" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$279),"")</f>
-        <v/>
-      </c>
-      <c r="D279" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$279),"")</f>
-        <v/>
-      </c>
-      <c r="E279" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$279),"")</f>
-        <v/>
-      </c>
-      <c r="F279" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$279)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280">
-      <c r="B280" s="2" t="inlineStr">
+      <c r="C354" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$354),"")</f>
+        <v/>
+      </c>
+      <c r="D354" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$354),"")</f>
+        <v/>
+      </c>
+      <c r="E354" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$354),"")</f>
+        <v/>
+      </c>
+      <c r="F354" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$354)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C280" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$280),"")</f>
-        <v/>
-      </c>
-      <c r="D280" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$280),"")</f>
-        <v/>
-      </c>
-      <c r="E280" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$280),"")</f>
-        <v/>
-      </c>
-      <c r="F280" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$280)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="B281" s="2" t="inlineStr">
+      <c r="C355" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$355),"")</f>
+        <v/>
+      </c>
+      <c r="D355" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$355),"")</f>
+        <v/>
+      </c>
+      <c r="E355" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$355),"")</f>
+        <v/>
+      </c>
+      <c r="F355" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$355)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C281" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$281),"")</f>
-        <v/>
-      </c>
-      <c r="D281" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$281),"")</f>
-        <v/>
-      </c>
-      <c r="E281" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$281),"")</f>
-        <v/>
-      </c>
-      <c r="F281" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$281)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282">
-      <c r="B282" s="2" t="inlineStr">
+      <c r="C356" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$356),"")</f>
+        <v/>
+      </c>
+      <c r="D356" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$356),"")</f>
+        <v/>
+      </c>
+      <c r="E356" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$356),"")</f>
+        <v/>
+      </c>
+      <c r="F356" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$356)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C282" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$282),"")</f>
-        <v/>
-      </c>
-      <c r="D282" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$282),"")</f>
-        <v/>
-      </c>
-      <c r="E282" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$282),"")</f>
-        <v/>
-      </c>
-      <c r="F282" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$282)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283">
-      <c r="B283" s="2" t="inlineStr">
+      <c r="C357" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$357),"")</f>
+        <v/>
+      </c>
+      <c r="D357" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$357),"")</f>
+        <v/>
+      </c>
+      <c r="E357" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$357),"")</f>
+        <v/>
+      </c>
+      <c r="F357" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$357)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C283" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$283),"")</f>
-        <v/>
-      </c>
-      <c r="D283" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$283),"")</f>
-        <v/>
-      </c>
-      <c r="E283" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$283),"")</f>
-        <v/>
-      </c>
-      <c r="F283" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$283)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="284">
-      <c r="B284" s="2" t="inlineStr">
+      <c r="C358" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$358),"")</f>
+        <v/>
+      </c>
+      <c r="D358" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$358),"")</f>
+        <v/>
+      </c>
+      <c r="E358" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$358),"")</f>
+        <v/>
+      </c>
+      <c r="F358" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$358)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C284" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$284),"")</f>
-        <v/>
-      </c>
-      <c r="D284" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$284),"")</f>
-        <v/>
-      </c>
-      <c r="E284" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$284),"")</f>
-        <v/>
-      </c>
-      <c r="F284" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$284)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285">
-      <c r="B285" s="2" t="inlineStr">
+      <c r="C359" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$359),"")</f>
+        <v/>
+      </c>
+      <c r="D359" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$359),"")</f>
+        <v/>
+      </c>
+      <c r="E359" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$359),"")</f>
+        <v/>
+      </c>
+      <c r="F359" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$359)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C285" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$285),"")</f>
-        <v/>
-      </c>
-      <c r="D285" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$285),"")</f>
-        <v/>
-      </c>
-      <c r="E285" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$285),"")</f>
-        <v/>
-      </c>
-      <c r="F285" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$285)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="286">
-      <c r="B286" s="2" t="inlineStr">
+      <c r="C360" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$360),"")</f>
+        <v/>
+      </c>
+      <c r="D360" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$360),"")</f>
+        <v/>
+      </c>
+      <c r="E360" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$360),"")</f>
+        <v/>
+      </c>
+      <c r="F360" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$360)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C286" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$286),"")</f>
-        <v/>
-      </c>
-      <c r="D286" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$286),"")</f>
-        <v/>
-      </c>
-      <c r="E286" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$286),"")</f>
-        <v/>
-      </c>
-      <c r="F286" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$286)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="287">
-      <c r="B287" s="2" t="inlineStr">
+      <c r="C361" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$361),"")</f>
+        <v/>
+      </c>
+      <c r="D361" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$361),"")</f>
+        <v/>
+      </c>
+      <c r="E361" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$361),"")</f>
+        <v/>
+      </c>
+      <c r="F361" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$361)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C287" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$287),"")</f>
-        <v/>
-      </c>
-      <c r="D287" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$287),"")</f>
-        <v/>
-      </c>
-      <c r="E287" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$287),"")</f>
-        <v/>
-      </c>
-      <c r="F287" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$287)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288">
-      <c r="B288" s="2" t="inlineStr">
+      <c r="C362" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$362),"")</f>
+        <v/>
+      </c>
+      <c r="D362" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$362),"")</f>
+        <v/>
+      </c>
+      <c r="E362" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$362),"")</f>
+        <v/>
+      </c>
+      <c r="F362" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$362)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C288" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$288),"")</f>
-        <v/>
-      </c>
-      <c r="D288" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$288),"")</f>
-        <v/>
-      </c>
-      <c r="E288" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$288),"")</f>
-        <v/>
-      </c>
-      <c r="F288" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$288)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289">
-      <c r="B289" s="2" t="inlineStr">
+      <c r="C363" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$363),"")</f>
+        <v/>
+      </c>
+      <c r="D363" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$363),"")</f>
+        <v/>
+      </c>
+      <c r="E363" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$363),"")</f>
+        <v/>
+      </c>
+      <c r="F363" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$363)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C289" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$289),"")</f>
-        <v/>
-      </c>
-      <c r="D289" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$289),"")</f>
-        <v/>
-      </c>
-      <c r="E289" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$289),"")</f>
-        <v/>
-      </c>
-      <c r="F289" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$289)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290">
-      <c r="B290" s="2" t="inlineStr">
+      <c r="C364" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$364),"")</f>
+        <v/>
+      </c>
+      <c r="D364" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$364),"")</f>
+        <v/>
+      </c>
+      <c r="E364" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$364),"")</f>
+        <v/>
+      </c>
+      <c r="F364" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$364)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C290" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$290),"")</f>
-        <v/>
-      </c>
-      <c r="D290" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$290),"")</f>
-        <v/>
-      </c>
-      <c r="E290" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$290),"")</f>
-        <v/>
-      </c>
-      <c r="F290" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$290)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="291">
-      <c r="B291" s="2" t="inlineStr">
+      <c r="C365" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$365),"")</f>
+        <v/>
+      </c>
+      <c r="D365" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$365),"")</f>
+        <v/>
+      </c>
+      <c r="E365" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$365),"")</f>
+        <v/>
+      </c>
+      <c r="F365" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$365)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C291" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$291),"")</f>
-        <v/>
-      </c>
-      <c r="D291" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$291),"")</f>
-        <v/>
-      </c>
-      <c r="E291" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$291),"")</f>
-        <v/>
-      </c>
-      <c r="F291" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$291)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292">
-      <c r="B292" s="2" t="inlineStr">
+      <c r="C366" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$366),"")</f>
+        <v/>
+      </c>
+      <c r="D366" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$366),"")</f>
+        <v/>
+      </c>
+      <c r="E366" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$366),"")</f>
+        <v/>
+      </c>
+      <c r="F366" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$366)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C292" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$292),"")</f>
-        <v/>
-      </c>
-      <c r="D292" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$292),"")</f>
-        <v/>
-      </c>
-      <c r="E292" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$292),"")</f>
-        <v/>
-      </c>
-      <c r="F292" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$292)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="293">
-      <c r="B293" s="2" t="inlineStr">
+      <c r="C367" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$367),"")</f>
+        <v/>
+      </c>
+      <c r="D367" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$367),"")</f>
+        <v/>
+      </c>
+      <c r="E367" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$367),"")</f>
+        <v/>
+      </c>
+      <c r="F367" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$367)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C293" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$293),"")</f>
-        <v/>
-      </c>
-      <c r="D293" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$293),"")</f>
-        <v/>
-      </c>
-      <c r="E293" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$293),"")</f>
-        <v/>
-      </c>
-      <c r="F293" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$293)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294">
-      <c r="B294" s="2" t="inlineStr">
+      <c r="C368" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$368),"")</f>
+        <v/>
+      </c>
+      <c r="D368" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$368),"")</f>
+        <v/>
+      </c>
+      <c r="E368" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$368),"")</f>
+        <v/>
+      </c>
+      <c r="F368" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$368)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C294" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$294),"")</f>
-        <v/>
-      </c>
-      <c r="D294" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$294),"")</f>
-        <v/>
-      </c>
-      <c r="E294" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$294),"")</f>
-        <v/>
-      </c>
-      <c r="F294" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$294)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295">
-      <c r="B295" s="2" t="inlineStr">
+      <c r="C369" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$369),"")</f>
+        <v/>
+      </c>
+      <c r="D369" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$369),"")</f>
+        <v/>
+      </c>
+      <c r="E369" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$369),"")</f>
+        <v/>
+      </c>
+      <c r="F369" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$369)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C295" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$295),"")</f>
-        <v/>
-      </c>
-      <c r="D295" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$295),"")</f>
-        <v/>
-      </c>
-      <c r="E295" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$295),"")</f>
-        <v/>
-      </c>
-      <c r="F295" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$295)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296">
-      <c r="B296" s="2" t="inlineStr">
+      <c r="C370" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$370),"")</f>
+        <v/>
+      </c>
+      <c r="D370" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$370),"")</f>
+        <v/>
+      </c>
+      <c r="E370" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$370),"")</f>
+        <v/>
+      </c>
+      <c r="F370" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$370)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C296" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$296),"")</f>
-        <v/>
-      </c>
-      <c r="D296" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$296),"")</f>
-        <v/>
-      </c>
-      <c r="E296" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$296),"")</f>
-        <v/>
-      </c>
-      <c r="F296" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$296)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297">
-      <c r="B297" s="2" t="inlineStr">
+      <c r="C371" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$371),"")</f>
+        <v/>
+      </c>
+      <c r="D371" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$371),"")</f>
+        <v/>
+      </c>
+      <c r="E371" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$371),"")</f>
+        <v/>
+      </c>
+      <c r="F371" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$371)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C297" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$297),"")</f>
-        <v/>
-      </c>
-      <c r="D297" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$297),"")</f>
-        <v/>
-      </c>
-      <c r="E297" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$297),"")</f>
-        <v/>
-      </c>
-      <c r="F297" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$297)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298">
-      <c r="B298" s="2" t="inlineStr">
+      <c r="C372" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$372),"")</f>
+        <v/>
+      </c>
+      <c r="D372" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$372),"")</f>
+        <v/>
+      </c>
+      <c r="E372" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$372),"")</f>
+        <v/>
+      </c>
+      <c r="F372" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$372)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C298" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$298),"")</f>
-        <v/>
-      </c>
-      <c r="D298" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$298),"")</f>
-        <v/>
-      </c>
-      <c r="E298" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$298),"")</f>
-        <v/>
-      </c>
-      <c r="F298" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$298)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="299">
-      <c r="B299" s="2" t="inlineStr">
+      <c r="C373" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$373),"")</f>
+        <v/>
+      </c>
+      <c r="D373" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$373),"")</f>
+        <v/>
+      </c>
+      <c r="E373" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$373),"")</f>
+        <v/>
+      </c>
+      <c r="F373" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$373)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C299" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$299),"")</f>
-        <v/>
-      </c>
-      <c r="D299" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$299),"")</f>
-        <v/>
-      </c>
-      <c r="E299" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$299),"")</f>
-        <v/>
-      </c>
-      <c r="F299" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$299)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300">
-      <c r="B300" s="2" t="inlineStr">
+      <c r="C374" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$374),"")</f>
+        <v/>
+      </c>
+      <c r="D374" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$374),"")</f>
+        <v/>
+      </c>
+      <c r="E374" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$374),"")</f>
+        <v/>
+      </c>
+      <c r="F374" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$374)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C300" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$300),"")</f>
-        <v/>
-      </c>
-      <c r="D300" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$300),"")</f>
-        <v/>
-      </c>
-      <c r="E300" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$300),"")</f>
-        <v/>
-      </c>
-      <c r="F300" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$300)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="301">
-      <c r="B301" s="2" t="inlineStr">
+      <c r="C375" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$375),"")</f>
+        <v/>
+      </c>
+      <c r="D375" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$375),"")</f>
+        <v/>
+      </c>
+      <c r="E375" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$375),"")</f>
+        <v/>
+      </c>
+      <c r="F375" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$375)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C301" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$301),"")</f>
-        <v/>
-      </c>
-      <c r="D301" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$301),"")</f>
-        <v/>
-      </c>
-      <c r="E301" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$301),"")</f>
-        <v/>
-      </c>
-      <c r="F301" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$301)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302">
-      <c r="B302" s="2" t="inlineStr">
+      <c r="C376" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$376),"")</f>
+        <v/>
+      </c>
+      <c r="D376" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$376),"")</f>
+        <v/>
+      </c>
+      <c r="E376" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$376),"")</f>
+        <v/>
+      </c>
+      <c r="F376" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$376)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C302" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$302),"")</f>
-        <v/>
-      </c>
-      <c r="D302" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$302),"")</f>
-        <v/>
-      </c>
-      <c r="E302" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$302),"")</f>
-        <v/>
-      </c>
-      <c r="F302" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$302)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="303">
-      <c r="B303" s="2" t="inlineStr">
+      <c r="C377" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$377),"")</f>
+        <v/>
+      </c>
+      <c r="D377" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$377),"")</f>
+        <v/>
+      </c>
+      <c r="E377" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$377),"")</f>
+        <v/>
+      </c>
+      <c r="F377" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$377)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C303" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$303),"")</f>
-        <v/>
-      </c>
-      <c r="D303" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$303),"")</f>
-        <v/>
-      </c>
-      <c r="E303" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$303),"")</f>
-        <v/>
-      </c>
-      <c r="F303" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$303)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="304">
-      <c r="B304" s="2" t="inlineStr">
+      <c r="C378" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$378),"")</f>
+        <v/>
+      </c>
+      <c r="D378" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$378),"")</f>
+        <v/>
+      </c>
+      <c r="E378" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$378),"")</f>
+        <v/>
+      </c>
+      <c r="F378" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$378)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C304" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$304),"")</f>
-        <v/>
-      </c>
-      <c r="D304" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$304),"")</f>
-        <v/>
-      </c>
-      <c r="E304" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$304),"")</f>
-        <v/>
-      </c>
-      <c r="F304" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$304)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305">
-      <c r="B305" s="2" t="inlineStr">
+      <c r="C379" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$379),"")</f>
+        <v/>
+      </c>
+      <c r="D379" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$379),"")</f>
+        <v/>
+      </c>
+      <c r="E379" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$379),"")</f>
+        <v/>
+      </c>
+      <c r="F379" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$379)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C305" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$305),"")</f>
-        <v/>
-      </c>
-      <c r="D305" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$305),"")</f>
-        <v/>
-      </c>
-      <c r="E305" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$305),"")</f>
-        <v/>
-      </c>
-      <c r="F305" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$305)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="306">
-      <c r="B306" s="2" t="inlineStr">
+      <c r="C380" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$380),"")</f>
+        <v/>
+      </c>
+      <c r="D380" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$380),"")</f>
+        <v/>
+      </c>
+      <c r="E380" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$380),"")</f>
+        <v/>
+      </c>
+      <c r="F380" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$380)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C306" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$306),"")</f>
-        <v/>
-      </c>
-      <c r="D306" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$306),"")</f>
-        <v/>
-      </c>
-      <c r="E306" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$306),"")</f>
-        <v/>
-      </c>
-      <c r="F306" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$306)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="307">
-      <c r="B307" s="2" t="inlineStr">
+      <c r="C381" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$381),"")</f>
+        <v/>
+      </c>
+      <c r="D381" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$381),"")</f>
+        <v/>
+      </c>
+      <c r="E381" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$381),"")</f>
+        <v/>
+      </c>
+      <c r="F381" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$381)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C307" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$307),"")</f>
-        <v/>
-      </c>
-      <c r="D307" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$307),"")</f>
-        <v/>
-      </c>
-      <c r="E307" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$307),"")</f>
-        <v/>
-      </c>
-      <c r="F307" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$307)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="308">
-      <c r="B308" s="2" t="inlineStr">
+      <c r="C382" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$382),"")</f>
+        <v/>
+      </c>
+      <c r="D382" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$382),"")</f>
+        <v/>
+      </c>
+      <c r="E382" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$382),"")</f>
+        <v/>
+      </c>
+      <c r="F382" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$382)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C308" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$308),"")</f>
-        <v/>
-      </c>
-      <c r="D308" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$308),"")</f>
-        <v/>
-      </c>
-      <c r="E308" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$308),"")</f>
-        <v/>
-      </c>
-      <c r="F308" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$308)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="309">
-      <c r="B309" s="2" t="inlineStr">
+      <c r="C383" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$383),"")</f>
+        <v/>
+      </c>
+      <c r="D383" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$383),"")</f>
+        <v/>
+      </c>
+      <c r="E383" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$383),"")</f>
+        <v/>
+      </c>
+      <c r="F383" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$383)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C309" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$309),"")</f>
-        <v/>
-      </c>
-      <c r="D309" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$309),"")</f>
-        <v/>
-      </c>
-      <c r="E309" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$309),"")</f>
-        <v/>
-      </c>
-      <c r="F309" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$309)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310">
-      <c r="B310" s="2" t="inlineStr">
+      <c r="C384" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$384),"")</f>
+        <v/>
+      </c>
+      <c r="D384" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$384),"")</f>
+        <v/>
+      </c>
+      <c r="E384" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$384),"")</f>
+        <v/>
+      </c>
+      <c r="F384" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$384)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C310" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$310),"")</f>
-        <v/>
-      </c>
-      <c r="D310" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$310),"")</f>
-        <v/>
-      </c>
-      <c r="E310" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$310),"")</f>
-        <v/>
-      </c>
-      <c r="F310" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$310)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="311">
-      <c r="B311" s="2" t="inlineStr">
+      <c r="C385" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$385),"")</f>
+        <v/>
+      </c>
+      <c r="D385" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$385),"")</f>
+        <v/>
+      </c>
+      <c r="E385" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$385),"")</f>
+        <v/>
+      </c>
+      <c r="F385" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$385)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C311" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$311),"")</f>
-        <v/>
-      </c>
-      <c r="D311" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$311),"")</f>
-        <v/>
-      </c>
-      <c r="E311" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$311),"")</f>
-        <v/>
-      </c>
-      <c r="F311" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$311)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312">
-      <c r="B312" s="2" t="inlineStr">
+      <c r="C386" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$386),"")</f>
+        <v/>
+      </c>
+      <c r="D386" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$386),"")</f>
+        <v/>
+      </c>
+      <c r="E386" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$386),"")</f>
+        <v/>
+      </c>
+      <c r="F386" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$386)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C312" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$312),"")</f>
-        <v/>
-      </c>
-      <c r="D312" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$312),"")</f>
-        <v/>
-      </c>
-      <c r="E312" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$312),"")</f>
-        <v/>
-      </c>
-      <c r="F312" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$312)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="313">
-      <c r="B313" s="2" t="inlineStr">
+      <c r="C387" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$387),"")</f>
+        <v/>
+      </c>
+      <c r="D387" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$387),"")</f>
+        <v/>
+      </c>
+      <c r="E387" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$387),"")</f>
+        <v/>
+      </c>
+      <c r="F387" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$387)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C313" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$313),"")</f>
-        <v/>
-      </c>
-      <c r="D313" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$313),"")</f>
-        <v/>
-      </c>
-      <c r="E313" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$313),"")</f>
-        <v/>
-      </c>
-      <c r="F313" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$313)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314">
-      <c r="B314" s="2" t="inlineStr">
+      <c r="C388" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$388),"")</f>
+        <v/>
+      </c>
+      <c r="D388" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$388),"")</f>
+        <v/>
+      </c>
+      <c r="E388" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$388),"")</f>
+        <v/>
+      </c>
+      <c r="F388" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$388)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C314" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$314),"")</f>
-        <v/>
-      </c>
-      <c r="D314" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$314),"")</f>
-        <v/>
-      </c>
-      <c r="E314" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$314),"")</f>
-        <v/>
-      </c>
-      <c r="F314" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$314)*(F$2:F$238),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315">
-      <c r="B315" s="2" t="inlineStr">
+      <c r="C389" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$389),"")</f>
+        <v/>
+      </c>
+      <c r="D389" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$389),"")</f>
+        <v/>
+      </c>
+      <c r="E389" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$389),"")</f>
+        <v/>
+      </c>
+      <c r="F389" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$389)*(F$2:F$313),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C315" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$315),"")</f>
-        <v/>
-      </c>
-      <c r="D315" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$315),"")</f>
-        <v/>
-      </c>
-      <c r="E315" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$238,A$2:A$238,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$238,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$238,$B$315),"")</f>
-        <v/>
-      </c>
-      <c r="F315" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$238)=YEAR(TODAY()))*(MONTH(A$2:A$238)=MONTH(TODAY()))*(B$2:B$238=$B$315)*(F$2:F$238),"")</f>
+      <c r="C390" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$390),"")</f>
+        <v/>
+      </c>
+      <c r="D390" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$390),"")</f>
+        <v/>
+      </c>
+      <c r="E390" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$390),"")</f>
+        <v/>
+      </c>
+      <c r="F390" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$390)*(F$2:F$313),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H238"/>
+  <autoFilter ref="A1:H313"/>
   <mergeCells count="1">
-    <mergeCell ref="A240:H240"/>
+    <mergeCell ref="A315:H315"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10496,7 +13046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11255,161 +13805,355 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>131640</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>133550</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>133980</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>131780</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-1850</v>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>160100</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>171800</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>160500</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>160560</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>-12400</v>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>6.7682</v>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="n">
+        <v>6.7681</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>6.7598</v>
+      </c>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/19</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D22" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
-        <v/>
-      </c>
-      <c r="E22" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$22),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$22)*(H$2:H$19),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="2" t="inlineStr">
+      <c r="D27" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$27)*(H$2:H$24),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D23" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$23),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$23)*(H$2:H$19),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" s="2" t="inlineStr">
+      <c r="D28" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$28)*(H$2:H$24),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D24" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$24),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$24)*(H$2:H$19),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" s="2" t="inlineStr">
+      <c r="D29" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$29)*(H$2:H$24),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>碳酸锂(LC)连续</t>
         </is>
       </c>
-      <c r="D25" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
-        <v/>
-      </c>
-      <c r="E25" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$25),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$25)*(H$2:H$19),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="2" t="inlineStr">
+      <c r="D30" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$30)*(H$2:H$24),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D26" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$19,A$2:A$19,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$19,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$19,$C$26),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$19)=YEAR(TODAY()))*(MONTH(A$2:A$19)=MONTH(TODAY()))*(C$2:C$19=$C$26)*(H$2:H$19),"")</f>
+      <c r="D31" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$31)*(H$2:H$24),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J24"/>
   <mergeCells count="1">
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A26:J26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$313</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$388</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H390"/>
+  <dimension ref="A1:H465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11292,1749 +11292,4299 @@
         </is>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C314" s="3" t="n">
+        <v>100400</v>
+      </c>
+      <c r="D314" s="4" t="n">
+        <v>105600</v>
+      </c>
+      <c r="E314" s="4" t="n">
+        <v>103000</v>
+      </c>
+      <c r="F314" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G314" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H314" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="315">
-      <c r="A315" s="8" t="inlineStr">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C315" s="3" t="n">
+        <v>181800</v>
+      </c>
+      <c r="D315" s="4" t="n">
+        <v>189700</v>
+      </c>
+      <c r="E315" s="4" t="n">
+        <v>185750</v>
+      </c>
+      <c r="F315" s="4" t="n">
+        <v>-3700</v>
+      </c>
+      <c r="G315" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H315" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C316" s="3" t="n">
+        <v>93250</v>
+      </c>
+      <c r="D316" s="4" t="n">
+        <v>97950</v>
+      </c>
+      <c r="E316" s="4" t="n">
+        <v>95600</v>
+      </c>
+      <c r="F316" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G316" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H316" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C317" s="3" t="n">
+        <v>186400</v>
+      </c>
+      <c r="D317" s="4" t="n">
+        <v>195900</v>
+      </c>
+      <c r="E317" s="4" t="n">
+        <v>191150</v>
+      </c>
+      <c r="F317" s="4" t="n">
+        <v>-3600</v>
+      </c>
+      <c r="G317" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H317" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C318" s="3" t="n">
+        <v>115600</v>
+      </c>
+      <c r="D318" s="4" t="n">
+        <v>121300</v>
+      </c>
+      <c r="E318" s="4" t="n">
+        <v>118450</v>
+      </c>
+      <c r="F318" s="4" t="n">
+        <v>-700</v>
+      </c>
+      <c r="G318" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H318" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C319" s="3" t="n">
+        <v>209500</v>
+      </c>
+      <c r="D319" s="4" t="n">
+        <v>219100</v>
+      </c>
+      <c r="E319" s="4" t="n">
+        <v>214300</v>
+      </c>
+      <c r="F319" s="4" t="n">
+        <v>-3700</v>
+      </c>
+      <c r="G319" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H319" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C320" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="D320" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E320" s="6" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="F320" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H320" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C321" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D321" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E321" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F321" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H321" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C322" s="3" t="n">
+        <v>206300</v>
+      </c>
+      <c r="D322" s="4" t="n">
+        <v>214600</v>
+      </c>
+      <c r="E322" s="4" t="n">
+        <v>210450</v>
+      </c>
+      <c r="F322" s="4" t="n">
+        <v>-4000</v>
+      </c>
+      <c r="G322" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H322" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C323" s="7" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="D323" s="6" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="E323" s="6" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="F323" s="6" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="G323" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H323" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C324" s="7" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="D324" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="E324" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F324" s="6" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="G324" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H324" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C325" s="7" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="D325" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="E325" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F325" s="6" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="G325" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H325" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C326" s="7" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="D326" s="6" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E326" s="6" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="F326" s="6" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="G326" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H326" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C327" s="7" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="D327" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="E327" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="F327" s="6" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="G327" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H327" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C328" s="7" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="D328" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="E328" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="F328" s="6" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="G328" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H328" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C329" s="3" t="n">
+        <v>101464</v>
+      </c>
+      <c r="D329" s="4" t="n">
+        <v>105605</v>
+      </c>
+      <c r="E329" s="4" t="n">
+        <v>103534.5</v>
+      </c>
+      <c r="F329" s="4" t="n">
+        <v>-345.5</v>
+      </c>
+      <c r="G329" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H329" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C330" s="3" t="n">
+        <v>144244</v>
+      </c>
+      <c r="D330" s="4" t="n">
+        <v>144244</v>
+      </c>
+      <c r="E330" s="4" t="n">
+        <v>144244</v>
+      </c>
+      <c r="F330" s="4" t="n">
+        <v>-8373</v>
+      </c>
+      <c r="G330" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H330" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C331" s="3" t="n">
+        <v>7643</v>
+      </c>
+      <c r="D331" s="4" t="n">
+        <v>7643</v>
+      </c>
+      <c r="E331" s="4" t="n">
+        <v>7643</v>
+      </c>
+      <c r="F331" s="6" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G331" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H331" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C332" s="3" t="n">
+        <v>32938</v>
+      </c>
+      <c r="D332" s="4" t="n">
+        <v>32938</v>
+      </c>
+      <c r="E332" s="4" t="n">
+        <v>32938</v>
+      </c>
+      <c r="F332" s="6" t="n">
+        <v>-62</v>
+      </c>
+      <c r="G332" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H332" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C333" s="3" t="n">
+        <v>155793</v>
+      </c>
+      <c r="D333" s="4" t="n">
+        <v>155793</v>
+      </c>
+      <c r="E333" s="4" t="n">
+        <v>155793</v>
+      </c>
+      <c r="F333" s="4" t="n">
+        <v>-11260</v>
+      </c>
+      <c r="G333" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H333" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C334" s="3" t="n">
+        <v>87725</v>
+      </c>
+      <c r="D334" s="4" t="n">
+        <v>87725</v>
+      </c>
+      <c r="E334" s="4" t="n">
+        <v>87725</v>
+      </c>
+      <c r="F334" s="4" t="n">
+        <v>-562</v>
+      </c>
+      <c r="G334" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H334" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C335" s="3" t="n">
+        <v>7068</v>
+      </c>
+      <c r="D335" s="4" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E335" s="4" t="n">
+        <v>7068</v>
+      </c>
+      <c r="F335" s="4" t="n">
+        <v>-390</v>
+      </c>
+      <c r="G335" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H335" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C336" s="3" t="n">
+        <v>6606</v>
+      </c>
+      <c r="D336" s="4" t="n">
+        <v>6606</v>
+      </c>
+      <c r="E336" s="4" t="n">
+        <v>6606</v>
+      </c>
+      <c r="F336" s="4" t="n">
+        <v>-369</v>
+      </c>
+      <c r="G336" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H336" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C337" s="7" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="D337" s="6" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="E337" s="6" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="F337" s="6" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="G337" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H337" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C338" s="7" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D338" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E338" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F338" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H338" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C339" s="7" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="D339" s="6" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="E339" s="6" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="F339" s="6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="G339" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H339" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C340" s="7" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="D340" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="E340" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="F340" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H340" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C341" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D341" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E341" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F341" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H341" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C342" s="3" t="n">
+        <v>108000</v>
+      </c>
+      <c r="D342" s="4" t="n">
+        <v>112000</v>
+      </c>
+      <c r="E342" s="4" t="n">
+        <v>110000</v>
+      </c>
+      <c r="F342" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G342" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H342" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C343" s="3" t="n">
+        <v>332000</v>
+      </c>
+      <c r="D343" s="4" t="n">
+        <v>342000</v>
+      </c>
+      <c r="E343" s="4" t="n">
+        <v>337000</v>
+      </c>
+      <c r="F343" s="4" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="G343" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H343" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C344" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D344" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E344" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F344" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H344" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C345" s="3" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D345" s="4" t="n">
+        <v>134000</v>
+      </c>
+      <c r="E345" s="4" t="n">
+        <v>131000</v>
+      </c>
+      <c r="F345" s="4" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="G345" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H345" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C346" s="3" t="n">
+        <v>147000</v>
+      </c>
+      <c r="D346" s="4" t="n">
+        <v>159000</v>
+      </c>
+      <c r="E346" s="4" t="n">
+        <v>153000</v>
+      </c>
+      <c r="F346" s="4" t="n">
+        <v>-10250</v>
+      </c>
+      <c r="G346" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H346" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C347" s="3" t="n">
+        <v>1070000</v>
+      </c>
+      <c r="D347" s="4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="E347" s="4" t="n">
+        <v>1085000</v>
+      </c>
+      <c r="F347" s="4" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="G347" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H347" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C348" s="3" t="n">
+        <v>2160</v>
+      </c>
+      <c r="D348" s="4" t="n">
+        <v>2330</v>
+      </c>
+      <c r="E348" s="4" t="n">
+        <v>2245</v>
+      </c>
+      <c r="F348" s="4" t="n">
+        <v>-190</v>
+      </c>
+      <c r="G348" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H348" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C349" s="3" t="n">
+        <v>20900</v>
+      </c>
+      <c r="D349" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E349" s="4" t="n">
+        <v>22450</v>
+      </c>
+      <c r="F349" s="4" t="n">
+        <v>-1050</v>
+      </c>
+      <c r="G349" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H349" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C350" s="3" t="n">
+        <v>24800</v>
+      </c>
+      <c r="D350" s="4" t="n">
+        <v>28750</v>
+      </c>
+      <c r="E350" s="4" t="n">
+        <v>26775</v>
+      </c>
+      <c r="F350" s="4" t="n">
+        <v>-1325</v>
+      </c>
+      <c r="G350" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H350" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C351" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D351" s="4" t="n">
+        <v>17200</v>
+      </c>
+      <c r="E351" s="4" t="n">
+        <v>16600</v>
+      </c>
+      <c r="F351" s="4" t="n">
+        <v>-350</v>
+      </c>
+      <c r="G351" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H351" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C352" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D352" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="E352" s="4" t="n">
+        <v>10750</v>
+      </c>
+      <c r="F352" s="4" t="n">
+        <v>-250</v>
+      </c>
+      <c r="G352" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H352" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C353" s="3" t="n">
+        <v>17400</v>
+      </c>
+      <c r="D353" s="4" t="n">
+        <v>18200</v>
+      </c>
+      <c r="E353" s="4" t="n">
+        <v>17800</v>
+      </c>
+      <c r="F353" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G353" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H353" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C354" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D354" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E354" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F354" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H354" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C355" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D355" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E355" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F355" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H355" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C356" s="3" t="n">
+        <v>305000</v>
+      </c>
+      <c r="D356" s="4" t="n">
+        <v>320000</v>
+      </c>
+      <c r="E356" s="4" t="n">
+        <v>312500</v>
+      </c>
+      <c r="F356" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H356" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C357" s="3" t="n">
+        <v>105800</v>
+      </c>
+      <c r="D357" s="4" t="n">
+        <v>109000</v>
+      </c>
+      <c r="E357" s="4" t="n">
+        <v>107400</v>
+      </c>
+      <c r="F357" s="4" t="n">
+        <v>-1600</v>
+      </c>
+      <c r="G357" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H357" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C358" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D358" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E358" s="4" t="n">
+        <v>39750</v>
+      </c>
+      <c r="F358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H358" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C359" s="3" t="n">
+        <v>2380</v>
+      </c>
+      <c r="D359" s="4" t="n">
+        <v>2450</v>
+      </c>
+      <c r="E359" s="4" t="n">
+        <v>2415</v>
+      </c>
+      <c r="F359" s="6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G359" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H359" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C360" s="3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="D360" s="4" t="n">
+        <v>2340</v>
+      </c>
+      <c r="E360" s="4" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F360" s="4" t="n">
+        <v>-190</v>
+      </c>
+      <c r="G360" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H360" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C361" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="D361" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="E361" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="F361" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H361" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C362" s="3" t="n">
+        <v>275000</v>
+      </c>
+      <c r="D362" s="4" t="n">
+        <v>285000</v>
+      </c>
+      <c r="E362" s="4" t="n">
+        <v>280000</v>
+      </c>
+      <c r="F362" s="4" t="n">
+        <v>-7500</v>
+      </c>
+      <c r="G362" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H362" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C363" s="7" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D363" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E363" s="6" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="F363" s="6" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="G363" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H363" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C364" s="7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D364" s="6" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E364" s="6" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F364" s="6" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="G364" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H364" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C365" s="3" t="n">
+        <v>141000</v>
+      </c>
+      <c r="D365" s="4" t="n">
+        <v>158000</v>
+      </c>
+      <c r="E365" s="4" t="n">
+        <v>149500</v>
+      </c>
+      <c r="F365" s="4" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="G365" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H365" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="n">
+        <v>133000</v>
+      </c>
+      <c r="D366" s="4" t="n">
+        <v>154000</v>
+      </c>
+      <c r="E366" s="4" t="n">
+        <v>143500</v>
+      </c>
+      <c r="F366" s="4" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="G366" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H366" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C367" s="3" t="n">
+        <v>7570</v>
+      </c>
+      <c r="D367" s="4" t="n">
+        <v>7770</v>
+      </c>
+      <c r="E367" s="4" t="n">
+        <v>7670</v>
+      </c>
+      <c r="F367" s="6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G367" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H367" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C368" s="3" t="n">
+        <v>33170</v>
+      </c>
+      <c r="D368" s="4" t="n">
+        <v>33550</v>
+      </c>
+      <c r="E368" s="4" t="n">
+        <v>33360</v>
+      </c>
+      <c r="F368" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G368" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H368" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C369" s="3" t="n">
+        <v>151000</v>
+      </c>
+      <c r="D369" s="4" t="n">
+        <v>163000</v>
+      </c>
+      <c r="E369" s="4" t="n">
+        <v>157000</v>
+      </c>
+      <c r="F369" s="4" t="n">
+        <v>-10250</v>
+      </c>
+      <c r="G369" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H369" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C370" s="7" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D370" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E370" s="6" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="F370" s="6" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="G370" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H370" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C371" s="7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D371" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E371" s="6" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F371" s="6" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G371" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H371" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C372" s="3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="D372" s="4" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="E372" s="4" t="n">
+        <v>1115000</v>
+      </c>
+      <c r="F372" s="4" t="n">
+        <v>-15000</v>
+      </c>
+      <c r="G372" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H372" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C373" s="3" t="n">
+        <v>370000</v>
+      </c>
+      <c r="D373" s="4" t="n">
+        <v>395000</v>
+      </c>
+      <c r="E373" s="4" t="n">
+        <v>382500</v>
+      </c>
+      <c r="F373" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G373" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H373" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C374" s="7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D374" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E374" s="6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F374" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H374" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C375" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D375" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E375" s="4" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F375" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H375" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C376" s="3" t="n">
+        <v>86500</v>
+      </c>
+      <c r="D376" s="4" t="n">
+        <v>89500</v>
+      </c>
+      <c r="E376" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="F376" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G376" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H376" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C377" s="3" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D377" s="4" t="n">
+        <v>218000</v>
+      </c>
+      <c r="E377" s="4" t="n">
+        <v>213000</v>
+      </c>
+      <c r="F377" s="4" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G377" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H377" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C378" s="3" t="n">
+        <v>56670</v>
+      </c>
+      <c r="D378" s="4" t="n">
+        <v>57270</v>
+      </c>
+      <c r="E378" s="4" t="n">
+        <v>56970</v>
+      </c>
+      <c r="F378" s="4" t="n">
+        <v>-2510</v>
+      </c>
+      <c r="G378" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H378" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C379" s="3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="D379" s="4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="E379" s="4" t="n">
+        <v>64500</v>
+      </c>
+      <c r="F379" s="4" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="G379" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H379" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C380" s="7" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D380" s="6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E380" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="F380" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H380" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C381" s="3" t="n">
+        <v>26783</v>
+      </c>
+      <c r="D381" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="E381" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="F381" s="4" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G381" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H381" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C382" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D382" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E382" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F382" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H382" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C383" s="3" t="n">
+        <v>379000</v>
+      </c>
+      <c r="D383" s="4" t="n">
+        <v>382000</v>
+      </c>
+      <c r="E383" s="4" t="n">
+        <v>380500</v>
+      </c>
+      <c r="F383" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G383" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H383" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C384" s="3" t="n">
+        <v>98000</v>
+      </c>
+      <c r="D384" s="4" t="n">
+        <v>100400</v>
+      </c>
+      <c r="E384" s="4" t="n">
+        <v>99200</v>
+      </c>
+      <c r="F384" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G384" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H384" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C385" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D385" s="4" t="n">
+        <v>93400</v>
+      </c>
+      <c r="E385" s="4" t="n">
+        <v>88700</v>
+      </c>
+      <c r="F385" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G385" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H385" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C386" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D386" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E386" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F386" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H386" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C387" s="3" t="n">
+        <v>7278</v>
+      </c>
+      <c r="D387" s="4" t="n">
+        <v>7929</v>
+      </c>
+      <c r="E387" s="4" t="n">
+        <v>7603.5</v>
+      </c>
+      <c r="F387" s="4" t="n">
+        <v>-566</v>
+      </c>
+      <c r="G387" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H387" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C388" s="3" t="n">
+        <v>2398</v>
+      </c>
+      <c r="D388" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="E388" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F388" s="6" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G388" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H388" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B315" s="9" t="n"/>
-      <c r="C315" s="9" t="n"/>
-      <c r="D315" s="9" t="n"/>
-      <c r="E315" s="9" t="n"/>
-      <c r="F315" s="9" t="n"/>
-      <c r="G315" s="9" t="n"/>
-      <c r="H315" s="9" t="n"/>
-    </row>
-    <row r="316">
-      <c r="B316" s="2" t="inlineStr">
+      <c r="B390" s="9" t="n"/>
+      <c r="C390" s="9" t="n"/>
+      <c r="D390" s="9" t="n"/>
+      <c r="E390" s="9" t="n"/>
+      <c r="F390" s="9" t="n"/>
+      <c r="G390" s="9" t="n"/>
+      <c r="H390" s="9" t="n"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C316" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$316),"")</f>
-        <v/>
-      </c>
-      <c r="D316" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$316),"")</f>
-        <v/>
-      </c>
-      <c r="E316" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$316),"")</f>
-        <v/>
-      </c>
-      <c r="F316" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$316)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="317">
-      <c r="B317" s="2" t="inlineStr">
+      <c r="C391" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$391),"")</f>
+        <v/>
+      </c>
+      <c r="D391" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$391),"")</f>
+        <v/>
+      </c>
+      <c r="E391" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$391),"")</f>
+        <v/>
+      </c>
+      <c r="F391" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$391)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C317" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$317),"")</f>
-        <v/>
-      </c>
-      <c r="D317" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$317),"")</f>
-        <v/>
-      </c>
-      <c r="E317" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$317),"")</f>
-        <v/>
-      </c>
-      <c r="F317" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$317)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="318">
-      <c r="B318" s="2" t="inlineStr">
+      <c r="C392" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$392),"")</f>
+        <v/>
+      </c>
+      <c r="D392" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$392),"")</f>
+        <v/>
+      </c>
+      <c r="E392" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$392),"")</f>
+        <v/>
+      </c>
+      <c r="F392" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$392)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C318" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$318),"")</f>
-        <v/>
-      </c>
-      <c r="D318" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$318),"")</f>
-        <v/>
-      </c>
-      <c r="E318" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$318),"")</f>
-        <v/>
-      </c>
-      <c r="F318" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$318)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="319">
-      <c r="B319" s="2" t="inlineStr">
+      <c r="C393" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$393),"")</f>
+        <v/>
+      </c>
+      <c r="D393" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$393),"")</f>
+        <v/>
+      </c>
+      <c r="E393" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$393),"")</f>
+        <v/>
+      </c>
+      <c r="F393" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$393)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C319" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$319),"")</f>
-        <v/>
-      </c>
-      <c r="D319" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$319),"")</f>
-        <v/>
-      </c>
-      <c r="E319" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$319),"")</f>
-        <v/>
-      </c>
-      <c r="F319" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$319)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="320">
-      <c r="B320" s="2" t="inlineStr">
+      <c r="C394" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$394),"")</f>
+        <v/>
+      </c>
+      <c r="D394" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$394),"")</f>
+        <v/>
+      </c>
+      <c r="E394" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$394),"")</f>
+        <v/>
+      </c>
+      <c r="F394" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$394)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C320" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$320),"")</f>
-        <v/>
-      </c>
-      <c r="D320" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$320),"")</f>
-        <v/>
-      </c>
-      <c r="E320" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$320),"")</f>
-        <v/>
-      </c>
-      <c r="F320" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$320)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="321">
-      <c r="B321" s="2" t="inlineStr">
+      <c r="C395" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$395),"")</f>
+        <v/>
+      </c>
+      <c r="D395" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$395),"")</f>
+        <v/>
+      </c>
+      <c r="E395" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$395),"")</f>
+        <v/>
+      </c>
+      <c r="F395" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$395)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C321" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$321),"")</f>
-        <v/>
-      </c>
-      <c r="D321" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$321),"")</f>
-        <v/>
-      </c>
-      <c r="E321" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$321),"")</f>
-        <v/>
-      </c>
-      <c r="F321" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$321)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="322">
-      <c r="B322" s="2" t="inlineStr">
+      <c r="C396" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$396),"")</f>
+        <v/>
+      </c>
+      <c r="D396" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$396),"")</f>
+        <v/>
+      </c>
+      <c r="E396" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$396),"")</f>
+        <v/>
+      </c>
+      <c r="F396" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$396)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C322" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$322),"")</f>
-        <v/>
-      </c>
-      <c r="D322" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$322),"")</f>
-        <v/>
-      </c>
-      <c r="E322" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$322),"")</f>
-        <v/>
-      </c>
-      <c r="F322" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$322)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="323">
-      <c r="B323" s="2" t="inlineStr">
+      <c r="C397" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$397),"")</f>
+        <v/>
+      </c>
+      <c r="D397" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$397),"")</f>
+        <v/>
+      </c>
+      <c r="E397" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$397),"")</f>
+        <v/>
+      </c>
+      <c r="F397" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$397)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C323" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$323),"")</f>
-        <v/>
-      </c>
-      <c r="D323" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$323),"")</f>
-        <v/>
-      </c>
-      <c r="E323" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$323),"")</f>
-        <v/>
-      </c>
-      <c r="F323" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$323)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="324">
-      <c r="B324" s="2" t="inlineStr">
+      <c r="C398" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$398),"")</f>
+        <v/>
+      </c>
+      <c r="D398" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$398),"")</f>
+        <v/>
+      </c>
+      <c r="E398" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$398),"")</f>
+        <v/>
+      </c>
+      <c r="F398" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$398)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C324" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$324),"")</f>
-        <v/>
-      </c>
-      <c r="D324" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$324),"")</f>
-        <v/>
-      </c>
-      <c r="E324" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$324),"")</f>
-        <v/>
-      </c>
-      <c r="F324" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$324)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="325">
-      <c r="B325" s="2" t="inlineStr">
+      <c r="C399" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$399),"")</f>
+        <v/>
+      </c>
+      <c r="D399" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$399),"")</f>
+        <v/>
+      </c>
+      <c r="E399" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$399),"")</f>
+        <v/>
+      </c>
+      <c r="F399" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$399)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C325" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$325),"")</f>
-        <v/>
-      </c>
-      <c r="D325" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$325),"")</f>
-        <v/>
-      </c>
-      <c r="E325" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$325),"")</f>
-        <v/>
-      </c>
-      <c r="F325" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$325)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326">
-      <c r="B326" s="2" t="inlineStr">
+      <c r="C400" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$400),"")</f>
+        <v/>
+      </c>
+      <c r="D400" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$400),"")</f>
+        <v/>
+      </c>
+      <c r="E400" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$400),"")</f>
+        <v/>
+      </c>
+      <c r="F400" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$400)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C326" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$326),"")</f>
-        <v/>
-      </c>
-      <c r="D326" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$326),"")</f>
-        <v/>
-      </c>
-      <c r="E326" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$326),"")</f>
-        <v/>
-      </c>
-      <c r="F326" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$326)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="327">
-      <c r="B327" s="2" t="inlineStr">
+      <c r="C401" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$401),"")</f>
+        <v/>
+      </c>
+      <c r="D401" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$401),"")</f>
+        <v/>
+      </c>
+      <c r="E401" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$401),"")</f>
+        <v/>
+      </c>
+      <c r="F401" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$401)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C327" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$327),"")</f>
-        <v/>
-      </c>
-      <c r="D327" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$327),"")</f>
-        <v/>
-      </c>
-      <c r="E327" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$327),"")</f>
-        <v/>
-      </c>
-      <c r="F327" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$327)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328">
-      <c r="B328" s="2" t="inlineStr">
+      <c r="C402" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$402),"")</f>
+        <v/>
+      </c>
+      <c r="D402" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$402),"")</f>
+        <v/>
+      </c>
+      <c r="E402" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$402),"")</f>
+        <v/>
+      </c>
+      <c r="F402" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$402)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C328" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$328),"")</f>
-        <v/>
-      </c>
-      <c r="D328" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$328),"")</f>
-        <v/>
-      </c>
-      <c r="E328" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$328),"")</f>
-        <v/>
-      </c>
-      <c r="F328" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$328)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="329">
-      <c r="B329" s="2" t="inlineStr">
+      <c r="C403" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$403),"")</f>
+        <v/>
+      </c>
+      <c r="D403" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$403),"")</f>
+        <v/>
+      </c>
+      <c r="E403" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$403),"")</f>
+        <v/>
+      </c>
+      <c r="F403" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$403)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C329" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$329),"")</f>
-        <v/>
-      </c>
-      <c r="D329" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$329),"")</f>
-        <v/>
-      </c>
-      <c r="E329" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$329),"")</f>
-        <v/>
-      </c>
-      <c r="F329" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$329)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="330">
-      <c r="B330" s="2" t="inlineStr">
+      <c r="C404" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$404),"")</f>
+        <v/>
+      </c>
+      <c r="D404" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$404),"")</f>
+        <v/>
+      </c>
+      <c r="E404" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$404),"")</f>
+        <v/>
+      </c>
+      <c r="F404" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$404)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C330" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$330),"")</f>
-        <v/>
-      </c>
-      <c r="D330" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$330),"")</f>
-        <v/>
-      </c>
-      <c r="E330" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$330),"")</f>
-        <v/>
-      </c>
-      <c r="F330" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$330)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="331">
-      <c r="B331" s="2" t="inlineStr">
+      <c r="C405" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$405),"")</f>
+        <v/>
+      </c>
+      <c r="D405" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$405),"")</f>
+        <v/>
+      </c>
+      <c r="E405" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$405),"")</f>
+        <v/>
+      </c>
+      <c r="F405" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$405)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C331" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$331),"")</f>
-        <v/>
-      </c>
-      <c r="D331" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$331),"")</f>
-        <v/>
-      </c>
-      <c r="E331" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$331),"")</f>
-        <v/>
-      </c>
-      <c r="F331" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$331)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="332">
-      <c r="B332" s="2" t="inlineStr">
+      <c r="C406" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$406),"")</f>
+        <v/>
+      </c>
+      <c r="D406" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$406),"")</f>
+        <v/>
+      </c>
+      <c r="E406" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$406),"")</f>
+        <v/>
+      </c>
+      <c r="F406" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$406)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C332" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$332),"")</f>
-        <v/>
-      </c>
-      <c r="D332" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$332),"")</f>
-        <v/>
-      </c>
-      <c r="E332" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$332),"")</f>
-        <v/>
-      </c>
-      <c r="F332" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$332)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="333">
-      <c r="B333" s="2" t="inlineStr">
+      <c r="C407" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$407),"")</f>
+        <v/>
+      </c>
+      <c r="D407" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$407),"")</f>
+        <v/>
+      </c>
+      <c r="E407" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$407),"")</f>
+        <v/>
+      </c>
+      <c r="F407" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$407)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C333" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$333),"")</f>
-        <v/>
-      </c>
-      <c r="D333" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$333),"")</f>
-        <v/>
-      </c>
-      <c r="E333" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$333),"")</f>
-        <v/>
-      </c>
-      <c r="F333" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$333)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="334">
-      <c r="B334" s="2" t="inlineStr">
+      <c r="C408" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$408),"")</f>
+        <v/>
+      </c>
+      <c r="D408" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$408),"")</f>
+        <v/>
+      </c>
+      <c r="E408" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$408),"")</f>
+        <v/>
+      </c>
+      <c r="F408" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$408)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C334" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$334),"")</f>
-        <v/>
-      </c>
-      <c r="D334" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$334),"")</f>
-        <v/>
-      </c>
-      <c r="E334" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$334),"")</f>
-        <v/>
-      </c>
-      <c r="F334" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$334)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="335">
-      <c r="B335" s="2" t="inlineStr">
+      <c r="C409" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$409),"")</f>
+        <v/>
+      </c>
+      <c r="D409" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$409),"")</f>
+        <v/>
+      </c>
+      <c r="E409" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$409),"")</f>
+        <v/>
+      </c>
+      <c r="F409" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$409)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C335" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$335),"")</f>
-        <v/>
-      </c>
-      <c r="D335" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$335),"")</f>
-        <v/>
-      </c>
-      <c r="E335" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$335),"")</f>
-        <v/>
-      </c>
-      <c r="F335" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$335)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336">
-      <c r="B336" s="2" t="inlineStr">
+      <c r="C410" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$410),"")</f>
+        <v/>
+      </c>
+      <c r="D410" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$410),"")</f>
+        <v/>
+      </c>
+      <c r="E410" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$410),"")</f>
+        <v/>
+      </c>
+      <c r="F410" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$410)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C336" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$336),"")</f>
-        <v/>
-      </c>
-      <c r="D336" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$336),"")</f>
-        <v/>
-      </c>
-      <c r="E336" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$336),"")</f>
-        <v/>
-      </c>
-      <c r="F336" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$336)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="337">
-      <c r="B337" s="2" t="inlineStr">
+      <c r="C411" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$411),"")</f>
+        <v/>
+      </c>
+      <c r="D411" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$411),"")</f>
+        <v/>
+      </c>
+      <c r="E411" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$411),"")</f>
+        <v/>
+      </c>
+      <c r="F411" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$411)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C337" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$337),"")</f>
-        <v/>
-      </c>
-      <c r="D337" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$337),"")</f>
-        <v/>
-      </c>
-      <c r="E337" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$337),"")</f>
-        <v/>
-      </c>
-      <c r="F337" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$337)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338">
-      <c r="B338" s="2" t="inlineStr">
+      <c r="C412" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$412),"")</f>
+        <v/>
+      </c>
+      <c r="D412" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$412),"")</f>
+        <v/>
+      </c>
+      <c r="E412" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$412),"")</f>
+        <v/>
+      </c>
+      <c r="F412" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$412)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C338" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$338),"")</f>
-        <v/>
-      </c>
-      <c r="D338" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$338),"")</f>
-        <v/>
-      </c>
-      <c r="E338" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$338),"")</f>
-        <v/>
-      </c>
-      <c r="F338" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$338)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="339">
-      <c r="B339" s="2" t="inlineStr">
+      <c r="C413" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$413),"")</f>
+        <v/>
+      </c>
+      <c r="D413" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$413),"")</f>
+        <v/>
+      </c>
+      <c r="E413" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$413),"")</f>
+        <v/>
+      </c>
+      <c r="F413" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$413)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C339" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$339),"")</f>
-        <v/>
-      </c>
-      <c r="D339" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$339),"")</f>
-        <v/>
-      </c>
-      <c r="E339" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$339),"")</f>
-        <v/>
-      </c>
-      <c r="F339" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$339)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="B340" s="2" t="inlineStr">
+      <c r="C414" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$414),"")</f>
+        <v/>
+      </c>
+      <c r="D414" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$414),"")</f>
+        <v/>
+      </c>
+      <c r="E414" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$414),"")</f>
+        <v/>
+      </c>
+      <c r="F414" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$414)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C340" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$340),"")</f>
-        <v/>
-      </c>
-      <c r="D340" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$340),"")</f>
-        <v/>
-      </c>
-      <c r="E340" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$340),"")</f>
-        <v/>
-      </c>
-      <c r="F340" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$340)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341">
-      <c r="B341" s="2" t="inlineStr">
+      <c r="C415" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$415),"")</f>
+        <v/>
+      </c>
+      <c r="D415" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$415),"")</f>
+        <v/>
+      </c>
+      <c r="E415" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$415),"")</f>
+        <v/>
+      </c>
+      <c r="F415" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$415)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C341" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$341),"")</f>
-        <v/>
-      </c>
-      <c r="D341" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$341),"")</f>
-        <v/>
-      </c>
-      <c r="E341" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$341),"")</f>
-        <v/>
-      </c>
-      <c r="F341" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$341)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="342">
-      <c r="B342" s="2" t="inlineStr">
+      <c r="C416" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$416),"")</f>
+        <v/>
+      </c>
+      <c r="D416" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$416),"")</f>
+        <v/>
+      </c>
+      <c r="E416" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$416),"")</f>
+        <v/>
+      </c>
+      <c r="F416" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$416)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C342" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$342),"")</f>
-        <v/>
-      </c>
-      <c r="D342" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$342),"")</f>
-        <v/>
-      </c>
-      <c r="E342" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$342),"")</f>
-        <v/>
-      </c>
-      <c r="F342" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$342)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="343">
-      <c r="B343" s="2" t="inlineStr">
+      <c r="C417" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$417),"")</f>
+        <v/>
+      </c>
+      <c r="D417" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$417),"")</f>
+        <v/>
+      </c>
+      <c r="E417" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$417),"")</f>
+        <v/>
+      </c>
+      <c r="F417" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$417)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C343" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$343),"")</f>
-        <v/>
-      </c>
-      <c r="D343" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$343),"")</f>
-        <v/>
-      </c>
-      <c r="E343" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$343),"")</f>
-        <v/>
-      </c>
-      <c r="F343" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$343)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="344">
-      <c r="B344" s="2" t="inlineStr">
+      <c r="C418" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$418),"")</f>
+        <v/>
+      </c>
+      <c r="D418" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$418),"")</f>
+        <v/>
+      </c>
+      <c r="E418" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$418),"")</f>
+        <v/>
+      </c>
+      <c r="F418" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$418)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C344" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$344),"")</f>
-        <v/>
-      </c>
-      <c r="D344" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$344),"")</f>
-        <v/>
-      </c>
-      <c r="E344" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$344),"")</f>
-        <v/>
-      </c>
-      <c r="F344" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$344)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="345">
-      <c r="B345" s="2" t="inlineStr">
+      <c r="C419" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$419),"")</f>
+        <v/>
+      </c>
+      <c r="D419" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$419),"")</f>
+        <v/>
+      </c>
+      <c r="E419" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$419),"")</f>
+        <v/>
+      </c>
+      <c r="F419" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$419)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C345" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$345),"")</f>
-        <v/>
-      </c>
-      <c r="D345" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$345),"")</f>
-        <v/>
-      </c>
-      <c r="E345" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$345),"")</f>
-        <v/>
-      </c>
-      <c r="F345" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$345)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="346">
-      <c r="B346" s="2" t="inlineStr">
+      <c r="C420" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$420),"")</f>
+        <v/>
+      </c>
+      <c r="D420" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$420),"")</f>
+        <v/>
+      </c>
+      <c r="E420" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$420),"")</f>
+        <v/>
+      </c>
+      <c r="F420" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$420)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C346" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$346),"")</f>
-        <v/>
-      </c>
-      <c r="D346" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$346),"")</f>
-        <v/>
-      </c>
-      <c r="E346" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$346),"")</f>
-        <v/>
-      </c>
-      <c r="F346" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$346)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347">
-      <c r="B347" s="2" t="inlineStr">
+      <c r="C421" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$421),"")</f>
+        <v/>
+      </c>
+      <c r="D421" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$421),"")</f>
+        <v/>
+      </c>
+      <c r="E421" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$421),"")</f>
+        <v/>
+      </c>
+      <c r="F421" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$421)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C347" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$347),"")</f>
-        <v/>
-      </c>
-      <c r="D347" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$347),"")</f>
-        <v/>
-      </c>
-      <c r="E347" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$347),"")</f>
-        <v/>
-      </c>
-      <c r="F347" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$347)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="348">
-      <c r="B348" s="2" t="inlineStr">
+      <c r="C422" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$422),"")</f>
+        <v/>
+      </c>
+      <c r="D422" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$422),"")</f>
+        <v/>
+      </c>
+      <c r="E422" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$422),"")</f>
+        <v/>
+      </c>
+      <c r="F422" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$422)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C348" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$348),"")</f>
-        <v/>
-      </c>
-      <c r="D348" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$348),"")</f>
-        <v/>
-      </c>
-      <c r="E348" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$348),"")</f>
-        <v/>
-      </c>
-      <c r="F348" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$348)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="349">
-      <c r="B349" s="2" t="inlineStr">
+      <c r="C423" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$423),"")</f>
+        <v/>
+      </c>
+      <c r="D423" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$423),"")</f>
+        <v/>
+      </c>
+      <c r="E423" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$423),"")</f>
+        <v/>
+      </c>
+      <c r="F423" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$423)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C349" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$349),"")</f>
-        <v/>
-      </c>
-      <c r="D349" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$349),"")</f>
-        <v/>
-      </c>
-      <c r="E349" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$349),"")</f>
-        <v/>
-      </c>
-      <c r="F349" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$349)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="350">
-      <c r="B350" s="2" t="inlineStr">
+      <c r="C424" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$424),"")</f>
+        <v/>
+      </c>
+      <c r="D424" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$424),"")</f>
+        <v/>
+      </c>
+      <c r="E424" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$424),"")</f>
+        <v/>
+      </c>
+      <c r="F424" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$424)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C350" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$350),"")</f>
-        <v/>
-      </c>
-      <c r="D350" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$350),"")</f>
-        <v/>
-      </c>
-      <c r="E350" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$350),"")</f>
-        <v/>
-      </c>
-      <c r="F350" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$350)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="351">
-      <c r="B351" s="2" t="inlineStr">
+      <c r="C425" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$425),"")</f>
+        <v/>
+      </c>
+      <c r="D425" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$425),"")</f>
+        <v/>
+      </c>
+      <c r="E425" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$425),"")</f>
+        <v/>
+      </c>
+      <c r="F425" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$425)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C351" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$351),"")</f>
-        <v/>
-      </c>
-      <c r="D351" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$351),"")</f>
-        <v/>
-      </c>
-      <c r="E351" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$351),"")</f>
-        <v/>
-      </c>
-      <c r="F351" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$351)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="352">
-      <c r="B352" s="2" t="inlineStr">
+      <c r="C426" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$426),"")</f>
+        <v/>
+      </c>
+      <c r="D426" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$426),"")</f>
+        <v/>
+      </c>
+      <c r="E426" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$426),"")</f>
+        <v/>
+      </c>
+      <c r="F426" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$426)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C352" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$352),"")</f>
-        <v/>
-      </c>
-      <c r="D352" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$352),"")</f>
-        <v/>
-      </c>
-      <c r="E352" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$352),"")</f>
-        <v/>
-      </c>
-      <c r="F352" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$352)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="353">
-      <c r="B353" s="2" t="inlineStr">
+      <c r="C427" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$427),"")</f>
+        <v/>
+      </c>
+      <c r="D427" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$427),"")</f>
+        <v/>
+      </c>
+      <c r="E427" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$427),"")</f>
+        <v/>
+      </c>
+      <c r="F427" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$427)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C353" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$353),"")</f>
-        <v/>
-      </c>
-      <c r="D353" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$353),"")</f>
-        <v/>
-      </c>
-      <c r="E353" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$353),"")</f>
-        <v/>
-      </c>
-      <c r="F353" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$353)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354">
-      <c r="B354" s="2" t="inlineStr">
+      <c r="C428" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$428),"")</f>
+        <v/>
+      </c>
+      <c r="D428" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$428),"")</f>
+        <v/>
+      </c>
+      <c r="E428" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$428),"")</f>
+        <v/>
+      </c>
+      <c r="F428" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$428)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C354" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$354),"")</f>
-        <v/>
-      </c>
-      <c r="D354" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$354),"")</f>
-        <v/>
-      </c>
-      <c r="E354" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$354),"")</f>
-        <v/>
-      </c>
-      <c r="F354" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$354)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="355">
-      <c r="B355" s="2" t="inlineStr">
+      <c r="C429" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$429),"")</f>
+        <v/>
+      </c>
+      <c r="D429" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$429),"")</f>
+        <v/>
+      </c>
+      <c r="E429" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$429),"")</f>
+        <v/>
+      </c>
+      <c r="F429" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$429)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C355" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$355),"")</f>
-        <v/>
-      </c>
-      <c r="D355" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$355),"")</f>
-        <v/>
-      </c>
-      <c r="E355" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$355),"")</f>
-        <v/>
-      </c>
-      <c r="F355" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$355)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="356">
-      <c r="B356" s="2" t="inlineStr">
+      <c r="C430" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$430),"")</f>
+        <v/>
+      </c>
+      <c r="D430" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$430),"")</f>
+        <v/>
+      </c>
+      <c r="E430" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$430),"")</f>
+        <v/>
+      </c>
+      <c r="F430" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$430)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C356" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$356),"")</f>
-        <v/>
-      </c>
-      <c r="D356" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$356),"")</f>
-        <v/>
-      </c>
-      <c r="E356" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$356),"")</f>
-        <v/>
-      </c>
-      <c r="F356" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$356)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="357">
-      <c r="B357" s="2" t="inlineStr">
+      <c r="C431" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$431),"")</f>
+        <v/>
+      </c>
+      <c r="D431" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$431),"")</f>
+        <v/>
+      </c>
+      <c r="E431" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$431),"")</f>
+        <v/>
+      </c>
+      <c r="F431" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$431)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C357" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$357),"")</f>
-        <v/>
-      </c>
-      <c r="D357" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$357),"")</f>
-        <v/>
-      </c>
-      <c r="E357" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$357),"")</f>
-        <v/>
-      </c>
-      <c r="F357" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$357)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="358">
-      <c r="B358" s="2" t="inlineStr">
+      <c r="C432" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$432),"")</f>
+        <v/>
+      </c>
+      <c r="D432" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$432),"")</f>
+        <v/>
+      </c>
+      <c r="E432" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$432),"")</f>
+        <v/>
+      </c>
+      <c r="F432" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$432)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C358" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$358),"")</f>
-        <v/>
-      </c>
-      <c r="D358" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$358),"")</f>
-        <v/>
-      </c>
-      <c r="E358" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$358),"")</f>
-        <v/>
-      </c>
-      <c r="F358" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$358)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="359">
-      <c r="B359" s="2" t="inlineStr">
+      <c r="C433" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$433),"")</f>
+        <v/>
+      </c>
+      <c r="D433" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$433),"")</f>
+        <v/>
+      </c>
+      <c r="E433" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$433),"")</f>
+        <v/>
+      </c>
+      <c r="F433" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$433)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C359" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$359),"")</f>
-        <v/>
-      </c>
-      <c r="D359" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$359),"")</f>
-        <v/>
-      </c>
-      <c r="E359" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$359),"")</f>
-        <v/>
-      </c>
-      <c r="F359" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$359)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="360">
-      <c r="B360" s="2" t="inlineStr">
+      <c r="C434" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$434),"")</f>
+        <v/>
+      </c>
+      <c r="D434" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$434),"")</f>
+        <v/>
+      </c>
+      <c r="E434" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$434),"")</f>
+        <v/>
+      </c>
+      <c r="F434" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$434)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C360" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$360),"")</f>
-        <v/>
-      </c>
-      <c r="D360" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$360),"")</f>
-        <v/>
-      </c>
-      <c r="E360" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$360),"")</f>
-        <v/>
-      </c>
-      <c r="F360" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$360)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="361">
-      <c r="B361" s="2" t="inlineStr">
+      <c r="C435" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$435),"")</f>
+        <v/>
+      </c>
+      <c r="D435" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$435),"")</f>
+        <v/>
+      </c>
+      <c r="E435" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$435),"")</f>
+        <v/>
+      </c>
+      <c r="F435" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$435)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C361" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$361),"")</f>
-        <v/>
-      </c>
-      <c r="D361" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$361),"")</f>
-        <v/>
-      </c>
-      <c r="E361" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$361),"")</f>
-        <v/>
-      </c>
-      <c r="F361" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$361)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="362">
-      <c r="B362" s="2" t="inlineStr">
+      <c r="C436" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$436),"")</f>
+        <v/>
+      </c>
+      <c r="D436" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$436),"")</f>
+        <v/>
+      </c>
+      <c r="E436" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$436),"")</f>
+        <v/>
+      </c>
+      <c r="F436" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$436)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C362" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$362),"")</f>
-        <v/>
-      </c>
-      <c r="D362" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$362),"")</f>
-        <v/>
-      </c>
-      <c r="E362" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$362),"")</f>
-        <v/>
-      </c>
-      <c r="F362" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$362)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="363">
-      <c r="B363" s="2" t="inlineStr">
+      <c r="C437" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$437),"")</f>
+        <v/>
+      </c>
+      <c r="D437" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$437),"")</f>
+        <v/>
+      </c>
+      <c r="E437" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$437),"")</f>
+        <v/>
+      </c>
+      <c r="F437" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$437)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C363" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$363),"")</f>
-        <v/>
-      </c>
-      <c r="D363" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$363),"")</f>
-        <v/>
-      </c>
-      <c r="E363" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$363),"")</f>
-        <v/>
-      </c>
-      <c r="F363" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$363)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="364">
-      <c r="B364" s="2" t="inlineStr">
+      <c r="C438" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$438),"")</f>
+        <v/>
+      </c>
+      <c r="D438" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$438),"")</f>
+        <v/>
+      </c>
+      <c r="E438" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$438),"")</f>
+        <v/>
+      </c>
+      <c r="F438" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$438)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C364" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$364),"")</f>
-        <v/>
-      </c>
-      <c r="D364" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$364),"")</f>
-        <v/>
-      </c>
-      <c r="E364" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$364),"")</f>
-        <v/>
-      </c>
-      <c r="F364" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$364)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="365">
-      <c r="B365" s="2" t="inlineStr">
+      <c r="C439" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$439),"")</f>
+        <v/>
+      </c>
+      <c r="D439" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$439),"")</f>
+        <v/>
+      </c>
+      <c r="E439" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$439),"")</f>
+        <v/>
+      </c>
+      <c r="F439" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$439)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C365" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$365),"")</f>
-        <v/>
-      </c>
-      <c r="D365" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$365),"")</f>
-        <v/>
-      </c>
-      <c r="E365" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$365),"")</f>
-        <v/>
-      </c>
-      <c r="F365" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$365)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366">
-      <c r="B366" s="2" t="inlineStr">
+      <c r="C440" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$440),"")</f>
+        <v/>
+      </c>
+      <c r="D440" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$440),"")</f>
+        <v/>
+      </c>
+      <c r="E440" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$440),"")</f>
+        <v/>
+      </c>
+      <c r="F440" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$440)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C366" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$366),"")</f>
-        <v/>
-      </c>
-      <c r="D366" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$366),"")</f>
-        <v/>
-      </c>
-      <c r="E366" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$366),"")</f>
-        <v/>
-      </c>
-      <c r="F366" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$366)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367">
-      <c r="B367" s="2" t="inlineStr">
+      <c r="C441" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$441),"")</f>
+        <v/>
+      </c>
+      <c r="D441" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$441),"")</f>
+        <v/>
+      </c>
+      <c r="E441" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$441),"")</f>
+        <v/>
+      </c>
+      <c r="F441" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$441)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C367" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$367),"")</f>
-        <v/>
-      </c>
-      <c r="D367" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$367),"")</f>
-        <v/>
-      </c>
-      <c r="E367" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$367),"")</f>
-        <v/>
-      </c>
-      <c r="F367" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$367)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="368">
-      <c r="B368" s="2" t="inlineStr">
+      <c r="C442" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$442),"")</f>
+        <v/>
+      </c>
+      <c r="D442" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$442),"")</f>
+        <v/>
+      </c>
+      <c r="E442" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$442),"")</f>
+        <v/>
+      </c>
+      <c r="F442" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$442)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C368" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$368),"")</f>
-        <v/>
-      </c>
-      <c r="D368" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$368),"")</f>
-        <v/>
-      </c>
-      <c r="E368" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$368),"")</f>
-        <v/>
-      </c>
-      <c r="F368" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$368)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="369">
-      <c r="B369" s="2" t="inlineStr">
+      <c r="C443" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$443),"")</f>
+        <v/>
+      </c>
+      <c r="D443" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$443),"")</f>
+        <v/>
+      </c>
+      <c r="E443" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$443),"")</f>
+        <v/>
+      </c>
+      <c r="F443" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$443)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C369" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$369),"")</f>
-        <v/>
-      </c>
-      <c r="D369" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$369),"")</f>
-        <v/>
-      </c>
-      <c r="E369" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$369),"")</f>
-        <v/>
-      </c>
-      <c r="F369" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$369)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="370">
-      <c r="B370" s="2" t="inlineStr">
+      <c r="C444" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$444),"")</f>
+        <v/>
+      </c>
+      <c r="D444" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$444),"")</f>
+        <v/>
+      </c>
+      <c r="E444" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$444),"")</f>
+        <v/>
+      </c>
+      <c r="F444" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$444)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C370" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$370),"")</f>
-        <v/>
-      </c>
-      <c r="D370" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$370),"")</f>
-        <v/>
-      </c>
-      <c r="E370" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$370),"")</f>
-        <v/>
-      </c>
-      <c r="F370" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$370)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="371">
-      <c r="B371" s="2" t="inlineStr">
+      <c r="C445" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$445),"")</f>
+        <v/>
+      </c>
+      <c r="D445" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$445),"")</f>
+        <v/>
+      </c>
+      <c r="E445" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$445),"")</f>
+        <v/>
+      </c>
+      <c r="F445" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$445)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C371" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$371),"")</f>
-        <v/>
-      </c>
-      <c r="D371" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$371),"")</f>
-        <v/>
-      </c>
-      <c r="E371" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$371),"")</f>
-        <v/>
-      </c>
-      <c r="F371" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$371)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="372">
-      <c r="B372" s="2" t="inlineStr">
+      <c r="C446" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$446),"")</f>
+        <v/>
+      </c>
+      <c r="D446" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$446),"")</f>
+        <v/>
+      </c>
+      <c r="E446" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$446),"")</f>
+        <v/>
+      </c>
+      <c r="F446" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$446)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C372" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$372),"")</f>
-        <v/>
-      </c>
-      <c r="D372" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$372),"")</f>
-        <v/>
-      </c>
-      <c r="E372" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$372),"")</f>
-        <v/>
-      </c>
-      <c r="F372" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$372)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="373">
-      <c r="B373" s="2" t="inlineStr">
+      <c r="C447" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$447),"")</f>
+        <v/>
+      </c>
+      <c r="D447" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$447),"")</f>
+        <v/>
+      </c>
+      <c r="E447" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$447),"")</f>
+        <v/>
+      </c>
+      <c r="F447" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$447)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C373" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$373),"")</f>
-        <v/>
-      </c>
-      <c r="D373" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$373),"")</f>
-        <v/>
-      </c>
-      <c r="E373" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$373),"")</f>
-        <v/>
-      </c>
-      <c r="F373" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$373)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="374">
-      <c r="B374" s="2" t="inlineStr">
+      <c r="C448" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$448),"")</f>
+        <v/>
+      </c>
+      <c r="D448" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$448),"")</f>
+        <v/>
+      </c>
+      <c r="E448" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$448),"")</f>
+        <v/>
+      </c>
+      <c r="F448" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$448)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C374" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$374),"")</f>
-        <v/>
-      </c>
-      <c r="D374" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$374),"")</f>
-        <v/>
-      </c>
-      <c r="E374" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$374),"")</f>
-        <v/>
-      </c>
-      <c r="F374" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$374)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="375">
-      <c r="B375" s="2" t="inlineStr">
+      <c r="C449" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$449),"")</f>
+        <v/>
+      </c>
+      <c r="D449" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$449),"")</f>
+        <v/>
+      </c>
+      <c r="E449" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$449),"")</f>
+        <v/>
+      </c>
+      <c r="F449" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$449)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C375" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$375),"")</f>
-        <v/>
-      </c>
-      <c r="D375" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$375),"")</f>
-        <v/>
-      </c>
-      <c r="E375" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$375),"")</f>
-        <v/>
-      </c>
-      <c r="F375" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$375)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="376">
-      <c r="B376" s="2" t="inlineStr">
+      <c r="C450" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$450),"")</f>
+        <v/>
+      </c>
+      <c r="D450" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$450),"")</f>
+        <v/>
+      </c>
+      <c r="E450" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$450),"")</f>
+        <v/>
+      </c>
+      <c r="F450" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$450)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C376" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$376),"")</f>
-        <v/>
-      </c>
-      <c r="D376" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$376),"")</f>
-        <v/>
-      </c>
-      <c r="E376" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$376),"")</f>
-        <v/>
-      </c>
-      <c r="F376" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$376)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="377">
-      <c r="B377" s="2" t="inlineStr">
+      <c r="C451" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$451),"")</f>
+        <v/>
+      </c>
+      <c r="D451" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$451),"")</f>
+        <v/>
+      </c>
+      <c r="E451" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$451),"")</f>
+        <v/>
+      </c>
+      <c r="F451" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$451)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C377" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$377),"")</f>
-        <v/>
-      </c>
-      <c r="D377" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$377),"")</f>
-        <v/>
-      </c>
-      <c r="E377" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$377),"")</f>
-        <v/>
-      </c>
-      <c r="F377" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$377)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="378">
-      <c r="B378" s="2" t="inlineStr">
+      <c r="C452" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$452),"")</f>
+        <v/>
+      </c>
+      <c r="D452" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$452),"")</f>
+        <v/>
+      </c>
+      <c r="E452" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$452),"")</f>
+        <v/>
+      </c>
+      <c r="F452" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$452)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C378" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$378),"")</f>
-        <v/>
-      </c>
-      <c r="D378" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$378),"")</f>
-        <v/>
-      </c>
-      <c r="E378" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$378),"")</f>
-        <v/>
-      </c>
-      <c r="F378" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$378)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379">
-      <c r="B379" s="2" t="inlineStr">
+      <c r="C453" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$453),"")</f>
+        <v/>
+      </c>
+      <c r="D453" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$453),"")</f>
+        <v/>
+      </c>
+      <c r="E453" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$453),"")</f>
+        <v/>
+      </c>
+      <c r="F453" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$453)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C379" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$379),"")</f>
-        <v/>
-      </c>
-      <c r="D379" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$379),"")</f>
-        <v/>
-      </c>
-      <c r="E379" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$379),"")</f>
-        <v/>
-      </c>
-      <c r="F379" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$379)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380">
-      <c r="B380" s="2" t="inlineStr">
+      <c r="C454" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$454),"")</f>
+        <v/>
+      </c>
+      <c r="D454" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$454),"")</f>
+        <v/>
+      </c>
+      <c r="E454" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$454),"")</f>
+        <v/>
+      </c>
+      <c r="F454" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$454)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C380" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$380),"")</f>
-        <v/>
-      </c>
-      <c r="D380" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$380),"")</f>
-        <v/>
-      </c>
-      <c r="E380" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$380),"")</f>
-        <v/>
-      </c>
-      <c r="F380" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$380)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="381">
-      <c r="B381" s="2" t="inlineStr">
+      <c r="C455" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$455),"")</f>
+        <v/>
+      </c>
+      <c r="D455" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$455),"")</f>
+        <v/>
+      </c>
+      <c r="E455" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$455),"")</f>
+        <v/>
+      </c>
+      <c r="F455" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$455)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C381" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$381),"")</f>
-        <v/>
-      </c>
-      <c r="D381" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$381),"")</f>
-        <v/>
-      </c>
-      <c r="E381" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$381),"")</f>
-        <v/>
-      </c>
-      <c r="F381" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$381)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="382">
-      <c r="B382" s="2" t="inlineStr">
+      <c r="C456" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$456),"")</f>
+        <v/>
+      </c>
+      <c r="D456" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$456),"")</f>
+        <v/>
+      </c>
+      <c r="E456" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$456),"")</f>
+        <v/>
+      </c>
+      <c r="F456" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$456)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C382" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$382),"")</f>
-        <v/>
-      </c>
-      <c r="D382" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$382),"")</f>
-        <v/>
-      </c>
-      <c r="E382" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$382),"")</f>
-        <v/>
-      </c>
-      <c r="F382" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$382)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="383">
-      <c r="B383" s="2" t="inlineStr">
+      <c r="C457" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$457),"")</f>
+        <v/>
+      </c>
+      <c r="D457" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$457),"")</f>
+        <v/>
+      </c>
+      <c r="E457" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$457),"")</f>
+        <v/>
+      </c>
+      <c r="F457" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$457)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C383" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$383),"")</f>
-        <v/>
-      </c>
-      <c r="D383" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$383),"")</f>
-        <v/>
-      </c>
-      <c r="E383" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$383),"")</f>
-        <v/>
-      </c>
-      <c r="F383" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$383)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="384">
-      <c r="B384" s="2" t="inlineStr">
+      <c r="C458" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$458),"")</f>
+        <v/>
+      </c>
+      <c r="D458" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$458),"")</f>
+        <v/>
+      </c>
+      <c r="E458" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$458),"")</f>
+        <v/>
+      </c>
+      <c r="F458" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$458)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C384" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$384),"")</f>
-        <v/>
-      </c>
-      <c r="D384" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$384),"")</f>
-        <v/>
-      </c>
-      <c r="E384" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$384),"")</f>
-        <v/>
-      </c>
-      <c r="F384" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$384)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="385">
-      <c r="B385" s="2" t="inlineStr">
+      <c r="C459" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$459),"")</f>
+        <v/>
+      </c>
+      <c r="D459" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$459),"")</f>
+        <v/>
+      </c>
+      <c r="E459" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$459),"")</f>
+        <v/>
+      </c>
+      <c r="F459" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$459)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C385" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$385),"")</f>
-        <v/>
-      </c>
-      <c r="D385" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$385),"")</f>
-        <v/>
-      </c>
-      <c r="E385" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$385),"")</f>
-        <v/>
-      </c>
-      <c r="F385" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$385)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="386">
-      <c r="B386" s="2" t="inlineStr">
+      <c r="C460" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$460),"")</f>
+        <v/>
+      </c>
+      <c r="D460" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$460),"")</f>
+        <v/>
+      </c>
+      <c r="E460" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$460),"")</f>
+        <v/>
+      </c>
+      <c r="F460" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$460)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C386" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$386),"")</f>
-        <v/>
-      </c>
-      <c r="D386" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$386),"")</f>
-        <v/>
-      </c>
-      <c r="E386" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$386),"")</f>
-        <v/>
-      </c>
-      <c r="F386" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$386)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="387">
-      <c r="B387" s="2" t="inlineStr">
+      <c r="C461" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$461),"")</f>
+        <v/>
+      </c>
+      <c r="D461" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$461),"")</f>
+        <v/>
+      </c>
+      <c r="E461" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$461),"")</f>
+        <v/>
+      </c>
+      <c r="F461" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$461)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C387" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$387),"")</f>
-        <v/>
-      </c>
-      <c r="D387" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$387),"")</f>
-        <v/>
-      </c>
-      <c r="E387" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$387),"")</f>
-        <v/>
-      </c>
-      <c r="F387" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$387)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="388">
-      <c r="B388" s="2" t="inlineStr">
+      <c r="C462" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$462),"")</f>
+        <v/>
+      </c>
+      <c r="D462" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$462),"")</f>
+        <v/>
+      </c>
+      <c r="E462" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$462),"")</f>
+        <v/>
+      </c>
+      <c r="F462" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$462)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C388" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$388),"")</f>
-        <v/>
-      </c>
-      <c r="D388" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$388),"")</f>
-        <v/>
-      </c>
-      <c r="E388" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$388),"")</f>
-        <v/>
-      </c>
-      <c r="F388" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$388)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="389">
-      <c r="B389" s="2" t="inlineStr">
+      <c r="C463" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$463),"")</f>
+        <v/>
+      </c>
+      <c r="D463" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$463),"")</f>
+        <v/>
+      </c>
+      <c r="E463" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$463),"")</f>
+        <v/>
+      </c>
+      <c r="F463" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$463)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C389" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$389),"")</f>
-        <v/>
-      </c>
-      <c r="D389" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$389),"")</f>
-        <v/>
-      </c>
-      <c r="E389" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$389),"")</f>
-        <v/>
-      </c>
-      <c r="F389" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$389)*(F$2:F$313),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="390">
-      <c r="B390" s="2" t="inlineStr">
+      <c r="C464" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$464),"")</f>
+        <v/>
+      </c>
+      <c r="D464" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$464),"")</f>
+        <v/>
+      </c>
+      <c r="E464" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$464),"")</f>
+        <v/>
+      </c>
+      <c r="F464" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$464)*(F$2:F$388),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C390" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$390),"")</f>
-        <v/>
-      </c>
-      <c r="D390" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$390),"")</f>
-        <v/>
-      </c>
-      <c r="E390" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$313,A$2:A$313,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$313,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$313,$B$390),"")</f>
-        <v/>
-      </c>
-      <c r="F390" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$313)=YEAR(TODAY()))*(MONTH(A$2:A$313)=MONTH(TODAY()))*(B$2:B$313=$B$390)*(F$2:F$313),"")</f>
+      <c r="C465" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$465),"")</f>
+        <v/>
+      </c>
+      <c r="D465" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$465),"")</f>
+        <v/>
+      </c>
+      <c r="E465" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$465),"")</f>
+        <v/>
+      </c>
+      <c r="F465" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$465)*(F$2:F$388),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H313"/>
+  <autoFilter ref="A1:H388"/>
   <mergeCells count="1">
-    <mergeCell ref="A315:H315"/>
+    <mergeCell ref="A390:H390"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13046,7 +15596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13999,161 +16549,355 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>131640</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>133550</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>133980</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>131780</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>-1850</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>150860</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>165680</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>161740</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>161700</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>-10940</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>6.7743</v>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="n">
+        <v>6.7681</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>6.759</v>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/22</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D27" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$27),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$27)*(H$2:H$24),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" s="2" t="inlineStr">
+      <c r="D32" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$32)*(H$2:H$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D28" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$28),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$28)*(H$2:H$24),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" s="2" t="inlineStr">
+      <c r="D33" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$33)*(H$2:H$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D29" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$29),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$29)*(H$2:H$24),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" s="2" t="inlineStr">
+      <c r="D34" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$34)*(H$2:H$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>碳酸锂(LC)连续</t>
         </is>
       </c>
-      <c r="D30" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$30),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$30)*(H$2:H$24),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" s="2" t="inlineStr">
+      <c r="D35" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$35)*(H$2:H$29),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D31" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$24,A$2:A$24,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$24,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$24,$C$31),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$24)=YEAR(TODAY()))*(MONTH(A$2:A$24)=MONTH(TODAY()))*(C$2:C$24=$C$31)*(H$2:H$24),"")</f>
+      <c r="D36" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$36)*(H$2:H$29),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J24"/>
+  <autoFilter ref="A1:J29"/>
   <mergeCells count="1">
-    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A31:J31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$388</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$463</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H465"/>
+  <dimension ref="A1:H540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13842,1749 +13842,4299 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C389" s="3" t="n">
+        <v>99950</v>
+      </c>
+      <c r="D389" s="4" t="n">
+        <v>105150</v>
+      </c>
+      <c r="E389" s="4" t="n">
+        <v>102550</v>
+      </c>
+      <c r="F389" s="4" t="n">
+        <v>-450</v>
+      </c>
+      <c r="G389" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H389" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="390">
-      <c r="A390" s="8" t="inlineStr">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C390" s="3" t="n">
+        <v>181800</v>
+      </c>
+      <c r="D390" s="4" t="n">
+        <v>189700</v>
+      </c>
+      <c r="E390" s="4" t="n">
+        <v>185750</v>
+      </c>
+      <c r="F390" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H390" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C391" s="3" t="n">
+        <v>92850</v>
+      </c>
+      <c r="D391" s="4" t="n">
+        <v>97550</v>
+      </c>
+      <c r="E391" s="4" t="n">
+        <v>95200</v>
+      </c>
+      <c r="F391" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="G391" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H391" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C392" s="3" t="n">
+        <v>186400</v>
+      </c>
+      <c r="D392" s="4" t="n">
+        <v>195900</v>
+      </c>
+      <c r="E392" s="4" t="n">
+        <v>191150</v>
+      </c>
+      <c r="F392" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G392" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H392" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C393" s="3" t="n">
+        <v>115000</v>
+      </c>
+      <c r="D393" s="4" t="n">
+        <v>120700</v>
+      </c>
+      <c r="E393" s="4" t="n">
+        <v>117850</v>
+      </c>
+      <c r="F393" s="4" t="n">
+        <v>-600</v>
+      </c>
+      <c r="G393" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C394" s="3" t="n">
+        <v>209500</v>
+      </c>
+      <c r="D394" s="4" t="n">
+        <v>219100</v>
+      </c>
+      <c r="E394" s="4" t="n">
+        <v>214300</v>
+      </c>
+      <c r="F394" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H394" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C395" s="7" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="D395" s="6" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="E395" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="F395" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G395" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H395" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C396" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D396" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E396" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F396" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H396" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C397" s="3" t="n">
+        <v>206300</v>
+      </c>
+      <c r="D397" s="4" t="n">
+        <v>214600</v>
+      </c>
+      <c r="E397" s="4" t="n">
+        <v>210450</v>
+      </c>
+      <c r="F397" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H397" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C398" s="7" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="D398" s="6" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="E398" s="6" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="F398" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H398" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C399" s="7" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="D399" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="E399" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F399" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G399" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H399" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C400" s="7" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="D400" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="E400" s="6" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F400" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G400" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H400" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C401" s="7" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="D401" s="6" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E401" s="6" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="F401" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G401" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H401" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C402" s="7" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="D402" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="E402" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="F402" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G402" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H402" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C403" s="7" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="D403" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="E403" s="6" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="F403" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G403" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H403" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>101338</v>
+      </c>
+      <c r="D404" s="4" t="n">
+        <v>105474</v>
+      </c>
+      <c r="E404" s="4" t="n">
+        <v>103406</v>
+      </c>
+      <c r="F404" s="4" t="n">
+        <v>-128.5</v>
+      </c>
+      <c r="G404" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H404" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C405" s="3" t="n">
+        <v>145750</v>
+      </c>
+      <c r="D405" s="4" t="n">
+        <v>145750</v>
+      </c>
+      <c r="E405" s="4" t="n">
+        <v>145750</v>
+      </c>
+      <c r="F405" s="4" t="n">
+        <v>1506</v>
+      </c>
+      <c r="G405" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H405" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C406" s="3" t="n">
+        <v>7643</v>
+      </c>
+      <c r="D406" s="4" t="n">
+        <v>7643</v>
+      </c>
+      <c r="E406" s="4" t="n">
+        <v>7643</v>
+      </c>
+      <c r="F406" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G406" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H406" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>32877</v>
+      </c>
+      <c r="D407" s="4" t="n">
+        <v>32877</v>
+      </c>
+      <c r="E407" s="4" t="n">
+        <v>32877</v>
+      </c>
+      <c r="F407" s="6" t="n">
+        <v>-61</v>
+      </c>
+      <c r="G407" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H407" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>157432</v>
+      </c>
+      <c r="D408" s="4" t="n">
+        <v>157432</v>
+      </c>
+      <c r="E408" s="4" t="n">
+        <v>157432</v>
+      </c>
+      <c r="F408" s="4" t="n">
+        <v>1639</v>
+      </c>
+      <c r="G408" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H408" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="n">
+        <v>87200</v>
+      </c>
+      <c r="D409" s="4" t="n">
+        <v>87200</v>
+      </c>
+      <c r="E409" s="4" t="n">
+        <v>87200</v>
+      </c>
+      <c r="F409" s="4" t="n">
+        <v>-525</v>
+      </c>
+      <c r="G409" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H409" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="n">
+        <v>7065</v>
+      </c>
+      <c r="D410" s="4" t="n">
+        <v>7065</v>
+      </c>
+      <c r="E410" s="4" t="n">
+        <v>7065</v>
+      </c>
+      <c r="F410" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G410" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H410" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C411" s="3" t="n">
+        <v>6603</v>
+      </c>
+      <c r="D411" s="4" t="n">
+        <v>6603</v>
+      </c>
+      <c r="E411" s="4" t="n">
+        <v>6603</v>
+      </c>
+      <c r="F411" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G411" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H411" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C412" s="7" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="D412" s="6" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="E412" s="6" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="F412" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G412" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H412" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C413" s="7" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="D413" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="E413" s="6" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F413" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G413" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H413" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C414" s="7" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="D414" s="6" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="E414" s="6" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="F414" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G414" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H414" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C415" s="7" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="D415" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="E415" s="6" t="n">
+        <v>76.11</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G415" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H415" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C416" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D416" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E416" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F416" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G416" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H416" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C417" s="3" t="n">
+        <v>108000</v>
+      </c>
+      <c r="D417" s="4" t="n">
+        <v>112000</v>
+      </c>
+      <c r="E417" s="4" t="n">
+        <v>110000</v>
+      </c>
+      <c r="F417" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G417" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H417" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C418" s="3" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D418" s="4" t="n">
+        <v>342000</v>
+      </c>
+      <c r="E418" s="4" t="n">
+        <v>336000</v>
+      </c>
+      <c r="F418" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G418" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H418" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C419" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D419" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E419" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F419" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G419" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H419" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="n">
+        <v>129500</v>
+      </c>
+      <c r="D420" s="4" t="n">
+        <v>135000</v>
+      </c>
+      <c r="E420" s="4" t="n">
+        <v>132250</v>
+      </c>
+      <c r="F420" s="4" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G420" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H420" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C421" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D421" s="4" t="n">
+        <v>159000</v>
+      </c>
+      <c r="E421" s="4" t="n">
+        <v>154500</v>
+      </c>
+      <c r="F421" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G421" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H421" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="D422" s="4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="E422" s="4" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="F422" s="4" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="G422" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H422" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C423" s="3" t="n">
+        <v>2170</v>
+      </c>
+      <c r="D423" s="4" t="n">
+        <v>2330</v>
+      </c>
+      <c r="E423" s="4" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F423" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G423" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H423" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="n">
+        <v>20900</v>
+      </c>
+      <c r="D424" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E424" s="4" t="n">
+        <v>22450</v>
+      </c>
+      <c r="F424" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G424" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H424" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C425" s="3" t="n">
+        <v>24800</v>
+      </c>
+      <c r="D425" s="4" t="n">
+        <v>28750</v>
+      </c>
+      <c r="E425" s="4" t="n">
+        <v>26775</v>
+      </c>
+      <c r="F425" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G425" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H425" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="n">
+        <v>15900</v>
+      </c>
+      <c r="D426" s="4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E426" s="4" t="n">
+        <v>16450</v>
+      </c>
+      <c r="F426" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G426" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H426" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C427" s="3" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D427" s="4" t="n">
+        <v>11500</v>
+      </c>
+      <c r="E427" s="4" t="n">
+        <v>10650</v>
+      </c>
+      <c r="F427" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G427" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H427" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C428" s="3" t="n">
+        <v>17100</v>
+      </c>
+      <c r="D428" s="4" t="n">
+        <v>18200</v>
+      </c>
+      <c r="E428" s="4" t="n">
+        <v>17650</v>
+      </c>
+      <c r="F428" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G428" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H428" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C429" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D429" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E429" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F429" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G429" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H429" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C430" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D430" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E430" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F430" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G430" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H430" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C431" s="3" t="n">
+        <v>302000</v>
+      </c>
+      <c r="D431" s="4" t="n">
+        <v>317000</v>
+      </c>
+      <c r="E431" s="4" t="n">
+        <v>309500</v>
+      </c>
+      <c r="F431" s="4" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="G431" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H431" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C432" s="3" t="n">
+        <v>105500</v>
+      </c>
+      <c r="D432" s="4" t="n">
+        <v>109000</v>
+      </c>
+      <c r="E432" s="4" t="n">
+        <v>107250</v>
+      </c>
+      <c r="F432" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G432" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H432" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C433" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D433" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E433" s="4" t="n">
+        <v>39750</v>
+      </c>
+      <c r="F433" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G433" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H433" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C434" s="3" t="n">
+        <v>2380</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>2450</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>2415</v>
+      </c>
+      <c r="F434" s="6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G434" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H434" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C435" s="3" t="n">
+        <v>2190</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>2340</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>2265</v>
+      </c>
+      <c r="F435" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G435" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H435" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C436" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="D436" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E436" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="F436" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G436" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H436" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C437" s="3" t="n">
+        <v>275000</v>
+      </c>
+      <c r="D437" s="4" t="n">
+        <v>280000</v>
+      </c>
+      <c r="E437" s="4" t="n">
+        <v>277500</v>
+      </c>
+      <c r="F437" s="4" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="G437" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H437" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C438" s="7" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D438" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E438" s="6" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="F438" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H438" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C439" s="7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D439" s="6" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E439" s="6" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="F439" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G439" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H439" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C440" s="3" t="n">
+        <v>143000</v>
+      </c>
+      <c r="D440" s="4" t="n">
+        <v>158500</v>
+      </c>
+      <c r="E440" s="4" t="n">
+        <v>150750</v>
+      </c>
+      <c r="F440" s="4" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G440" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H440" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C441" s="3" t="n">
+        <v>134500</v>
+      </c>
+      <c r="D441" s="4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="E441" s="4" t="n">
+        <v>144750</v>
+      </c>
+      <c r="F441" s="4" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G441" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H441" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C442" s="3" t="n">
+        <v>7570</v>
+      </c>
+      <c r="D442" s="4" t="n">
+        <v>7770</v>
+      </c>
+      <c r="E442" s="4" t="n">
+        <v>7670</v>
+      </c>
+      <c r="F442" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G442" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H442" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C443" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D443" s="4" t="n">
+        <v>33500</v>
+      </c>
+      <c r="E443" s="4" t="n">
+        <v>33250</v>
+      </c>
+      <c r="F443" s="4" t="n">
+        <v>-110</v>
+      </c>
+      <c r="G443" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H443" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C444" s="3" t="n">
+        <v>154000</v>
+      </c>
+      <c r="D444" s="4" t="n">
+        <v>163000</v>
+      </c>
+      <c r="E444" s="4" t="n">
+        <v>158500</v>
+      </c>
+      <c r="F444" s="4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G444" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H444" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C445" s="7" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D445" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E445" s="6" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="F445" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H445" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C446" s="7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D446" s="6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E446" s="6" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F446" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H446" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C447" s="3" t="n">
+        <v>1090000</v>
+      </c>
+      <c r="D447" s="4" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="E447" s="4" t="n">
+        <v>1110000</v>
+      </c>
+      <c r="F447" s="4" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="G447" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H447" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C448" s="3" t="n">
+        <v>370000</v>
+      </c>
+      <c r="D448" s="4" t="n">
+        <v>385000</v>
+      </c>
+      <c r="E448" s="4" t="n">
+        <v>377500</v>
+      </c>
+      <c r="F448" s="4" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="G448" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H448" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C449" s="7" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D449" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E449" s="6" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="F449" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G449" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H449" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C450" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D450" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E450" s="4" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F450" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G450" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H450" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C451" s="3" t="n">
+        <v>86000</v>
+      </c>
+      <c r="D451" s="4" t="n">
+        <v>88800</v>
+      </c>
+      <c r="E451" s="4" t="n">
+        <v>87400</v>
+      </c>
+      <c r="F451" s="4" t="n">
+        <v>-600</v>
+      </c>
+      <c r="G451" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H451" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C452" s="3" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D452" s="4" t="n">
+        <v>218000</v>
+      </c>
+      <c r="E452" s="4" t="n">
+        <v>213000</v>
+      </c>
+      <c r="F452" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H452" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C453" s="3" t="n">
+        <v>57030</v>
+      </c>
+      <c r="D453" s="4" t="n">
+        <v>57630</v>
+      </c>
+      <c r="E453" s="4" t="n">
+        <v>57330</v>
+      </c>
+      <c r="F453" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="G453" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H453" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C454" s="3" t="n">
+        <v>62500</v>
+      </c>
+      <c r="D454" s="4" t="n">
+        <v>67500</v>
+      </c>
+      <c r="E454" s="4" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F454" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="G454" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H454" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C455" s="7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D455" s="6" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E455" s="6" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="F455" s="6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G455" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H455" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C456" s="3" t="n">
+        <v>26783</v>
+      </c>
+      <c r="D456" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="E456" s="4" t="n">
+        <v>26783</v>
+      </c>
+      <c r="F456" s="4" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G456" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H456" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C457" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D457" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E457" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F457" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H457" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C458" s="3" t="n">
+        <v>379000</v>
+      </c>
+      <c r="D458" s="4" t="n">
+        <v>382000</v>
+      </c>
+      <c r="E458" s="4" t="n">
+        <v>380500</v>
+      </c>
+      <c r="F458" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G458" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H458" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C459" s="3" t="n">
+        <v>97800</v>
+      </c>
+      <c r="D459" s="4" t="n">
+        <v>99600</v>
+      </c>
+      <c r="E459" s="4" t="n">
+        <v>98700</v>
+      </c>
+      <c r="F459" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G459" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H459" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C460" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D460" s="4" t="n">
+        <v>92600</v>
+      </c>
+      <c r="E460" s="4" t="n">
+        <v>88300</v>
+      </c>
+      <c r="F460" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="G460" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H460" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C461" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D461" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E461" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F461" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G461" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H461" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C462" s="3" t="n">
+        <v>7436</v>
+      </c>
+      <c r="D462" s="4" t="n">
+        <v>7925</v>
+      </c>
+      <c r="E462" s="4" t="n">
+        <v>7680.5</v>
+      </c>
+      <c r="F462" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="G462" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H462" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C463" s="3" t="n">
+        <v>2398</v>
+      </c>
+      <c r="D463" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="E463" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F463" s="6" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G463" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H463" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B390" s="9" t="n"/>
-      <c r="C390" s="9" t="n"/>
-      <c r="D390" s="9" t="n"/>
-      <c r="E390" s="9" t="n"/>
-      <c r="F390" s="9" t="n"/>
-      <c r="G390" s="9" t="n"/>
-      <c r="H390" s="9" t="n"/>
-    </row>
-    <row r="391">
-      <c r="B391" s="2" t="inlineStr">
+      <c r="B465" s="9" t="n"/>
+      <c r="C465" s="9" t="n"/>
+      <c r="D465" s="9" t="n"/>
+      <c r="E465" s="9" t="n"/>
+      <c r="F465" s="9" t="n"/>
+      <c r="G465" s="9" t="n"/>
+      <c r="H465" s="9" t="n"/>
+    </row>
+    <row r="466">
+      <c r="B466" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C391" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$391),"")</f>
-        <v/>
-      </c>
-      <c r="D391" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$391),"")</f>
-        <v/>
-      </c>
-      <c r="E391" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$391),"")</f>
-        <v/>
-      </c>
-      <c r="F391" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$391)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="392">
-      <c r="B392" s="2" t="inlineStr">
+      <c r="C466" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$466),"")</f>
+        <v/>
+      </c>
+      <c r="D466" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$466),"")</f>
+        <v/>
+      </c>
+      <c r="E466" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$466),"")</f>
+        <v/>
+      </c>
+      <c r="F466" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$466)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C392" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$392),"")</f>
-        <v/>
-      </c>
-      <c r="D392" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$392),"")</f>
-        <v/>
-      </c>
-      <c r="E392" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$392),"")</f>
-        <v/>
-      </c>
-      <c r="F392" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$392)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="393">
-      <c r="B393" s="2" t="inlineStr">
+      <c r="C467" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$467),"")</f>
+        <v/>
+      </c>
+      <c r="D467" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$467),"")</f>
+        <v/>
+      </c>
+      <c r="E467" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$467),"")</f>
+        <v/>
+      </c>
+      <c r="F467" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$467)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C393" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$393),"")</f>
-        <v/>
-      </c>
-      <c r="D393" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$393),"")</f>
-        <v/>
-      </c>
-      <c r="E393" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$393),"")</f>
-        <v/>
-      </c>
-      <c r="F393" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$393)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="394">
-      <c r="B394" s="2" t="inlineStr">
+      <c r="C468" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$468),"")</f>
+        <v/>
+      </c>
+      <c r="D468" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$468),"")</f>
+        <v/>
+      </c>
+      <c r="E468" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$468),"")</f>
+        <v/>
+      </c>
+      <c r="F468" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$468)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C394" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$394),"")</f>
-        <v/>
-      </c>
-      <c r="D394" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$394),"")</f>
-        <v/>
-      </c>
-      <c r="E394" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$394),"")</f>
-        <v/>
-      </c>
-      <c r="F394" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$394)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="395">
-      <c r="B395" s="2" t="inlineStr">
+      <c r="C469" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$469),"")</f>
+        <v/>
+      </c>
+      <c r="D469" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$469),"")</f>
+        <v/>
+      </c>
+      <c r="E469" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$469),"")</f>
+        <v/>
+      </c>
+      <c r="F469" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$469)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C395" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$395),"")</f>
-        <v/>
-      </c>
-      <c r="D395" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$395),"")</f>
-        <v/>
-      </c>
-      <c r="E395" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$395),"")</f>
-        <v/>
-      </c>
-      <c r="F395" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$395)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="396">
-      <c r="B396" s="2" t="inlineStr">
+      <c r="C470" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$470),"")</f>
+        <v/>
+      </c>
+      <c r="D470" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$470),"")</f>
+        <v/>
+      </c>
+      <c r="E470" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$470),"")</f>
+        <v/>
+      </c>
+      <c r="F470" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$470)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C396" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$396),"")</f>
-        <v/>
-      </c>
-      <c r="D396" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$396),"")</f>
-        <v/>
-      </c>
-      <c r="E396" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$396),"")</f>
-        <v/>
-      </c>
-      <c r="F396" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$396)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="397">
-      <c r="B397" s="2" t="inlineStr">
+      <c r="C471" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$471),"")</f>
+        <v/>
+      </c>
+      <c r="D471" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$471),"")</f>
+        <v/>
+      </c>
+      <c r="E471" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$471),"")</f>
+        <v/>
+      </c>
+      <c r="F471" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$471)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C397" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$397),"")</f>
-        <v/>
-      </c>
-      <c r="D397" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$397),"")</f>
-        <v/>
-      </c>
-      <c r="E397" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$397),"")</f>
-        <v/>
-      </c>
-      <c r="F397" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$397)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="398">
-      <c r="B398" s="2" t="inlineStr">
+      <c r="C472" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$472),"")</f>
+        <v/>
+      </c>
+      <c r="D472" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$472),"")</f>
+        <v/>
+      </c>
+      <c r="E472" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$472),"")</f>
+        <v/>
+      </c>
+      <c r="F472" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$472)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C398" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$398),"")</f>
-        <v/>
-      </c>
-      <c r="D398" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$398),"")</f>
-        <v/>
-      </c>
-      <c r="E398" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$398),"")</f>
-        <v/>
-      </c>
-      <c r="F398" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$398)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="399">
-      <c r="B399" s="2" t="inlineStr">
+      <c r="C473" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$473),"")</f>
+        <v/>
+      </c>
+      <c r="D473" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$473),"")</f>
+        <v/>
+      </c>
+      <c r="E473" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$473),"")</f>
+        <v/>
+      </c>
+      <c r="F473" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$473)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C399" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$399),"")</f>
-        <v/>
-      </c>
-      <c r="D399" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$399),"")</f>
-        <v/>
-      </c>
-      <c r="E399" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$399),"")</f>
-        <v/>
-      </c>
-      <c r="F399" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$399)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="400">
-      <c r="B400" s="2" t="inlineStr">
+      <c r="C474" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$474),"")</f>
+        <v/>
+      </c>
+      <c r="D474" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$474),"")</f>
+        <v/>
+      </c>
+      <c r="E474" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$474),"")</f>
+        <v/>
+      </c>
+      <c r="F474" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$474)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C400" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$400),"")</f>
-        <v/>
-      </c>
-      <c r="D400" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$400),"")</f>
-        <v/>
-      </c>
-      <c r="E400" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$400),"")</f>
-        <v/>
-      </c>
-      <c r="F400" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$400)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="401">
-      <c r="B401" s="2" t="inlineStr">
+      <c r="C475" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$475),"")</f>
+        <v/>
+      </c>
+      <c r="D475" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$475),"")</f>
+        <v/>
+      </c>
+      <c r="E475" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$475),"")</f>
+        <v/>
+      </c>
+      <c r="F475" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$475)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C401" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$401),"")</f>
-        <v/>
-      </c>
-      <c r="D401" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$401),"")</f>
-        <v/>
-      </c>
-      <c r="E401" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$401),"")</f>
-        <v/>
-      </c>
-      <c r="F401" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$401)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="402">
-      <c r="B402" s="2" t="inlineStr">
+      <c r="C476" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$476),"")</f>
+        <v/>
+      </c>
+      <c r="D476" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$476),"")</f>
+        <v/>
+      </c>
+      <c r="E476" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$476),"")</f>
+        <v/>
+      </c>
+      <c r="F476" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$476)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C402" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$402),"")</f>
-        <v/>
-      </c>
-      <c r="D402" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$402),"")</f>
-        <v/>
-      </c>
-      <c r="E402" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$402),"")</f>
-        <v/>
-      </c>
-      <c r="F402" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$402)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="403">
-      <c r="B403" s="2" t="inlineStr">
+      <c r="C477" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$477),"")</f>
+        <v/>
+      </c>
+      <c r="D477" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$477),"")</f>
+        <v/>
+      </c>
+      <c r="E477" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$477),"")</f>
+        <v/>
+      </c>
+      <c r="F477" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$477)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C403" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$403),"")</f>
-        <v/>
-      </c>
-      <c r="D403" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$403),"")</f>
-        <v/>
-      </c>
-      <c r="E403" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$403),"")</f>
-        <v/>
-      </c>
-      <c r="F403" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$403)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="404">
-      <c r="B404" s="2" t="inlineStr">
+      <c r="C478" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$478),"")</f>
+        <v/>
+      </c>
+      <c r="D478" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$478),"")</f>
+        <v/>
+      </c>
+      <c r="E478" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$478),"")</f>
+        <v/>
+      </c>
+      <c r="F478" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$478)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C404" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$404),"")</f>
-        <v/>
-      </c>
-      <c r="D404" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$404),"")</f>
-        <v/>
-      </c>
-      <c r="E404" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$404),"")</f>
-        <v/>
-      </c>
-      <c r="F404" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$404)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="405">
-      <c r="B405" s="2" t="inlineStr">
+      <c r="C479" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$479),"")</f>
+        <v/>
+      </c>
+      <c r="D479" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$479),"")</f>
+        <v/>
+      </c>
+      <c r="E479" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$479),"")</f>
+        <v/>
+      </c>
+      <c r="F479" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$479)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C405" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$405),"")</f>
-        <v/>
-      </c>
-      <c r="D405" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$405),"")</f>
-        <v/>
-      </c>
-      <c r="E405" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$405),"")</f>
-        <v/>
-      </c>
-      <c r="F405" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$405)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="406">
-      <c r="B406" s="2" t="inlineStr">
+      <c r="C480" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$480),"")</f>
+        <v/>
+      </c>
+      <c r="D480" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$480),"")</f>
+        <v/>
+      </c>
+      <c r="E480" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$480),"")</f>
+        <v/>
+      </c>
+      <c r="F480" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$480)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C406" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$406),"")</f>
-        <v/>
-      </c>
-      <c r="D406" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$406),"")</f>
-        <v/>
-      </c>
-      <c r="E406" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$406),"")</f>
-        <v/>
-      </c>
-      <c r="F406" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$406)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="407">
-      <c r="B407" s="2" t="inlineStr">
+      <c r="C481" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$481),"")</f>
+        <v/>
+      </c>
+      <c r="D481" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$481),"")</f>
+        <v/>
+      </c>
+      <c r="E481" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$481),"")</f>
+        <v/>
+      </c>
+      <c r="F481" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$481)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C407" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$407),"")</f>
-        <v/>
-      </c>
-      <c r="D407" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$407),"")</f>
-        <v/>
-      </c>
-      <c r="E407" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$407),"")</f>
-        <v/>
-      </c>
-      <c r="F407" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$407)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="408">
-      <c r="B408" s="2" t="inlineStr">
+      <c r="C482" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$482),"")</f>
+        <v/>
+      </c>
+      <c r="D482" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$482),"")</f>
+        <v/>
+      </c>
+      <c r="E482" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$482),"")</f>
+        <v/>
+      </c>
+      <c r="F482" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$482)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C408" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$408),"")</f>
-        <v/>
-      </c>
-      <c r="D408" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$408),"")</f>
-        <v/>
-      </c>
-      <c r="E408" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$408),"")</f>
-        <v/>
-      </c>
-      <c r="F408" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$408)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="409">
-      <c r="B409" s="2" t="inlineStr">
+      <c r="C483" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$483),"")</f>
+        <v/>
+      </c>
+      <c r="D483" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$483),"")</f>
+        <v/>
+      </c>
+      <c r="E483" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$483),"")</f>
+        <v/>
+      </c>
+      <c r="F483" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$483)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C409" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$409),"")</f>
-        <v/>
-      </c>
-      <c r="D409" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$409),"")</f>
-        <v/>
-      </c>
-      <c r="E409" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$409),"")</f>
-        <v/>
-      </c>
-      <c r="F409" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$409)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="410">
-      <c r="B410" s="2" t="inlineStr">
+      <c r="C484" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$484),"")</f>
+        <v/>
+      </c>
+      <c r="D484" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$484),"")</f>
+        <v/>
+      </c>
+      <c r="E484" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$484),"")</f>
+        <v/>
+      </c>
+      <c r="F484" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$484)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C410" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$410),"")</f>
-        <v/>
-      </c>
-      <c r="D410" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$410),"")</f>
-        <v/>
-      </c>
-      <c r="E410" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$410),"")</f>
-        <v/>
-      </c>
-      <c r="F410" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$410)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="411">
-      <c r="B411" s="2" t="inlineStr">
+      <c r="C485" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$485),"")</f>
+        <v/>
+      </c>
+      <c r="D485" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$485),"")</f>
+        <v/>
+      </c>
+      <c r="E485" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$485),"")</f>
+        <v/>
+      </c>
+      <c r="F485" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$485)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C411" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$411),"")</f>
-        <v/>
-      </c>
-      <c r="D411" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$411),"")</f>
-        <v/>
-      </c>
-      <c r="E411" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$411),"")</f>
-        <v/>
-      </c>
-      <c r="F411" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$411)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="412">
-      <c r="B412" s="2" t="inlineStr">
+      <c r="C486" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$486),"")</f>
+        <v/>
+      </c>
+      <c r="D486" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$486),"")</f>
+        <v/>
+      </c>
+      <c r="E486" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$486),"")</f>
+        <v/>
+      </c>
+      <c r="F486" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$486)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C412" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$412),"")</f>
-        <v/>
-      </c>
-      <c r="D412" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$412),"")</f>
-        <v/>
-      </c>
-      <c r="E412" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$412),"")</f>
-        <v/>
-      </c>
-      <c r="F412" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$412)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="413">
-      <c r="B413" s="2" t="inlineStr">
+      <c r="C487" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$487),"")</f>
+        <v/>
+      </c>
+      <c r="D487" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$487),"")</f>
+        <v/>
+      </c>
+      <c r="E487" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$487),"")</f>
+        <v/>
+      </c>
+      <c r="F487" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$487)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C413" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$413),"")</f>
-        <v/>
-      </c>
-      <c r="D413" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$413),"")</f>
-        <v/>
-      </c>
-      <c r="E413" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$413),"")</f>
-        <v/>
-      </c>
-      <c r="F413" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$413)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="414">
-      <c r="B414" s="2" t="inlineStr">
+      <c r="C488" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$488),"")</f>
+        <v/>
+      </c>
+      <c r="D488" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$488),"")</f>
+        <v/>
+      </c>
+      <c r="E488" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$488),"")</f>
+        <v/>
+      </c>
+      <c r="F488" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$488)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C414" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$414),"")</f>
-        <v/>
-      </c>
-      <c r="D414" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$414),"")</f>
-        <v/>
-      </c>
-      <c r="E414" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$414),"")</f>
-        <v/>
-      </c>
-      <c r="F414" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$414)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="415">
-      <c r="B415" s="2" t="inlineStr">
+      <c r="C489" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$489),"")</f>
+        <v/>
+      </c>
+      <c r="D489" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$489),"")</f>
+        <v/>
+      </c>
+      <c r="E489" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$489),"")</f>
+        <v/>
+      </c>
+      <c r="F489" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$489)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C415" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$415),"")</f>
-        <v/>
-      </c>
-      <c r="D415" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$415),"")</f>
-        <v/>
-      </c>
-      <c r="E415" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$415),"")</f>
-        <v/>
-      </c>
-      <c r="F415" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$415)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="416">
-      <c r="B416" s="2" t="inlineStr">
+      <c r="C490" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$490),"")</f>
+        <v/>
+      </c>
+      <c r="D490" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$490),"")</f>
+        <v/>
+      </c>
+      <c r="E490" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$490),"")</f>
+        <v/>
+      </c>
+      <c r="F490" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$490)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C416" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$416),"")</f>
-        <v/>
-      </c>
-      <c r="D416" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$416),"")</f>
-        <v/>
-      </c>
-      <c r="E416" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$416),"")</f>
-        <v/>
-      </c>
-      <c r="F416" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$416)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="417">
-      <c r="B417" s="2" t="inlineStr">
+      <c r="C491" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$491),"")</f>
+        <v/>
+      </c>
+      <c r="D491" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$491),"")</f>
+        <v/>
+      </c>
+      <c r="E491" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$491),"")</f>
+        <v/>
+      </c>
+      <c r="F491" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$491)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C417" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$417),"")</f>
-        <v/>
-      </c>
-      <c r="D417" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$417),"")</f>
-        <v/>
-      </c>
-      <c r="E417" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$417),"")</f>
-        <v/>
-      </c>
-      <c r="F417" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$417)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="418">
-      <c r="B418" s="2" t="inlineStr">
+      <c r="C492" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$492),"")</f>
+        <v/>
+      </c>
+      <c r="D492" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$492),"")</f>
+        <v/>
+      </c>
+      <c r="E492" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$492),"")</f>
+        <v/>
+      </c>
+      <c r="F492" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$492)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C418" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$418),"")</f>
-        <v/>
-      </c>
-      <c r="D418" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$418),"")</f>
-        <v/>
-      </c>
-      <c r="E418" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$418),"")</f>
-        <v/>
-      </c>
-      <c r="F418" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$418)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="419">
-      <c r="B419" s="2" t="inlineStr">
+      <c r="C493" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$493),"")</f>
+        <v/>
+      </c>
+      <c r="D493" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$493),"")</f>
+        <v/>
+      </c>
+      <c r="E493" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$493),"")</f>
+        <v/>
+      </c>
+      <c r="F493" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$493)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C419" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$419),"")</f>
-        <v/>
-      </c>
-      <c r="D419" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$419),"")</f>
-        <v/>
-      </c>
-      <c r="E419" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$419),"")</f>
-        <v/>
-      </c>
-      <c r="F419" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$419)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="420">
-      <c r="B420" s="2" t="inlineStr">
+      <c r="C494" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$494),"")</f>
+        <v/>
+      </c>
+      <c r="D494" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$494),"")</f>
+        <v/>
+      </c>
+      <c r="E494" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$494),"")</f>
+        <v/>
+      </c>
+      <c r="F494" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$494)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C420" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$420),"")</f>
-        <v/>
-      </c>
-      <c r="D420" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$420),"")</f>
-        <v/>
-      </c>
-      <c r="E420" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$420),"")</f>
-        <v/>
-      </c>
-      <c r="F420" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$420)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="421">
-      <c r="B421" s="2" t="inlineStr">
+      <c r="C495" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$495),"")</f>
+        <v/>
+      </c>
+      <c r="D495" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$495),"")</f>
+        <v/>
+      </c>
+      <c r="E495" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$495),"")</f>
+        <v/>
+      </c>
+      <c r="F495" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$495)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C421" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$421),"")</f>
-        <v/>
-      </c>
-      <c r="D421" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$421),"")</f>
-        <v/>
-      </c>
-      <c r="E421" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$421),"")</f>
-        <v/>
-      </c>
-      <c r="F421" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$421)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="422">
-      <c r="B422" s="2" t="inlineStr">
+      <c r="C496" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$496),"")</f>
+        <v/>
+      </c>
+      <c r="D496" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$496),"")</f>
+        <v/>
+      </c>
+      <c r="E496" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$496),"")</f>
+        <v/>
+      </c>
+      <c r="F496" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$496)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C422" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$422),"")</f>
-        <v/>
-      </c>
-      <c r="D422" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$422),"")</f>
-        <v/>
-      </c>
-      <c r="E422" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$422),"")</f>
-        <v/>
-      </c>
-      <c r="F422" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$422)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="423">
-      <c r="B423" s="2" t="inlineStr">
+      <c r="C497" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$497),"")</f>
+        <v/>
+      </c>
+      <c r="D497" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$497),"")</f>
+        <v/>
+      </c>
+      <c r="E497" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$497),"")</f>
+        <v/>
+      </c>
+      <c r="F497" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$497)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C423" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$423),"")</f>
-        <v/>
-      </c>
-      <c r="D423" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$423),"")</f>
-        <v/>
-      </c>
-      <c r="E423" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$423),"")</f>
-        <v/>
-      </c>
-      <c r="F423" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$423)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="424">
-      <c r="B424" s="2" t="inlineStr">
+      <c r="C498" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$498),"")</f>
+        <v/>
+      </c>
+      <c r="D498" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$498),"")</f>
+        <v/>
+      </c>
+      <c r="E498" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$498),"")</f>
+        <v/>
+      </c>
+      <c r="F498" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$498)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C424" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$424),"")</f>
-        <v/>
-      </c>
-      <c r="D424" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$424),"")</f>
-        <v/>
-      </c>
-      <c r="E424" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$424),"")</f>
-        <v/>
-      </c>
-      <c r="F424" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$424)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="425">
-      <c r="B425" s="2" t="inlineStr">
+      <c r="C499" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$499),"")</f>
+        <v/>
+      </c>
+      <c r="D499" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$499),"")</f>
+        <v/>
+      </c>
+      <c r="E499" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$499),"")</f>
+        <v/>
+      </c>
+      <c r="F499" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$499)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C425" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$425),"")</f>
-        <v/>
-      </c>
-      <c r="D425" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$425),"")</f>
-        <v/>
-      </c>
-      <c r="E425" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$425),"")</f>
-        <v/>
-      </c>
-      <c r="F425" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$425)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="426">
-      <c r="B426" s="2" t="inlineStr">
+      <c r="C500" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$500),"")</f>
+        <v/>
+      </c>
+      <c r="D500" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$500),"")</f>
+        <v/>
+      </c>
+      <c r="E500" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$500),"")</f>
+        <v/>
+      </c>
+      <c r="F500" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$500)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C426" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$426),"")</f>
-        <v/>
-      </c>
-      <c r="D426" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$426),"")</f>
-        <v/>
-      </c>
-      <c r="E426" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$426),"")</f>
-        <v/>
-      </c>
-      <c r="F426" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$426)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="427">
-      <c r="B427" s="2" t="inlineStr">
+      <c r="C501" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$501),"")</f>
+        <v/>
+      </c>
+      <c r="D501" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$501),"")</f>
+        <v/>
+      </c>
+      <c r="E501" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$501),"")</f>
+        <v/>
+      </c>
+      <c r="F501" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$501)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C427" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$427),"")</f>
-        <v/>
-      </c>
-      <c r="D427" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$427),"")</f>
-        <v/>
-      </c>
-      <c r="E427" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$427),"")</f>
-        <v/>
-      </c>
-      <c r="F427" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$427)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="428">
-      <c r="B428" s="2" t="inlineStr">
+      <c r="C502" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$502),"")</f>
+        <v/>
+      </c>
+      <c r="D502" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$502),"")</f>
+        <v/>
+      </c>
+      <c r="E502" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$502),"")</f>
+        <v/>
+      </c>
+      <c r="F502" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$502)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C428" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$428),"")</f>
-        <v/>
-      </c>
-      <c r="D428" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$428),"")</f>
-        <v/>
-      </c>
-      <c r="E428" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$428),"")</f>
-        <v/>
-      </c>
-      <c r="F428" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$428)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="429">
-      <c r="B429" s="2" t="inlineStr">
+      <c r="C503" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$503),"")</f>
+        <v/>
+      </c>
+      <c r="D503" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$503),"")</f>
+        <v/>
+      </c>
+      <c r="E503" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$503),"")</f>
+        <v/>
+      </c>
+      <c r="F503" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$503)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C429" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$429),"")</f>
-        <v/>
-      </c>
-      <c r="D429" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$429),"")</f>
-        <v/>
-      </c>
-      <c r="E429" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$429),"")</f>
-        <v/>
-      </c>
-      <c r="F429" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$429)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="430">
-      <c r="B430" s="2" t="inlineStr">
+      <c r="C504" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$504),"")</f>
+        <v/>
+      </c>
+      <c r="D504" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$504),"")</f>
+        <v/>
+      </c>
+      <c r="E504" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$504),"")</f>
+        <v/>
+      </c>
+      <c r="F504" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$504)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C430" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$430),"")</f>
-        <v/>
-      </c>
-      <c r="D430" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$430),"")</f>
-        <v/>
-      </c>
-      <c r="E430" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$430),"")</f>
-        <v/>
-      </c>
-      <c r="F430" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$430)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="431">
-      <c r="B431" s="2" t="inlineStr">
+      <c r="C505" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$505),"")</f>
+        <v/>
+      </c>
+      <c r="D505" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$505),"")</f>
+        <v/>
+      </c>
+      <c r="E505" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$505),"")</f>
+        <v/>
+      </c>
+      <c r="F505" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$505)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C431" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$431),"")</f>
-        <v/>
-      </c>
-      <c r="D431" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$431),"")</f>
-        <v/>
-      </c>
-      <c r="E431" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$431),"")</f>
-        <v/>
-      </c>
-      <c r="F431" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$431)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="432">
-      <c r="B432" s="2" t="inlineStr">
+      <c r="C506" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$506),"")</f>
+        <v/>
+      </c>
+      <c r="D506" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$506),"")</f>
+        <v/>
+      </c>
+      <c r="E506" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$506),"")</f>
+        <v/>
+      </c>
+      <c r="F506" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$506)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C432" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$432),"")</f>
-        <v/>
-      </c>
-      <c r="D432" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$432),"")</f>
-        <v/>
-      </c>
-      <c r="E432" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$432),"")</f>
-        <v/>
-      </c>
-      <c r="F432" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$432)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="433">
-      <c r="B433" s="2" t="inlineStr">
+      <c r="C507" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$507),"")</f>
+        <v/>
+      </c>
+      <c r="D507" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$507),"")</f>
+        <v/>
+      </c>
+      <c r="E507" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$507),"")</f>
+        <v/>
+      </c>
+      <c r="F507" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$507)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C433" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$433),"")</f>
-        <v/>
-      </c>
-      <c r="D433" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$433),"")</f>
-        <v/>
-      </c>
-      <c r="E433" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$433),"")</f>
-        <v/>
-      </c>
-      <c r="F433" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$433)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="434">
-      <c r="B434" s="2" t="inlineStr">
+      <c r="C508" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$508),"")</f>
+        <v/>
+      </c>
+      <c r="D508" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$508),"")</f>
+        <v/>
+      </c>
+      <c r="E508" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$508),"")</f>
+        <v/>
+      </c>
+      <c r="F508" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$508)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C434" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$434),"")</f>
-        <v/>
-      </c>
-      <c r="D434" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$434),"")</f>
-        <v/>
-      </c>
-      <c r="E434" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$434),"")</f>
-        <v/>
-      </c>
-      <c r="F434" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$434)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="435">
-      <c r="B435" s="2" t="inlineStr">
+      <c r="C509" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$509),"")</f>
+        <v/>
+      </c>
+      <c r="D509" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$509),"")</f>
+        <v/>
+      </c>
+      <c r="E509" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$509),"")</f>
+        <v/>
+      </c>
+      <c r="F509" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$509)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C435" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$435),"")</f>
-        <v/>
-      </c>
-      <c r="D435" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$435),"")</f>
-        <v/>
-      </c>
-      <c r="E435" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$435),"")</f>
-        <v/>
-      </c>
-      <c r="F435" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$435)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="436">
-      <c r="B436" s="2" t="inlineStr">
+      <c r="C510" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$510),"")</f>
+        <v/>
+      </c>
+      <c r="D510" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$510),"")</f>
+        <v/>
+      </c>
+      <c r="E510" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$510),"")</f>
+        <v/>
+      </c>
+      <c r="F510" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$510)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C436" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$436),"")</f>
-        <v/>
-      </c>
-      <c r="D436" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$436),"")</f>
-        <v/>
-      </c>
-      <c r="E436" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$436),"")</f>
-        <v/>
-      </c>
-      <c r="F436" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$436)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="437">
-      <c r="B437" s="2" t="inlineStr">
+      <c r="C511" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$511),"")</f>
+        <v/>
+      </c>
+      <c r="D511" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$511),"")</f>
+        <v/>
+      </c>
+      <c r="E511" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$511),"")</f>
+        <v/>
+      </c>
+      <c r="F511" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$511)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C437" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$437),"")</f>
-        <v/>
-      </c>
-      <c r="D437" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$437),"")</f>
-        <v/>
-      </c>
-      <c r="E437" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$437),"")</f>
-        <v/>
-      </c>
-      <c r="F437" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$437)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="438">
-      <c r="B438" s="2" t="inlineStr">
+      <c r="C512" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$512),"")</f>
+        <v/>
+      </c>
+      <c r="D512" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$512),"")</f>
+        <v/>
+      </c>
+      <c r="E512" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$512),"")</f>
+        <v/>
+      </c>
+      <c r="F512" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$512)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C438" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$438),"")</f>
-        <v/>
-      </c>
-      <c r="D438" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$438),"")</f>
-        <v/>
-      </c>
-      <c r="E438" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$438),"")</f>
-        <v/>
-      </c>
-      <c r="F438" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$438)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="439">
-      <c r="B439" s="2" t="inlineStr">
+      <c r="C513" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$513),"")</f>
+        <v/>
+      </c>
+      <c r="D513" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$513),"")</f>
+        <v/>
+      </c>
+      <c r="E513" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$513),"")</f>
+        <v/>
+      </c>
+      <c r="F513" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$513)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C439" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$439),"")</f>
-        <v/>
-      </c>
-      <c r="D439" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$439),"")</f>
-        <v/>
-      </c>
-      <c r="E439" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$439),"")</f>
-        <v/>
-      </c>
-      <c r="F439" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$439)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="440">
-      <c r="B440" s="2" t="inlineStr">
+      <c r="C514" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$514),"")</f>
+        <v/>
+      </c>
+      <c r="D514" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$514),"")</f>
+        <v/>
+      </c>
+      <c r="E514" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$514),"")</f>
+        <v/>
+      </c>
+      <c r="F514" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$514)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C440" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$440),"")</f>
-        <v/>
-      </c>
-      <c r="D440" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$440),"")</f>
-        <v/>
-      </c>
-      <c r="E440" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$440),"")</f>
-        <v/>
-      </c>
-      <c r="F440" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$440)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="441">
-      <c r="B441" s="2" t="inlineStr">
+      <c r="C515" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$515),"")</f>
+        <v/>
+      </c>
+      <c r="D515" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$515),"")</f>
+        <v/>
+      </c>
+      <c r="E515" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$515),"")</f>
+        <v/>
+      </c>
+      <c r="F515" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$515)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C441" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$441),"")</f>
-        <v/>
-      </c>
-      <c r="D441" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$441),"")</f>
-        <v/>
-      </c>
-      <c r="E441" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$441),"")</f>
-        <v/>
-      </c>
-      <c r="F441" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$441)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="442">
-      <c r="B442" s="2" t="inlineStr">
+      <c r="C516" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$516),"")</f>
+        <v/>
+      </c>
+      <c r="D516" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$516),"")</f>
+        <v/>
+      </c>
+      <c r="E516" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$516),"")</f>
+        <v/>
+      </c>
+      <c r="F516" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$516)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C442" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$442),"")</f>
-        <v/>
-      </c>
-      <c r="D442" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$442),"")</f>
-        <v/>
-      </c>
-      <c r="E442" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$442),"")</f>
-        <v/>
-      </c>
-      <c r="F442" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$442)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="443">
-      <c r="B443" s="2" t="inlineStr">
+      <c r="C517" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$517),"")</f>
+        <v/>
+      </c>
+      <c r="D517" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$517),"")</f>
+        <v/>
+      </c>
+      <c r="E517" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$517),"")</f>
+        <v/>
+      </c>
+      <c r="F517" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$517)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C443" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$443),"")</f>
-        <v/>
-      </c>
-      <c r="D443" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$443),"")</f>
-        <v/>
-      </c>
-      <c r="E443" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$443),"")</f>
-        <v/>
-      </c>
-      <c r="F443" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$443)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="444">
-      <c r="B444" s="2" t="inlineStr">
+      <c r="C518" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$518),"")</f>
+        <v/>
+      </c>
+      <c r="D518" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$518),"")</f>
+        <v/>
+      </c>
+      <c r="E518" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$518),"")</f>
+        <v/>
+      </c>
+      <c r="F518" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$518)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C444" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$444),"")</f>
-        <v/>
-      </c>
-      <c r="D444" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$444),"")</f>
-        <v/>
-      </c>
-      <c r="E444" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$444),"")</f>
-        <v/>
-      </c>
-      <c r="F444" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$444)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="445">
-      <c r="B445" s="2" t="inlineStr">
+      <c r="C519" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$519),"")</f>
+        <v/>
+      </c>
+      <c r="D519" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$519),"")</f>
+        <v/>
+      </c>
+      <c r="E519" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$519),"")</f>
+        <v/>
+      </c>
+      <c r="F519" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$519)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C445" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$445),"")</f>
-        <v/>
-      </c>
-      <c r="D445" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$445),"")</f>
-        <v/>
-      </c>
-      <c r="E445" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$445),"")</f>
-        <v/>
-      </c>
-      <c r="F445" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$445)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="446">
-      <c r="B446" s="2" t="inlineStr">
+      <c r="C520" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$520),"")</f>
+        <v/>
+      </c>
+      <c r="D520" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$520),"")</f>
+        <v/>
+      </c>
+      <c r="E520" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$520),"")</f>
+        <v/>
+      </c>
+      <c r="F520" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$520)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C446" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$446),"")</f>
-        <v/>
-      </c>
-      <c r="D446" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$446),"")</f>
-        <v/>
-      </c>
-      <c r="E446" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$446),"")</f>
-        <v/>
-      </c>
-      <c r="F446" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$446)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="447">
-      <c r="B447" s="2" t="inlineStr">
+      <c r="C521" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$521),"")</f>
+        <v/>
+      </c>
+      <c r="D521" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$521),"")</f>
+        <v/>
+      </c>
+      <c r="E521" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$521),"")</f>
+        <v/>
+      </c>
+      <c r="F521" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$521)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C447" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$447),"")</f>
-        <v/>
-      </c>
-      <c r="D447" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$447),"")</f>
-        <v/>
-      </c>
-      <c r="E447" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$447),"")</f>
-        <v/>
-      </c>
-      <c r="F447" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$447)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="448">
-      <c r="B448" s="2" t="inlineStr">
+      <c r="C522" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$522),"")</f>
+        <v/>
+      </c>
+      <c r="D522" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$522),"")</f>
+        <v/>
+      </c>
+      <c r="E522" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$522),"")</f>
+        <v/>
+      </c>
+      <c r="F522" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$522)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C448" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$448),"")</f>
-        <v/>
-      </c>
-      <c r="D448" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$448),"")</f>
-        <v/>
-      </c>
-      <c r="E448" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$448),"")</f>
-        <v/>
-      </c>
-      <c r="F448" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$448)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="449">
-      <c r="B449" s="2" t="inlineStr">
+      <c r="C523" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$523),"")</f>
+        <v/>
+      </c>
+      <c r="D523" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$523),"")</f>
+        <v/>
+      </c>
+      <c r="E523" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$523),"")</f>
+        <v/>
+      </c>
+      <c r="F523" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$523)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C449" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$449),"")</f>
-        <v/>
-      </c>
-      <c r="D449" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$449),"")</f>
-        <v/>
-      </c>
-      <c r="E449" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$449),"")</f>
-        <v/>
-      </c>
-      <c r="F449" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$449)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="450">
-      <c r="B450" s="2" t="inlineStr">
+      <c r="C524" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$524),"")</f>
+        <v/>
+      </c>
+      <c r="D524" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$524),"")</f>
+        <v/>
+      </c>
+      <c r="E524" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$524),"")</f>
+        <v/>
+      </c>
+      <c r="F524" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$524)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C450" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$450),"")</f>
-        <v/>
-      </c>
-      <c r="D450" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$450),"")</f>
-        <v/>
-      </c>
-      <c r="E450" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$450),"")</f>
-        <v/>
-      </c>
-      <c r="F450" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$450)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="451">
-      <c r="B451" s="2" t="inlineStr">
+      <c r="C525" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$525),"")</f>
+        <v/>
+      </c>
+      <c r="D525" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$525),"")</f>
+        <v/>
+      </c>
+      <c r="E525" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$525),"")</f>
+        <v/>
+      </c>
+      <c r="F525" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$525)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C451" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$451),"")</f>
-        <v/>
-      </c>
-      <c r="D451" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$451),"")</f>
-        <v/>
-      </c>
-      <c r="E451" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$451),"")</f>
-        <v/>
-      </c>
-      <c r="F451" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$451)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="452">
-      <c r="B452" s="2" t="inlineStr">
+      <c r="C526" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$526),"")</f>
+        <v/>
+      </c>
+      <c r="D526" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$526),"")</f>
+        <v/>
+      </c>
+      <c r="E526" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$526),"")</f>
+        <v/>
+      </c>
+      <c r="F526" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$526)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C452" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$452),"")</f>
-        <v/>
-      </c>
-      <c r="D452" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$452),"")</f>
-        <v/>
-      </c>
-      <c r="E452" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$452),"")</f>
-        <v/>
-      </c>
-      <c r="F452" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$452)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="453">
-      <c r="B453" s="2" t="inlineStr">
+      <c r="C527" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$527),"")</f>
+        <v/>
+      </c>
+      <c r="D527" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$527),"")</f>
+        <v/>
+      </c>
+      <c r="E527" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$527),"")</f>
+        <v/>
+      </c>
+      <c r="F527" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$527)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C453" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$453),"")</f>
-        <v/>
-      </c>
-      <c r="D453" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$453),"")</f>
-        <v/>
-      </c>
-      <c r="E453" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$453),"")</f>
-        <v/>
-      </c>
-      <c r="F453" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$453)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="454">
-      <c r="B454" s="2" t="inlineStr">
+      <c r="C528" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$528),"")</f>
+        <v/>
+      </c>
+      <c r="D528" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$528),"")</f>
+        <v/>
+      </c>
+      <c r="E528" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$528),"")</f>
+        <v/>
+      </c>
+      <c r="F528" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$528)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C454" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$454),"")</f>
-        <v/>
-      </c>
-      <c r="D454" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$454),"")</f>
-        <v/>
-      </c>
-      <c r="E454" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$454),"")</f>
-        <v/>
-      </c>
-      <c r="F454" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$454)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="455">
-      <c r="B455" s="2" t="inlineStr">
+      <c r="C529" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$529),"")</f>
+        <v/>
+      </c>
+      <c r="D529" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$529),"")</f>
+        <v/>
+      </c>
+      <c r="E529" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$529),"")</f>
+        <v/>
+      </c>
+      <c r="F529" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$529)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C455" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$455),"")</f>
-        <v/>
-      </c>
-      <c r="D455" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$455),"")</f>
-        <v/>
-      </c>
-      <c r="E455" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$455),"")</f>
-        <v/>
-      </c>
-      <c r="F455" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$455)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="456">
-      <c r="B456" s="2" t="inlineStr">
+      <c r="C530" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$530),"")</f>
+        <v/>
+      </c>
+      <c r="D530" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$530),"")</f>
+        <v/>
+      </c>
+      <c r="E530" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$530),"")</f>
+        <v/>
+      </c>
+      <c r="F530" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$530)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C456" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$456),"")</f>
-        <v/>
-      </c>
-      <c r="D456" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$456),"")</f>
-        <v/>
-      </c>
-      <c r="E456" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$456),"")</f>
-        <v/>
-      </c>
-      <c r="F456" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$456)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="457">
-      <c r="B457" s="2" t="inlineStr">
+      <c r="C531" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$531),"")</f>
+        <v/>
+      </c>
+      <c r="D531" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$531),"")</f>
+        <v/>
+      </c>
+      <c r="E531" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$531),"")</f>
+        <v/>
+      </c>
+      <c r="F531" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$531)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C457" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$457),"")</f>
-        <v/>
-      </c>
-      <c r="D457" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$457),"")</f>
-        <v/>
-      </c>
-      <c r="E457" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$457),"")</f>
-        <v/>
-      </c>
-      <c r="F457" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$457)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="458">
-      <c r="B458" s="2" t="inlineStr">
+      <c r="C532" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$532),"")</f>
+        <v/>
+      </c>
+      <c r="D532" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$532),"")</f>
+        <v/>
+      </c>
+      <c r="E532" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$532),"")</f>
+        <v/>
+      </c>
+      <c r="F532" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$532)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C458" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$458),"")</f>
-        <v/>
-      </c>
-      <c r="D458" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$458),"")</f>
-        <v/>
-      </c>
-      <c r="E458" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$458),"")</f>
-        <v/>
-      </c>
-      <c r="F458" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$458)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="459">
-      <c r="B459" s="2" t="inlineStr">
+      <c r="C533" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$533),"")</f>
+        <v/>
+      </c>
+      <c r="D533" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$533),"")</f>
+        <v/>
+      </c>
+      <c r="E533" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$533),"")</f>
+        <v/>
+      </c>
+      <c r="F533" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$533)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C459" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$459),"")</f>
-        <v/>
-      </c>
-      <c r="D459" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$459),"")</f>
-        <v/>
-      </c>
-      <c r="E459" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$459),"")</f>
-        <v/>
-      </c>
-      <c r="F459" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$459)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="460">
-      <c r="B460" s="2" t="inlineStr">
+      <c r="C534" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$534),"")</f>
+        <v/>
+      </c>
+      <c r="D534" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$534),"")</f>
+        <v/>
+      </c>
+      <c r="E534" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$534),"")</f>
+        <v/>
+      </c>
+      <c r="F534" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$534)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C460" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$460),"")</f>
-        <v/>
-      </c>
-      <c r="D460" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$460),"")</f>
-        <v/>
-      </c>
-      <c r="E460" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$460),"")</f>
-        <v/>
-      </c>
-      <c r="F460" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$460)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="461">
-      <c r="B461" s="2" t="inlineStr">
+      <c r="C535" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$535),"")</f>
+        <v/>
+      </c>
+      <c r="D535" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$535),"")</f>
+        <v/>
+      </c>
+      <c r="E535" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$535),"")</f>
+        <v/>
+      </c>
+      <c r="F535" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$535)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C461" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$461),"")</f>
-        <v/>
-      </c>
-      <c r="D461" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$461),"")</f>
-        <v/>
-      </c>
-      <c r="E461" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$461),"")</f>
-        <v/>
-      </c>
-      <c r="F461" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$461)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="462">
-      <c r="B462" s="2" t="inlineStr">
+      <c r="C536" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$536),"")</f>
+        <v/>
+      </c>
+      <c r="D536" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$536),"")</f>
+        <v/>
+      </c>
+      <c r="E536" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$536),"")</f>
+        <v/>
+      </c>
+      <c r="F536" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$536)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C462" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$462),"")</f>
-        <v/>
-      </c>
-      <c r="D462" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$462),"")</f>
-        <v/>
-      </c>
-      <c r="E462" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$462),"")</f>
-        <v/>
-      </c>
-      <c r="F462" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$462)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="463">
-      <c r="B463" s="2" t="inlineStr">
+      <c r="C537" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$537),"")</f>
+        <v/>
+      </c>
+      <c r="D537" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$537),"")</f>
+        <v/>
+      </c>
+      <c r="E537" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$537),"")</f>
+        <v/>
+      </c>
+      <c r="F537" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$537)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C463" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$463),"")</f>
-        <v/>
-      </c>
-      <c r="D463" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$463),"")</f>
-        <v/>
-      </c>
-      <c r="E463" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$463),"")</f>
-        <v/>
-      </c>
-      <c r="F463" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$463)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="464">
-      <c r="B464" s="2" t="inlineStr">
+      <c r="C538" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$538),"")</f>
+        <v/>
+      </c>
+      <c r="D538" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$538),"")</f>
+        <v/>
+      </c>
+      <c r="E538" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$538),"")</f>
+        <v/>
+      </c>
+      <c r="F538" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$538)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C464" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$464),"")</f>
-        <v/>
-      </c>
-      <c r="D464" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$464),"")</f>
-        <v/>
-      </c>
-      <c r="E464" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$464),"")</f>
-        <v/>
-      </c>
-      <c r="F464" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$464)*(F$2:F$388),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="465">
-      <c r="B465" s="2" t="inlineStr">
+      <c r="C539" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$539),"")</f>
+        <v/>
+      </c>
+      <c r="D539" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$539),"")</f>
+        <v/>
+      </c>
+      <c r="E539" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$539),"")</f>
+        <v/>
+      </c>
+      <c r="F539" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$539)*(F$2:F$463),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C465" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$465),"")</f>
-        <v/>
-      </c>
-      <c r="D465" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$465),"")</f>
-        <v/>
-      </c>
-      <c r="E465" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$388,A$2:A$388,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$388,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$388,$B$465),"")</f>
-        <v/>
-      </c>
-      <c r="F465" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$388)=YEAR(TODAY()))*(MONTH(A$2:A$388)=MONTH(TODAY()))*(B$2:B$388=$B$465)*(F$2:F$388),"")</f>
+      <c r="C540" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$540),"")</f>
+        <v/>
+      </c>
+      <c r="D540" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$540),"")</f>
+        <v/>
+      </c>
+      <c r="E540" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$540),"")</f>
+        <v/>
+      </c>
+      <c r="F540" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$540)*(F$2:F$463),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H388"/>
+  <autoFilter ref="A1:H463"/>
   <mergeCells count="1">
-    <mergeCell ref="A390:H390"/>
+    <mergeCell ref="A465:H465"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15596,7 +18146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16743,161 +19293,355 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>132570</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>134980</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>133100</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>131020</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>460</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>156240</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>156580</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>158100</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>154600</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>6.7886</v>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>6.7844</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>6.7757</v>
+      </c>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>21.42</v>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/24</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D32" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$32),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$32)*(H$2:H$29),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="2" t="inlineStr">
+      <c r="D37" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$37)*(H$2:H$34),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D33" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$33),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$33)*(H$2:H$29),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" s="2" t="inlineStr">
+      <c r="D38" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$38)*(H$2:H$34),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D34" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$34),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$34)*(H$2:H$29),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" s="2" t="inlineStr">
+      <c r="D39" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$39)*(H$2:H$34),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>碳酸锂(LC)连续</t>
         </is>
       </c>
-      <c r="D35" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$35),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$35)*(H$2:H$29),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" s="2" t="inlineStr">
+      <c r="D40" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$40)*(H$2:H$34),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D36" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$29,A$2:A$29,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$29,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$29,$C$36),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$29)=YEAR(TODAY()))*(MONTH(A$2:A$29)=MONTH(TODAY()))*(C$2:C$29=$C$36)*(H$2:H$29),"")</f>
+      <c r="D41" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$41)*(H$2:H$34),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J34"/>
   <mergeCells count="1">
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A36:J36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -13854,16 +13854,16 @@
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>99950</v>
+        <v>99350</v>
       </c>
       <c r="D389" s="4" t="n">
-        <v>105150</v>
+        <v>104450</v>
       </c>
       <c r="E389" s="4" t="n">
-        <v>102550</v>
+        <v>101900</v>
       </c>
       <c r="F389" s="4" t="n">
-        <v>-450</v>
+        <v>-650</v>
       </c>
       <c r="G389" s="5" t="inlineStr">
         <is>
@@ -13891,13 +13891,13 @@
         <v>181800</v>
       </c>
       <c r="D390" s="4" t="n">
-        <v>189700</v>
+        <v>188900</v>
       </c>
       <c r="E390" s="4" t="n">
-        <v>185750</v>
+        <v>185350</v>
       </c>
       <c r="F390" s="4" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="G390" s="5" t="inlineStr">
         <is>
@@ -13922,16 +13922,16 @@
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>92850</v>
+        <v>92200</v>
       </c>
       <c r="D391" s="4" t="n">
-        <v>97550</v>
+        <v>96900</v>
       </c>
       <c r="E391" s="4" t="n">
-        <v>95200</v>
+        <v>94550</v>
       </c>
       <c r="F391" s="4" t="n">
-        <v>-400</v>
+        <v>-650</v>
       </c>
       <c r="G391" s="5" t="inlineStr">
         <is>
@@ -13956,16 +13956,16 @@
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>186400</v>
+        <v>185600</v>
       </c>
       <c r="D392" s="4" t="n">
-        <v>195900</v>
+        <v>195100</v>
       </c>
       <c r="E392" s="4" t="n">
-        <v>191150</v>
+        <v>190350</v>
       </c>
       <c r="F392" s="4" t="n">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G392" s="5" t="inlineStr">
         <is>
@@ -13990,16 +13990,16 @@
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>115000</v>
+        <v>114100</v>
       </c>
       <c r="D393" s="4" t="n">
-        <v>120700</v>
+        <v>119800</v>
       </c>
       <c r="E393" s="4" t="n">
-        <v>117850</v>
+        <v>116950</v>
       </c>
       <c r="F393" s="4" t="n">
-        <v>-600</v>
+        <v>-900</v>
       </c>
       <c r="G393" s="5" t="inlineStr">
         <is>
@@ -14024,16 +14024,16 @@
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>209500</v>
+        <v>208600</v>
       </c>
       <c r="D394" s="4" t="n">
-        <v>219100</v>
+        <v>218200</v>
       </c>
       <c r="E394" s="4" t="n">
-        <v>214300</v>
+        <v>213400</v>
       </c>
       <c r="F394" s="4" t="n">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="G394" s="5" t="inlineStr">
         <is>
@@ -14058,16 +14058,16 @@
         </is>
       </c>
       <c r="C395" s="7" t="n">
-        <v>85.5</v>
+        <v>83.5</v>
       </c>
       <c r="D395" s="6" t="n">
-        <v>86.5</v>
+        <v>84.5</v>
       </c>
       <c r="E395" s="6" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F395" s="6" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="G395" s="5" t="inlineStr">
         <is>
@@ -14126,16 +14126,16 @@
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>206300</v>
+        <v>205400</v>
       </c>
       <c r="D397" s="4" t="n">
-        <v>214600</v>
+        <v>213700</v>
       </c>
       <c r="E397" s="4" t="n">
-        <v>210450</v>
+        <v>209550</v>
       </c>
       <c r="F397" s="4" t="n">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="G397" s="5" t="inlineStr">
         <is>
@@ -14160,16 +14160,16 @@
         </is>
       </c>
       <c r="C398" s="7" t="n">
-        <v>78.70999999999999</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="D398" s="6" t="n">
-        <v>78.70999999999999</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E398" s="6" t="n">
-        <v>78.70999999999999</v>
-      </c>
-      <c r="F398" s="4" t="n">
-        <v>0</v>
+        <v>78.34999999999999</v>
+      </c>
+      <c r="F398" s="6" t="n">
+        <v>-0.36</v>
       </c>
       <c r="G398" s="5" t="inlineStr">
         <is>
@@ -14194,16 +14194,16 @@
         </is>
       </c>
       <c r="C399" s="7" t="n">
-        <v>78.72</v>
+        <v>78.36</v>
       </c>
       <c r="D399" s="6" t="n">
-        <v>78.72</v>
+        <v>78.36</v>
       </c>
       <c r="E399" s="6" t="n">
-        <v>78.72</v>
-      </c>
-      <c r="F399" s="4" t="n">
-        <v>0</v>
+        <v>78.36</v>
+      </c>
+      <c r="F399" s="6" t="n">
+        <v>-0.36</v>
       </c>
       <c r="G399" s="5" t="inlineStr">
         <is>
@@ -14228,16 +14228,16 @@
         </is>
       </c>
       <c r="C400" s="7" t="n">
-        <v>78.72</v>
+        <v>78.36</v>
       </c>
       <c r="D400" s="6" t="n">
-        <v>78.72</v>
+        <v>78.36</v>
       </c>
       <c r="E400" s="6" t="n">
-        <v>78.72</v>
-      </c>
-      <c r="F400" s="4" t="n">
-        <v>0</v>
+        <v>78.36</v>
+      </c>
+      <c r="F400" s="6" t="n">
+        <v>-0.36</v>
       </c>
       <c r="G400" s="5" t="inlineStr">
         <is>
@@ -14262,16 +14262,16 @@
         </is>
       </c>
       <c r="C401" s="7" t="n">
-        <v>75.2</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="D401" s="6" t="n">
-        <v>75.2</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E401" s="6" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="F401" s="4" t="n">
-        <v>0</v>
+        <v>74.84999999999999</v>
+      </c>
+      <c r="F401" s="6" t="n">
+        <v>-0.35</v>
       </c>
       <c r="G401" s="5" t="inlineStr">
         <is>
@@ -14296,16 +14296,16 @@
         </is>
       </c>
       <c r="C402" s="7" t="n">
-        <v>75.22</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="D402" s="6" t="n">
-        <v>75.22</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E402" s="6" t="n">
-        <v>75.22</v>
-      </c>
-      <c r="F402" s="4" t="n">
-        <v>0</v>
+        <v>74.84999999999999</v>
+      </c>
+      <c r="F402" s="6" t="n">
+        <v>-0.37</v>
       </c>
       <c r="G402" s="5" t="inlineStr">
         <is>
@@ -14330,16 +14330,16 @@
         </is>
       </c>
       <c r="C403" s="7" t="n">
-        <v>75.22</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="D403" s="6" t="n">
-        <v>75.22</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E403" s="6" t="n">
-        <v>75.22</v>
-      </c>
-      <c r="F403" s="4" t="n">
-        <v>0</v>
+        <v>74.84999999999999</v>
+      </c>
+      <c r="F403" s="6" t="n">
+        <v>-0.37</v>
       </c>
       <c r="G403" s="5" t="inlineStr">
         <is>
@@ -14364,16 +14364,16 @@
         </is>
       </c>
       <c r="C404" s="3" t="n">
-        <v>101338</v>
+        <v>100926</v>
       </c>
       <c r="D404" s="4" t="n">
-        <v>105474</v>
+        <v>105045</v>
       </c>
       <c r="E404" s="4" t="n">
-        <v>103406</v>
+        <v>102985.5</v>
       </c>
       <c r="F404" s="4" t="n">
-        <v>-128.5</v>
+        <v>-420.5</v>
       </c>
       <c r="G404" s="5" t="inlineStr">
         <is>
@@ -14398,16 +14398,16 @@
         </is>
       </c>
       <c r="C405" s="3" t="n">
-        <v>145750</v>
+        <v>144252</v>
       </c>
       <c r="D405" s="4" t="n">
-        <v>145750</v>
+        <v>144252</v>
       </c>
       <c r="E405" s="4" t="n">
-        <v>145750</v>
+        <v>144252</v>
       </c>
       <c r="F405" s="4" t="n">
-        <v>1506</v>
+        <v>-1498</v>
       </c>
       <c r="G405" s="5" t="inlineStr">
         <is>
@@ -14432,16 +14432,16 @@
         </is>
       </c>
       <c r="C406" s="3" t="n">
-        <v>7643</v>
+        <v>7647</v>
       </c>
       <c r="D406" s="4" t="n">
-        <v>7643</v>
+        <v>7647</v>
       </c>
       <c r="E406" s="4" t="n">
-        <v>7643</v>
-      </c>
-      <c r="F406" s="4" t="n">
-        <v>0</v>
+        <v>7647</v>
+      </c>
+      <c r="F406" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="G406" s="5" t="inlineStr">
         <is>
@@ -14466,16 +14466,16 @@
         </is>
       </c>
       <c r="C407" s="3" t="n">
-        <v>32877</v>
+        <v>32797</v>
       </c>
       <c r="D407" s="4" t="n">
-        <v>32877</v>
+        <v>32797</v>
       </c>
       <c r="E407" s="4" t="n">
-        <v>32877</v>
+        <v>32797</v>
       </c>
       <c r="F407" s="6" t="n">
-        <v>-61</v>
+        <v>-80</v>
       </c>
       <c r="G407" s="5" t="inlineStr">
         <is>
@@ -14500,16 +14500,16 @@
         </is>
       </c>
       <c r="C408" s="3" t="n">
-        <v>157432</v>
+        <v>156870</v>
       </c>
       <c r="D408" s="4" t="n">
-        <v>157432</v>
+        <v>156870</v>
       </c>
       <c r="E408" s="4" t="n">
-        <v>157432</v>
+        <v>156870</v>
       </c>
       <c r="F408" s="4" t="n">
-        <v>1639</v>
+        <v>-562</v>
       </c>
       <c r="G408" s="5" t="inlineStr">
         <is>
@@ -14534,16 +14534,16 @@
         </is>
       </c>
       <c r="C409" s="3" t="n">
-        <v>87200</v>
+        <v>87011</v>
       </c>
       <c r="D409" s="4" t="n">
-        <v>87200</v>
+        <v>87011</v>
       </c>
       <c r="E409" s="4" t="n">
-        <v>87200</v>
+        <v>87011</v>
       </c>
       <c r="F409" s="4" t="n">
-        <v>-525</v>
+        <v>-189</v>
       </c>
       <c r="G409" s="5" t="inlineStr">
         <is>
@@ -14568,16 +14568,16 @@
         </is>
       </c>
       <c r="C410" s="3" t="n">
-        <v>7065</v>
+        <v>7048</v>
       </c>
       <c r="D410" s="4" t="n">
-        <v>7065</v>
+        <v>7048</v>
       </c>
       <c r="E410" s="4" t="n">
-        <v>7065</v>
+        <v>7048</v>
       </c>
       <c r="F410" s="6" t="n">
-        <v>-3</v>
+        <v>-17</v>
       </c>
       <c r="G410" s="5" t="inlineStr">
         <is>
@@ -14602,16 +14602,16 @@
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>6603</v>
+        <v>6596</v>
       </c>
       <c r="D411" s="4" t="n">
-        <v>6603</v>
+        <v>6596</v>
       </c>
       <c r="E411" s="4" t="n">
-        <v>6603</v>
+        <v>6596</v>
       </c>
       <c r="F411" s="6" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G411" s="5" t="inlineStr">
         <is>
@@ -14670,16 +14670,16 @@
         </is>
       </c>
       <c r="C413" s="7" t="n">
-        <v>76.5</v>
+        <v>76.23</v>
       </c>
       <c r="D413" s="6" t="n">
-        <v>76.5</v>
+        <v>76.23</v>
       </c>
       <c r="E413" s="6" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="F413" s="4" t="n">
-        <v>0</v>
+        <v>76.23</v>
+      </c>
+      <c r="F413" s="6" t="n">
+        <v>-0.27</v>
       </c>
       <c r="G413" s="5" t="inlineStr">
         <is>
@@ -14738,16 +14738,16 @@
         </is>
       </c>
       <c r="C415" s="7" t="n">
-        <v>76.11</v>
+        <v>75.92</v>
       </c>
       <c r="D415" s="6" t="n">
-        <v>76.11</v>
+        <v>75.92</v>
       </c>
       <c r="E415" s="6" t="n">
-        <v>76.11</v>
-      </c>
-      <c r="F415" s="4" t="n">
-        <v>0</v>
+        <v>75.92</v>
+      </c>
+      <c r="F415" s="6" t="n">
+        <v>-0.19</v>
       </c>
       <c r="G415" s="5" t="inlineStr">
         <is>
@@ -14806,16 +14806,16 @@
         </is>
       </c>
       <c r="C417" s="3" t="n">
+        <v>106000</v>
+      </c>
+      <c r="D417" s="4" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E417" s="4" t="n">
         <v>108000</v>
       </c>
-      <c r="D417" s="4" t="n">
-        <v>112000</v>
-      </c>
-      <c r="E417" s="4" t="n">
-        <v>110000</v>
-      </c>
       <c r="F417" s="4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="G417" s="5" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>336000</v>
       </c>
       <c r="F418" s="4" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="G418" s="5" t="inlineStr">
         <is>
@@ -14908,16 +14908,16 @@
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>129500</v>
+        <v>128500</v>
       </c>
       <c r="D420" s="4" t="n">
-        <v>135000</v>
+        <v>134500</v>
       </c>
       <c r="E420" s="4" t="n">
-        <v>132250</v>
+        <v>131500</v>
       </c>
       <c r="F420" s="4" t="n">
-        <v>1250</v>
+        <v>-750</v>
       </c>
       <c r="G420" s="5" t="inlineStr">
         <is>
@@ -14945,13 +14945,13 @@
         <v>150000</v>
       </c>
       <c r="D421" s="4" t="n">
-        <v>159000</v>
+        <v>157000</v>
       </c>
       <c r="E421" s="4" t="n">
-        <v>154500</v>
+        <v>153500</v>
       </c>
       <c r="F421" s="4" t="n">
-        <v>1500</v>
+        <v>-1000</v>
       </c>
       <c r="G421" s="5" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>1080000</v>
       </c>
       <c r="F422" s="4" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G422" s="5" t="inlineStr">
         <is>
@@ -15010,16 +15010,16 @@
         </is>
       </c>
       <c r="C423" s="3" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="D423" s="4" t="n">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="E423" s="4" t="n">
         <v>2250</v>
       </c>
-      <c r="F423" s="6" t="n">
-        <v>5</v>
+      <c r="F423" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G423" s="5" t="inlineStr">
         <is>
@@ -15044,16 +15044,16 @@
         </is>
       </c>
       <c r="C424" s="3" t="n">
-        <v>20900</v>
+        <v>20700</v>
       </c>
       <c r="D424" s="4" t="n">
-        <v>24000</v>
+        <v>23750</v>
       </c>
       <c r="E424" s="4" t="n">
-        <v>22450</v>
+        <v>22225</v>
       </c>
       <c r="F424" s="4" t="n">
-        <v>0</v>
+        <v>-225</v>
       </c>
       <c r="G424" s="5" t="inlineStr">
         <is>
@@ -15078,16 +15078,16 @@
         </is>
       </c>
       <c r="C425" s="3" t="n">
-        <v>24800</v>
+        <v>24600</v>
       </c>
       <c r="D425" s="4" t="n">
-        <v>28750</v>
+        <v>28650</v>
       </c>
       <c r="E425" s="4" t="n">
-        <v>26775</v>
+        <v>26625</v>
       </c>
       <c r="F425" s="4" t="n">
-        <v>0</v>
+        <v>-150</v>
       </c>
       <c r="G425" s="5" t="inlineStr">
         <is>
@@ -15112,16 +15112,16 @@
         </is>
       </c>
       <c r="C426" s="3" t="n">
-        <v>15900</v>
+        <v>15700</v>
       </c>
       <c r="D426" s="4" t="n">
         <v>17000</v>
       </c>
       <c r="E426" s="4" t="n">
-        <v>16450</v>
+        <v>16350</v>
       </c>
       <c r="F426" s="4" t="n">
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="G426" s="5" t="inlineStr">
         <is>
@@ -15149,10 +15149,10 @@
         <v>9800</v>
       </c>
       <c r="D427" s="4" t="n">
-        <v>11500</v>
+        <v>11300</v>
       </c>
       <c r="E427" s="4" t="n">
-        <v>10650</v>
+        <v>10550</v>
       </c>
       <c r="F427" s="4" t="n">
         <v>-100</v>
@@ -15180,16 +15180,16 @@
         </is>
       </c>
       <c r="C428" s="3" t="n">
-        <v>17100</v>
+        <v>17000</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>18200</v>
+        <v>18100</v>
       </c>
       <c r="E428" s="4" t="n">
-        <v>17650</v>
+        <v>17550</v>
       </c>
       <c r="F428" s="4" t="n">
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="G428" s="5" t="inlineStr">
         <is>
@@ -15285,13 +15285,13 @@
         <v>302000</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>317000</v>
+        <v>315000</v>
       </c>
       <c r="E431" s="4" t="n">
-        <v>309500</v>
+        <v>308500</v>
       </c>
       <c r="F431" s="4" t="n">
-        <v>-3000</v>
+        <v>-1000</v>
       </c>
       <c r="G431" s="5" t="inlineStr">
         <is>
@@ -15316,16 +15316,16 @@
         </is>
       </c>
       <c r="C432" s="3" t="n">
-        <v>105500</v>
+        <v>105300</v>
       </c>
       <c r="D432" s="4" t="n">
         <v>109000</v>
       </c>
       <c r="E432" s="4" t="n">
-        <v>107250</v>
+        <v>107150</v>
       </c>
       <c r="F432" s="4" t="n">
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="G432" s="5" t="inlineStr">
         <is>
@@ -15418,16 +15418,16 @@
         </is>
       </c>
       <c r="C435" s="3" t="n">
-        <v>2190</v>
+        <v>2200</v>
       </c>
       <c r="D435" s="4" t="n">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="E435" s="4" t="n">
         <v>2265</v>
       </c>
-      <c r="F435" s="6" t="n">
-        <v>5</v>
+      <c r="F435" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G435" s="5" t="inlineStr">
         <is>
@@ -15460,8 +15460,8 @@
       <c r="E436" s="4" t="n">
         <v>260</v>
       </c>
-      <c r="F436" s="6" t="n">
-        <v>-3</v>
+      <c r="F436" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="G436" s="5" t="inlineStr">
         <is>
@@ -15486,16 +15486,16 @@
         </is>
       </c>
       <c r="C437" s="3" t="n">
-        <v>275000</v>
+        <v>272000</v>
       </c>
       <c r="D437" s="4" t="n">
         <v>280000</v>
       </c>
       <c r="E437" s="4" t="n">
-        <v>277500</v>
+        <v>276000</v>
       </c>
       <c r="F437" s="4" t="n">
-        <v>-2500</v>
+        <v>-1500</v>
       </c>
       <c r="G437" s="5" t="inlineStr">
         <is>
@@ -15588,16 +15588,16 @@
         </is>
       </c>
       <c r="C440" s="3" t="n">
-        <v>143000</v>
+        <v>142000</v>
       </c>
       <c r="D440" s="4" t="n">
-        <v>158500</v>
+        <v>158000</v>
       </c>
       <c r="E440" s="4" t="n">
-        <v>150750</v>
+        <v>150000</v>
       </c>
       <c r="F440" s="4" t="n">
-        <v>1250</v>
+        <v>-750</v>
       </c>
       <c r="G440" s="5" t="inlineStr">
         <is>
@@ -15622,16 +15622,16 @@
         </is>
       </c>
       <c r="C441" s="3" t="n">
-        <v>134500</v>
+        <v>134000</v>
       </c>
       <c r="D441" s="4" t="n">
-        <v>155000</v>
+        <v>154000</v>
       </c>
       <c r="E441" s="4" t="n">
-        <v>144750</v>
+        <v>144000</v>
       </c>
       <c r="F441" s="4" t="n">
-        <v>1250</v>
+        <v>-750</v>
       </c>
       <c r="G441" s="5" t="inlineStr">
         <is>
@@ -15690,16 +15690,16 @@
         </is>
       </c>
       <c r="C443" s="3" t="n">
+        <v>32600</v>
+      </c>
+      <c r="D443" s="4" t="n">
         <v>33000</v>
       </c>
-      <c r="D443" s="4" t="n">
-        <v>33500</v>
-      </c>
       <c r="E443" s="4" t="n">
-        <v>33250</v>
+        <v>32800</v>
       </c>
       <c r="F443" s="4" t="n">
-        <v>-110</v>
+        <v>-450</v>
       </c>
       <c r="G443" s="5" t="inlineStr">
         <is>
@@ -15727,13 +15727,13 @@
         <v>154000</v>
       </c>
       <c r="D444" s="4" t="n">
-        <v>163000</v>
+        <v>161000</v>
       </c>
       <c r="E444" s="4" t="n">
-        <v>158500</v>
+        <v>157500</v>
       </c>
       <c r="F444" s="4" t="n">
-        <v>1500</v>
+        <v>-1000</v>
       </c>
       <c r="G444" s="5" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>1110000</v>
       </c>
       <c r="F447" s="4" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G447" s="5" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>377500</v>
       </c>
       <c r="F448" s="4" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="G448" s="5" t="inlineStr">
         <is>
@@ -15965,13 +15965,13 @@
         <v>86000</v>
       </c>
       <c r="D451" s="4" t="n">
-        <v>88800</v>
+        <v>88500</v>
       </c>
       <c r="E451" s="4" t="n">
-        <v>87400</v>
+        <v>87250</v>
       </c>
       <c r="F451" s="4" t="n">
-        <v>-600</v>
+        <v>-150</v>
       </c>
       <c r="G451" s="5" t="inlineStr">
         <is>
@@ -16030,16 +16030,16 @@
         </is>
       </c>
       <c r="C453" s="3" t="n">
-        <v>57030</v>
+        <v>56790</v>
       </c>
       <c r="D453" s="4" t="n">
-        <v>57630</v>
+        <v>57390</v>
       </c>
       <c r="E453" s="4" t="n">
-        <v>57330</v>
+        <v>57090</v>
       </c>
       <c r="F453" s="4" t="n">
-        <v>360</v>
+        <v>-240</v>
       </c>
       <c r="G453" s="5" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>65000</v>
       </c>
       <c r="F454" s="4" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G454" s="5" t="inlineStr">
         <is>
@@ -16098,13 +16098,13 @@
         </is>
       </c>
       <c r="C455" s="7" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="D455" s="6" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="E455" s="6" t="n">
-        <v>24.75</v>
+        <v>24.5</v>
       </c>
       <c r="F455" s="6" t="n">
         <v>-0.25</v>
@@ -16132,16 +16132,16 @@
         </is>
       </c>
       <c r="C456" s="3" t="n">
-        <v>26783</v>
+        <v>26122</v>
       </c>
       <c r="D456" s="4" t="n">
-        <v>26783</v>
+        <v>26122</v>
       </c>
       <c r="E456" s="4" t="n">
-        <v>26783</v>
+        <v>26122</v>
       </c>
       <c r="F456" s="4" t="n">
-        <v>1046</v>
+        <v>-661</v>
       </c>
       <c r="G456" s="5" t="inlineStr">
         <is>
@@ -16200,16 +16200,16 @@
         </is>
       </c>
       <c r="C458" s="3" t="n">
+        <v>376000</v>
+      </c>
+      <c r="D458" s="4" t="n">
         <v>379000</v>
       </c>
-      <c r="D458" s="4" t="n">
-        <v>382000</v>
-      </c>
       <c r="E458" s="4" t="n">
-        <v>380500</v>
+        <v>377500</v>
       </c>
       <c r="F458" s="4" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="G458" s="5" t="inlineStr">
         <is>
@@ -16234,16 +16234,16 @@
         </is>
       </c>
       <c r="C459" s="3" t="n">
-        <v>97800</v>
+        <v>97500</v>
       </c>
       <c r="D459" s="4" t="n">
-        <v>99600</v>
+        <v>99500</v>
       </c>
       <c r="E459" s="4" t="n">
-        <v>98700</v>
+        <v>98500</v>
       </c>
       <c r="F459" s="4" t="n">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="G459" s="5" t="inlineStr">
         <is>
@@ -16268,16 +16268,16 @@
         </is>
       </c>
       <c r="C460" s="3" t="n">
-        <v>84000</v>
+        <v>84200</v>
       </c>
       <c r="D460" s="4" t="n">
-        <v>92600</v>
+        <v>92000</v>
       </c>
       <c r="E460" s="4" t="n">
-        <v>88300</v>
+        <v>88100</v>
       </c>
       <c r="F460" s="4" t="n">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="G460" s="5" t="inlineStr">
         <is>
@@ -16336,16 +16336,16 @@
         </is>
       </c>
       <c r="C462" s="3" t="n">
-        <v>7436</v>
+        <v>7419</v>
       </c>
       <c r="D462" s="4" t="n">
-        <v>7925</v>
+        <v>7799</v>
       </c>
       <c r="E462" s="4" t="n">
-        <v>7680.5</v>
+        <v>7609</v>
       </c>
       <c r="F462" s="6" t="n">
-        <v>77</v>
+        <v>-71.5</v>
       </c>
       <c r="G462" s="5" t="inlineStr">
         <is>
@@ -19310,19 +19310,19 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>132570</v>
+        <v>130690</v>
       </c>
       <c r="E30" s="4" t="n">
         <v>134980</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>133100</v>
+        <v>130700</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>131020</v>
+        <v>130670</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>460</v>
+        <v>-1420</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
@@ -19352,19 +19352,19 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>156240</v>
+        <v>162740</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>156580</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>158100</v>
+        <v>162740</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>154600</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>240</v>
+        <v>6740</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>6.7886</v>
+        <v>6.8008</v>
       </c>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="6" t="n">
@@ -19432,13 +19432,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>21.42</v>
+        <v>21.1</v>
       </c>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="6" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -19394,7 +19394,7 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>6.8008</v>
+        <v>6.8004</v>
       </c>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="6" t="n">

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$463</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$538</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H540"/>
+  <dimension ref="A1:H615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16392,1749 +16392,4299 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C464" s="3" t="n">
+        <v>98700</v>
+      </c>
+      <c r="D464" s="4" t="n">
+        <v>103800</v>
+      </c>
+      <c r="E464" s="4" t="n">
+        <v>101250</v>
+      </c>
+      <c r="F464" s="4" t="n">
+        <v>-650</v>
+      </c>
+      <c r="G464" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H464" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="465">
-      <c r="A465" s="8" t="inlineStr">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C465" s="3" t="n">
+        <v>181400</v>
+      </c>
+      <c r="D465" s="4" t="n">
+        <v>188500</v>
+      </c>
+      <c r="E465" s="4" t="n">
+        <v>184950</v>
+      </c>
+      <c r="F465" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="G465" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H465" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C466" s="3" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D466" s="4" t="n">
+        <v>96250</v>
+      </c>
+      <c r="E466" s="4" t="n">
+        <v>93900</v>
+      </c>
+      <c r="F466" s="4" t="n">
+        <v>-650</v>
+      </c>
+      <c r="G466" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H466" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C467" s="3" t="n">
+        <v>184900</v>
+      </c>
+      <c r="D467" s="4" t="n">
+        <v>194400</v>
+      </c>
+      <c r="E467" s="4" t="n">
+        <v>189650</v>
+      </c>
+      <c r="F467" s="4" t="n">
+        <v>-700</v>
+      </c>
+      <c r="G467" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H467" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C468" s="3" t="n">
+        <v>113200</v>
+      </c>
+      <c r="D468" s="4" t="n">
+        <v>118900</v>
+      </c>
+      <c r="E468" s="4" t="n">
+        <v>116050</v>
+      </c>
+      <c r="F468" s="4" t="n">
+        <v>-900</v>
+      </c>
+      <c r="G468" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H468" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C469" s="3" t="n">
+        <v>207800</v>
+      </c>
+      <c r="D469" s="4" t="n">
+        <v>217400</v>
+      </c>
+      <c r="E469" s="4" t="n">
+        <v>212600</v>
+      </c>
+      <c r="F469" s="4" t="n">
+        <v>-800</v>
+      </c>
+      <c r="G469" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H469" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C470" s="7" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D470" s="6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E470" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="F470" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G470" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H470" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C471" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D471" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E471" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F471" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G471" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H471" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C472" s="3" t="n">
+        <v>205000</v>
+      </c>
+      <c r="D472" s="4" t="n">
+        <v>213500</v>
+      </c>
+      <c r="E472" s="4" t="n">
+        <v>209250</v>
+      </c>
+      <c r="F472" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G472" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H472" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C473" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D473" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E473" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F473" s="6" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G473" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H473" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C474" s="7" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="D474" s="6" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="E474" s="6" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="F474" s="6" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G474" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H474" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C475" s="7" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="D475" s="6" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="E475" s="6" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="F475" s="6" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G475" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H475" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C476" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D476" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E476" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F476" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G476" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H476" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C477" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D477" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E477" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F477" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G477" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H477" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C478" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D478" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E478" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F478" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G478" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H478" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C479" s="3" t="n">
+        <v>100740</v>
+      </c>
+      <c r="D479" s="4" t="n">
+        <v>104852</v>
+      </c>
+      <c r="E479" s="4" t="n">
+        <v>102796</v>
+      </c>
+      <c r="F479" s="4" t="n">
+        <v>-189.5</v>
+      </c>
+      <c r="G479" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H479" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C480" s="3" t="n">
+        <v>143670</v>
+      </c>
+      <c r="D480" s="4" t="n">
+        <v>143670</v>
+      </c>
+      <c r="E480" s="4" t="n">
+        <v>143670</v>
+      </c>
+      <c r="F480" s="4" t="n">
+        <v>-582</v>
+      </c>
+      <c r="G480" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H480" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C481" s="3" t="n">
+        <v>7654</v>
+      </c>
+      <c r="D481" s="4" t="n">
+        <v>7654</v>
+      </c>
+      <c r="E481" s="4" t="n">
+        <v>7654</v>
+      </c>
+      <c r="F481" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G481" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H481" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C482" s="3" t="n">
+        <v>32642</v>
+      </c>
+      <c r="D482" s="4" t="n">
+        <v>32642</v>
+      </c>
+      <c r="E482" s="4" t="n">
+        <v>32642</v>
+      </c>
+      <c r="F482" s="4" t="n">
+        <v>-155</v>
+      </c>
+      <c r="G482" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H482" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C483" s="3" t="n">
+        <v>156755</v>
+      </c>
+      <c r="D483" s="4" t="n">
+        <v>156755</v>
+      </c>
+      <c r="E483" s="4" t="n">
+        <v>156755</v>
+      </c>
+      <c r="F483" s="4" t="n">
+        <v>-115</v>
+      </c>
+      <c r="G483" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H483" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C484" s="3" t="n">
+        <v>86510</v>
+      </c>
+      <c r="D484" s="4" t="n">
+        <v>86510</v>
+      </c>
+      <c r="E484" s="4" t="n">
+        <v>86510</v>
+      </c>
+      <c r="F484" s="4" t="n">
+        <v>-501</v>
+      </c>
+      <c r="G484" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H484" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C485" s="3" t="n">
+        <v>7039</v>
+      </c>
+      <c r="D485" s="4" t="n">
+        <v>7039</v>
+      </c>
+      <c r="E485" s="4" t="n">
+        <v>7039</v>
+      </c>
+      <c r="F485" s="6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="G485" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H485" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C486" s="3" t="n">
+        <v>6595</v>
+      </c>
+      <c r="D486" s="4" t="n">
+        <v>6595</v>
+      </c>
+      <c r="E486" s="4" t="n">
+        <v>6595</v>
+      </c>
+      <c r="F486" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G486" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H486" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C487" s="7" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="D487" s="6" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="E487" s="6" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="F487" s="6" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="G487" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H487" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C488" s="7" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="D488" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="E488" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="F488" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G488" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H488" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C489" s="7" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="D489" s="6" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="E489" s="6" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="F489" s="6" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="G489" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H489" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C490" s="7" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="D490" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="E490" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="F490" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G490" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H490" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C491" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D491" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E491" s="6" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="F491" s="6" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="G491" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H491" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C492" s="3" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D492" s="4" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E492" s="4" t="n">
+        <v>107500</v>
+      </c>
+      <c r="F492" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G492" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H492" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C493" s="3" t="n">
+        <v>330000</v>
+      </c>
+      <c r="D493" s="4" t="n">
+        <v>342000</v>
+      </c>
+      <c r="E493" s="4" t="n">
+        <v>336000</v>
+      </c>
+      <c r="F493" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G493" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H493" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C494" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D494" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E494" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F494" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G494" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H494" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B495" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C495" s="3" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D495" s="4" t="n">
+        <v>134000</v>
+      </c>
+      <c r="E495" s="4" t="n">
+        <v>131000</v>
+      </c>
+      <c r="F495" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G495" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H495" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B496" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C496" s="3" t="n">
+        <v>149000</v>
+      </c>
+      <c r="D496" s="4" t="n">
+        <v>157000</v>
+      </c>
+      <c r="E496" s="4" t="n">
+        <v>153000</v>
+      </c>
+      <c r="F496" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G496" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H496" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C497" s="3" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="D497" s="4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="E497" s="4" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="F497" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G497" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H497" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B498" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C498" s="3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="D498" s="4" t="n">
+        <v>2320</v>
+      </c>
+      <c r="E498" s="4" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F498" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G498" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H498" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B499" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C499" s="3" t="n">
+        <v>20600</v>
+      </c>
+      <c r="D499" s="4" t="n">
+        <v>23750</v>
+      </c>
+      <c r="E499" s="4" t="n">
+        <v>22175</v>
+      </c>
+      <c r="F499" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G499" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H499" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B500" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C500" s="3" t="n">
+        <v>24400</v>
+      </c>
+      <c r="D500" s="4" t="n">
+        <v>28650</v>
+      </c>
+      <c r="E500" s="4" t="n">
+        <v>26525</v>
+      </c>
+      <c r="F500" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G500" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H500" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B501" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C501" s="3" t="n">
+        <v>15500</v>
+      </c>
+      <c r="D501" s="4" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E501" s="4" t="n">
+        <v>16250</v>
+      </c>
+      <c r="F501" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G501" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H501" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B502" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C502" s="3" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D502" s="4" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E502" s="4" t="n">
+        <v>10400</v>
+      </c>
+      <c r="F502" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G502" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H502" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B503" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C503" s="3" t="n">
+        <v>16800</v>
+      </c>
+      <c r="D503" s="4" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E503" s="4" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F503" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G503" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H503" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B504" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C504" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D504" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E504" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F504" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G504" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H504" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C505" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D505" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E505" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F505" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H505" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C506" s="3" t="n">
+        <v>302000</v>
+      </c>
+      <c r="D506" s="4" t="n">
+        <v>315000</v>
+      </c>
+      <c r="E506" s="4" t="n">
+        <v>308500</v>
+      </c>
+      <c r="F506" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G506" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H506" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C507" s="3" t="n">
+        <v>104500</v>
+      </c>
+      <c r="D507" s="4" t="n">
+        <v>108000</v>
+      </c>
+      <c r="E507" s="4" t="n">
+        <v>106250</v>
+      </c>
+      <c r="F507" s="4" t="n">
+        <v>-900</v>
+      </c>
+      <c r="G507" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H507" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D508" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E508" s="4" t="n">
+        <v>39750</v>
+      </c>
+      <c r="F508" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H508" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B509" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C509" s="3" t="n">
+        <v>2380</v>
+      </c>
+      <c r="D509" s="4" t="n">
+        <v>2450</v>
+      </c>
+      <c r="E509" s="4" t="n">
+        <v>2415</v>
+      </c>
+      <c r="F509" s="6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="G509" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H509" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B510" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C510" s="3" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D510" s="4" t="n">
+        <v>2330</v>
+      </c>
+      <c r="E510" s="4" t="n">
+        <v>2265</v>
+      </c>
+      <c r="F510" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H510" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B511" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C511" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="D511" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E511" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="F511" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G511" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H511" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B512" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C512" s="3" t="n">
+        <v>270000</v>
+      </c>
+      <c r="D512" s="4" t="n">
+        <v>280000</v>
+      </c>
+      <c r="E512" s="4" t="n">
+        <v>275000</v>
+      </c>
+      <c r="F512" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G512" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H512" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C513" s="7" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D513" s="6" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E513" s="6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F513" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G513" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H513" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C514" s="7" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="D514" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E514" s="6" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="F514" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G514" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H514" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C515" s="3" t="n">
+        <v>141500</v>
+      </c>
+      <c r="D515" s="4" t="n">
+        <v>157500</v>
+      </c>
+      <c r="E515" s="4" t="n">
+        <v>149500</v>
+      </c>
+      <c r="F515" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G515" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H515" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C516" s="3" t="n">
+        <v>133500</v>
+      </c>
+      <c r="D516" s="4" t="n">
+        <v>153500</v>
+      </c>
+      <c r="E516" s="4" t="n">
+        <v>143500</v>
+      </c>
+      <c r="F516" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G516" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H516" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C517" s="3" t="n">
+        <v>7570</v>
+      </c>
+      <c r="D517" s="4" t="n">
+        <v>7770</v>
+      </c>
+      <c r="E517" s="4" t="n">
+        <v>7670</v>
+      </c>
+      <c r="F517" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G517" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H517" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C518" s="3" t="n">
+        <v>32300</v>
+      </c>
+      <c r="D518" s="4" t="n">
+        <v>32700</v>
+      </c>
+      <c r="E518" s="4" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F518" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G518" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H518" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C519" s="3" t="n">
+        <v>153000</v>
+      </c>
+      <c r="D519" s="4" t="n">
+        <v>161000</v>
+      </c>
+      <c r="E519" s="4" t="n">
+        <v>157000</v>
+      </c>
+      <c r="F519" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G519" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H519" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C520" s="7" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="D520" s="6" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E520" s="6" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F520" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G520" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H520" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B521" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C521" s="7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D521" s="6" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E521" s="6" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="F521" s="6" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G521" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H521" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B522" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C522" s="3" t="n">
+        <v>1090000</v>
+      </c>
+      <c r="D522" s="4" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="E522" s="4" t="n">
+        <v>1110000</v>
+      </c>
+      <c r="F522" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G522" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H522" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B523" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C523" s="3" t="n">
+        <v>369000</v>
+      </c>
+      <c r="D523" s="4" t="n">
+        <v>385000</v>
+      </c>
+      <c r="E523" s="4" t="n">
+        <v>377000</v>
+      </c>
+      <c r="F523" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G523" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H523" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B524" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C524" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D524" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E524" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F524" s="6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G524" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H524" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C525" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D525" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E525" s="4" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F525" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H525" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C526" s="3" t="n">
+        <v>85500</v>
+      </c>
+      <c r="D526" s="4" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E526" s="4" t="n">
+        <v>86750</v>
+      </c>
+      <c r="F526" s="4" t="n">
+        <v>-500</v>
+      </c>
+      <c r="G526" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H526" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B527" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C527" s="3" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D527" s="4" t="n">
+        <v>215000</v>
+      </c>
+      <c r="E527" s="4" t="n">
+        <v>211500</v>
+      </c>
+      <c r="F527" s="4" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="G527" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H527" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C528" s="3" t="n">
+        <v>56670</v>
+      </c>
+      <c r="D528" s="4" t="n">
+        <v>57270</v>
+      </c>
+      <c r="E528" s="4" t="n">
+        <v>56970</v>
+      </c>
+      <c r="F528" s="4" t="n">
+        <v>-120</v>
+      </c>
+      <c r="G528" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H528" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C529" s="3" t="n">
+        <v>62500</v>
+      </c>
+      <c r="D529" s="4" t="n">
+        <v>67500</v>
+      </c>
+      <c r="E529" s="4" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F529" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G529" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H529" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C530" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D530" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E530" s="6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F530" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G530" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H530" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B531" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C531" s="3" t="n">
+        <v>26122</v>
+      </c>
+      <c r="D531" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="E531" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="F531" s="4" t="n">
+        <v>-661</v>
+      </c>
+      <c r="G531" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H531" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B532" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C532" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D532" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E532" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F532" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G532" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H532" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B533" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C533" s="3" t="n">
+        <v>373000</v>
+      </c>
+      <c r="D533" s="4" t="n">
+        <v>376000</v>
+      </c>
+      <c r="E533" s="4" t="n">
+        <v>374500</v>
+      </c>
+      <c r="F533" s="4" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="G533" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H533" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B534" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C534" s="3" t="n">
+        <v>97000</v>
+      </c>
+      <c r="D534" s="4" t="n">
+        <v>99400</v>
+      </c>
+      <c r="E534" s="4" t="n">
+        <v>98200</v>
+      </c>
+      <c r="F534" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G534" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H534" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B535" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C535" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D535" s="4" t="n">
+        <v>91500</v>
+      </c>
+      <c r="E535" s="4" t="n">
+        <v>87750</v>
+      </c>
+      <c r="F535" s="4" t="n">
+        <v>-350</v>
+      </c>
+      <c r="G535" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H535" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B536" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C536" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D536" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E536" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F536" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G536" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H536" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B537" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C537" s="3" t="n">
+        <v>7347</v>
+      </c>
+      <c r="D537" s="4" t="n">
+        <v>7779</v>
+      </c>
+      <c r="E537" s="4" t="n">
+        <v>7563</v>
+      </c>
+      <c r="F537" s="6" t="n">
+        <v>-46</v>
+      </c>
+      <c r="G537" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H537" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B538" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C538" s="3" t="n">
+        <v>2398</v>
+      </c>
+      <c r="D538" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="E538" s="4" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F538" s="6" t="n">
+        <v>-72</v>
+      </c>
+      <c r="G538" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H538" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B465" s="9" t="n"/>
-      <c r="C465" s="9" t="n"/>
-      <c r="D465" s="9" t="n"/>
-      <c r="E465" s="9" t="n"/>
-      <c r="F465" s="9" t="n"/>
-      <c r="G465" s="9" t="n"/>
-      <c r="H465" s="9" t="n"/>
-    </row>
-    <row r="466">
-      <c r="B466" s="2" t="inlineStr">
+      <c r="B540" s="9" t="n"/>
+      <c r="C540" s="9" t="n"/>
+      <c r="D540" s="9" t="n"/>
+      <c r="E540" s="9" t="n"/>
+      <c r="F540" s="9" t="n"/>
+      <c r="G540" s="9" t="n"/>
+      <c r="H540" s="9" t="n"/>
+    </row>
+    <row r="541">
+      <c r="B541" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C466" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$466),"")</f>
-        <v/>
-      </c>
-      <c r="D466" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$466),"")</f>
-        <v/>
-      </c>
-      <c r="E466" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$466),"")</f>
-        <v/>
-      </c>
-      <c r="F466" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$466)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="467">
-      <c r="B467" s="2" t="inlineStr">
+      <c r="C541" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$541),"")</f>
+        <v/>
+      </c>
+      <c r="D541" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$541),"")</f>
+        <v/>
+      </c>
+      <c r="E541" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$541),"")</f>
+        <v/>
+      </c>
+      <c r="F541" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$541)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C467" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$467),"")</f>
-        <v/>
-      </c>
-      <c r="D467" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$467),"")</f>
-        <v/>
-      </c>
-      <c r="E467" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$467),"")</f>
-        <v/>
-      </c>
-      <c r="F467" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$467)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="468">
-      <c r="B468" s="2" t="inlineStr">
+      <c r="C542" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$542),"")</f>
+        <v/>
+      </c>
+      <c r="D542" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$542),"")</f>
+        <v/>
+      </c>
+      <c r="E542" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$542),"")</f>
+        <v/>
+      </c>
+      <c r="F542" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$542)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C468" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$468),"")</f>
-        <v/>
-      </c>
-      <c r="D468" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$468),"")</f>
-        <v/>
-      </c>
-      <c r="E468" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$468),"")</f>
-        <v/>
-      </c>
-      <c r="F468" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$468)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="469">
-      <c r="B469" s="2" t="inlineStr">
+      <c r="C543" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$543),"")</f>
+        <v/>
+      </c>
+      <c r="D543" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$543),"")</f>
+        <v/>
+      </c>
+      <c r="E543" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$543),"")</f>
+        <v/>
+      </c>
+      <c r="F543" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$543)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C469" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$469),"")</f>
-        <v/>
-      </c>
-      <c r="D469" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$469),"")</f>
-        <v/>
-      </c>
-      <c r="E469" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$469),"")</f>
-        <v/>
-      </c>
-      <c r="F469" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$469)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="470">
-      <c r="B470" s="2" t="inlineStr">
+      <c r="C544" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$544),"")</f>
+        <v/>
+      </c>
+      <c r="D544" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$544),"")</f>
+        <v/>
+      </c>
+      <c r="E544" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$544),"")</f>
+        <v/>
+      </c>
+      <c r="F544" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$544)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C470" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$470),"")</f>
-        <v/>
-      </c>
-      <c r="D470" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$470),"")</f>
-        <v/>
-      </c>
-      <c r="E470" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$470),"")</f>
-        <v/>
-      </c>
-      <c r="F470" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$470)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="471">
-      <c r="B471" s="2" t="inlineStr">
+      <c r="C545" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$545),"")</f>
+        <v/>
+      </c>
+      <c r="D545" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$545),"")</f>
+        <v/>
+      </c>
+      <c r="E545" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$545),"")</f>
+        <v/>
+      </c>
+      <c r="F545" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$545)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C471" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$471),"")</f>
-        <v/>
-      </c>
-      <c r="D471" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$471),"")</f>
-        <v/>
-      </c>
-      <c r="E471" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$471),"")</f>
-        <v/>
-      </c>
-      <c r="F471" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$471)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="472">
-      <c r="B472" s="2" t="inlineStr">
+      <c r="C546" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$546),"")</f>
+        <v/>
+      </c>
+      <c r="D546" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$546),"")</f>
+        <v/>
+      </c>
+      <c r="E546" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$546),"")</f>
+        <v/>
+      </c>
+      <c r="F546" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$546)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C472" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$472),"")</f>
-        <v/>
-      </c>
-      <c r="D472" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$472),"")</f>
-        <v/>
-      </c>
-      <c r="E472" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$472),"")</f>
-        <v/>
-      </c>
-      <c r="F472" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$472)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="473">
-      <c r="B473" s="2" t="inlineStr">
+      <c r="C547" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$547),"")</f>
+        <v/>
+      </c>
+      <c r="D547" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$547),"")</f>
+        <v/>
+      </c>
+      <c r="E547" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$547),"")</f>
+        <v/>
+      </c>
+      <c r="F547" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$547)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C473" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$473),"")</f>
-        <v/>
-      </c>
-      <c r="D473" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$473),"")</f>
-        <v/>
-      </c>
-      <c r="E473" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$473),"")</f>
-        <v/>
-      </c>
-      <c r="F473" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$473)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="474">
-      <c r="B474" s="2" t="inlineStr">
+      <c r="C548" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$548),"")</f>
+        <v/>
+      </c>
+      <c r="D548" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$548),"")</f>
+        <v/>
+      </c>
+      <c r="E548" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$548),"")</f>
+        <v/>
+      </c>
+      <c r="F548" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$548)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C474" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$474),"")</f>
-        <v/>
-      </c>
-      <c r="D474" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$474),"")</f>
-        <v/>
-      </c>
-      <c r="E474" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$474),"")</f>
-        <v/>
-      </c>
-      <c r="F474" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$474)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="475">
-      <c r="B475" s="2" t="inlineStr">
+      <c r="C549" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$549),"")</f>
+        <v/>
+      </c>
+      <c r="D549" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$549),"")</f>
+        <v/>
+      </c>
+      <c r="E549" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$549),"")</f>
+        <v/>
+      </c>
+      <c r="F549" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$549)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C475" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$475),"")</f>
-        <v/>
-      </c>
-      <c r="D475" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$475),"")</f>
-        <v/>
-      </c>
-      <c r="E475" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$475),"")</f>
-        <v/>
-      </c>
-      <c r="F475" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$475)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="476">
-      <c r="B476" s="2" t="inlineStr">
+      <c r="C550" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$550),"")</f>
+        <v/>
+      </c>
+      <c r="D550" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$550),"")</f>
+        <v/>
+      </c>
+      <c r="E550" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$550),"")</f>
+        <v/>
+      </c>
+      <c r="F550" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$550)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C476" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$476),"")</f>
-        <v/>
-      </c>
-      <c r="D476" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$476),"")</f>
-        <v/>
-      </c>
-      <c r="E476" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$476),"")</f>
-        <v/>
-      </c>
-      <c r="F476" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$476)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="477">
-      <c r="B477" s="2" t="inlineStr">
+      <c r="C551" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$551),"")</f>
+        <v/>
+      </c>
+      <c r="D551" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$551),"")</f>
+        <v/>
+      </c>
+      <c r="E551" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$551),"")</f>
+        <v/>
+      </c>
+      <c r="F551" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$551)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C477" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$477),"")</f>
-        <v/>
-      </c>
-      <c r="D477" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$477),"")</f>
-        <v/>
-      </c>
-      <c r="E477" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$477),"")</f>
-        <v/>
-      </c>
-      <c r="F477" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$477)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="478">
-      <c r="B478" s="2" t="inlineStr">
+      <c r="C552" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$552),"")</f>
+        <v/>
+      </c>
+      <c r="D552" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$552),"")</f>
+        <v/>
+      </c>
+      <c r="E552" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$552),"")</f>
+        <v/>
+      </c>
+      <c r="F552" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$552)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C478" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$478),"")</f>
-        <v/>
-      </c>
-      <c r="D478" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$478),"")</f>
-        <v/>
-      </c>
-      <c r="E478" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$478),"")</f>
-        <v/>
-      </c>
-      <c r="F478" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$478)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="479">
-      <c r="B479" s="2" t="inlineStr">
+      <c r="C553" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$553),"")</f>
+        <v/>
+      </c>
+      <c r="D553" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$553),"")</f>
+        <v/>
+      </c>
+      <c r="E553" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$553),"")</f>
+        <v/>
+      </c>
+      <c r="F553" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$553)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C479" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$479),"")</f>
-        <v/>
-      </c>
-      <c r="D479" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$479),"")</f>
-        <v/>
-      </c>
-      <c r="E479" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$479),"")</f>
-        <v/>
-      </c>
-      <c r="F479" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$479)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="480">
-      <c r="B480" s="2" t="inlineStr">
+      <c r="C554" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$554),"")</f>
+        <v/>
+      </c>
+      <c r="D554" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$554),"")</f>
+        <v/>
+      </c>
+      <c r="E554" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$554),"")</f>
+        <v/>
+      </c>
+      <c r="F554" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$554)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C480" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$480),"")</f>
-        <v/>
-      </c>
-      <c r="D480" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$480),"")</f>
-        <v/>
-      </c>
-      <c r="E480" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$480),"")</f>
-        <v/>
-      </c>
-      <c r="F480" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$480)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="481">
-      <c r="B481" s="2" t="inlineStr">
+      <c r="C555" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$555),"")</f>
+        <v/>
+      </c>
+      <c r="D555" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$555),"")</f>
+        <v/>
+      </c>
+      <c r="E555" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$555),"")</f>
+        <v/>
+      </c>
+      <c r="F555" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$555)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C481" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$481),"")</f>
-        <v/>
-      </c>
-      <c r="D481" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$481),"")</f>
-        <v/>
-      </c>
-      <c r="E481" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$481),"")</f>
-        <v/>
-      </c>
-      <c r="F481" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$481)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="482">
-      <c r="B482" s="2" t="inlineStr">
+      <c r="C556" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$556),"")</f>
+        <v/>
+      </c>
+      <c r="D556" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$556),"")</f>
+        <v/>
+      </c>
+      <c r="E556" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$556),"")</f>
+        <v/>
+      </c>
+      <c r="F556" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$556)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C482" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$482),"")</f>
-        <v/>
-      </c>
-      <c r="D482" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$482),"")</f>
-        <v/>
-      </c>
-      <c r="E482" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$482),"")</f>
-        <v/>
-      </c>
-      <c r="F482" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$482)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="483">
-      <c r="B483" s="2" t="inlineStr">
+      <c r="C557" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$557),"")</f>
+        <v/>
+      </c>
+      <c r="D557" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$557),"")</f>
+        <v/>
+      </c>
+      <c r="E557" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$557),"")</f>
+        <v/>
+      </c>
+      <c r="F557" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$557)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C483" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$483),"")</f>
-        <v/>
-      </c>
-      <c r="D483" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$483),"")</f>
-        <v/>
-      </c>
-      <c r="E483" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$483),"")</f>
-        <v/>
-      </c>
-      <c r="F483" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$483)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="484">
-      <c r="B484" s="2" t="inlineStr">
+      <c r="C558" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$558),"")</f>
+        <v/>
+      </c>
+      <c r="D558" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$558),"")</f>
+        <v/>
+      </c>
+      <c r="E558" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$558),"")</f>
+        <v/>
+      </c>
+      <c r="F558" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$558)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C484" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$484),"")</f>
-        <v/>
-      </c>
-      <c r="D484" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$484),"")</f>
-        <v/>
-      </c>
-      <c r="E484" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$484),"")</f>
-        <v/>
-      </c>
-      <c r="F484" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$484)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="485">
-      <c r="B485" s="2" t="inlineStr">
+      <c r="C559" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$559),"")</f>
+        <v/>
+      </c>
+      <c r="D559" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$559),"")</f>
+        <v/>
+      </c>
+      <c r="E559" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$559),"")</f>
+        <v/>
+      </c>
+      <c r="F559" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$559)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C485" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$485),"")</f>
-        <v/>
-      </c>
-      <c r="D485" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$485),"")</f>
-        <v/>
-      </c>
-      <c r="E485" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$485),"")</f>
-        <v/>
-      </c>
-      <c r="F485" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$485)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="486">
-      <c r="B486" s="2" t="inlineStr">
+      <c r="C560" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$560),"")</f>
+        <v/>
+      </c>
+      <c r="D560" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$560),"")</f>
+        <v/>
+      </c>
+      <c r="E560" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$560),"")</f>
+        <v/>
+      </c>
+      <c r="F560" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$560)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C486" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$486),"")</f>
-        <v/>
-      </c>
-      <c r="D486" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$486),"")</f>
-        <v/>
-      </c>
-      <c r="E486" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$486),"")</f>
-        <v/>
-      </c>
-      <c r="F486" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$486)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="487">
-      <c r="B487" s="2" t="inlineStr">
+      <c r="C561" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$561),"")</f>
+        <v/>
+      </c>
+      <c r="D561" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$561),"")</f>
+        <v/>
+      </c>
+      <c r="E561" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$561),"")</f>
+        <v/>
+      </c>
+      <c r="F561" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$561)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C487" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$487),"")</f>
-        <v/>
-      </c>
-      <c r="D487" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$487),"")</f>
-        <v/>
-      </c>
-      <c r="E487" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$487),"")</f>
-        <v/>
-      </c>
-      <c r="F487" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$487)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="488">
-      <c r="B488" s="2" t="inlineStr">
+      <c r="C562" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$562),"")</f>
+        <v/>
+      </c>
+      <c r="D562" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$562),"")</f>
+        <v/>
+      </c>
+      <c r="E562" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$562),"")</f>
+        <v/>
+      </c>
+      <c r="F562" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$562)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C488" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$488),"")</f>
-        <v/>
-      </c>
-      <c r="D488" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$488),"")</f>
-        <v/>
-      </c>
-      <c r="E488" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$488),"")</f>
-        <v/>
-      </c>
-      <c r="F488" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$488)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="489">
-      <c r="B489" s="2" t="inlineStr">
+      <c r="C563" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$563),"")</f>
+        <v/>
+      </c>
+      <c r="D563" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$563),"")</f>
+        <v/>
+      </c>
+      <c r="E563" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$563),"")</f>
+        <v/>
+      </c>
+      <c r="F563" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$563)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C489" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$489),"")</f>
-        <v/>
-      </c>
-      <c r="D489" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$489),"")</f>
-        <v/>
-      </c>
-      <c r="E489" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$489),"")</f>
-        <v/>
-      </c>
-      <c r="F489" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$489)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="490">
-      <c r="B490" s="2" t="inlineStr">
+      <c r="C564" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$564),"")</f>
+        <v/>
+      </c>
+      <c r="D564" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$564),"")</f>
+        <v/>
+      </c>
+      <c r="E564" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$564),"")</f>
+        <v/>
+      </c>
+      <c r="F564" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$564)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C490" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$490),"")</f>
-        <v/>
-      </c>
-      <c r="D490" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$490),"")</f>
-        <v/>
-      </c>
-      <c r="E490" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$490),"")</f>
-        <v/>
-      </c>
-      <c r="F490" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$490)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="491">
-      <c r="B491" s="2" t="inlineStr">
+      <c r="C565" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$565),"")</f>
+        <v/>
+      </c>
+      <c r="D565" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$565),"")</f>
+        <v/>
+      </c>
+      <c r="E565" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$565),"")</f>
+        <v/>
+      </c>
+      <c r="F565" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$565)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C491" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$491),"")</f>
-        <v/>
-      </c>
-      <c r="D491" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$491),"")</f>
-        <v/>
-      </c>
-      <c r="E491" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$491),"")</f>
-        <v/>
-      </c>
-      <c r="F491" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$491)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="492">
-      <c r="B492" s="2" t="inlineStr">
+      <c r="C566" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$566),"")</f>
+        <v/>
+      </c>
+      <c r="D566" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$566),"")</f>
+        <v/>
+      </c>
+      <c r="E566" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$566),"")</f>
+        <v/>
+      </c>
+      <c r="F566" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$566)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C492" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$492),"")</f>
-        <v/>
-      </c>
-      <c r="D492" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$492),"")</f>
-        <v/>
-      </c>
-      <c r="E492" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$492),"")</f>
-        <v/>
-      </c>
-      <c r="F492" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$492)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="493">
-      <c r="B493" s="2" t="inlineStr">
+      <c r="C567" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$567),"")</f>
+        <v/>
+      </c>
+      <c r="D567" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$567),"")</f>
+        <v/>
+      </c>
+      <c r="E567" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$567),"")</f>
+        <v/>
+      </c>
+      <c r="F567" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$567)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C493" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$493),"")</f>
-        <v/>
-      </c>
-      <c r="D493" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$493),"")</f>
-        <v/>
-      </c>
-      <c r="E493" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$493),"")</f>
-        <v/>
-      </c>
-      <c r="F493" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$493)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="494">
-      <c r="B494" s="2" t="inlineStr">
+      <c r="C568" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$568),"")</f>
+        <v/>
+      </c>
+      <c r="D568" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$568),"")</f>
+        <v/>
+      </c>
+      <c r="E568" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$568),"")</f>
+        <v/>
+      </c>
+      <c r="F568" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$568)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C494" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$494),"")</f>
-        <v/>
-      </c>
-      <c r="D494" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$494),"")</f>
-        <v/>
-      </c>
-      <c r="E494" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$494),"")</f>
-        <v/>
-      </c>
-      <c r="F494" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$494)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="495">
-      <c r="B495" s="2" t="inlineStr">
+      <c r="C569" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$569),"")</f>
+        <v/>
+      </c>
+      <c r="D569" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$569),"")</f>
+        <v/>
+      </c>
+      <c r="E569" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$569),"")</f>
+        <v/>
+      </c>
+      <c r="F569" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$569)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C495" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$495),"")</f>
-        <v/>
-      </c>
-      <c r="D495" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$495),"")</f>
-        <v/>
-      </c>
-      <c r="E495" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$495),"")</f>
-        <v/>
-      </c>
-      <c r="F495" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$495)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="496">
-      <c r="B496" s="2" t="inlineStr">
+      <c r="C570" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$570),"")</f>
+        <v/>
+      </c>
+      <c r="D570" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$570),"")</f>
+        <v/>
+      </c>
+      <c r="E570" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$570),"")</f>
+        <v/>
+      </c>
+      <c r="F570" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$570)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C496" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$496),"")</f>
-        <v/>
-      </c>
-      <c r="D496" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$496),"")</f>
-        <v/>
-      </c>
-      <c r="E496" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$496),"")</f>
-        <v/>
-      </c>
-      <c r="F496" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$496)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="497">
-      <c r="B497" s="2" t="inlineStr">
+      <c r="C571" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$571),"")</f>
+        <v/>
+      </c>
+      <c r="D571" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$571),"")</f>
+        <v/>
+      </c>
+      <c r="E571" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$571),"")</f>
+        <v/>
+      </c>
+      <c r="F571" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$571)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C497" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$497),"")</f>
-        <v/>
-      </c>
-      <c r="D497" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$497),"")</f>
-        <v/>
-      </c>
-      <c r="E497" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$497),"")</f>
-        <v/>
-      </c>
-      <c r="F497" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$497)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="498">
-      <c r="B498" s="2" t="inlineStr">
+      <c r="C572" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$572),"")</f>
+        <v/>
+      </c>
+      <c r="D572" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$572),"")</f>
+        <v/>
+      </c>
+      <c r="E572" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$572),"")</f>
+        <v/>
+      </c>
+      <c r="F572" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$572)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C498" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$498),"")</f>
-        <v/>
-      </c>
-      <c r="D498" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$498),"")</f>
-        <v/>
-      </c>
-      <c r="E498" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$498),"")</f>
-        <v/>
-      </c>
-      <c r="F498" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$498)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="499">
-      <c r="B499" s="2" t="inlineStr">
+      <c r="C573" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$573),"")</f>
+        <v/>
+      </c>
+      <c r="D573" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$573),"")</f>
+        <v/>
+      </c>
+      <c r="E573" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$573),"")</f>
+        <v/>
+      </c>
+      <c r="F573" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$573)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C499" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$499),"")</f>
-        <v/>
-      </c>
-      <c r="D499" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$499),"")</f>
-        <v/>
-      </c>
-      <c r="E499" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$499),"")</f>
-        <v/>
-      </c>
-      <c r="F499" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$499)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="500">
-      <c r="B500" s="2" t="inlineStr">
+      <c r="C574" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$574),"")</f>
+        <v/>
+      </c>
+      <c r="D574" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$574),"")</f>
+        <v/>
+      </c>
+      <c r="E574" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$574),"")</f>
+        <v/>
+      </c>
+      <c r="F574" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$574)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C500" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$500),"")</f>
-        <v/>
-      </c>
-      <c r="D500" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$500),"")</f>
-        <v/>
-      </c>
-      <c r="E500" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$500),"")</f>
-        <v/>
-      </c>
-      <c r="F500" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$500)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="501">
-      <c r="B501" s="2" t="inlineStr">
+      <c r="C575" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$575),"")</f>
+        <v/>
+      </c>
+      <c r="D575" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$575),"")</f>
+        <v/>
+      </c>
+      <c r="E575" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$575),"")</f>
+        <v/>
+      </c>
+      <c r="F575" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$575)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="576">
+      <c r="B576" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C501" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$501),"")</f>
-        <v/>
-      </c>
-      <c r="D501" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$501),"")</f>
-        <v/>
-      </c>
-      <c r="E501" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$501),"")</f>
-        <v/>
-      </c>
-      <c r="F501" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$501)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="502">
-      <c r="B502" s="2" t="inlineStr">
+      <c r="C576" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$576),"")</f>
+        <v/>
+      </c>
+      <c r="D576" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$576),"")</f>
+        <v/>
+      </c>
+      <c r="E576" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$576),"")</f>
+        <v/>
+      </c>
+      <c r="F576" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$576)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C502" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$502),"")</f>
-        <v/>
-      </c>
-      <c r="D502" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$502),"")</f>
-        <v/>
-      </c>
-      <c r="E502" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$502),"")</f>
-        <v/>
-      </c>
-      <c r="F502" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$502)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="503">
-      <c r="B503" s="2" t="inlineStr">
+      <c r="C577" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$577),"")</f>
+        <v/>
+      </c>
+      <c r="D577" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$577),"")</f>
+        <v/>
+      </c>
+      <c r="E577" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$577),"")</f>
+        <v/>
+      </c>
+      <c r="F577" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$577)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C503" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$503),"")</f>
-        <v/>
-      </c>
-      <c r="D503" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$503),"")</f>
-        <v/>
-      </c>
-      <c r="E503" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$503),"")</f>
-        <v/>
-      </c>
-      <c r="F503" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$503)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="504">
-      <c r="B504" s="2" t="inlineStr">
+      <c r="C578" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$578),"")</f>
+        <v/>
+      </c>
+      <c r="D578" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$578),"")</f>
+        <v/>
+      </c>
+      <c r="E578" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$578),"")</f>
+        <v/>
+      </c>
+      <c r="F578" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$578)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C504" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$504),"")</f>
-        <v/>
-      </c>
-      <c r="D504" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$504),"")</f>
-        <v/>
-      </c>
-      <c r="E504" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$504),"")</f>
-        <v/>
-      </c>
-      <c r="F504" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$504)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="505">
-      <c r="B505" s="2" t="inlineStr">
+      <c r="C579" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$579),"")</f>
+        <v/>
+      </c>
+      <c r="D579" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$579),"")</f>
+        <v/>
+      </c>
+      <c r="E579" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$579),"")</f>
+        <v/>
+      </c>
+      <c r="F579" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$579)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C505" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$505),"")</f>
-        <v/>
-      </c>
-      <c r="D505" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$505),"")</f>
-        <v/>
-      </c>
-      <c r="E505" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$505),"")</f>
-        <v/>
-      </c>
-      <c r="F505" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$505)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="506">
-      <c r="B506" s="2" t="inlineStr">
+      <c r="C580" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$580),"")</f>
+        <v/>
+      </c>
+      <c r="D580" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$580),"")</f>
+        <v/>
+      </c>
+      <c r="E580" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$580),"")</f>
+        <v/>
+      </c>
+      <c r="F580" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$580)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C506" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$506),"")</f>
-        <v/>
-      </c>
-      <c r="D506" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$506),"")</f>
-        <v/>
-      </c>
-      <c r="E506" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$506),"")</f>
-        <v/>
-      </c>
-      <c r="F506" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$506)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="507">
-      <c r="B507" s="2" t="inlineStr">
+      <c r="C581" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$581),"")</f>
+        <v/>
+      </c>
+      <c r="D581" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$581),"")</f>
+        <v/>
+      </c>
+      <c r="E581" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$581),"")</f>
+        <v/>
+      </c>
+      <c r="F581" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$581)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C507" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$507),"")</f>
-        <v/>
-      </c>
-      <c r="D507" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$507),"")</f>
-        <v/>
-      </c>
-      <c r="E507" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$507),"")</f>
-        <v/>
-      </c>
-      <c r="F507" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$507)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="508">
-      <c r="B508" s="2" t="inlineStr">
+      <c r="C582" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$582),"")</f>
+        <v/>
+      </c>
+      <c r="D582" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$582),"")</f>
+        <v/>
+      </c>
+      <c r="E582" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$582),"")</f>
+        <v/>
+      </c>
+      <c r="F582" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$582)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C508" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$508),"")</f>
-        <v/>
-      </c>
-      <c r="D508" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$508),"")</f>
-        <v/>
-      </c>
-      <c r="E508" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$508),"")</f>
-        <v/>
-      </c>
-      <c r="F508" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$508)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="509">
-      <c r="B509" s="2" t="inlineStr">
+      <c r="C583" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$583),"")</f>
+        <v/>
+      </c>
+      <c r="D583" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$583),"")</f>
+        <v/>
+      </c>
+      <c r="E583" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$583),"")</f>
+        <v/>
+      </c>
+      <c r="F583" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$583)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C509" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$509),"")</f>
-        <v/>
-      </c>
-      <c r="D509" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$509),"")</f>
-        <v/>
-      </c>
-      <c r="E509" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$509),"")</f>
-        <v/>
-      </c>
-      <c r="F509" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$509)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="510">
-      <c r="B510" s="2" t="inlineStr">
+      <c r="C584" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$584),"")</f>
+        <v/>
+      </c>
+      <c r="D584" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$584),"")</f>
+        <v/>
+      </c>
+      <c r="E584" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$584),"")</f>
+        <v/>
+      </c>
+      <c r="F584" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$584)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C510" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$510),"")</f>
-        <v/>
-      </c>
-      <c r="D510" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$510),"")</f>
-        <v/>
-      </c>
-      <c r="E510" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$510),"")</f>
-        <v/>
-      </c>
-      <c r="F510" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$510)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="511">
-      <c r="B511" s="2" t="inlineStr">
+      <c r="C585" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$585),"")</f>
+        <v/>
+      </c>
+      <c r="D585" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$585),"")</f>
+        <v/>
+      </c>
+      <c r="E585" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$585),"")</f>
+        <v/>
+      </c>
+      <c r="F585" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$585)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="586">
+      <c r="B586" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C511" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$511),"")</f>
-        <v/>
-      </c>
-      <c r="D511" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$511),"")</f>
-        <v/>
-      </c>
-      <c r="E511" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$511),"")</f>
-        <v/>
-      </c>
-      <c r="F511" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$511)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="512">
-      <c r="B512" s="2" t="inlineStr">
+      <c r="C586" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$586),"")</f>
+        <v/>
+      </c>
+      <c r="D586" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$586),"")</f>
+        <v/>
+      </c>
+      <c r="E586" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$586),"")</f>
+        <v/>
+      </c>
+      <c r="F586" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$586)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C512" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$512),"")</f>
-        <v/>
-      </c>
-      <c r="D512" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$512),"")</f>
-        <v/>
-      </c>
-      <c r="E512" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$512),"")</f>
-        <v/>
-      </c>
-      <c r="F512" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$512)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="513">
-      <c r="B513" s="2" t="inlineStr">
+      <c r="C587" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$587),"")</f>
+        <v/>
+      </c>
+      <c r="D587" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$587),"")</f>
+        <v/>
+      </c>
+      <c r="E587" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$587),"")</f>
+        <v/>
+      </c>
+      <c r="F587" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$587)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C513" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$513),"")</f>
-        <v/>
-      </c>
-      <c r="D513" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$513),"")</f>
-        <v/>
-      </c>
-      <c r="E513" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$513),"")</f>
-        <v/>
-      </c>
-      <c r="F513" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$513)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="514">
-      <c r="B514" s="2" t="inlineStr">
+      <c r="C588" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$588),"")</f>
+        <v/>
+      </c>
+      <c r="D588" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$588),"")</f>
+        <v/>
+      </c>
+      <c r="E588" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$588),"")</f>
+        <v/>
+      </c>
+      <c r="F588" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$588)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C514" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$514),"")</f>
-        <v/>
-      </c>
-      <c r="D514" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$514),"")</f>
-        <v/>
-      </c>
-      <c r="E514" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$514),"")</f>
-        <v/>
-      </c>
-      <c r="F514" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$514)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="515">
-      <c r="B515" s="2" t="inlineStr">
+      <c r="C589" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$589),"")</f>
+        <v/>
+      </c>
+      <c r="D589" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$589),"")</f>
+        <v/>
+      </c>
+      <c r="E589" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$589),"")</f>
+        <v/>
+      </c>
+      <c r="F589" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$589)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C515" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$515),"")</f>
-        <v/>
-      </c>
-      <c r="D515" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$515),"")</f>
-        <v/>
-      </c>
-      <c r="E515" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$515),"")</f>
-        <v/>
-      </c>
-      <c r="F515" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$515)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="516">
-      <c r="B516" s="2" t="inlineStr">
+      <c r="C590" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$590),"")</f>
+        <v/>
+      </c>
+      <c r="D590" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$590),"")</f>
+        <v/>
+      </c>
+      <c r="E590" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$590),"")</f>
+        <v/>
+      </c>
+      <c r="F590" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$590)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C516" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$516),"")</f>
-        <v/>
-      </c>
-      <c r="D516" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$516),"")</f>
-        <v/>
-      </c>
-      <c r="E516" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$516),"")</f>
-        <v/>
-      </c>
-      <c r="F516" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$516)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="517">
-      <c r="B517" s="2" t="inlineStr">
+      <c r="C591" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$591),"")</f>
+        <v/>
+      </c>
+      <c r="D591" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$591),"")</f>
+        <v/>
+      </c>
+      <c r="E591" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$591),"")</f>
+        <v/>
+      </c>
+      <c r="F591" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$591)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C517" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$517),"")</f>
-        <v/>
-      </c>
-      <c r="D517" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$517),"")</f>
-        <v/>
-      </c>
-      <c r="E517" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$517),"")</f>
-        <v/>
-      </c>
-      <c r="F517" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$517)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="518">
-      <c r="B518" s="2" t="inlineStr">
+      <c r="C592" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$592),"")</f>
+        <v/>
+      </c>
+      <c r="D592" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$592),"")</f>
+        <v/>
+      </c>
+      <c r="E592" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$592),"")</f>
+        <v/>
+      </c>
+      <c r="F592" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$592)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C518" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$518),"")</f>
-        <v/>
-      </c>
-      <c r="D518" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$518),"")</f>
-        <v/>
-      </c>
-      <c r="E518" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$518),"")</f>
-        <v/>
-      </c>
-      <c r="F518" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$518)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="519">
-      <c r="B519" s="2" t="inlineStr">
+      <c r="C593" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$593),"")</f>
+        <v/>
+      </c>
+      <c r="D593" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$593),"")</f>
+        <v/>
+      </c>
+      <c r="E593" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$593),"")</f>
+        <v/>
+      </c>
+      <c r="F593" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$593)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C519" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$519),"")</f>
-        <v/>
-      </c>
-      <c r="D519" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$519),"")</f>
-        <v/>
-      </c>
-      <c r="E519" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$519),"")</f>
-        <v/>
-      </c>
-      <c r="F519" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$519)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="520">
-      <c r="B520" s="2" t="inlineStr">
+      <c r="C594" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$594),"")</f>
+        <v/>
+      </c>
+      <c r="D594" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$594),"")</f>
+        <v/>
+      </c>
+      <c r="E594" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$594),"")</f>
+        <v/>
+      </c>
+      <c r="F594" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$594)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C520" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$520),"")</f>
-        <v/>
-      </c>
-      <c r="D520" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$520),"")</f>
-        <v/>
-      </c>
-      <c r="E520" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$520),"")</f>
-        <v/>
-      </c>
-      <c r="F520" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$520)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="521">
-      <c r="B521" s="2" t="inlineStr">
+      <c r="C595" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$595),"")</f>
+        <v/>
+      </c>
+      <c r="D595" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$595),"")</f>
+        <v/>
+      </c>
+      <c r="E595" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$595),"")</f>
+        <v/>
+      </c>
+      <c r="F595" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$595)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C521" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$521),"")</f>
-        <v/>
-      </c>
-      <c r="D521" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$521),"")</f>
-        <v/>
-      </c>
-      <c r="E521" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$521),"")</f>
-        <v/>
-      </c>
-      <c r="F521" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$521)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="522">
-      <c r="B522" s="2" t="inlineStr">
+      <c r="C596" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$596),"")</f>
+        <v/>
+      </c>
+      <c r="D596" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$596),"")</f>
+        <v/>
+      </c>
+      <c r="E596" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$596),"")</f>
+        <v/>
+      </c>
+      <c r="F596" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$596)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C522" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$522),"")</f>
-        <v/>
-      </c>
-      <c r="D522" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$522),"")</f>
-        <v/>
-      </c>
-      <c r="E522" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$522),"")</f>
-        <v/>
-      </c>
-      <c r="F522" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$522)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="523">
-      <c r="B523" s="2" t="inlineStr">
+      <c r="C597" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$597),"")</f>
+        <v/>
+      </c>
+      <c r="D597" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$597),"")</f>
+        <v/>
+      </c>
+      <c r="E597" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$597),"")</f>
+        <v/>
+      </c>
+      <c r="F597" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$597)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C523" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$523),"")</f>
-        <v/>
-      </c>
-      <c r="D523" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$523),"")</f>
-        <v/>
-      </c>
-      <c r="E523" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$523),"")</f>
-        <v/>
-      </c>
-      <c r="F523" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$523)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="524">
-      <c r="B524" s="2" t="inlineStr">
+      <c r="C598" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$598),"")</f>
+        <v/>
+      </c>
+      <c r="D598" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$598),"")</f>
+        <v/>
+      </c>
+      <c r="E598" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$598),"")</f>
+        <v/>
+      </c>
+      <c r="F598" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$598)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C524" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$524),"")</f>
-        <v/>
-      </c>
-      <c r="D524" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$524),"")</f>
-        <v/>
-      </c>
-      <c r="E524" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$524),"")</f>
-        <v/>
-      </c>
-      <c r="F524" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$524)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="525">
-      <c r="B525" s="2" t="inlineStr">
+      <c r="C599" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$599),"")</f>
+        <v/>
+      </c>
+      <c r="D599" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$599),"")</f>
+        <v/>
+      </c>
+      <c r="E599" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$599),"")</f>
+        <v/>
+      </c>
+      <c r="F599" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$599)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C525" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$525),"")</f>
-        <v/>
-      </c>
-      <c r="D525" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$525),"")</f>
-        <v/>
-      </c>
-      <c r="E525" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$525),"")</f>
-        <v/>
-      </c>
-      <c r="F525" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$525)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="526">
-      <c r="B526" s="2" t="inlineStr">
+      <c r="C600" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$600),"")</f>
+        <v/>
+      </c>
+      <c r="D600" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$600),"")</f>
+        <v/>
+      </c>
+      <c r="E600" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$600),"")</f>
+        <v/>
+      </c>
+      <c r="F600" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$600)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C526" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$526),"")</f>
-        <v/>
-      </c>
-      <c r="D526" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$526),"")</f>
-        <v/>
-      </c>
-      <c r="E526" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$526),"")</f>
-        <v/>
-      </c>
-      <c r="F526" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$526)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="527">
-      <c r="B527" s="2" t="inlineStr">
+      <c r="C601" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$601),"")</f>
+        <v/>
+      </c>
+      <c r="D601" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$601),"")</f>
+        <v/>
+      </c>
+      <c r="E601" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$601),"")</f>
+        <v/>
+      </c>
+      <c r="F601" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$601)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C527" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$527),"")</f>
-        <v/>
-      </c>
-      <c r="D527" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$527),"")</f>
-        <v/>
-      </c>
-      <c r="E527" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$527),"")</f>
-        <v/>
-      </c>
-      <c r="F527" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$527)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="528">
-      <c r="B528" s="2" t="inlineStr">
+      <c r="C602" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$602),"")</f>
+        <v/>
+      </c>
+      <c r="D602" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$602),"")</f>
+        <v/>
+      </c>
+      <c r="E602" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$602),"")</f>
+        <v/>
+      </c>
+      <c r="F602" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$602)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C528" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$528),"")</f>
-        <v/>
-      </c>
-      <c r="D528" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$528),"")</f>
-        <v/>
-      </c>
-      <c r="E528" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$528),"")</f>
-        <v/>
-      </c>
-      <c r="F528" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$528)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="529">
-      <c r="B529" s="2" t="inlineStr">
+      <c r="C603" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$603),"")</f>
+        <v/>
+      </c>
+      <c r="D603" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$603),"")</f>
+        <v/>
+      </c>
+      <c r="E603" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$603),"")</f>
+        <v/>
+      </c>
+      <c r="F603" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$603)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C529" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$529),"")</f>
-        <v/>
-      </c>
-      <c r="D529" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$529),"")</f>
-        <v/>
-      </c>
-      <c r="E529" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$529),"")</f>
-        <v/>
-      </c>
-      <c r="F529" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$529)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="530">
-      <c r="B530" s="2" t="inlineStr">
+      <c r="C604" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$604),"")</f>
+        <v/>
+      </c>
+      <c r="D604" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$604),"")</f>
+        <v/>
+      </c>
+      <c r="E604" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$604),"")</f>
+        <v/>
+      </c>
+      <c r="F604" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$604)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C530" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$530),"")</f>
-        <v/>
-      </c>
-      <c r="D530" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$530),"")</f>
-        <v/>
-      </c>
-      <c r="E530" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$530),"")</f>
-        <v/>
-      </c>
-      <c r="F530" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$530)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="531">
-      <c r="B531" s="2" t="inlineStr">
+      <c r="C605" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$605),"")</f>
+        <v/>
+      </c>
+      <c r="D605" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$605),"")</f>
+        <v/>
+      </c>
+      <c r="E605" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$605),"")</f>
+        <v/>
+      </c>
+      <c r="F605" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$605)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C531" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$531),"")</f>
-        <v/>
-      </c>
-      <c r="D531" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$531),"")</f>
-        <v/>
-      </c>
-      <c r="E531" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$531),"")</f>
-        <v/>
-      </c>
-      <c r="F531" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$531)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="532">
-      <c r="B532" s="2" t="inlineStr">
+      <c r="C606" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$606),"")</f>
+        <v/>
+      </c>
+      <c r="D606" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$606),"")</f>
+        <v/>
+      </c>
+      <c r="E606" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$606),"")</f>
+        <v/>
+      </c>
+      <c r="F606" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$606)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C532" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$532),"")</f>
-        <v/>
-      </c>
-      <c r="D532" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$532),"")</f>
-        <v/>
-      </c>
-      <c r="E532" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$532),"")</f>
-        <v/>
-      </c>
-      <c r="F532" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$532)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="533">
-      <c r="B533" s="2" t="inlineStr">
+      <c r="C607" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$607),"")</f>
+        <v/>
+      </c>
+      <c r="D607" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$607),"")</f>
+        <v/>
+      </c>
+      <c r="E607" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$607),"")</f>
+        <v/>
+      </c>
+      <c r="F607" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$607)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C533" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$533),"")</f>
-        <v/>
-      </c>
-      <c r="D533" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$533),"")</f>
-        <v/>
-      </c>
-      <c r="E533" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$533),"")</f>
-        <v/>
-      </c>
-      <c r="F533" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$533)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="534">
-      <c r="B534" s="2" t="inlineStr">
+      <c r="C608" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$608),"")</f>
+        <v/>
+      </c>
+      <c r="D608" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$608),"")</f>
+        <v/>
+      </c>
+      <c r="E608" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$608),"")</f>
+        <v/>
+      </c>
+      <c r="F608" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$608)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C534" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$534),"")</f>
-        <v/>
-      </c>
-      <c r="D534" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$534),"")</f>
-        <v/>
-      </c>
-      <c r="E534" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$534),"")</f>
-        <v/>
-      </c>
-      <c r="F534" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$534)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="535">
-      <c r="B535" s="2" t="inlineStr">
+      <c r="C609" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$609),"")</f>
+        <v/>
+      </c>
+      <c r="D609" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$609),"")</f>
+        <v/>
+      </c>
+      <c r="E609" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$609),"")</f>
+        <v/>
+      </c>
+      <c r="F609" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$609)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C535" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$535),"")</f>
-        <v/>
-      </c>
-      <c r="D535" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$535),"")</f>
-        <v/>
-      </c>
-      <c r="E535" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$535),"")</f>
-        <v/>
-      </c>
-      <c r="F535" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$535)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="536">
-      <c r="B536" s="2" t="inlineStr">
+      <c r="C610" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$610),"")</f>
+        <v/>
+      </c>
+      <c r="D610" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$610),"")</f>
+        <v/>
+      </c>
+      <c r="E610" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$610),"")</f>
+        <v/>
+      </c>
+      <c r="F610" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$610)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C536" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$536),"")</f>
-        <v/>
-      </c>
-      <c r="D536" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$536),"")</f>
-        <v/>
-      </c>
-      <c r="E536" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$536),"")</f>
-        <v/>
-      </c>
-      <c r="F536" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$536)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="537">
-      <c r="B537" s="2" t="inlineStr">
+      <c r="C611" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$611),"")</f>
+        <v/>
+      </c>
+      <c r="D611" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$611),"")</f>
+        <v/>
+      </c>
+      <c r="E611" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$611),"")</f>
+        <v/>
+      </c>
+      <c r="F611" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$611)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C537" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$537),"")</f>
-        <v/>
-      </c>
-      <c r="D537" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$537),"")</f>
-        <v/>
-      </c>
-      <c r="E537" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$537),"")</f>
-        <v/>
-      </c>
-      <c r="F537" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$537)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="538">
-      <c r="B538" s="2" t="inlineStr">
+      <c r="C612" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$612),"")</f>
+        <v/>
+      </c>
+      <c r="D612" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$612),"")</f>
+        <v/>
+      </c>
+      <c r="E612" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$612),"")</f>
+        <v/>
+      </c>
+      <c r="F612" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$612)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C538" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$538),"")</f>
-        <v/>
-      </c>
-      <c r="D538" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$538),"")</f>
-        <v/>
-      </c>
-      <c r="E538" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$538),"")</f>
-        <v/>
-      </c>
-      <c r="F538" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$538)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="539">
-      <c r="B539" s="2" t="inlineStr">
+      <c r="C613" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$613),"")</f>
+        <v/>
+      </c>
+      <c r="D613" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$613),"")</f>
+        <v/>
+      </c>
+      <c r="E613" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$613),"")</f>
+        <v/>
+      </c>
+      <c r="F613" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$613)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="614">
+      <c r="B614" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C539" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$539),"")</f>
-        <v/>
-      </c>
-      <c r="D539" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$539),"")</f>
-        <v/>
-      </c>
-      <c r="E539" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$539),"")</f>
-        <v/>
-      </c>
-      <c r="F539" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$539)*(F$2:F$463),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="540">
-      <c r="B540" s="2" t="inlineStr">
+      <c r="C614" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$614),"")</f>
+        <v/>
+      </c>
+      <c r="D614" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$614),"")</f>
+        <v/>
+      </c>
+      <c r="E614" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$614),"")</f>
+        <v/>
+      </c>
+      <c r="F614" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$614)*(F$2:F$538),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C540" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$540),"")</f>
-        <v/>
-      </c>
-      <c r="D540" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$540),"")</f>
-        <v/>
-      </c>
-      <c r="E540" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$463,A$2:A$463,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$463,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$463,$B$540),"")</f>
-        <v/>
-      </c>
-      <c r="F540" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$463)=YEAR(TODAY()))*(MONTH(A$2:A$463)=MONTH(TODAY()))*(B$2:B$463=$B$540)*(F$2:F$463),"")</f>
+      <c r="C615" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$615),"")</f>
+        <v/>
+      </c>
+      <c r="D615" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$615),"")</f>
+        <v/>
+      </c>
+      <c r="E615" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$615),"")</f>
+        <v/>
+      </c>
+      <c r="F615" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$615)*(F$2:F$538),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H463"/>
+  <autoFilter ref="A1:H538"/>
   <mergeCells count="1">
-    <mergeCell ref="A465:H465"/>
+    <mergeCell ref="A540:H540"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18146,7 +20696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19487,161 +22037,355 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>130840</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>132020</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>130860</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>127960</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1090</v>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>150820</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>159680</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>150840</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>150320</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>-9180</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>6.7973</v>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="6" t="n">
+        <v>6.8101</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>6.7878</v>
+      </c>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/25</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-    </row>
-    <row r="37">
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D37" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$37),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$37)*(H$2:H$34),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" s="2" t="inlineStr">
+      <c r="D42" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$42)*(H$2:H$39),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D38" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$38),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$38)*(H$2:H$34),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" s="2" t="inlineStr">
+      <c r="D43" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$43)*(H$2:H$39),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D39" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$39),"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$39)*(H$2:H$34),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" s="2" t="inlineStr">
+      <c r="D44" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$44)*(H$2:H$39),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>碳酸锂(LC)连续</t>
         </is>
       </c>
-      <c r="D40" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$40),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$40)*(H$2:H$34),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" s="2" t="inlineStr">
+      <c r="D45" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$45)*(H$2:H$39),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D41" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$34,A$2:A$34,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$34,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$34,$C$41),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$34)=YEAR(TODAY()))*(MONTH(A$2:A$34)=MONTH(TODAY()))*(C$2:C$34=$C$41)*(H$2:H$34),"")</f>
+      <c r="D46" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$46)*(H$2:H$39),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J34"/>
+  <autoFilter ref="A1:J39"/>
   <mergeCells count="1">
-    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A41:J41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$538</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$613</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H615"/>
+  <dimension ref="A1:H690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18942,1749 +18942,4299 @@
         </is>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B539" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C539" s="3" t="n">
+        <v>98350</v>
+      </c>
+      <c r="D539" s="4" t="n">
+        <v>103450</v>
+      </c>
+      <c r="E539" s="4" t="n">
+        <v>100900</v>
+      </c>
+      <c r="F539" s="4" t="n">
+        <v>-350</v>
+      </c>
+      <c r="G539" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H539" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="540">
-      <c r="A540" s="8" t="inlineStr">
+      <c r="A540" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B540" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C540" s="3" t="n">
+        <v>180100</v>
+      </c>
+      <c r="D540" s="4" t="n">
+        <v>187200</v>
+      </c>
+      <c r="E540" s="4" t="n">
+        <v>183650</v>
+      </c>
+      <c r="F540" s="4" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="G540" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H540" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C541" s="3" t="n">
+        <v>91250</v>
+      </c>
+      <c r="D541" s="4" t="n">
+        <v>95950</v>
+      </c>
+      <c r="E541" s="4" t="n">
+        <v>93600</v>
+      </c>
+      <c r="F541" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G541" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H541" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B542" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C542" s="3" t="n">
+        <v>183200</v>
+      </c>
+      <c r="D542" s="4" t="n">
+        <v>192700</v>
+      </c>
+      <c r="E542" s="4" t="n">
+        <v>187950</v>
+      </c>
+      <c r="F542" s="4" t="n">
+        <v>-1700</v>
+      </c>
+      <c r="G542" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H542" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B543" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C543" s="3" t="n">
+        <v>112800</v>
+      </c>
+      <c r="D543" s="4" t="n">
+        <v>118500</v>
+      </c>
+      <c r="E543" s="4" t="n">
+        <v>115650</v>
+      </c>
+      <c r="F543" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="G543" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H543" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B544" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C544" s="3" t="n">
+        <v>206000</v>
+      </c>
+      <c r="D544" s="4" t="n">
+        <v>215600</v>
+      </c>
+      <c r="E544" s="4" t="n">
+        <v>210800</v>
+      </c>
+      <c r="F544" s="4" t="n">
+        <v>-1800</v>
+      </c>
+      <c r="G544" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H544" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B545" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C545" s="7" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D545" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="E545" s="6" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="F545" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G545" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H545" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B546" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C546" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D546" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E546" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F546" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G546" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H546" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B547" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C547" s="3" t="n">
+        <v>204200</v>
+      </c>
+      <c r="D547" s="4" t="n">
+        <v>212700</v>
+      </c>
+      <c r="E547" s="4" t="n">
+        <v>208450</v>
+      </c>
+      <c r="F547" s="4" t="n">
+        <v>-800</v>
+      </c>
+      <c r="G547" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H547" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B548" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C548" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D548" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E548" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F548" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G548" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H548" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B549" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C549" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D549" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E549" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F549" s="6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G549" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H549" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B550" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C550" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D550" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E550" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F550" s="6" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G550" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H550" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B551" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C551" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D551" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E551" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F551" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G551" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H551" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C552" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D552" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E552" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F552" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G552" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H552" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B553" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C553" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D553" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E553" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F553" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H553" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B554" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C554" s="3" t="n">
+        <v>100240</v>
+      </c>
+      <c r="D554" s="4" t="n">
+        <v>104331</v>
+      </c>
+      <c r="E554" s="4" t="n">
+        <v>102285.5</v>
+      </c>
+      <c r="F554" s="4" t="n">
+        <v>-510.5</v>
+      </c>
+      <c r="G554" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H554" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B555" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C555" s="3" t="n">
+        <v>139288</v>
+      </c>
+      <c r="D555" s="4" t="n">
+        <v>139288</v>
+      </c>
+      <c r="E555" s="4" t="n">
+        <v>139288</v>
+      </c>
+      <c r="F555" s="4" t="n">
+        <v>-4382</v>
+      </c>
+      <c r="G555" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H555" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B556" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C556" s="3" t="n">
+        <v>7666</v>
+      </c>
+      <c r="D556" s="4" t="n">
+        <v>7666</v>
+      </c>
+      <c r="E556" s="4" t="n">
+        <v>7666</v>
+      </c>
+      <c r="F556" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G556" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H556" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B557" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C557" s="3" t="n">
+        <v>32551</v>
+      </c>
+      <c r="D557" s="4" t="n">
+        <v>32551</v>
+      </c>
+      <c r="E557" s="4" t="n">
+        <v>32551</v>
+      </c>
+      <c r="F557" s="6" t="n">
+        <v>-91</v>
+      </c>
+      <c r="G557" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H557" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B558" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C558" s="3" t="n">
+        <v>152571</v>
+      </c>
+      <c r="D558" s="4" t="n">
+        <v>152571</v>
+      </c>
+      <c r="E558" s="4" t="n">
+        <v>152571</v>
+      </c>
+      <c r="F558" s="4" t="n">
+        <v>-4184</v>
+      </c>
+      <c r="G558" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H558" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B559" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C559" s="3" t="n">
+        <v>85909</v>
+      </c>
+      <c r="D559" s="4" t="n">
+        <v>85909</v>
+      </c>
+      <c r="E559" s="4" t="n">
+        <v>85909</v>
+      </c>
+      <c r="F559" s="4" t="n">
+        <v>-601</v>
+      </c>
+      <c r="G559" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H559" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B560" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C560" s="3" t="n">
+        <v>6803</v>
+      </c>
+      <c r="D560" s="4" t="n">
+        <v>6803</v>
+      </c>
+      <c r="E560" s="4" t="n">
+        <v>6803</v>
+      </c>
+      <c r="F560" s="4" t="n">
+        <v>-236</v>
+      </c>
+      <c r="G560" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H560" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B561" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C561" s="3" t="n">
+        <v>6464</v>
+      </c>
+      <c r="D561" s="4" t="n">
+        <v>6464</v>
+      </c>
+      <c r="E561" s="4" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F561" s="4" t="n">
+        <v>-131</v>
+      </c>
+      <c r="G561" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H561" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B562" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C562" s="7" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="D562" s="6" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="E562" s="6" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="F562" s="6" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G562" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H562" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C563" s="7" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="D563" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="E563" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="F563" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H563" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B564" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C564" s="7" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="D564" s="6" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="E564" s="6" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="F564" s="6" t="n">
+        <v>-2.51</v>
+      </c>
+      <c r="G564" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H564" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B565" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C565" s="7" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="D565" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="E565" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="F565" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H565" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B566" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C566" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D566" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E566" s="6" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="F566" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H566" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B567" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C567" s="3" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D567" s="4" t="n">
+        <v>108000</v>
+      </c>
+      <c r="E567" s="4" t="n">
+        <v>106500</v>
+      </c>
+      <c r="F567" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G567" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H567" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B568" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C568" s="3" t="n">
+        <v>329000</v>
+      </c>
+      <c r="D568" s="4" t="n">
+        <v>341000</v>
+      </c>
+      <c r="E568" s="4" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F568" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G568" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H568" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B569" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C569" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D569" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E569" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F569" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G569" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H569" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B570" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C570" s="3" t="n">
+        <v>124000</v>
+      </c>
+      <c r="D570" s="4" t="n">
+        <v>129000</v>
+      </c>
+      <c r="E570" s="4" t="n">
+        <v>126500</v>
+      </c>
+      <c r="F570" s="4" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="G570" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H570" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B571" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C571" s="3" t="n">
+        <v>143000</v>
+      </c>
+      <c r="D571" s="4" t="n">
+        <v>154000</v>
+      </c>
+      <c r="E571" s="4" t="n">
+        <v>148500</v>
+      </c>
+      <c r="F571" s="4" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="G571" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H571" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B572" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C572" s="3" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="D572" s="4" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="E572" s="4" t="n">
+        <v>1070000</v>
+      </c>
+      <c r="F572" s="4" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="G572" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H572" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B573" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C573" s="3" t="n">
+        <v>2090</v>
+      </c>
+      <c r="D573" s="4" t="n">
+        <v>2240</v>
+      </c>
+      <c r="E573" s="4" t="n">
+        <v>2165</v>
+      </c>
+      <c r="F573" s="6" t="n">
+        <v>-85</v>
+      </c>
+      <c r="G573" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H573" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C574" s="3" t="n">
+        <v>20050</v>
+      </c>
+      <c r="D574" s="4" t="n">
+        <v>23200</v>
+      </c>
+      <c r="E574" s="4" t="n">
+        <v>21625</v>
+      </c>
+      <c r="F574" s="4" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G574" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H574" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B575" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C575" s="3" t="n">
+        <v>23850</v>
+      </c>
+      <c r="D575" s="4" t="n">
+        <v>28100</v>
+      </c>
+      <c r="E575" s="4" t="n">
+        <v>25975</v>
+      </c>
+      <c r="F575" s="4" t="n">
+        <v>-550</v>
+      </c>
+      <c r="G575" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H575" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B576" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C576" s="3" t="n">
+        <v>15300</v>
+      </c>
+      <c r="D576" s="4" t="n">
+        <v>16800</v>
+      </c>
+      <c r="E576" s="4" t="n">
+        <v>16050</v>
+      </c>
+      <c r="F576" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G576" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H576" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B577" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C577" s="3" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D577" s="4" t="n">
+        <v>10800</v>
+      </c>
+      <c r="E577" s="4" t="n">
+        <v>10300</v>
+      </c>
+      <c r="F577" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G577" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H577" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B578" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C578" s="3" t="n">
+        <v>16700</v>
+      </c>
+      <c r="D578" s="4" t="n">
+        <v>17800</v>
+      </c>
+      <c r="E578" s="4" t="n">
+        <v>17250</v>
+      </c>
+      <c r="F578" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G578" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H578" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B579" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C579" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D579" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E579" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F579" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G579" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H579" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B580" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C580" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D580" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E580" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F580" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G580" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H580" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B581" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C581" s="3" t="n">
+        <v>302000</v>
+      </c>
+      <c r="D581" s="4" t="n">
+        <v>315000</v>
+      </c>
+      <c r="E581" s="4" t="n">
+        <v>308500</v>
+      </c>
+      <c r="F581" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G581" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H581" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B582" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C582" s="3" t="n">
+        <v>104000</v>
+      </c>
+      <c r="D582" s="4" t="n">
+        <v>106500</v>
+      </c>
+      <c r="E582" s="4" t="n">
+        <v>105250</v>
+      </c>
+      <c r="F582" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G582" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H582" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B583" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C583" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D583" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E583" s="4" t="n">
+        <v>39750</v>
+      </c>
+      <c r="F583" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G583" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H583" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B584" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C584" s="3" t="n">
+        <v>2060</v>
+      </c>
+      <c r="D584" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E584" s="4" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F584" s="4" t="n">
+        <v>-285</v>
+      </c>
+      <c r="G584" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H584" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C585" s="3" t="n">
+        <v>2110</v>
+      </c>
+      <c r="D585" s="4" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E585" s="4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F585" s="6" t="n">
+        <v>-85</v>
+      </c>
+      <c r="G585" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H585" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B586" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C586" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="D586" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E586" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="F586" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G586" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H586" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B587" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C587" s="3" t="n">
+        <v>265000</v>
+      </c>
+      <c r="D587" s="4" t="n">
+        <v>273000</v>
+      </c>
+      <c r="E587" s="4" t="n">
+        <v>269000</v>
+      </c>
+      <c r="F587" s="4" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="G587" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H587" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B588" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C588" s="7" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D588" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E588" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="F588" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G588" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H588" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B589" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C589" s="7" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D589" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E589" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F589" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G589" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H589" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B590" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C590" s="3" t="n">
+        <v>137000</v>
+      </c>
+      <c r="D590" s="4" t="n">
+        <v>153000</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>145000</v>
+      </c>
+      <c r="F590" s="4" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="G590" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H590" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B591" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C591" s="3" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D591" s="4" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E591" s="4" t="n">
+        <v>139000</v>
+      </c>
+      <c r="F591" s="4" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="G591" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H591" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B592" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C592" s="3" t="n">
+        <v>7570</v>
+      </c>
+      <c r="D592" s="4" t="n">
+        <v>7770</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>7670</v>
+      </c>
+      <c r="F592" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G592" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H592" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B593" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C593" s="3" t="n">
+        <v>32200</v>
+      </c>
+      <c r="D593" s="4" t="n">
+        <v>32600</v>
+      </c>
+      <c r="E593" s="4" t="n">
+        <v>32400</v>
+      </c>
+      <c r="F593" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G593" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H593" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C594" s="3" t="n">
+        <v>147000</v>
+      </c>
+      <c r="D594" s="4" t="n">
+        <v>158000</v>
+      </c>
+      <c r="E594" s="4" t="n">
+        <v>152500</v>
+      </c>
+      <c r="F594" s="4" t="n">
+        <v>-4500</v>
+      </c>
+      <c r="G594" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H594" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C595" s="7" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D595" s="6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E595" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F595" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G595" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H595" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C596" s="7" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D596" s="6" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="E596" s="6" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="F596" s="6" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G596" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H596" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C597" s="3" t="n">
+        <v>1090000</v>
+      </c>
+      <c r="D597" s="4" t="n">
+        <v>1110000</v>
+      </c>
+      <c r="E597" s="4" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="F597" s="4" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="G597" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H597" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C598" s="3" t="n">
+        <v>374000</v>
+      </c>
+      <c r="D598" s="4" t="n">
+        <v>385000</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>379500</v>
+      </c>
+      <c r="F598" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G598" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H598" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C599" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D599" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E599" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F599" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G599" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H599" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C600" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D600" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E600" s="4" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F600" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G600" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H600" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C601" s="3" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D601" s="4" t="n">
+        <v>87300</v>
+      </c>
+      <c r="E601" s="4" t="n">
+        <v>86150</v>
+      </c>
+      <c r="F601" s="4" t="n">
+        <v>-600</v>
+      </c>
+      <c r="G601" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H601" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C602" s="3" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D602" s="4" t="n">
+        <v>215000</v>
+      </c>
+      <c r="E602" s="4" t="n">
+        <v>211500</v>
+      </c>
+      <c r="F602" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G602" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H602" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C603" s="3" t="n">
+        <v>55660</v>
+      </c>
+      <c r="D603" s="4" t="n">
+        <v>56360</v>
+      </c>
+      <c r="E603" s="4" t="n">
+        <v>56010</v>
+      </c>
+      <c r="F603" s="4" t="n">
+        <v>-960</v>
+      </c>
+      <c r="G603" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H603" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C604" s="3" t="n">
+        <v>61500</v>
+      </c>
+      <c r="D604" s="4" t="n">
+        <v>66500</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>64000</v>
+      </c>
+      <c r="F604" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G604" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H604" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B605" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C605" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D605" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E605" s="6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F605" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G605" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H605" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B606" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C606" s="3" t="n">
+        <v>26122</v>
+      </c>
+      <c r="D606" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="F606" s="4" t="n">
+        <v>-661</v>
+      </c>
+      <c r="G606" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H606" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C607" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D607" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E607" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F607" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G607" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H607" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B608" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C608" s="3" t="n">
+        <v>373000</v>
+      </c>
+      <c r="D608" s="4" t="n">
+        <v>376000</v>
+      </c>
+      <c r="E608" s="4" t="n">
+        <v>374500</v>
+      </c>
+      <c r="F608" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G608" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H608" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B609" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C609" s="3" t="n">
+        <v>96500</v>
+      </c>
+      <c r="D609" s="4" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E609" s="4" t="n">
+        <v>97750</v>
+      </c>
+      <c r="F609" s="4" t="n">
+        <v>-450</v>
+      </c>
+      <c r="G609" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H609" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B610" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C610" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D610" s="4" t="n">
+        <v>91000</v>
+      </c>
+      <c r="E610" s="4" t="n">
+        <v>87500</v>
+      </c>
+      <c r="F610" s="4" t="n">
+        <v>-250</v>
+      </c>
+      <c r="G610" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H610" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B611" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C611" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D611" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E611" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F611" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G611" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H611" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B612" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C612" s="3" t="n">
+        <v>7027</v>
+      </c>
+      <c r="D612" s="4" t="n">
+        <v>7622</v>
+      </c>
+      <c r="E612" s="4" t="n">
+        <v>7324.5</v>
+      </c>
+      <c r="F612" s="4" t="n">
+        <v>-238.5</v>
+      </c>
+      <c r="G612" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H612" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C613" s="3" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D613" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E613" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="F613" s="4" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G613" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H613" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B540" s="9" t="n"/>
-      <c r="C540" s="9" t="n"/>
-      <c r="D540" s="9" t="n"/>
-      <c r="E540" s="9" t="n"/>
-      <c r="F540" s="9" t="n"/>
-      <c r="G540" s="9" t="n"/>
-      <c r="H540" s="9" t="n"/>
-    </row>
-    <row r="541">
-      <c r="B541" s="2" t="inlineStr">
+      <c r="B615" s="9" t="n"/>
+      <c r="C615" s="9" t="n"/>
+      <c r="D615" s="9" t="n"/>
+      <c r="E615" s="9" t="n"/>
+      <c r="F615" s="9" t="n"/>
+      <c r="G615" s="9" t="n"/>
+      <c r="H615" s="9" t="n"/>
+    </row>
+    <row r="616">
+      <c r="B616" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C541" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$541),"")</f>
-        <v/>
-      </c>
-      <c r="D541" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$541),"")</f>
-        <v/>
-      </c>
-      <c r="E541" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$541),"")</f>
-        <v/>
-      </c>
-      <c r="F541" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$541)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="542">
-      <c r="B542" s="2" t="inlineStr">
+      <c r="C616" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$616),"")</f>
+        <v/>
+      </c>
+      <c r="D616" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$616),"")</f>
+        <v/>
+      </c>
+      <c r="E616" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$616),"")</f>
+        <v/>
+      </c>
+      <c r="F616" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$616)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C542" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$542),"")</f>
-        <v/>
-      </c>
-      <c r="D542" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$542),"")</f>
-        <v/>
-      </c>
-      <c r="E542" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$542),"")</f>
-        <v/>
-      </c>
-      <c r="F542" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$542)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="543">
-      <c r="B543" s="2" t="inlineStr">
+      <c r="C617" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$617),"")</f>
+        <v/>
+      </c>
+      <c r="D617" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$617),"")</f>
+        <v/>
+      </c>
+      <c r="E617" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$617),"")</f>
+        <v/>
+      </c>
+      <c r="F617" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$617)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C543" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$543),"")</f>
-        <v/>
-      </c>
-      <c r="D543" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$543),"")</f>
-        <v/>
-      </c>
-      <c r="E543" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$543),"")</f>
-        <v/>
-      </c>
-      <c r="F543" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$543)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="544">
-      <c r="B544" s="2" t="inlineStr">
+      <c r="C618" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$618),"")</f>
+        <v/>
+      </c>
+      <c r="D618" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$618),"")</f>
+        <v/>
+      </c>
+      <c r="E618" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$618),"")</f>
+        <v/>
+      </c>
+      <c r="F618" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$618)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C544" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$544),"")</f>
-        <v/>
-      </c>
-      <c r="D544" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$544),"")</f>
-        <v/>
-      </c>
-      <c r="E544" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$544),"")</f>
-        <v/>
-      </c>
-      <c r="F544" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$544)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="545">
-      <c r="B545" s="2" t="inlineStr">
+      <c r="C619" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$619),"")</f>
+        <v/>
+      </c>
+      <c r="D619" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$619),"")</f>
+        <v/>
+      </c>
+      <c r="E619" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$619),"")</f>
+        <v/>
+      </c>
+      <c r="F619" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$619)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C545" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$545),"")</f>
-        <v/>
-      </c>
-      <c r="D545" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$545),"")</f>
-        <v/>
-      </c>
-      <c r="E545" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$545),"")</f>
-        <v/>
-      </c>
-      <c r="F545" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$545)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="546">
-      <c r="B546" s="2" t="inlineStr">
+      <c r="C620" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$620),"")</f>
+        <v/>
+      </c>
+      <c r="D620" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$620),"")</f>
+        <v/>
+      </c>
+      <c r="E620" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$620),"")</f>
+        <v/>
+      </c>
+      <c r="F620" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$620)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C546" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$546),"")</f>
-        <v/>
-      </c>
-      <c r="D546" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$546),"")</f>
-        <v/>
-      </c>
-      <c r="E546" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$546),"")</f>
-        <v/>
-      </c>
-      <c r="F546" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$546)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="547">
-      <c r="B547" s="2" t="inlineStr">
+      <c r="C621" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$621),"")</f>
+        <v/>
+      </c>
+      <c r="D621" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$621),"")</f>
+        <v/>
+      </c>
+      <c r="E621" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$621),"")</f>
+        <v/>
+      </c>
+      <c r="F621" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$621)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C547" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$547),"")</f>
-        <v/>
-      </c>
-      <c r="D547" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$547),"")</f>
-        <v/>
-      </c>
-      <c r="E547" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$547),"")</f>
-        <v/>
-      </c>
-      <c r="F547" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$547)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="548">
-      <c r="B548" s="2" t="inlineStr">
+      <c r="C622" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$622),"")</f>
+        <v/>
+      </c>
+      <c r="D622" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$622),"")</f>
+        <v/>
+      </c>
+      <c r="E622" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$622),"")</f>
+        <v/>
+      </c>
+      <c r="F622" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$622)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C548" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$548),"")</f>
-        <v/>
-      </c>
-      <c r="D548" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$548),"")</f>
-        <v/>
-      </c>
-      <c r="E548" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$548),"")</f>
-        <v/>
-      </c>
-      <c r="F548" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$548)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="549">
-      <c r="B549" s="2" t="inlineStr">
+      <c r="C623" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$623),"")</f>
+        <v/>
+      </c>
+      <c r="D623" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$623),"")</f>
+        <v/>
+      </c>
+      <c r="E623" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$623),"")</f>
+        <v/>
+      </c>
+      <c r="F623" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$623)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C549" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$549),"")</f>
-        <v/>
-      </c>
-      <c r="D549" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$549),"")</f>
-        <v/>
-      </c>
-      <c r="E549" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$549),"")</f>
-        <v/>
-      </c>
-      <c r="F549" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$549)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="550">
-      <c r="B550" s="2" t="inlineStr">
+      <c r="C624" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$624),"")</f>
+        <v/>
+      </c>
+      <c r="D624" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$624),"")</f>
+        <v/>
+      </c>
+      <c r="E624" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$624),"")</f>
+        <v/>
+      </c>
+      <c r="F624" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$624)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C550" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$550),"")</f>
-        <v/>
-      </c>
-      <c r="D550" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$550),"")</f>
-        <v/>
-      </c>
-      <c r="E550" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$550),"")</f>
-        <v/>
-      </c>
-      <c r="F550" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$550)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="551">
-      <c r="B551" s="2" t="inlineStr">
+      <c r="C625" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$625),"")</f>
+        <v/>
+      </c>
+      <c r="D625" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$625),"")</f>
+        <v/>
+      </c>
+      <c r="E625" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$625),"")</f>
+        <v/>
+      </c>
+      <c r="F625" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$625)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C551" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$551),"")</f>
-        <v/>
-      </c>
-      <c r="D551" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$551),"")</f>
-        <v/>
-      </c>
-      <c r="E551" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$551),"")</f>
-        <v/>
-      </c>
-      <c r="F551" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$551)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="552">
-      <c r="B552" s="2" t="inlineStr">
+      <c r="C626" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$626),"")</f>
+        <v/>
+      </c>
+      <c r="D626" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$626),"")</f>
+        <v/>
+      </c>
+      <c r="E626" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$626),"")</f>
+        <v/>
+      </c>
+      <c r="F626" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$626)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C552" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$552),"")</f>
-        <v/>
-      </c>
-      <c r="D552" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$552),"")</f>
-        <v/>
-      </c>
-      <c r="E552" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$552),"")</f>
-        <v/>
-      </c>
-      <c r="F552" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$552)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="553">
-      <c r="B553" s="2" t="inlineStr">
+      <c r="C627" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$627),"")</f>
+        <v/>
+      </c>
+      <c r="D627" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$627),"")</f>
+        <v/>
+      </c>
+      <c r="E627" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$627),"")</f>
+        <v/>
+      </c>
+      <c r="F627" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$627)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C553" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$553),"")</f>
-        <v/>
-      </c>
-      <c r="D553" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$553),"")</f>
-        <v/>
-      </c>
-      <c r="E553" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$553),"")</f>
-        <v/>
-      </c>
-      <c r="F553" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$553)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="554">
-      <c r="B554" s="2" t="inlineStr">
+      <c r="C628" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$628),"")</f>
+        <v/>
+      </c>
+      <c r="D628" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$628),"")</f>
+        <v/>
+      </c>
+      <c r="E628" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$628),"")</f>
+        <v/>
+      </c>
+      <c r="F628" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$628)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C554" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$554),"")</f>
-        <v/>
-      </c>
-      <c r="D554" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$554),"")</f>
-        <v/>
-      </c>
-      <c r="E554" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$554),"")</f>
-        <v/>
-      </c>
-      <c r="F554" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$554)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="555">
-      <c r="B555" s="2" t="inlineStr">
+      <c r="C629" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$629),"")</f>
+        <v/>
+      </c>
+      <c r="D629" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$629),"")</f>
+        <v/>
+      </c>
+      <c r="E629" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$629),"")</f>
+        <v/>
+      </c>
+      <c r="F629" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$629)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C555" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$555),"")</f>
-        <v/>
-      </c>
-      <c r="D555" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$555),"")</f>
-        <v/>
-      </c>
-      <c r="E555" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$555),"")</f>
-        <v/>
-      </c>
-      <c r="F555" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$555)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="556">
-      <c r="B556" s="2" t="inlineStr">
+      <c r="C630" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$630),"")</f>
+        <v/>
+      </c>
+      <c r="D630" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$630),"")</f>
+        <v/>
+      </c>
+      <c r="E630" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$630),"")</f>
+        <v/>
+      </c>
+      <c r="F630" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$630)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C556" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$556),"")</f>
-        <v/>
-      </c>
-      <c r="D556" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$556),"")</f>
-        <v/>
-      </c>
-      <c r="E556" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$556),"")</f>
-        <v/>
-      </c>
-      <c r="F556" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$556)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="557">
-      <c r="B557" s="2" t="inlineStr">
+      <c r="C631" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$631),"")</f>
+        <v/>
+      </c>
+      <c r="D631" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$631),"")</f>
+        <v/>
+      </c>
+      <c r="E631" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$631),"")</f>
+        <v/>
+      </c>
+      <c r="F631" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$631)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C557" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$557),"")</f>
-        <v/>
-      </c>
-      <c r="D557" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$557),"")</f>
-        <v/>
-      </c>
-      <c r="E557" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$557),"")</f>
-        <v/>
-      </c>
-      <c r="F557" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$557)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="558">
-      <c r="B558" s="2" t="inlineStr">
+      <c r="C632" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$632),"")</f>
+        <v/>
+      </c>
+      <c r="D632" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$632),"")</f>
+        <v/>
+      </c>
+      <c r="E632" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$632),"")</f>
+        <v/>
+      </c>
+      <c r="F632" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$632)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C558" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$558),"")</f>
-        <v/>
-      </c>
-      <c r="D558" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$558),"")</f>
-        <v/>
-      </c>
-      <c r="E558" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$558),"")</f>
-        <v/>
-      </c>
-      <c r="F558" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$558)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="559">
-      <c r="B559" s="2" t="inlineStr">
+      <c r="C633" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$633),"")</f>
+        <v/>
+      </c>
+      <c r="D633" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$633),"")</f>
+        <v/>
+      </c>
+      <c r="E633" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$633),"")</f>
+        <v/>
+      </c>
+      <c r="F633" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$633)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C559" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$559),"")</f>
-        <v/>
-      </c>
-      <c r="D559" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$559),"")</f>
-        <v/>
-      </c>
-      <c r="E559" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$559),"")</f>
-        <v/>
-      </c>
-      <c r="F559" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$559)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="560">
-      <c r="B560" s="2" t="inlineStr">
+      <c r="C634" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$634),"")</f>
+        <v/>
+      </c>
+      <c r="D634" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$634),"")</f>
+        <v/>
+      </c>
+      <c r="E634" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$634),"")</f>
+        <v/>
+      </c>
+      <c r="F634" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$634)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C560" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$560),"")</f>
-        <v/>
-      </c>
-      <c r="D560" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$560),"")</f>
-        <v/>
-      </c>
-      <c r="E560" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$560),"")</f>
-        <v/>
-      </c>
-      <c r="F560" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$560)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="561">
-      <c r="B561" s="2" t="inlineStr">
+      <c r="C635" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$635),"")</f>
+        <v/>
+      </c>
+      <c r="D635" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$635),"")</f>
+        <v/>
+      </c>
+      <c r="E635" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$635),"")</f>
+        <v/>
+      </c>
+      <c r="F635" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$635)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C561" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$561),"")</f>
-        <v/>
-      </c>
-      <c r="D561" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$561),"")</f>
-        <v/>
-      </c>
-      <c r="E561" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$561),"")</f>
-        <v/>
-      </c>
-      <c r="F561" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$561)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="562">
-      <c r="B562" s="2" t="inlineStr">
+      <c r="C636" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$636),"")</f>
+        <v/>
+      </c>
+      <c r="D636" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$636),"")</f>
+        <v/>
+      </c>
+      <c r="E636" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$636),"")</f>
+        <v/>
+      </c>
+      <c r="F636" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$636)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C562" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$562),"")</f>
-        <v/>
-      </c>
-      <c r="D562" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$562),"")</f>
-        <v/>
-      </c>
-      <c r="E562" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$562),"")</f>
-        <v/>
-      </c>
-      <c r="F562" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$562)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="563">
-      <c r="B563" s="2" t="inlineStr">
+      <c r="C637" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$637),"")</f>
+        <v/>
+      </c>
+      <c r="D637" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$637),"")</f>
+        <v/>
+      </c>
+      <c r="E637" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$637),"")</f>
+        <v/>
+      </c>
+      <c r="F637" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$637)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C563" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$563),"")</f>
-        <v/>
-      </c>
-      <c r="D563" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$563),"")</f>
-        <v/>
-      </c>
-      <c r="E563" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$563),"")</f>
-        <v/>
-      </c>
-      <c r="F563" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$563)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="564">
-      <c r="B564" s="2" t="inlineStr">
+      <c r="C638" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$638),"")</f>
+        <v/>
+      </c>
+      <c r="D638" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$638),"")</f>
+        <v/>
+      </c>
+      <c r="E638" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$638),"")</f>
+        <v/>
+      </c>
+      <c r="F638" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$638)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C564" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$564),"")</f>
-        <v/>
-      </c>
-      <c r="D564" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$564),"")</f>
-        <v/>
-      </c>
-      <c r="E564" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$564),"")</f>
-        <v/>
-      </c>
-      <c r="F564" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$564)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="565">
-      <c r="B565" s="2" t="inlineStr">
+      <c r="C639" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$639),"")</f>
+        <v/>
+      </c>
+      <c r="D639" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$639),"")</f>
+        <v/>
+      </c>
+      <c r="E639" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$639),"")</f>
+        <v/>
+      </c>
+      <c r="F639" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$639)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C565" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$565),"")</f>
-        <v/>
-      </c>
-      <c r="D565" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$565),"")</f>
-        <v/>
-      </c>
-      <c r="E565" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$565),"")</f>
-        <v/>
-      </c>
-      <c r="F565" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$565)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="566">
-      <c r="B566" s="2" t="inlineStr">
+      <c r="C640" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$640),"")</f>
+        <v/>
+      </c>
+      <c r="D640" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$640),"")</f>
+        <v/>
+      </c>
+      <c r="E640" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$640),"")</f>
+        <v/>
+      </c>
+      <c r="F640" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$640)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C566" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$566),"")</f>
-        <v/>
-      </c>
-      <c r="D566" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$566),"")</f>
-        <v/>
-      </c>
-      <c r="E566" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$566),"")</f>
-        <v/>
-      </c>
-      <c r="F566" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$566)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="567">
-      <c r="B567" s="2" t="inlineStr">
+      <c r="C641" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$641),"")</f>
+        <v/>
+      </c>
+      <c r="D641" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$641),"")</f>
+        <v/>
+      </c>
+      <c r="E641" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$641),"")</f>
+        <v/>
+      </c>
+      <c r="F641" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$641)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C567" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$567),"")</f>
-        <v/>
-      </c>
-      <c r="D567" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$567),"")</f>
-        <v/>
-      </c>
-      <c r="E567" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$567),"")</f>
-        <v/>
-      </c>
-      <c r="F567" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$567)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="568">
-      <c r="B568" s="2" t="inlineStr">
+      <c r="C642" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$642),"")</f>
+        <v/>
+      </c>
+      <c r="D642" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$642),"")</f>
+        <v/>
+      </c>
+      <c r="E642" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$642),"")</f>
+        <v/>
+      </c>
+      <c r="F642" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$642)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C568" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$568),"")</f>
-        <v/>
-      </c>
-      <c r="D568" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$568),"")</f>
-        <v/>
-      </c>
-      <c r="E568" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$568),"")</f>
-        <v/>
-      </c>
-      <c r="F568" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$568)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="569">
-      <c r="B569" s="2" t="inlineStr">
+      <c r="C643" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$643),"")</f>
+        <v/>
+      </c>
+      <c r="D643" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$643),"")</f>
+        <v/>
+      </c>
+      <c r="E643" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$643),"")</f>
+        <v/>
+      </c>
+      <c r="F643" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$643)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C569" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$569),"")</f>
-        <v/>
-      </c>
-      <c r="D569" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$569),"")</f>
-        <v/>
-      </c>
-      <c r="E569" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$569),"")</f>
-        <v/>
-      </c>
-      <c r="F569" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$569)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="570">
-      <c r="B570" s="2" t="inlineStr">
+      <c r="C644" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$644),"")</f>
+        <v/>
+      </c>
+      <c r="D644" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$644),"")</f>
+        <v/>
+      </c>
+      <c r="E644" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$644),"")</f>
+        <v/>
+      </c>
+      <c r="F644" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$644)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C570" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$570),"")</f>
-        <v/>
-      </c>
-      <c r="D570" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$570),"")</f>
-        <v/>
-      </c>
-      <c r="E570" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$570),"")</f>
-        <v/>
-      </c>
-      <c r="F570" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$570)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="571">
-      <c r="B571" s="2" t="inlineStr">
+      <c r="C645" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$645),"")</f>
+        <v/>
+      </c>
+      <c r="D645" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$645),"")</f>
+        <v/>
+      </c>
+      <c r="E645" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$645),"")</f>
+        <v/>
+      </c>
+      <c r="F645" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$645)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C571" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$571),"")</f>
-        <v/>
-      </c>
-      <c r="D571" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$571),"")</f>
-        <v/>
-      </c>
-      <c r="E571" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$571),"")</f>
-        <v/>
-      </c>
-      <c r="F571" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$571)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="572">
-      <c r="B572" s="2" t="inlineStr">
+      <c r="C646" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$646),"")</f>
+        <v/>
+      </c>
+      <c r="D646" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$646),"")</f>
+        <v/>
+      </c>
+      <c r="E646" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$646),"")</f>
+        <v/>
+      </c>
+      <c r="F646" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$646)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C572" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$572),"")</f>
-        <v/>
-      </c>
-      <c r="D572" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$572),"")</f>
-        <v/>
-      </c>
-      <c r="E572" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$572),"")</f>
-        <v/>
-      </c>
-      <c r="F572" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$572)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="573">
-      <c r="B573" s="2" t="inlineStr">
+      <c r="C647" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$647),"")</f>
+        <v/>
+      </c>
+      <c r="D647" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$647),"")</f>
+        <v/>
+      </c>
+      <c r="E647" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$647),"")</f>
+        <v/>
+      </c>
+      <c r="F647" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$647)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C573" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$573),"")</f>
-        <v/>
-      </c>
-      <c r="D573" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$573),"")</f>
-        <v/>
-      </c>
-      <c r="E573" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$573),"")</f>
-        <v/>
-      </c>
-      <c r="F573" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$573)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="574">
-      <c r="B574" s="2" t="inlineStr">
+      <c r="C648" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$648),"")</f>
+        <v/>
+      </c>
+      <c r="D648" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$648),"")</f>
+        <v/>
+      </c>
+      <c r="E648" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$648),"")</f>
+        <v/>
+      </c>
+      <c r="F648" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$648)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C574" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$574),"")</f>
-        <v/>
-      </c>
-      <c r="D574" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$574),"")</f>
-        <v/>
-      </c>
-      <c r="E574" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$574),"")</f>
-        <v/>
-      </c>
-      <c r="F574" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$574)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="575">
-      <c r="B575" s="2" t="inlineStr">
+      <c r="C649" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$649),"")</f>
+        <v/>
+      </c>
+      <c r="D649" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$649),"")</f>
+        <v/>
+      </c>
+      <c r="E649" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$649),"")</f>
+        <v/>
+      </c>
+      <c r="F649" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$649)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C575" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$575),"")</f>
-        <v/>
-      </c>
-      <c r="D575" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$575),"")</f>
-        <v/>
-      </c>
-      <c r="E575" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$575),"")</f>
-        <v/>
-      </c>
-      <c r="F575" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$575)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="576">
-      <c r="B576" s="2" t="inlineStr">
+      <c r="C650" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$650),"")</f>
+        <v/>
+      </c>
+      <c r="D650" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$650),"")</f>
+        <v/>
+      </c>
+      <c r="E650" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$650),"")</f>
+        <v/>
+      </c>
+      <c r="F650" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$650)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C576" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$576),"")</f>
-        <v/>
-      </c>
-      <c r="D576" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$576),"")</f>
-        <v/>
-      </c>
-      <c r="E576" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$576),"")</f>
-        <v/>
-      </c>
-      <c r="F576" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$576)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="577">
-      <c r="B577" s="2" t="inlineStr">
+      <c r="C651" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$651),"")</f>
+        <v/>
+      </c>
+      <c r="D651" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$651),"")</f>
+        <v/>
+      </c>
+      <c r="E651" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$651),"")</f>
+        <v/>
+      </c>
+      <c r="F651" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$651)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C577" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$577),"")</f>
-        <v/>
-      </c>
-      <c r="D577" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$577),"")</f>
-        <v/>
-      </c>
-      <c r="E577" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$577),"")</f>
-        <v/>
-      </c>
-      <c r="F577" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$577)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="578">
-      <c r="B578" s="2" t="inlineStr">
+      <c r="C652" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$652),"")</f>
+        <v/>
+      </c>
+      <c r="D652" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$652),"")</f>
+        <v/>
+      </c>
+      <c r="E652" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$652),"")</f>
+        <v/>
+      </c>
+      <c r="F652" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$652)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C578" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$578),"")</f>
-        <v/>
-      </c>
-      <c r="D578" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$578),"")</f>
-        <v/>
-      </c>
-      <c r="E578" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$578),"")</f>
-        <v/>
-      </c>
-      <c r="F578" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$578)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="579">
-      <c r="B579" s="2" t="inlineStr">
+      <c r="C653" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$653),"")</f>
+        <v/>
+      </c>
+      <c r="D653" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$653),"")</f>
+        <v/>
+      </c>
+      <c r="E653" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$653),"")</f>
+        <v/>
+      </c>
+      <c r="F653" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$653)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C579" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$579),"")</f>
-        <v/>
-      </c>
-      <c r="D579" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$579),"")</f>
-        <v/>
-      </c>
-      <c r="E579" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$579),"")</f>
-        <v/>
-      </c>
-      <c r="F579" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$579)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="580">
-      <c r="B580" s="2" t="inlineStr">
+      <c r="C654" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$654),"")</f>
+        <v/>
+      </c>
+      <c r="D654" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$654),"")</f>
+        <v/>
+      </c>
+      <c r="E654" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$654),"")</f>
+        <v/>
+      </c>
+      <c r="F654" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$654)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C580" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$580),"")</f>
-        <v/>
-      </c>
-      <c r="D580" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$580),"")</f>
-        <v/>
-      </c>
-      <c r="E580" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$580),"")</f>
-        <v/>
-      </c>
-      <c r="F580" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$580)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="581">
-      <c r="B581" s="2" t="inlineStr">
+      <c r="C655" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$655),"")</f>
+        <v/>
+      </c>
+      <c r="D655" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$655),"")</f>
+        <v/>
+      </c>
+      <c r="E655" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$655),"")</f>
+        <v/>
+      </c>
+      <c r="F655" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$655)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C581" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$581),"")</f>
-        <v/>
-      </c>
-      <c r="D581" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$581),"")</f>
-        <v/>
-      </c>
-      <c r="E581" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$581),"")</f>
-        <v/>
-      </c>
-      <c r="F581" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$581)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="582">
-      <c r="B582" s="2" t="inlineStr">
+      <c r="C656" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$656),"")</f>
+        <v/>
+      </c>
+      <c r="D656" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$656),"")</f>
+        <v/>
+      </c>
+      <c r="E656" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$656),"")</f>
+        <v/>
+      </c>
+      <c r="F656" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$656)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C582" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$582),"")</f>
-        <v/>
-      </c>
-      <c r="D582" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$582),"")</f>
-        <v/>
-      </c>
-      <c r="E582" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$582),"")</f>
-        <v/>
-      </c>
-      <c r="F582" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$582)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="583">
-      <c r="B583" s="2" t="inlineStr">
+      <c r="C657" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$657),"")</f>
+        <v/>
+      </c>
+      <c r="D657" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$657),"")</f>
+        <v/>
+      </c>
+      <c r="E657" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$657),"")</f>
+        <v/>
+      </c>
+      <c r="F657" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$657)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C583" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$583),"")</f>
-        <v/>
-      </c>
-      <c r="D583" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$583),"")</f>
-        <v/>
-      </c>
-      <c r="E583" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$583),"")</f>
-        <v/>
-      </c>
-      <c r="F583" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$583)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="584">
-      <c r="B584" s="2" t="inlineStr">
+      <c r="C658" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$658),"")</f>
+        <v/>
+      </c>
+      <c r="D658" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$658),"")</f>
+        <v/>
+      </c>
+      <c r="E658" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$658),"")</f>
+        <v/>
+      </c>
+      <c r="F658" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$658)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C584" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$584),"")</f>
-        <v/>
-      </c>
-      <c r="D584" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$584),"")</f>
-        <v/>
-      </c>
-      <c r="E584" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$584),"")</f>
-        <v/>
-      </c>
-      <c r="F584" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$584)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="585">
-      <c r="B585" s="2" t="inlineStr">
+      <c r="C659" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$659),"")</f>
+        <v/>
+      </c>
+      <c r="D659" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$659),"")</f>
+        <v/>
+      </c>
+      <c r="E659" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$659),"")</f>
+        <v/>
+      </c>
+      <c r="F659" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$659)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C585" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$585),"")</f>
-        <v/>
-      </c>
-      <c r="D585" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$585),"")</f>
-        <v/>
-      </c>
-      <c r="E585" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$585),"")</f>
-        <v/>
-      </c>
-      <c r="F585" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$585)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="586">
-      <c r="B586" s="2" t="inlineStr">
+      <c r="C660" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$660),"")</f>
+        <v/>
+      </c>
+      <c r="D660" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$660),"")</f>
+        <v/>
+      </c>
+      <c r="E660" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$660),"")</f>
+        <v/>
+      </c>
+      <c r="F660" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$660)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="661">
+      <c r="B661" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C586" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$586),"")</f>
-        <v/>
-      </c>
-      <c r="D586" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$586),"")</f>
-        <v/>
-      </c>
-      <c r="E586" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$586),"")</f>
-        <v/>
-      </c>
-      <c r="F586" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$586)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="587">
-      <c r="B587" s="2" t="inlineStr">
+      <c r="C661" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$661),"")</f>
+        <v/>
+      </c>
+      <c r="D661" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$661),"")</f>
+        <v/>
+      </c>
+      <c r="E661" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$661),"")</f>
+        <v/>
+      </c>
+      <c r="F661" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$661)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="662">
+      <c r="B662" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C587" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$587),"")</f>
-        <v/>
-      </c>
-      <c r="D587" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$587),"")</f>
-        <v/>
-      </c>
-      <c r="E587" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$587),"")</f>
-        <v/>
-      </c>
-      <c r="F587" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$587)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="588">
-      <c r="B588" s="2" t="inlineStr">
+      <c r="C662" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$662),"")</f>
+        <v/>
+      </c>
+      <c r="D662" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$662),"")</f>
+        <v/>
+      </c>
+      <c r="E662" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$662),"")</f>
+        <v/>
+      </c>
+      <c r="F662" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$662)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="663">
+      <c r="B663" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C588" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$588),"")</f>
-        <v/>
-      </c>
-      <c r="D588" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$588),"")</f>
-        <v/>
-      </c>
-      <c r="E588" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$588),"")</f>
-        <v/>
-      </c>
-      <c r="F588" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$588)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="589">
-      <c r="B589" s="2" t="inlineStr">
+      <c r="C663" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$663),"")</f>
+        <v/>
+      </c>
+      <c r="D663" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$663),"")</f>
+        <v/>
+      </c>
+      <c r="E663" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$663),"")</f>
+        <v/>
+      </c>
+      <c r="F663" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$663)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="664">
+      <c r="B664" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C589" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$589),"")</f>
-        <v/>
-      </c>
-      <c r="D589" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$589),"")</f>
-        <v/>
-      </c>
-      <c r="E589" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$589),"")</f>
-        <v/>
-      </c>
-      <c r="F589" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$589)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="590">
-      <c r="B590" s="2" t="inlineStr">
+      <c r="C664" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$664),"")</f>
+        <v/>
+      </c>
+      <c r="D664" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$664),"")</f>
+        <v/>
+      </c>
+      <c r="E664" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$664),"")</f>
+        <v/>
+      </c>
+      <c r="F664" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$664)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="665">
+      <c r="B665" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C590" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$590),"")</f>
-        <v/>
-      </c>
-      <c r="D590" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$590),"")</f>
-        <v/>
-      </c>
-      <c r="E590" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$590),"")</f>
-        <v/>
-      </c>
-      <c r="F590" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$590)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="591">
-      <c r="B591" s="2" t="inlineStr">
+      <c r="C665" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$665),"")</f>
+        <v/>
+      </c>
+      <c r="D665" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$665),"")</f>
+        <v/>
+      </c>
+      <c r="E665" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$665),"")</f>
+        <v/>
+      </c>
+      <c r="F665" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$665)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="666">
+      <c r="B666" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C591" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$591),"")</f>
-        <v/>
-      </c>
-      <c r="D591" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$591),"")</f>
-        <v/>
-      </c>
-      <c r="E591" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$591),"")</f>
-        <v/>
-      </c>
-      <c r="F591" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$591)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="592">
-      <c r="B592" s="2" t="inlineStr">
+      <c r="C666" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$666),"")</f>
+        <v/>
+      </c>
+      <c r="D666" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$666),"")</f>
+        <v/>
+      </c>
+      <c r="E666" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$666),"")</f>
+        <v/>
+      </c>
+      <c r="F666" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$666)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="667">
+      <c r="B667" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C592" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$592),"")</f>
-        <v/>
-      </c>
-      <c r="D592" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$592),"")</f>
-        <v/>
-      </c>
-      <c r="E592" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$592),"")</f>
-        <v/>
-      </c>
-      <c r="F592" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$592)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="593">
-      <c r="B593" s="2" t="inlineStr">
+      <c r="C667" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$667),"")</f>
+        <v/>
+      </c>
+      <c r="D667" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$667),"")</f>
+        <v/>
+      </c>
+      <c r="E667" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$667),"")</f>
+        <v/>
+      </c>
+      <c r="F667" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$667)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="668">
+      <c r="B668" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C593" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$593),"")</f>
-        <v/>
-      </c>
-      <c r="D593" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$593),"")</f>
-        <v/>
-      </c>
-      <c r="E593" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$593),"")</f>
-        <v/>
-      </c>
-      <c r="F593" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$593)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="594">
-      <c r="B594" s="2" t="inlineStr">
+      <c r="C668" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$668),"")</f>
+        <v/>
+      </c>
+      <c r="D668" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$668),"")</f>
+        <v/>
+      </c>
+      <c r="E668" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$668),"")</f>
+        <v/>
+      </c>
+      <c r="F668" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$668)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="669">
+      <c r="B669" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C594" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$594),"")</f>
-        <v/>
-      </c>
-      <c r="D594" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$594),"")</f>
-        <v/>
-      </c>
-      <c r="E594" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$594),"")</f>
-        <v/>
-      </c>
-      <c r="F594" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$594)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="595">
-      <c r="B595" s="2" t="inlineStr">
+      <c r="C669" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$669),"")</f>
+        <v/>
+      </c>
+      <c r="D669" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$669),"")</f>
+        <v/>
+      </c>
+      <c r="E669" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$669),"")</f>
+        <v/>
+      </c>
+      <c r="F669" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$669)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="670">
+      <c r="B670" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C595" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$595),"")</f>
-        <v/>
-      </c>
-      <c r="D595" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$595),"")</f>
-        <v/>
-      </c>
-      <c r="E595" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$595),"")</f>
-        <v/>
-      </c>
-      <c r="F595" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$595)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="596">
-      <c r="B596" s="2" t="inlineStr">
+      <c r="C670" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$670),"")</f>
+        <v/>
+      </c>
+      <c r="D670" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$670),"")</f>
+        <v/>
+      </c>
+      <c r="E670" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$670),"")</f>
+        <v/>
+      </c>
+      <c r="F670" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$670)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="671">
+      <c r="B671" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C596" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$596),"")</f>
-        <v/>
-      </c>
-      <c r="D596" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$596),"")</f>
-        <v/>
-      </c>
-      <c r="E596" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$596),"")</f>
-        <v/>
-      </c>
-      <c r="F596" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$596)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="597">
-      <c r="B597" s="2" t="inlineStr">
+      <c r="C671" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$671),"")</f>
+        <v/>
+      </c>
+      <c r="D671" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$671),"")</f>
+        <v/>
+      </c>
+      <c r="E671" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$671),"")</f>
+        <v/>
+      </c>
+      <c r="F671" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$671)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="672">
+      <c r="B672" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C597" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$597),"")</f>
-        <v/>
-      </c>
-      <c r="D597" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$597),"")</f>
-        <v/>
-      </c>
-      <c r="E597" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$597),"")</f>
-        <v/>
-      </c>
-      <c r="F597" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$597)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="598">
-      <c r="B598" s="2" t="inlineStr">
+      <c r="C672" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$672),"")</f>
+        <v/>
+      </c>
+      <c r="D672" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$672),"")</f>
+        <v/>
+      </c>
+      <c r="E672" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$672),"")</f>
+        <v/>
+      </c>
+      <c r="F672" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$672)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="673">
+      <c r="B673" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C598" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$598),"")</f>
-        <v/>
-      </c>
-      <c r="D598" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$598),"")</f>
-        <v/>
-      </c>
-      <c r="E598" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$598),"")</f>
-        <v/>
-      </c>
-      <c r="F598" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$598)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="599">
-      <c r="B599" s="2" t="inlineStr">
+      <c r="C673" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$673),"")</f>
+        <v/>
+      </c>
+      <c r="D673" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$673),"")</f>
+        <v/>
+      </c>
+      <c r="E673" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$673),"")</f>
+        <v/>
+      </c>
+      <c r="F673" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$673)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="674">
+      <c r="B674" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C599" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$599),"")</f>
-        <v/>
-      </c>
-      <c r="D599" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$599),"")</f>
-        <v/>
-      </c>
-      <c r="E599" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$599),"")</f>
-        <v/>
-      </c>
-      <c r="F599" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$599)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="600">
-      <c r="B600" s="2" t="inlineStr">
+      <c r="C674" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$674),"")</f>
+        <v/>
+      </c>
+      <c r="D674" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$674),"")</f>
+        <v/>
+      </c>
+      <c r="E674" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$674),"")</f>
+        <v/>
+      </c>
+      <c r="F674" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$674)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="675">
+      <c r="B675" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C600" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$600),"")</f>
-        <v/>
-      </c>
-      <c r="D600" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$600),"")</f>
-        <v/>
-      </c>
-      <c r="E600" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$600),"")</f>
-        <v/>
-      </c>
-      <c r="F600" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$600)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="601">
-      <c r="B601" s="2" t="inlineStr">
+      <c r="C675" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$675),"")</f>
+        <v/>
+      </c>
+      <c r="D675" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$675),"")</f>
+        <v/>
+      </c>
+      <c r="E675" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$675),"")</f>
+        <v/>
+      </c>
+      <c r="F675" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$675)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="676">
+      <c r="B676" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C601" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$601),"")</f>
-        <v/>
-      </c>
-      <c r="D601" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$601),"")</f>
-        <v/>
-      </c>
-      <c r="E601" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$601),"")</f>
-        <v/>
-      </c>
-      <c r="F601" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$601)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="602">
-      <c r="B602" s="2" t="inlineStr">
+      <c r="C676" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$676),"")</f>
+        <v/>
+      </c>
+      <c r="D676" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$676),"")</f>
+        <v/>
+      </c>
+      <c r="E676" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$676),"")</f>
+        <v/>
+      </c>
+      <c r="F676" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$676)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="677">
+      <c r="B677" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C602" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$602),"")</f>
-        <v/>
-      </c>
-      <c r="D602" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$602),"")</f>
-        <v/>
-      </c>
-      <c r="E602" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$602),"")</f>
-        <v/>
-      </c>
-      <c r="F602" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$602)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="603">
-      <c r="B603" s="2" t="inlineStr">
+      <c r="C677" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$677),"")</f>
+        <v/>
+      </c>
+      <c r="D677" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$677),"")</f>
+        <v/>
+      </c>
+      <c r="E677" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$677),"")</f>
+        <v/>
+      </c>
+      <c r="F677" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$677)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="678">
+      <c r="B678" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C603" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$603),"")</f>
-        <v/>
-      </c>
-      <c r="D603" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$603),"")</f>
-        <v/>
-      </c>
-      <c r="E603" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$603),"")</f>
-        <v/>
-      </c>
-      <c r="F603" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$603)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="604">
-      <c r="B604" s="2" t="inlineStr">
+      <c r="C678" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$678),"")</f>
+        <v/>
+      </c>
+      <c r="D678" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$678),"")</f>
+        <v/>
+      </c>
+      <c r="E678" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$678),"")</f>
+        <v/>
+      </c>
+      <c r="F678" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$678)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="679">
+      <c r="B679" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C604" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$604),"")</f>
-        <v/>
-      </c>
-      <c r="D604" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$604),"")</f>
-        <v/>
-      </c>
-      <c r="E604" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$604),"")</f>
-        <v/>
-      </c>
-      <c r="F604" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$604)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="605">
-      <c r="B605" s="2" t="inlineStr">
+      <c r="C679" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$679),"")</f>
+        <v/>
+      </c>
+      <c r="D679" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$679),"")</f>
+        <v/>
+      </c>
+      <c r="E679" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$679),"")</f>
+        <v/>
+      </c>
+      <c r="F679" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$679)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="680">
+      <c r="B680" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C605" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$605),"")</f>
-        <v/>
-      </c>
-      <c r="D605" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$605),"")</f>
-        <v/>
-      </c>
-      <c r="E605" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$605),"")</f>
-        <v/>
-      </c>
-      <c r="F605" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$605)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="606">
-      <c r="B606" s="2" t="inlineStr">
+      <c r="C680" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$680),"")</f>
+        <v/>
+      </c>
+      <c r="D680" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$680),"")</f>
+        <v/>
+      </c>
+      <c r="E680" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$680),"")</f>
+        <v/>
+      </c>
+      <c r="F680" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$680)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="681">
+      <c r="B681" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C606" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$606),"")</f>
-        <v/>
-      </c>
-      <c r="D606" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$606),"")</f>
-        <v/>
-      </c>
-      <c r="E606" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$606),"")</f>
-        <v/>
-      </c>
-      <c r="F606" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$606)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="607">
-      <c r="B607" s="2" t="inlineStr">
+      <c r="C681" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$681),"")</f>
+        <v/>
+      </c>
+      <c r="D681" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$681),"")</f>
+        <v/>
+      </c>
+      <c r="E681" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$681),"")</f>
+        <v/>
+      </c>
+      <c r="F681" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$681)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="682">
+      <c r="B682" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C607" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$607),"")</f>
-        <v/>
-      </c>
-      <c r="D607" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$607),"")</f>
-        <v/>
-      </c>
-      <c r="E607" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$607),"")</f>
-        <v/>
-      </c>
-      <c r="F607" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$607)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="608">
-      <c r="B608" s="2" t="inlineStr">
+      <c r="C682" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$682),"")</f>
+        <v/>
+      </c>
+      <c r="D682" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$682),"")</f>
+        <v/>
+      </c>
+      <c r="E682" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$682),"")</f>
+        <v/>
+      </c>
+      <c r="F682" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$682)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="683">
+      <c r="B683" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C608" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$608),"")</f>
-        <v/>
-      </c>
-      <c r="D608" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$608),"")</f>
-        <v/>
-      </c>
-      <c r="E608" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$608),"")</f>
-        <v/>
-      </c>
-      <c r="F608" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$608)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="609">
-      <c r="B609" s="2" t="inlineStr">
+      <c r="C683" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$683),"")</f>
+        <v/>
+      </c>
+      <c r="D683" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$683),"")</f>
+        <v/>
+      </c>
+      <c r="E683" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$683),"")</f>
+        <v/>
+      </c>
+      <c r="F683" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$683)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="684">
+      <c r="B684" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C609" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$609),"")</f>
-        <v/>
-      </c>
-      <c r="D609" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$609),"")</f>
-        <v/>
-      </c>
-      <c r="E609" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$609),"")</f>
-        <v/>
-      </c>
-      <c r="F609" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$609)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="610">
-      <c r="B610" s="2" t="inlineStr">
+      <c r="C684" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$684),"")</f>
+        <v/>
+      </c>
+      <c r="D684" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$684),"")</f>
+        <v/>
+      </c>
+      <c r="E684" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$684),"")</f>
+        <v/>
+      </c>
+      <c r="F684" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$684)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="685">
+      <c r="B685" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C610" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$610),"")</f>
-        <v/>
-      </c>
-      <c r="D610" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$610),"")</f>
-        <v/>
-      </c>
-      <c r="E610" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$610),"")</f>
-        <v/>
-      </c>
-      <c r="F610" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$610)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="611">
-      <c r="B611" s="2" t="inlineStr">
+      <c r="C685" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$685),"")</f>
+        <v/>
+      </c>
+      <c r="D685" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$685),"")</f>
+        <v/>
+      </c>
+      <c r="E685" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$685),"")</f>
+        <v/>
+      </c>
+      <c r="F685" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$685)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="686">
+      <c r="B686" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C611" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$611),"")</f>
-        <v/>
-      </c>
-      <c r="D611" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$611),"")</f>
-        <v/>
-      </c>
-      <c r="E611" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$611),"")</f>
-        <v/>
-      </c>
-      <c r="F611" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$611)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="612">
-      <c r="B612" s="2" t="inlineStr">
+      <c r="C686" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$686),"")</f>
+        <v/>
+      </c>
+      <c r="D686" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$686),"")</f>
+        <v/>
+      </c>
+      <c r="E686" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$686),"")</f>
+        <v/>
+      </c>
+      <c r="F686" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$686)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="687">
+      <c r="B687" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C612" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$612),"")</f>
-        <v/>
-      </c>
-      <c r="D612" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$612),"")</f>
-        <v/>
-      </c>
-      <c r="E612" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$612),"")</f>
-        <v/>
-      </c>
-      <c r="F612" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$612)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="613">
-      <c r="B613" s="2" t="inlineStr">
+      <c r="C687" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$687),"")</f>
+        <v/>
+      </c>
+      <c r="D687" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$687),"")</f>
+        <v/>
+      </c>
+      <c r="E687" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$687),"")</f>
+        <v/>
+      </c>
+      <c r="F687" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$687)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="688">
+      <c r="B688" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C613" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$613),"")</f>
-        <v/>
-      </c>
-      <c r="D613" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$613),"")</f>
-        <v/>
-      </c>
-      <c r="E613" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$613),"")</f>
-        <v/>
-      </c>
-      <c r="F613" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$613)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="614">
-      <c r="B614" s="2" t="inlineStr">
+      <c r="C688" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$688),"")</f>
+        <v/>
+      </c>
+      <c r="D688" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$688),"")</f>
+        <v/>
+      </c>
+      <c r="E688" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$688),"")</f>
+        <v/>
+      </c>
+      <c r="F688" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$688)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="689">
+      <c r="B689" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C614" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$614),"")</f>
-        <v/>
-      </c>
-      <c r="D614" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$614),"")</f>
-        <v/>
-      </c>
-      <c r="E614" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$614),"")</f>
-        <v/>
-      </c>
-      <c r="F614" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$614)*(F$2:F$538),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="615">
-      <c r="B615" s="2" t="inlineStr">
+      <c r="C689" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$689),"")</f>
+        <v/>
+      </c>
+      <c r="D689" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$689),"")</f>
+        <v/>
+      </c>
+      <c r="E689" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$689),"")</f>
+        <v/>
+      </c>
+      <c r="F689" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$689)*(F$2:F$613),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="690">
+      <c r="B690" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C615" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$615),"")</f>
-        <v/>
-      </c>
-      <c r="D615" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$615),"")</f>
-        <v/>
-      </c>
-      <c r="E615" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$538,A$2:A$538,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$538,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$538,$B$615),"")</f>
-        <v/>
-      </c>
-      <c r="F615" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$538)=YEAR(TODAY()))*(MONTH(A$2:A$538)=MONTH(TODAY()))*(B$2:B$538=$B$615)*(F$2:F$538),"")</f>
+      <c r="C690" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$690),"")</f>
+        <v/>
+      </c>
+      <c r="D690" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$690),"")</f>
+        <v/>
+      </c>
+      <c r="E690" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$690),"")</f>
+        <v/>
+      </c>
+      <c r="F690" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$690)*(F$2:F$613),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H538"/>
+  <autoFilter ref="A1:H613"/>
   <mergeCells count="1">
-    <mergeCell ref="A540:H540"/>
+    <mergeCell ref="A615:H615"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20696,7 +23246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22231,161 +24781,355 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>129060</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>129720</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>129060</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>127050</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>-1800</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>150200</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>155240</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>150220</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>145000</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>6.8001</v>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="6" t="n">
+        <v>6.7892</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>6.7851</v>
+      </c>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D42" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$42),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$42)*(H$2:H$39),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" s="2" t="inlineStr">
+      <c r="D47" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$47)*(H$2:H$44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D43" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$43),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$43)*(H$2:H$39),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" s="2" t="inlineStr">
+      <c r="D48" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$48)*(H$2:H$44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D44" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$44),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$44)*(H$2:H$39),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" s="2" t="inlineStr">
+      <c r="D49" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$49)*(H$2:H$44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>碳酸锂(LC)连续</t>
         </is>
       </c>
-      <c r="D45" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$45),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$45)*(H$2:H$39),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" s="2" t="inlineStr">
+      <c r="D50" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$50)*(H$2:H$44),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D46" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$39,A$2:A$39,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$39,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$39,$C$46),"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$39)=YEAR(TODAY()))*(MONTH(A$2:A$39)=MONTH(TODAY()))*(C$2:C$39=$C$46)*(H$2:H$39),"")</f>
+      <c r="D51" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$51)*(H$2:H$44),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J39"/>
+  <autoFilter ref="A1:J44"/>
   <mergeCells count="1">
-    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A46:J46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$613</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$688</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H690"/>
+  <dimension ref="A1:H765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21492,1749 +21492,4299 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C614" s="3" t="n">
+        <v>98300</v>
+      </c>
+      <c r="D614" s="4" t="n">
+        <v>103400</v>
+      </c>
+      <c r="E614" s="4" t="n">
+        <v>100850</v>
+      </c>
+      <c r="F614" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G614" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H614" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="615">
-      <c r="A615" s="8" t="inlineStr">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C615" s="3" t="n">
+        <v>179900</v>
+      </c>
+      <c r="D615" s="4" t="n">
+        <v>187000</v>
+      </c>
+      <c r="E615" s="4" t="n">
+        <v>183450</v>
+      </c>
+      <c r="F615" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G615" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H615" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C616" s="3" t="n">
+        <v>91200</v>
+      </c>
+      <c r="D616" s="4" t="n">
+        <v>95900</v>
+      </c>
+      <c r="E616" s="4" t="n">
+        <v>93550</v>
+      </c>
+      <c r="F616" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G616" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H616" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C617" s="3" t="n">
+        <v>182900</v>
+      </c>
+      <c r="D617" s="4" t="n">
+        <v>192400</v>
+      </c>
+      <c r="E617" s="4" t="n">
+        <v>187650</v>
+      </c>
+      <c r="F617" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G617" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H617" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C618" s="3" t="n">
+        <v>112700</v>
+      </c>
+      <c r="D618" s="4" t="n">
+        <v>118400</v>
+      </c>
+      <c r="E618" s="4" t="n">
+        <v>115550</v>
+      </c>
+      <c r="F618" s="4" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G618" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H618" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C619" s="3" t="n">
+        <v>205700</v>
+      </c>
+      <c r="D619" s="4" t="n">
+        <v>215300</v>
+      </c>
+      <c r="E619" s="4" t="n">
+        <v>210500</v>
+      </c>
+      <c r="F619" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G619" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H619" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C620" s="7" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D620" s="6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E620" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="F620" s="6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G620" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H620" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C621" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D621" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E621" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F621" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G621" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H621" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C622" s="3" t="n">
+        <v>204200</v>
+      </c>
+      <c r="D622" s="4" t="n">
+        <v>212700</v>
+      </c>
+      <c r="E622" s="4" t="n">
+        <v>208450</v>
+      </c>
+      <c r="F622" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G622" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H622" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C623" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D623" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E623" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F623" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G623" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H623" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C624" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D624" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E624" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F624" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G624" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H624" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C625" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D625" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E625" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F625" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G625" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H625" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C626" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D626" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E626" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F626" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G626" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H626" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C627" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D627" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E627" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F627" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G627" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H627" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C628" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D628" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E628" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F628" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G628" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H628" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C629" s="3" t="n">
+        <v>99957</v>
+      </c>
+      <c r="D629" s="4" t="n">
+        <v>104037</v>
+      </c>
+      <c r="E629" s="4" t="n">
+        <v>101997</v>
+      </c>
+      <c r="F629" s="4" t="n">
+        <v>-288.5</v>
+      </c>
+      <c r="G629" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H629" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C630" s="3" t="n">
+        <v>138755</v>
+      </c>
+      <c r="D630" s="4" t="n">
+        <v>138755</v>
+      </c>
+      <c r="E630" s="4" t="n">
+        <v>138755</v>
+      </c>
+      <c r="F630" s="4" t="n">
+        <v>-533</v>
+      </c>
+      <c r="G630" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C631" s="3" t="n">
+        <v>7679</v>
+      </c>
+      <c r="D631" s="4" t="n">
+        <v>7679</v>
+      </c>
+      <c r="E631" s="4" t="n">
+        <v>7679</v>
+      </c>
+      <c r="F631" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G631" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H631" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C632" s="3" t="n">
+        <v>32506</v>
+      </c>
+      <c r="D632" s="4" t="n">
+        <v>32506</v>
+      </c>
+      <c r="E632" s="4" t="n">
+        <v>32506</v>
+      </c>
+      <c r="F632" s="6" t="n">
+        <v>-45</v>
+      </c>
+      <c r="G632" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H632" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C633" s="3" t="n">
+        <v>149891</v>
+      </c>
+      <c r="D633" s="4" t="n">
+        <v>149891</v>
+      </c>
+      <c r="E633" s="4" t="n">
+        <v>149891</v>
+      </c>
+      <c r="F633" s="4" t="n">
+        <v>-2680</v>
+      </c>
+      <c r="G633" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H633" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C634" s="3" t="n">
+        <v>85772</v>
+      </c>
+      <c r="D634" s="4" t="n">
+        <v>85772</v>
+      </c>
+      <c r="E634" s="4" t="n">
+        <v>85772</v>
+      </c>
+      <c r="F634" s="4" t="n">
+        <v>-137</v>
+      </c>
+      <c r="G634" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H634" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C635" s="3" t="n">
+        <v>6802</v>
+      </c>
+      <c r="D635" s="4" t="n">
+        <v>6802</v>
+      </c>
+      <c r="E635" s="4" t="n">
+        <v>6802</v>
+      </c>
+      <c r="F635" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G635" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H635" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C636" s="3" t="n">
+        <v>6460</v>
+      </c>
+      <c r="D636" s="4" t="n">
+        <v>6460</v>
+      </c>
+      <c r="E636" s="4" t="n">
+        <v>6460</v>
+      </c>
+      <c r="F636" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G636" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H636" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C637" s="7" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="D637" s="6" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="E637" s="6" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="F637" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G637" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H637" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C638" s="7" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="D638" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="E638" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="F638" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G638" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H638" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C639" s="7" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="D639" s="6" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="E639" s="6" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="F639" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G639" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H639" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C640" s="7" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="D640" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="E640" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="F640" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G640" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H640" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C641" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D641" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E641" s="6" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="F641" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G641" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H641" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C642" s="3" t="n">
+        <v>105000</v>
+      </c>
+      <c r="D642" s="4" t="n">
+        <v>108000</v>
+      </c>
+      <c r="E642" s="4" t="n">
+        <v>106500</v>
+      </c>
+      <c r="F642" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G642" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H642" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B643" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C643" s="3" t="n">
+        <v>329000</v>
+      </c>
+      <c r="D643" s="4" t="n">
+        <v>341000</v>
+      </c>
+      <c r="E643" s="4" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F643" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G643" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H643" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B644" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C644" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D644" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E644" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F644" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G644" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H644" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B645" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C645" s="3" t="n">
+        <v>125000</v>
+      </c>
+      <c r="D645" s="4" t="n">
+        <v>128000</v>
+      </c>
+      <c r="E645" s="4" t="n">
+        <v>126500</v>
+      </c>
+      <c r="F645" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G645" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H645" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B646" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C646" s="3" t="n">
+        <v>141500</v>
+      </c>
+      <c r="D646" s="4" t="n">
+        <v>154000</v>
+      </c>
+      <c r="E646" s="4" t="n">
+        <v>147750</v>
+      </c>
+      <c r="F646" s="4" t="n">
+        <v>-750</v>
+      </c>
+      <c r="G646" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H646" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B647" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C647" s="3" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="D647" s="4" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="E647" s="4" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="F647" s="4" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="G647" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H647" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B648" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C648" s="3" t="n">
+        <v>2090</v>
+      </c>
+      <c r="D648" s="4" t="n">
+        <v>2240</v>
+      </c>
+      <c r="E648" s="4" t="n">
+        <v>2165</v>
+      </c>
+      <c r="F648" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G648" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H648" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B649" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C649" s="3" t="n">
+        <v>20050</v>
+      </c>
+      <c r="D649" s="4" t="n">
+        <v>23100</v>
+      </c>
+      <c r="E649" s="4" t="n">
+        <v>21575</v>
+      </c>
+      <c r="F649" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G649" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H649" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B650" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C650" s="3" t="n">
+        <v>23850</v>
+      </c>
+      <c r="D650" s="4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E650" s="4" t="n">
+        <v>25925</v>
+      </c>
+      <c r="F650" s="6" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G650" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H650" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C651" s="3" t="n">
+        <v>15200</v>
+      </c>
+      <c r="D651" s="4" t="n">
+        <v>16500</v>
+      </c>
+      <c r="E651" s="4" t="n">
+        <v>15850</v>
+      </c>
+      <c r="F651" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G651" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H651" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B652" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C652" s="3" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D652" s="4" t="n">
+        <v>10500</v>
+      </c>
+      <c r="E652" s="4" t="n">
+        <v>10150</v>
+      </c>
+      <c r="F652" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G652" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H652" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B653" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C653" s="3" t="n">
+        <v>16400</v>
+      </c>
+      <c r="D653" s="4" t="n">
+        <v>17700</v>
+      </c>
+      <c r="E653" s="4" t="n">
+        <v>17050</v>
+      </c>
+      <c r="F653" s="4" t="n">
+        <v>-200</v>
+      </c>
+      <c r="G653" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H653" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B654" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C654" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D654" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E654" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F654" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G654" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H654" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B655" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C655" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D655" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E655" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F655" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G655" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H655" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B656" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C656" s="3" t="n">
+        <v>302000</v>
+      </c>
+      <c r="D656" s="4" t="n">
+        <v>315000</v>
+      </c>
+      <c r="E656" s="4" t="n">
+        <v>308500</v>
+      </c>
+      <c r="F656" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G656" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H656" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B657" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C657" s="3" t="n">
+        <v>104000</v>
+      </c>
+      <c r="D657" s="4" t="n">
+        <v>106500</v>
+      </c>
+      <c r="E657" s="4" t="n">
+        <v>105250</v>
+      </c>
+      <c r="F657" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G657" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H657" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B658" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C658" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D658" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E658" s="4" t="n">
+        <v>39750</v>
+      </c>
+      <c r="F658" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G658" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H658" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B659" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C659" s="3" t="n">
+        <v>2060</v>
+      </c>
+      <c r="D659" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E659" s="4" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F659" s="4" t="n">
+        <v>-285</v>
+      </c>
+      <c r="G659" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H659" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B660" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C660" s="3" t="n">
+        <v>2110</v>
+      </c>
+      <c r="D660" s="4" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E660" s="4" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F660" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G660" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H660" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B661" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C661" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="D661" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E661" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="F661" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G661" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H661" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C662" s="3" t="n">
+        <v>265000</v>
+      </c>
+      <c r="D662" s="4" t="n">
+        <v>273000</v>
+      </c>
+      <c r="E662" s="4" t="n">
+        <v>269000</v>
+      </c>
+      <c r="F662" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G662" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H662" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B663" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C663" s="7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D663" s="6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E663" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F663" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G663" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H663" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B664" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C664" s="7" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D664" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="E664" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F664" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G664" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H664" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B665" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C665" s="3" t="n">
+        <v>138000</v>
+      </c>
+      <c r="D665" s="4" t="n">
+        <v>152000</v>
+      </c>
+      <c r="E665" s="4" t="n">
+        <v>145000</v>
+      </c>
+      <c r="F665" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G665" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H665" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B666" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C666" s="3" t="n">
+        <v>129000</v>
+      </c>
+      <c r="D666" s="4" t="n">
+        <v>149000</v>
+      </c>
+      <c r="E666" s="4" t="n">
+        <v>139000</v>
+      </c>
+      <c r="F666" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G666" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H666" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B667" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C667" s="3" t="n">
+        <v>7580</v>
+      </c>
+      <c r="D667" s="4" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E667" s="4" t="n">
+        <v>7690</v>
+      </c>
+      <c r="F667" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G667" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H667" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B668" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C668" s="3" t="n">
+        <v>32160</v>
+      </c>
+      <c r="D668" s="4" t="n">
+        <v>32560</v>
+      </c>
+      <c r="E668" s="4" t="n">
+        <v>32360</v>
+      </c>
+      <c r="F668" s="6" t="n">
+        <v>-40</v>
+      </c>
+      <c r="G668" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H668" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B669" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C669" s="3" t="n">
+        <v>145500</v>
+      </c>
+      <c r="D669" s="4" t="n">
+        <v>158000</v>
+      </c>
+      <c r="E669" s="4" t="n">
+        <v>151750</v>
+      </c>
+      <c r="F669" s="4" t="n">
+        <v>-750</v>
+      </c>
+      <c r="G669" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H669" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B670" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C670" s="7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="D670" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E670" s="6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F670" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G670" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H670" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B671" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C671" s="7" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D671" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E671" s="6" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="F671" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G671" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H671" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B672" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C672" s="3" t="n">
+        <v>1070000</v>
+      </c>
+      <c r="D672" s="4" t="n">
+        <v>1090000</v>
+      </c>
+      <c r="E672" s="4" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="F672" s="4" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="G672" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H672" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C673" s="3" t="n">
+        <v>374000</v>
+      </c>
+      <c r="D673" s="4" t="n">
+        <v>385000</v>
+      </c>
+      <c r="E673" s="4" t="n">
+        <v>379500</v>
+      </c>
+      <c r="F673" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G673" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H673" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B674" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C674" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D674" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E674" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F674" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G674" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H674" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B675" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C675" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D675" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E675" s="4" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F675" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G675" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H675" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B676" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C676" s="3" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D676" s="4" t="n">
+        <v>87000</v>
+      </c>
+      <c r="E676" s="4" t="n">
+        <v>86000</v>
+      </c>
+      <c r="F676" s="4" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G676" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H676" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B677" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C677" s="3" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D677" s="4" t="n">
+        <v>213000</v>
+      </c>
+      <c r="E677" s="4" t="n">
+        <v>210500</v>
+      </c>
+      <c r="F677" s="4" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="G677" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H677" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B678" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C678" s="3" t="n">
+        <v>55480</v>
+      </c>
+      <c r="D678" s="4" t="n">
+        <v>56180</v>
+      </c>
+      <c r="E678" s="4" t="n">
+        <v>55830</v>
+      </c>
+      <c r="F678" s="4" t="n">
+        <v>-180</v>
+      </c>
+      <c r="G678" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H678" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B679" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C679" s="3" t="n">
+        <v>61500</v>
+      </c>
+      <c r="D679" s="4" t="n">
+        <v>66500</v>
+      </c>
+      <c r="E679" s="4" t="n">
+        <v>64000</v>
+      </c>
+      <c r="F679" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G679" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H679" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B680" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C680" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D680" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E680" s="6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F680" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G680" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H680" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B681" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C681" s="3" t="n">
+        <v>26122</v>
+      </c>
+      <c r="D681" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="E681" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="F681" s="4" t="n">
+        <v>-661</v>
+      </c>
+      <c r="G681" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H681" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B682" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C682" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D682" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E682" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F682" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G682" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H682" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B683" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C683" s="3" t="n">
+        <v>373000</v>
+      </c>
+      <c r="D683" s="4" t="n">
+        <v>376000</v>
+      </c>
+      <c r="E683" s="4" t="n">
+        <v>374500</v>
+      </c>
+      <c r="F683" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G683" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H683" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C684" s="3" t="n">
+        <v>96200</v>
+      </c>
+      <c r="D684" s="4" t="n">
+        <v>98500</v>
+      </c>
+      <c r="E684" s="4" t="n">
+        <v>97350</v>
+      </c>
+      <c r="F684" s="4" t="n">
+        <v>-400</v>
+      </c>
+      <c r="G684" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H684" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B685" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C685" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D685" s="4" t="n">
+        <v>90500</v>
+      </c>
+      <c r="E685" s="4" t="n">
+        <v>87250</v>
+      </c>
+      <c r="F685" s="4" t="n">
+        <v>-250</v>
+      </c>
+      <c r="G685" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H685" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B686" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C686" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D686" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E686" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F686" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G686" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H686" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B687" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C687" s="3" t="n">
+        <v>6953</v>
+      </c>
+      <c r="D687" s="4" t="n">
+        <v>7630</v>
+      </c>
+      <c r="E687" s="4" t="n">
+        <v>7291.5</v>
+      </c>
+      <c r="F687" s="6" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G687" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H687" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B688" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C688" s="3" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D688" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E688" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="F688" s="4" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G688" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H688" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B615" s="9" t="n"/>
-      <c r="C615" s="9" t="n"/>
-      <c r="D615" s="9" t="n"/>
-      <c r="E615" s="9" t="n"/>
-      <c r="F615" s="9" t="n"/>
-      <c r="G615" s="9" t="n"/>
-      <c r="H615" s="9" t="n"/>
-    </row>
-    <row r="616">
-      <c r="B616" s="2" t="inlineStr">
+      <c r="B690" s="9" t="n"/>
+      <c r="C690" s="9" t="n"/>
+      <c r="D690" s="9" t="n"/>
+      <c r="E690" s="9" t="n"/>
+      <c r="F690" s="9" t="n"/>
+      <c r="G690" s="9" t="n"/>
+      <c r="H690" s="9" t="n"/>
+    </row>
+    <row r="691">
+      <c r="B691" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C616" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$616),"")</f>
-        <v/>
-      </c>
-      <c r="D616" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$616),"")</f>
-        <v/>
-      </c>
-      <c r="E616" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$616),"")</f>
-        <v/>
-      </c>
-      <c r="F616" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$616)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="617">
-      <c r="B617" s="2" t="inlineStr">
+      <c r="C691" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$691),"")</f>
+        <v/>
+      </c>
+      <c r="D691" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$691),"")</f>
+        <v/>
+      </c>
+      <c r="E691" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$691),"")</f>
+        <v/>
+      </c>
+      <c r="F691" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$691)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="692">
+      <c r="B692" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C617" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$617),"")</f>
-        <v/>
-      </c>
-      <c r="D617" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$617),"")</f>
-        <v/>
-      </c>
-      <c r="E617" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$617),"")</f>
-        <v/>
-      </c>
-      <c r="F617" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$617)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="618">
-      <c r="B618" s="2" t="inlineStr">
+      <c r="C692" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$692),"")</f>
+        <v/>
+      </c>
+      <c r="D692" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$692),"")</f>
+        <v/>
+      </c>
+      <c r="E692" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$692),"")</f>
+        <v/>
+      </c>
+      <c r="F692" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$692)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="693">
+      <c r="B693" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C618" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$618),"")</f>
-        <v/>
-      </c>
-      <c r="D618" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$618),"")</f>
-        <v/>
-      </c>
-      <c r="E618" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$618),"")</f>
-        <v/>
-      </c>
-      <c r="F618" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$618)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="619">
-      <c r="B619" s="2" t="inlineStr">
+      <c r="C693" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$693),"")</f>
+        <v/>
+      </c>
+      <c r="D693" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$693),"")</f>
+        <v/>
+      </c>
+      <c r="E693" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$693),"")</f>
+        <v/>
+      </c>
+      <c r="F693" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$693)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="694">
+      <c r="B694" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C619" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$619),"")</f>
-        <v/>
-      </c>
-      <c r="D619" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$619),"")</f>
-        <v/>
-      </c>
-      <c r="E619" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$619),"")</f>
-        <v/>
-      </c>
-      <c r="F619" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$619)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="620">
-      <c r="B620" s="2" t="inlineStr">
+      <c r="C694" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$694),"")</f>
+        <v/>
+      </c>
+      <c r="D694" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$694),"")</f>
+        <v/>
+      </c>
+      <c r="E694" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$694),"")</f>
+        <v/>
+      </c>
+      <c r="F694" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$694)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="695">
+      <c r="B695" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C620" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$620),"")</f>
-        <v/>
-      </c>
-      <c r="D620" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$620),"")</f>
-        <v/>
-      </c>
-      <c r="E620" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$620),"")</f>
-        <v/>
-      </c>
-      <c r="F620" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$620)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="621">
-      <c r="B621" s="2" t="inlineStr">
+      <c r="C695" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$695),"")</f>
+        <v/>
+      </c>
+      <c r="D695" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$695),"")</f>
+        <v/>
+      </c>
+      <c r="E695" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$695),"")</f>
+        <v/>
+      </c>
+      <c r="F695" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$695)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="696">
+      <c r="B696" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C621" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$621),"")</f>
-        <v/>
-      </c>
-      <c r="D621" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$621),"")</f>
-        <v/>
-      </c>
-      <c r="E621" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$621),"")</f>
-        <v/>
-      </c>
-      <c r="F621" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$621)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="622">
-      <c r="B622" s="2" t="inlineStr">
+      <c r="C696" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$696),"")</f>
+        <v/>
+      </c>
+      <c r="D696" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$696),"")</f>
+        <v/>
+      </c>
+      <c r="E696" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$696),"")</f>
+        <v/>
+      </c>
+      <c r="F696" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$696)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="697">
+      <c r="B697" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C622" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$622),"")</f>
-        <v/>
-      </c>
-      <c r="D622" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$622),"")</f>
-        <v/>
-      </c>
-      <c r="E622" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$622),"")</f>
-        <v/>
-      </c>
-      <c r="F622" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$622)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="623">
-      <c r="B623" s="2" t="inlineStr">
+      <c r="C697" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$697),"")</f>
+        <v/>
+      </c>
+      <c r="D697" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$697),"")</f>
+        <v/>
+      </c>
+      <c r="E697" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$697),"")</f>
+        <v/>
+      </c>
+      <c r="F697" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$697)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="698">
+      <c r="B698" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C623" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$623),"")</f>
-        <v/>
-      </c>
-      <c r="D623" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$623),"")</f>
-        <v/>
-      </c>
-      <c r="E623" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$623),"")</f>
-        <v/>
-      </c>
-      <c r="F623" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$623)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="624">
-      <c r="B624" s="2" t="inlineStr">
+      <c r="C698" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$698),"")</f>
+        <v/>
+      </c>
+      <c r="D698" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$698),"")</f>
+        <v/>
+      </c>
+      <c r="E698" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$698),"")</f>
+        <v/>
+      </c>
+      <c r="F698" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$698)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="699">
+      <c r="B699" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C624" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$624),"")</f>
-        <v/>
-      </c>
-      <c r="D624" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$624),"")</f>
-        <v/>
-      </c>
-      <c r="E624" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$624),"")</f>
-        <v/>
-      </c>
-      <c r="F624" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$624)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="625">
-      <c r="B625" s="2" t="inlineStr">
+      <c r="C699" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$699),"")</f>
+        <v/>
+      </c>
+      <c r="D699" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$699),"")</f>
+        <v/>
+      </c>
+      <c r="E699" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$699),"")</f>
+        <v/>
+      </c>
+      <c r="F699" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$699)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="700">
+      <c r="B700" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C625" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$625),"")</f>
-        <v/>
-      </c>
-      <c r="D625" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$625),"")</f>
-        <v/>
-      </c>
-      <c r="E625" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$625),"")</f>
-        <v/>
-      </c>
-      <c r="F625" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$625)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="626">
-      <c r="B626" s="2" t="inlineStr">
+      <c r="C700" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$700),"")</f>
+        <v/>
+      </c>
+      <c r="D700" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$700),"")</f>
+        <v/>
+      </c>
+      <c r="E700" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$700),"")</f>
+        <v/>
+      </c>
+      <c r="F700" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$700)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="701">
+      <c r="B701" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C626" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$626),"")</f>
-        <v/>
-      </c>
-      <c r="D626" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$626),"")</f>
-        <v/>
-      </c>
-      <c r="E626" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$626),"")</f>
-        <v/>
-      </c>
-      <c r="F626" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$626)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="627">
-      <c r="B627" s="2" t="inlineStr">
+      <c r="C701" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$701),"")</f>
+        <v/>
+      </c>
+      <c r="D701" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$701),"")</f>
+        <v/>
+      </c>
+      <c r="E701" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$701),"")</f>
+        <v/>
+      </c>
+      <c r="F701" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$701)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="702">
+      <c r="B702" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C627" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$627),"")</f>
-        <v/>
-      </c>
-      <c r="D627" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$627),"")</f>
-        <v/>
-      </c>
-      <c r="E627" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$627),"")</f>
-        <v/>
-      </c>
-      <c r="F627" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$627)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="628">
-      <c r="B628" s="2" t="inlineStr">
+      <c r="C702" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$702),"")</f>
+        <v/>
+      </c>
+      <c r="D702" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$702),"")</f>
+        <v/>
+      </c>
+      <c r="E702" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$702),"")</f>
+        <v/>
+      </c>
+      <c r="F702" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$702)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="703">
+      <c r="B703" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C628" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$628),"")</f>
-        <v/>
-      </c>
-      <c r="D628" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$628),"")</f>
-        <v/>
-      </c>
-      <c r="E628" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$628),"")</f>
-        <v/>
-      </c>
-      <c r="F628" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$628)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="629">
-      <c r="B629" s="2" t="inlineStr">
+      <c r="C703" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$703),"")</f>
+        <v/>
+      </c>
+      <c r="D703" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$703),"")</f>
+        <v/>
+      </c>
+      <c r="E703" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$703),"")</f>
+        <v/>
+      </c>
+      <c r="F703" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$703)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="704">
+      <c r="B704" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C629" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$629),"")</f>
-        <v/>
-      </c>
-      <c r="D629" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$629),"")</f>
-        <v/>
-      </c>
-      <c r="E629" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$629),"")</f>
-        <v/>
-      </c>
-      <c r="F629" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$629)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="630">
-      <c r="B630" s="2" t="inlineStr">
+      <c r="C704" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$704),"")</f>
+        <v/>
+      </c>
+      <c r="D704" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$704),"")</f>
+        <v/>
+      </c>
+      <c r="E704" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$704),"")</f>
+        <v/>
+      </c>
+      <c r="F704" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$704)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="705">
+      <c r="B705" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C630" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$630),"")</f>
-        <v/>
-      </c>
-      <c r="D630" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$630),"")</f>
-        <v/>
-      </c>
-      <c r="E630" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$630),"")</f>
-        <v/>
-      </c>
-      <c r="F630" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$630)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="631">
-      <c r="B631" s="2" t="inlineStr">
+      <c r="C705" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$705),"")</f>
+        <v/>
+      </c>
+      <c r="D705" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$705),"")</f>
+        <v/>
+      </c>
+      <c r="E705" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$705),"")</f>
+        <v/>
+      </c>
+      <c r="F705" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$705)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="706">
+      <c r="B706" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C631" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$631),"")</f>
-        <v/>
-      </c>
-      <c r="D631" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$631),"")</f>
-        <v/>
-      </c>
-      <c r="E631" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$631),"")</f>
-        <v/>
-      </c>
-      <c r="F631" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$631)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="632">
-      <c r="B632" s="2" t="inlineStr">
+      <c r="C706" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$706),"")</f>
+        <v/>
+      </c>
+      <c r="D706" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$706),"")</f>
+        <v/>
+      </c>
+      <c r="E706" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$706),"")</f>
+        <v/>
+      </c>
+      <c r="F706" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$706)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="707">
+      <c r="B707" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C632" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$632),"")</f>
-        <v/>
-      </c>
-      <c r="D632" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$632),"")</f>
-        <v/>
-      </c>
-      <c r="E632" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$632),"")</f>
-        <v/>
-      </c>
-      <c r="F632" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$632)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="633">
-      <c r="B633" s="2" t="inlineStr">
+      <c r="C707" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$707),"")</f>
+        <v/>
+      </c>
+      <c r="D707" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$707),"")</f>
+        <v/>
+      </c>
+      <c r="E707" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$707),"")</f>
+        <v/>
+      </c>
+      <c r="F707" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$707)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="708">
+      <c r="B708" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C633" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$633),"")</f>
-        <v/>
-      </c>
-      <c r="D633" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$633),"")</f>
-        <v/>
-      </c>
-      <c r="E633" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$633),"")</f>
-        <v/>
-      </c>
-      <c r="F633" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$633)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="634">
-      <c r="B634" s="2" t="inlineStr">
+      <c r="C708" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$708),"")</f>
+        <v/>
+      </c>
+      <c r="D708" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$708),"")</f>
+        <v/>
+      </c>
+      <c r="E708" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$708),"")</f>
+        <v/>
+      </c>
+      <c r="F708" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$708)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="709">
+      <c r="B709" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C634" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$634),"")</f>
-        <v/>
-      </c>
-      <c r="D634" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$634),"")</f>
-        <v/>
-      </c>
-      <c r="E634" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$634),"")</f>
-        <v/>
-      </c>
-      <c r="F634" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$634)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="635">
-      <c r="B635" s="2" t="inlineStr">
+      <c r="C709" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$709),"")</f>
+        <v/>
+      </c>
+      <c r="D709" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$709),"")</f>
+        <v/>
+      </c>
+      <c r="E709" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$709),"")</f>
+        <v/>
+      </c>
+      <c r="F709" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$709)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="710">
+      <c r="B710" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C635" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$635),"")</f>
-        <v/>
-      </c>
-      <c r="D635" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$635),"")</f>
-        <v/>
-      </c>
-      <c r="E635" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$635),"")</f>
-        <v/>
-      </c>
-      <c r="F635" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$635)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="636">
-      <c r="B636" s="2" t="inlineStr">
+      <c r="C710" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$710),"")</f>
+        <v/>
+      </c>
+      <c r="D710" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$710),"")</f>
+        <v/>
+      </c>
+      <c r="E710" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$710),"")</f>
+        <v/>
+      </c>
+      <c r="F710" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$710)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="711">
+      <c r="B711" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C636" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$636),"")</f>
-        <v/>
-      </c>
-      <c r="D636" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$636),"")</f>
-        <v/>
-      </c>
-      <c r="E636" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$636),"")</f>
-        <v/>
-      </c>
-      <c r="F636" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$636)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="637">
-      <c r="B637" s="2" t="inlineStr">
+      <c r="C711" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$711),"")</f>
+        <v/>
+      </c>
+      <c r="D711" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$711),"")</f>
+        <v/>
+      </c>
+      <c r="E711" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$711),"")</f>
+        <v/>
+      </c>
+      <c r="F711" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$711)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="712">
+      <c r="B712" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C637" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$637),"")</f>
-        <v/>
-      </c>
-      <c r="D637" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$637),"")</f>
-        <v/>
-      </c>
-      <c r="E637" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$637),"")</f>
-        <v/>
-      </c>
-      <c r="F637" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$637)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="638">
-      <c r="B638" s="2" t="inlineStr">
+      <c r="C712" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$712),"")</f>
+        <v/>
+      </c>
+      <c r="D712" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$712),"")</f>
+        <v/>
+      </c>
+      <c r="E712" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$712),"")</f>
+        <v/>
+      </c>
+      <c r="F712" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$712)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="713">
+      <c r="B713" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C638" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$638),"")</f>
-        <v/>
-      </c>
-      <c r="D638" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$638),"")</f>
-        <v/>
-      </c>
-      <c r="E638" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$638),"")</f>
-        <v/>
-      </c>
-      <c r="F638" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$638)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="639">
-      <c r="B639" s="2" t="inlineStr">
+      <c r="C713" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$713),"")</f>
+        <v/>
+      </c>
+      <c r="D713" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$713),"")</f>
+        <v/>
+      </c>
+      <c r="E713" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$713),"")</f>
+        <v/>
+      </c>
+      <c r="F713" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$713)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="714">
+      <c r="B714" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C639" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$639),"")</f>
-        <v/>
-      </c>
-      <c r="D639" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$639),"")</f>
-        <v/>
-      </c>
-      <c r="E639" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$639),"")</f>
-        <v/>
-      </c>
-      <c r="F639" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$639)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="640">
-      <c r="B640" s="2" t="inlineStr">
+      <c r="C714" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$714),"")</f>
+        <v/>
+      </c>
+      <c r="D714" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$714),"")</f>
+        <v/>
+      </c>
+      <c r="E714" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$714),"")</f>
+        <v/>
+      </c>
+      <c r="F714" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$714)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="715">
+      <c r="B715" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C640" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$640),"")</f>
-        <v/>
-      </c>
-      <c r="D640" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$640),"")</f>
-        <v/>
-      </c>
-      <c r="E640" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$640),"")</f>
-        <v/>
-      </c>
-      <c r="F640" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$640)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="641">
-      <c r="B641" s="2" t="inlineStr">
+      <c r="C715" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$715),"")</f>
+        <v/>
+      </c>
+      <c r="D715" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$715),"")</f>
+        <v/>
+      </c>
+      <c r="E715" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$715),"")</f>
+        <v/>
+      </c>
+      <c r="F715" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$715)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="716">
+      <c r="B716" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C641" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$641),"")</f>
-        <v/>
-      </c>
-      <c r="D641" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$641),"")</f>
-        <v/>
-      </c>
-      <c r="E641" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$641),"")</f>
-        <v/>
-      </c>
-      <c r="F641" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$641)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="642">
-      <c r="B642" s="2" t="inlineStr">
+      <c r="C716" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$716),"")</f>
+        <v/>
+      </c>
+      <c r="D716" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$716),"")</f>
+        <v/>
+      </c>
+      <c r="E716" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$716),"")</f>
+        <v/>
+      </c>
+      <c r="F716" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$716)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="717">
+      <c r="B717" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C642" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$642),"")</f>
-        <v/>
-      </c>
-      <c r="D642" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$642),"")</f>
-        <v/>
-      </c>
-      <c r="E642" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$642),"")</f>
-        <v/>
-      </c>
-      <c r="F642" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$642)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="643">
-      <c r="B643" s="2" t="inlineStr">
+      <c r="C717" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$717),"")</f>
+        <v/>
+      </c>
+      <c r="D717" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$717),"")</f>
+        <v/>
+      </c>
+      <c r="E717" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$717),"")</f>
+        <v/>
+      </c>
+      <c r="F717" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$717)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="718">
+      <c r="B718" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C643" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$643),"")</f>
-        <v/>
-      </c>
-      <c r="D643" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$643),"")</f>
-        <v/>
-      </c>
-      <c r="E643" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$643),"")</f>
-        <v/>
-      </c>
-      <c r="F643" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$643)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="644">
-      <c r="B644" s="2" t="inlineStr">
+      <c r="C718" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$718),"")</f>
+        <v/>
+      </c>
+      <c r="D718" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$718),"")</f>
+        <v/>
+      </c>
+      <c r="E718" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$718),"")</f>
+        <v/>
+      </c>
+      <c r="F718" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$718)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="719">
+      <c r="B719" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C644" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$644),"")</f>
-        <v/>
-      </c>
-      <c r="D644" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$644),"")</f>
-        <v/>
-      </c>
-      <c r="E644" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$644),"")</f>
-        <v/>
-      </c>
-      <c r="F644" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$644)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="645">
-      <c r="B645" s="2" t="inlineStr">
+      <c r="C719" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$719),"")</f>
+        <v/>
+      </c>
+      <c r="D719" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$719),"")</f>
+        <v/>
+      </c>
+      <c r="E719" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$719),"")</f>
+        <v/>
+      </c>
+      <c r="F719" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$719)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="720">
+      <c r="B720" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C645" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$645),"")</f>
-        <v/>
-      </c>
-      <c r="D645" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$645),"")</f>
-        <v/>
-      </c>
-      <c r="E645" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$645),"")</f>
-        <v/>
-      </c>
-      <c r="F645" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$645)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="646">
-      <c r="B646" s="2" t="inlineStr">
+      <c r="C720" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$720),"")</f>
+        <v/>
+      </c>
+      <c r="D720" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$720),"")</f>
+        <v/>
+      </c>
+      <c r="E720" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$720),"")</f>
+        <v/>
+      </c>
+      <c r="F720" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$720)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="721">
+      <c r="B721" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C646" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$646),"")</f>
-        <v/>
-      </c>
-      <c r="D646" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$646),"")</f>
-        <v/>
-      </c>
-      <c r="E646" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$646),"")</f>
-        <v/>
-      </c>
-      <c r="F646" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$646)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="647">
-      <c r="B647" s="2" t="inlineStr">
+      <c r="C721" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$721),"")</f>
+        <v/>
+      </c>
+      <c r="D721" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$721),"")</f>
+        <v/>
+      </c>
+      <c r="E721" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$721),"")</f>
+        <v/>
+      </c>
+      <c r="F721" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$721)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="722">
+      <c r="B722" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C647" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$647),"")</f>
-        <v/>
-      </c>
-      <c r="D647" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$647),"")</f>
-        <v/>
-      </c>
-      <c r="E647" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$647),"")</f>
-        <v/>
-      </c>
-      <c r="F647" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$647)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="648">
-      <c r="B648" s="2" t="inlineStr">
+      <c r="C722" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$722),"")</f>
+        <v/>
+      </c>
+      <c r="D722" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$722),"")</f>
+        <v/>
+      </c>
+      <c r="E722" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$722),"")</f>
+        <v/>
+      </c>
+      <c r="F722" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$722)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="723">
+      <c r="B723" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C648" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$648),"")</f>
-        <v/>
-      </c>
-      <c r="D648" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$648),"")</f>
-        <v/>
-      </c>
-      <c r="E648" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$648),"")</f>
-        <v/>
-      </c>
-      <c r="F648" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$648)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="649">
-      <c r="B649" s="2" t="inlineStr">
+      <c r="C723" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$723),"")</f>
+        <v/>
+      </c>
+      <c r="D723" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$723),"")</f>
+        <v/>
+      </c>
+      <c r="E723" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$723),"")</f>
+        <v/>
+      </c>
+      <c r="F723" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$723)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="724">
+      <c r="B724" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C649" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$649),"")</f>
-        <v/>
-      </c>
-      <c r="D649" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$649),"")</f>
-        <v/>
-      </c>
-      <c r="E649" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$649),"")</f>
-        <v/>
-      </c>
-      <c r="F649" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$649)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="650">
-      <c r="B650" s="2" t="inlineStr">
+      <c r="C724" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$724),"")</f>
+        <v/>
+      </c>
+      <c r="D724" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$724),"")</f>
+        <v/>
+      </c>
+      <c r="E724" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$724),"")</f>
+        <v/>
+      </c>
+      <c r="F724" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$724)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="725">
+      <c r="B725" s="2" t="inlineStr">
         <is>
           <t>巴西锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C650" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$650),"")</f>
-        <v/>
-      </c>
-      <c r="D650" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$650),"")</f>
-        <v/>
-      </c>
-      <c r="E650" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$650),"")</f>
-        <v/>
-      </c>
-      <c r="F650" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$650)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="651">
-      <c r="B651" s="2" t="inlineStr">
+      <c r="C725" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$725),"")</f>
+        <v/>
+      </c>
+      <c r="D725" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$725),"")</f>
+        <v/>
+      </c>
+      <c r="E725" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$725),"")</f>
+        <v/>
+      </c>
+      <c r="F725" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$725)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="726">
+      <c r="B726" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂储能正极片</t>
         </is>
       </c>
-      <c r="C651" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$651),"")</f>
-        <v/>
-      </c>
-      <c r="D651" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$651),"")</f>
-        <v/>
-      </c>
-      <c r="E651" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$651),"")</f>
-        <v/>
-      </c>
-      <c r="F651" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$651)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="652">
-      <c r="B652" s="2" t="inlineStr">
+      <c r="C726" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$726),"")</f>
+        <v/>
+      </c>
+      <c r="D726" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$726),"")</f>
+        <v/>
+      </c>
+      <c r="E726" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$726),"")</f>
+        <v/>
+      </c>
+      <c r="F726" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$726)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="727">
+      <c r="B727" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂动力正极片</t>
         </is>
       </c>
-      <c r="C652" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$652),"")</f>
-        <v/>
-      </c>
-      <c r="D652" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$652),"")</f>
-        <v/>
-      </c>
-      <c r="E652" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$652),"")</f>
-        <v/>
-      </c>
-      <c r="F652" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$652)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="653">
-      <c r="B653" s="2" t="inlineStr">
+      <c r="C727" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$727),"")</f>
+        <v/>
+      </c>
+      <c r="D727" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$727),"")</f>
+        <v/>
+      </c>
+      <c r="E727" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$727),"")</f>
+        <v/>
+      </c>
+      <c r="F727" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$727)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="728">
+      <c r="B728" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂软包电池</t>
         </is>
       </c>
-      <c r="C653" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$653),"")</f>
-        <v/>
-      </c>
-      <c r="D653" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$653),"")</f>
-        <v/>
-      </c>
-      <c r="E653" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$653),"")</f>
-        <v/>
-      </c>
-      <c r="F653" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$653)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="654">
-      <c r="B654" s="2" t="inlineStr">
+      <c r="C728" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$728),"")</f>
+        <v/>
+      </c>
+      <c r="D728" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$728),"")</f>
+        <v/>
+      </c>
+      <c r="E728" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$728),"")</f>
+        <v/>
+      </c>
+      <c r="F728" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$728)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="729">
+      <c r="B729" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂钢壳电池</t>
         </is>
       </c>
-      <c r="C654" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$654),"")</f>
-        <v/>
-      </c>
-      <c r="D654" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$654),"")</f>
-        <v/>
-      </c>
-      <c r="E654" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$654),"")</f>
-        <v/>
-      </c>
-      <c r="F654" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$654)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="655">
-      <c r="B655" s="2" t="inlineStr">
+      <c r="C729" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$729),"")</f>
+        <v/>
+      </c>
+      <c r="D729" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$729),"")</f>
+        <v/>
+      </c>
+      <c r="E729" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$729),"")</f>
+        <v/>
+      </c>
+      <c r="F729" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$729)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="730">
+      <c r="B730" s="2" t="inlineStr">
         <is>
           <t>废旧磷酸铁锂铝壳电池</t>
         </is>
       </c>
-      <c r="C655" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$655),"")</f>
-        <v/>
-      </c>
-      <c r="D655" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$655),"")</f>
-        <v/>
-      </c>
-      <c r="E655" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$655),"")</f>
-        <v/>
-      </c>
-      <c r="F655" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$655)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="656">
-      <c r="B656" s="2" t="inlineStr">
+      <c r="C730" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$730),"")</f>
+        <v/>
+      </c>
+      <c r="D730" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$730),"")</f>
+        <v/>
+      </c>
+      <c r="E730" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$730),"")</f>
+        <v/>
+      </c>
+      <c r="F730" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$730)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="731">
+      <c r="B731" s="2" t="inlineStr">
         <is>
           <t>方形磷酸铁锂电池B品</t>
         </is>
       </c>
-      <c r="C656" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$656),"")</f>
-        <v/>
-      </c>
-      <c r="D656" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$656),"")</f>
-        <v/>
-      </c>
-      <c r="E656" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$656),"")</f>
-        <v/>
-      </c>
-      <c r="F656" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$656)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="657">
-      <c r="B657" s="2" t="inlineStr">
+      <c r="C731" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$731),"")</f>
+        <v/>
+      </c>
+      <c r="D731" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$731),"")</f>
+        <v/>
+      </c>
+      <c r="E731" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$731),"")</f>
+        <v/>
+      </c>
+      <c r="F731" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$731)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="732">
+      <c r="B732" s="2" t="inlineStr">
         <is>
           <t>氧化亚镍</t>
         </is>
       </c>
-      <c r="C657" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$657),"")</f>
-        <v/>
-      </c>
-      <c r="D657" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$657),"")</f>
-        <v/>
-      </c>
-      <c r="E657" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$657),"")</f>
-        <v/>
-      </c>
-      <c r="F657" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$657)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="658">
-      <c r="B658" s="2" t="inlineStr">
+      <c r="C732" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$732),"")</f>
+        <v/>
+      </c>
+      <c r="D732" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$732),"")</f>
+        <v/>
+      </c>
+      <c r="E732" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$732),"")</f>
+        <v/>
+      </c>
+      <c r="F732" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$732)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="733">
+      <c r="B733" s="2" t="inlineStr">
         <is>
           <t>氧化钴</t>
         </is>
       </c>
-      <c r="C658" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$658),"")</f>
-        <v/>
-      </c>
-      <c r="D658" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$658),"")</f>
-        <v/>
-      </c>
-      <c r="E658" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$658),"")</f>
-        <v/>
-      </c>
-      <c r="F658" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$658)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="659">
-      <c r="B659" s="2" t="inlineStr">
+      <c r="C733" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$733),"")</f>
+        <v/>
+      </c>
+      <c r="D733" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$733),"")</f>
+        <v/>
+      </c>
+      <c r="E733" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$733),"")</f>
+        <v/>
+      </c>
+      <c r="F733" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$733)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="734">
+      <c r="B734" s="2" t="inlineStr">
         <is>
           <t>氯化钴</t>
         </is>
       </c>
-      <c r="C659" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$659),"")</f>
-        <v/>
-      </c>
-      <c r="D659" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$659),"")</f>
-        <v/>
-      </c>
-      <c r="E659" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$659),"")</f>
-        <v/>
-      </c>
-      <c r="F659" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$659)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="660">
-      <c r="B660" s="2" t="inlineStr">
+      <c r="C734" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$734),"")</f>
+        <v/>
+      </c>
+      <c r="D734" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$734),"")</f>
+        <v/>
+      </c>
+      <c r="E734" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$734),"")</f>
+        <v/>
+      </c>
+      <c r="F734" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$734)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="735">
+      <c r="B735" s="2" t="inlineStr">
         <is>
           <t>氯化镍NiCl₂·6H₂O</t>
         </is>
       </c>
-      <c r="C660" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$660),"")</f>
-        <v/>
-      </c>
-      <c r="D660" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$660),"")</f>
-        <v/>
-      </c>
-      <c r="E660" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$660),"")</f>
-        <v/>
-      </c>
-      <c r="F660" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$660)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="661">
-      <c r="B661" s="2" t="inlineStr">
+      <c r="C735" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$735),"")</f>
+        <v/>
+      </c>
+      <c r="D735" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$735),"")</f>
+        <v/>
+      </c>
+      <c r="E735" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$735),"")</f>
+        <v/>
+      </c>
+      <c r="F735" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$735)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="736">
+      <c r="B736" s="2" t="inlineStr">
         <is>
           <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C661" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$661),"")</f>
-        <v/>
-      </c>
-      <c r="D661" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$661),"")</f>
-        <v/>
-      </c>
-      <c r="E661" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$661),"")</f>
-        <v/>
-      </c>
-      <c r="F661" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$661)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="662">
-      <c r="B662" s="2" t="inlineStr">
+      <c r="C736" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$736),"")</f>
+        <v/>
+      </c>
+      <c r="D736" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$736),"")</f>
+        <v/>
+      </c>
+      <c r="E736" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$736),"")</f>
+        <v/>
+      </c>
+      <c r="F736" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$736)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="737">
+      <c r="B737" s="2" t="inlineStr">
         <is>
           <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
         </is>
       </c>
-      <c r="C662" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$662),"")</f>
-        <v/>
-      </c>
-      <c r="D662" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$662),"")</f>
-        <v/>
-      </c>
-      <c r="E662" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$662),"")</f>
-        <v/>
-      </c>
-      <c r="F662" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$662)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="663">
-      <c r="B663" s="2" t="inlineStr">
+      <c r="C737" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$737),"")</f>
+        <v/>
+      </c>
+      <c r="D737" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$737),"")</f>
+        <v/>
+      </c>
+      <c r="E737" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$737),"")</f>
+        <v/>
+      </c>
+      <c r="F737" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$737)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="738">
+      <c r="B738" s="2" t="inlineStr">
         <is>
           <t>电池级无水氯化锂</t>
         </is>
       </c>
-      <c r="C663" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$663),"")</f>
-        <v/>
-      </c>
-      <c r="D663" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$663),"")</f>
-        <v/>
-      </c>
-      <c r="E663" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$663),"")</f>
-        <v/>
-      </c>
-      <c r="F663" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$663)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="664">
-      <c r="B664" s="2" t="inlineStr">
+      <c r="C738" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$738),"")</f>
+        <v/>
+      </c>
+      <c r="D738" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$738),"")</f>
+        <v/>
+      </c>
+      <c r="E738" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$738),"")</f>
+        <v/>
+      </c>
+      <c r="F738" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$738)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="739">
+      <c r="B739" s="2" t="inlineStr">
         <is>
           <t>电池级氟化锂</t>
         </is>
       </c>
-      <c r="C664" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$664),"")</f>
-        <v/>
-      </c>
-      <c r="D664" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$664),"")</f>
-        <v/>
-      </c>
-      <c r="E664" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$664),"")</f>
-        <v/>
-      </c>
-      <c r="F664" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$664)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="665">
-      <c r="B665" s="2" t="inlineStr">
+      <c r="C739" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$739),"")</f>
+        <v/>
+      </c>
+      <c r="D739" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$739),"")</f>
+        <v/>
+      </c>
+      <c r="E739" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$739),"")</f>
+        <v/>
+      </c>
+      <c r="F739" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$739)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="740">
+      <c r="B740" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF中日韩)</t>
         </is>
       </c>
-      <c r="C665" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$665),"")</f>
-        <v/>
-      </c>
-      <c r="D665" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$665),"")</f>
-        <v/>
-      </c>
-      <c r="E665" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$665),"")</f>
-        <v/>
-      </c>
-      <c r="F665" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$665)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="666">
-      <c r="B666" s="2" t="inlineStr">
+      <c r="C740" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$740),"")</f>
+        <v/>
+      </c>
+      <c r="D740" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$740),"")</f>
+        <v/>
+      </c>
+      <c r="E740" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$740),"")</f>
+        <v/>
+      </c>
+      <c r="F740" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$740)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="741">
+      <c r="B741" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C666" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$666),"")</f>
-        <v/>
-      </c>
-      <c r="D666" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$666),"")</f>
-        <v/>
-      </c>
-      <c r="E666" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$666),"")</f>
-        <v/>
-      </c>
-      <c r="F666" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$666)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="667">
-      <c r="B667" s="2" t="inlineStr">
+      <c r="C741" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$741),"")</f>
+        <v/>
+      </c>
+      <c r="D741" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$741),"")</f>
+        <v/>
+      </c>
+      <c r="E741" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$741),"")</f>
+        <v/>
+      </c>
+      <c r="F741" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$741)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="742">
+      <c r="B742" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂(微粉）</t>
         </is>
       </c>
-      <c r="C667" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$667),"")</f>
-        <v/>
-      </c>
-      <c r="D667" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$667),"")</f>
-        <v/>
-      </c>
-      <c r="E667" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$667),"")</f>
-        <v/>
-      </c>
-      <c r="F667" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$667)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="668">
-      <c r="B668" s="2" t="inlineStr">
+      <c r="C742" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$742),"")</f>
+        <v/>
+      </c>
+      <c r="D742" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$742),"")</f>
+        <v/>
+      </c>
+      <c r="E742" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$742),"")</f>
+        <v/>
+      </c>
+      <c r="F742" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$742)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="743">
+      <c r="B743" s="2" t="inlineStr">
         <is>
           <t>电池级氢氧化锂（粗颗粒）</t>
         </is>
       </c>
-      <c r="C668" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$668),"")</f>
-        <v/>
-      </c>
-      <c r="D668" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$668),"")</f>
-        <v/>
-      </c>
-      <c r="E668" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$668),"")</f>
-        <v/>
-      </c>
-      <c r="F668" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$668)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="669">
-      <c r="B669" s="2" t="inlineStr">
+      <c r="C743" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$743),"")</f>
+        <v/>
+      </c>
+      <c r="D743" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$743),"")</f>
+        <v/>
+      </c>
+      <c r="E743" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$743),"")</f>
+        <v/>
+      </c>
+      <c r="F743" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$743)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="744">
+      <c r="B744" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸锰（出厂价）</t>
         </is>
       </c>
-      <c r="C669" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$669),"")</f>
-        <v/>
-      </c>
-      <c r="D669" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$669),"")</f>
-        <v/>
-      </c>
-      <c r="E669" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$669),"")</f>
-        <v/>
-      </c>
-      <c r="F669" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$669)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="670">
-      <c r="B670" s="2" t="inlineStr">
+      <c r="C744" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$744),"")</f>
+        <v/>
+      </c>
+      <c r="D744" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$744),"")</f>
+        <v/>
+      </c>
+      <c r="E744" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$744),"")</f>
+        <v/>
+      </c>
+      <c r="F744" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$744)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="745">
+      <c r="B745" s="2" t="inlineStr">
         <is>
           <t>电池级硫酸镍</t>
         </is>
       </c>
-      <c r="C670" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$670),"")</f>
-        <v/>
-      </c>
-      <c r="D670" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$670),"")</f>
-        <v/>
-      </c>
-      <c r="E670" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$670),"")</f>
-        <v/>
-      </c>
-      <c r="F670" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$670)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="671">
-      <c r="B671" s="2" t="inlineStr">
+      <c r="C745" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$745),"")</f>
+        <v/>
+      </c>
+      <c r="D745" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$745),"")</f>
+        <v/>
+      </c>
+      <c r="E745" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$745),"")</f>
+        <v/>
+      </c>
+      <c r="F745" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$745)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="746">
+      <c r="B746" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂</t>
         </is>
       </c>
-      <c r="C671" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$671),"")</f>
-        <v/>
-      </c>
-      <c r="D671" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$671),"")</f>
-        <v/>
-      </c>
-      <c r="E671" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$671),"")</f>
-        <v/>
-      </c>
-      <c r="F671" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$671)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="672">
-      <c r="B672" s="2" t="inlineStr">
+      <c r="C746" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$746),"")</f>
+        <v/>
+      </c>
+      <c r="D746" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$746),"")</f>
+        <v/>
+      </c>
+      <c r="E746" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$746),"")</f>
+        <v/>
+      </c>
+      <c r="F746" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$746)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="747">
+      <c r="B747" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂(CIF韩国)</t>
         </is>
       </c>
-      <c r="C672" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$672),"")</f>
-        <v/>
-      </c>
-      <c r="D672" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$672),"")</f>
-        <v/>
-      </c>
-      <c r="E672" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$672),"")</f>
-        <v/>
-      </c>
-      <c r="F672" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$672)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="673">
-      <c r="B673" s="2" t="inlineStr">
+      <c r="C747" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$747),"")</f>
+        <v/>
+      </c>
+      <c r="D747" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$747),"")</f>
+        <v/>
+      </c>
+      <c r="E747" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$747),"")</f>
+        <v/>
+      </c>
+      <c r="F747" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$747)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="748">
+      <c r="B748" s="2" t="inlineStr">
         <is>
           <t>电池级碳酸锂（CIF中日韩）</t>
         </is>
       </c>
-      <c r="C673" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$673),"")</f>
-        <v/>
-      </c>
-      <c r="D673" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$673),"")</f>
-        <v/>
-      </c>
-      <c r="E673" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$673),"")</f>
-        <v/>
-      </c>
-      <c r="F673" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$673)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="674">
-      <c r="B674" s="2" t="inlineStr">
+      <c r="C748" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$748),"")</f>
+        <v/>
+      </c>
+      <c r="D748" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$748),"")</f>
+        <v/>
+      </c>
+      <c r="E748" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$748),"")</f>
+        <v/>
+      </c>
+      <c r="F748" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$748)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="749">
+      <c r="B749" s="2" t="inlineStr">
         <is>
           <t>电池级金属锂</t>
         </is>
       </c>
-      <c r="C674" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$674),"")</f>
-        <v/>
-      </c>
-      <c r="D674" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$674),"")</f>
-        <v/>
-      </c>
-      <c r="E674" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$674),"")</f>
-        <v/>
-      </c>
-      <c r="F674" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$674)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="675">
-      <c r="B675" s="2" t="inlineStr">
+      <c r="C749" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$749),"")</f>
+        <v/>
+      </c>
+      <c r="D749" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$749),"")</f>
+        <v/>
+      </c>
+      <c r="E749" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$749),"")</f>
+        <v/>
+      </c>
+      <c r="F749" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$749)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="750">
+      <c r="B750" s="2" t="inlineStr">
         <is>
           <t>电解钴</t>
         </is>
       </c>
-      <c r="C675" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$675),"")</f>
-        <v/>
-      </c>
-      <c r="D675" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$675),"")</f>
-        <v/>
-      </c>
-      <c r="E675" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$675),"")</f>
-        <v/>
-      </c>
-      <c r="F675" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$675)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="676">
-      <c r="B676" s="2" t="inlineStr">
+      <c r="C750" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$750),"")</f>
+        <v/>
+      </c>
+      <c r="D750" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$750),"")</f>
+        <v/>
+      </c>
+      <c r="E750" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$750),"")</f>
+        <v/>
+      </c>
+      <c r="F750" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$750)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="751">
+      <c r="B751" s="2" t="inlineStr">
         <is>
           <t>电解钴（鹿特丹仓库）</t>
         </is>
       </c>
-      <c r="C676" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$676),"")</f>
-        <v/>
-      </c>
-      <c r="D676" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$676),"")</f>
-        <v/>
-      </c>
-      <c r="E676" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$676),"")</f>
-        <v/>
-      </c>
-      <c r="F676" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$676)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="677">
-      <c r="B677" s="2" t="inlineStr">
+      <c r="C751" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$751),"")</f>
+        <v/>
+      </c>
+      <c r="D751" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$751),"")</f>
+        <v/>
+      </c>
+      <c r="E751" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$751),"")</f>
+        <v/>
+      </c>
+      <c r="F751" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$751)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="752">
+      <c r="B752" s="2" t="inlineStr">
         <is>
           <t>电镀级硫酸镍</t>
         </is>
       </c>
-      <c r="C677" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$677),"")</f>
-        <v/>
-      </c>
-      <c r="D677" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$677),"")</f>
-        <v/>
-      </c>
-      <c r="E677" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$677),"")</f>
-        <v/>
-      </c>
-      <c r="F677" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$677)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="678">
-      <c r="B678" s="2" t="inlineStr">
+      <c r="C752" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$752),"")</f>
+        <v/>
+      </c>
+      <c r="D752" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$752),"")</f>
+        <v/>
+      </c>
+      <c r="E752" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$752),"")</f>
+        <v/>
+      </c>
+      <c r="F752" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$752)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="753">
+      <c r="B753" s="2" t="inlineStr">
         <is>
           <t>硫酸钴</t>
         </is>
       </c>
-      <c r="C678" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$678),"")</f>
-        <v/>
-      </c>
-      <c r="D678" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$678),"")</f>
-        <v/>
-      </c>
-      <c r="E678" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$678),"")</f>
-        <v/>
-      </c>
-      <c r="F678" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$678)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="679">
-      <c r="B679" s="2" t="inlineStr">
+      <c r="C753" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$753),"")</f>
+        <v/>
+      </c>
+      <c r="D753" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$753),"")</f>
+        <v/>
+      </c>
+      <c r="E753" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$753),"")</f>
+        <v/>
+      </c>
+      <c r="F753" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$753)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="754">
+      <c r="B754" s="2" t="inlineStr">
         <is>
           <t>碳酸钴</t>
         </is>
       </c>
-      <c r="C679" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$679),"")</f>
-        <v/>
-      </c>
-      <c r="D679" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$679),"")</f>
-        <v/>
-      </c>
-      <c r="E679" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$679),"")</f>
-        <v/>
-      </c>
-      <c r="F679" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$679)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="680">
-      <c r="B680" s="2" t="inlineStr">
+      <c r="C754" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$754),"")</f>
+        <v/>
+      </c>
+      <c r="D754" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$754),"")</f>
+        <v/>
+      </c>
+      <c r="E754" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$754),"")</f>
+        <v/>
+      </c>
+      <c r="F754" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$754)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="755">
+      <c r="B755" s="2" t="inlineStr">
         <is>
           <t>磷酸铁锂</t>
         </is>
       </c>
-      <c r="C680" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$680),"")</f>
-        <v/>
-      </c>
-      <c r="D680" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$680),"")</f>
-        <v/>
-      </c>
-      <c r="E680" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$680),"")</f>
-        <v/>
-      </c>
-      <c r="F680" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$680)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="681">
-      <c r="B681" s="2" t="inlineStr">
+      <c r="C755" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$755),"")</f>
+        <v/>
+      </c>
+      <c r="D755" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$755),"")</f>
+        <v/>
+      </c>
+      <c r="E755" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$755),"")</f>
+        <v/>
+      </c>
+      <c r="F755" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$755)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="756">
+      <c r="B756" s="2" t="inlineStr">
         <is>
           <t>磷酸锰铁锂</t>
         </is>
       </c>
-      <c r="C681" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$681),"")</f>
-        <v/>
-      </c>
-      <c r="D681" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$681),"")</f>
-        <v/>
-      </c>
-      <c r="E681" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$681),"")</f>
-        <v/>
-      </c>
-      <c r="F681" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$681)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="682">
-      <c r="B682" s="2" t="inlineStr">
+      <c r="C756" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$756),"")</f>
+        <v/>
+      </c>
+      <c r="D756" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$756),"")</f>
+        <v/>
+      </c>
+      <c r="E756" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$756),"")</f>
+        <v/>
+      </c>
+      <c r="F756" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$756)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="757">
+      <c r="B757" s="2" t="inlineStr">
         <is>
           <t>金属钴FOB</t>
         </is>
       </c>
-      <c r="C682" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$682),"")</f>
-        <v/>
-      </c>
-      <c r="D682" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$682),"")</f>
-        <v/>
-      </c>
-      <c r="E682" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$682),"")</f>
-        <v/>
-      </c>
-      <c r="F682" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$682)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="683">
-      <c r="B683" s="2" t="inlineStr">
+      <c r="C757" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$757),"")</f>
+        <v/>
+      </c>
+      <c r="D757" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$757),"")</f>
+        <v/>
+      </c>
+      <c r="E757" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$757),"")</f>
+        <v/>
+      </c>
+      <c r="F757" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$757)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="758">
+      <c r="B758" s="2" t="inlineStr">
         <is>
           <t>钴中间品中钴含量≥30%</t>
         </is>
       </c>
-      <c r="C683" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$683),"")</f>
-        <v/>
-      </c>
-      <c r="D683" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$683),"")</f>
-        <v/>
-      </c>
-      <c r="E683" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$683),"")</f>
-        <v/>
-      </c>
-      <c r="F683" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$683)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="684">
-      <c r="B684" s="2" t="inlineStr">
+      <c r="C758" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$758),"")</f>
+        <v/>
+      </c>
+      <c r="D758" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$758),"")</f>
+        <v/>
+      </c>
+      <c r="E758" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$758),"")</f>
+        <v/>
+      </c>
+      <c r="F758" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$758)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="759">
+      <c r="B759" s="2" t="inlineStr">
         <is>
           <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C684" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$684),"")</f>
-        <v/>
-      </c>
-      <c r="D684" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$684),"")</f>
-        <v/>
-      </c>
-      <c r="E684" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$684),"")</f>
-        <v/>
-      </c>
-      <c r="F684" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$684)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="685">
-      <c r="B685" s="2" t="inlineStr">
+      <c r="C759" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$759),"")</f>
+        <v/>
+      </c>
+      <c r="D759" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$759),"")</f>
+        <v/>
+      </c>
+      <c r="E759" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$759),"")</f>
+        <v/>
+      </c>
+      <c r="F759" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$759)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="760">
+      <c r="B760" s="2" t="inlineStr">
         <is>
           <t>钴酸锂</t>
         </is>
       </c>
-      <c r="C685" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$685),"")</f>
-        <v/>
-      </c>
-      <c r="D685" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$685),"")</f>
-        <v/>
-      </c>
-      <c r="E685" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$685),"")</f>
-        <v/>
-      </c>
-      <c r="F685" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$685)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="686">
-      <c r="B686" s="2" t="inlineStr">
+      <c r="C760" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$760),"")</f>
+        <v/>
+      </c>
+      <c r="D760" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$760),"")</f>
+        <v/>
+      </c>
+      <c r="E760" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$760),"")</f>
+        <v/>
+      </c>
+      <c r="F760" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$760)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="761">
+      <c r="B761" s="2" t="inlineStr">
         <is>
           <t>钴酸锂聚合物软包</t>
         </is>
       </c>
-      <c r="C686" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$686),"")</f>
-        <v/>
-      </c>
-      <c r="D686" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$686),"")</f>
-        <v/>
-      </c>
-      <c r="E686" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$686),"")</f>
-        <v/>
-      </c>
-      <c r="F686" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$686)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="687">
-      <c r="B687" s="2" t="inlineStr">
+      <c r="C761" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$761),"")</f>
+        <v/>
+      </c>
+      <c r="D761" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$761),"")</f>
+        <v/>
+      </c>
+      <c r="E761" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$761),"")</f>
+        <v/>
+      </c>
+      <c r="F761" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$761)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="762">
+      <c r="B762" s="2" t="inlineStr">
         <is>
           <t>钴酸锂铝壳</t>
         </is>
       </c>
-      <c r="C687" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$687),"")</f>
-        <v/>
-      </c>
-      <c r="D687" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$687),"")</f>
-        <v/>
-      </c>
-      <c r="E687" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$687),"")</f>
-        <v/>
-      </c>
-      <c r="F687" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$687)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="688">
-      <c r="B688" s="2" t="inlineStr">
+      <c r="C762" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$762),"")</f>
+        <v/>
+      </c>
+      <c r="D762" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$762),"")</f>
+        <v/>
+      </c>
+      <c r="E762" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$762),"")</f>
+        <v/>
+      </c>
+      <c r="F762" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$762)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="763">
+      <c r="B763" s="2" t="inlineStr">
         <is>
           <t>锰酸锂圆柱钢壳</t>
         </is>
       </c>
-      <c r="C688" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$688),"")</f>
-        <v/>
-      </c>
-      <c r="D688" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$688),"")</f>
-        <v/>
-      </c>
-      <c r="E688" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$688),"")</f>
-        <v/>
-      </c>
-      <c r="F688" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$688)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="689">
-      <c r="B689" s="2" t="inlineStr">
+      <c r="C763" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$763),"")</f>
+        <v/>
+      </c>
+      <c r="D763" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$763),"")</f>
+        <v/>
+      </c>
+      <c r="E763" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$763),"")</f>
+        <v/>
+      </c>
+      <c r="F763" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$763)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="764">
+      <c r="B764" s="2" t="inlineStr">
         <is>
           <t>非洲硫酸锂(CIF中国)</t>
         </is>
       </c>
-      <c r="C689" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$689),"")</f>
-        <v/>
-      </c>
-      <c r="D689" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$689),"")</f>
-        <v/>
-      </c>
-      <c r="E689" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$689),"")</f>
-        <v/>
-      </c>
-      <c r="F689" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$689)*(F$2:F$613),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="690">
-      <c r="B690" s="2" t="inlineStr">
+      <c r="C764" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$764),"")</f>
+        <v/>
+      </c>
+      <c r="D764" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$764),"")</f>
+        <v/>
+      </c>
+      <c r="E764" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$764),"")</f>
+        <v/>
+      </c>
+      <c r="F764" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$764)*(F$2:F$688),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="765">
+      <c r="B765" s="2" t="inlineStr">
         <is>
           <t>非洲锂辉石精矿（CIF中国）指数</t>
         </is>
       </c>
-      <c r="C690" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$690),"")</f>
-        <v/>
-      </c>
-      <c r="D690" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$690),"")</f>
-        <v/>
-      </c>
-      <c r="E690" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$613,A$2:A$613,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$613,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$613,$B$690),"")</f>
-        <v/>
-      </c>
-      <c r="F690" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$613)=YEAR(TODAY()))*(MONTH(A$2:A$613)=MONTH(TODAY()))*(B$2:B$613=$B$690)*(F$2:F$613),"")</f>
+      <c r="C765" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$765),"")</f>
+        <v/>
+      </c>
+      <c r="D765" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$765),"")</f>
+        <v/>
+      </c>
+      <c r="E765" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$765),"")</f>
+        <v/>
+      </c>
+      <c r="F765" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$765)*(F$2:F$688),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H613"/>
+  <autoFilter ref="A1:H688"/>
   <mergeCells count="1">
-    <mergeCell ref="A615:H615"/>
+    <mergeCell ref="A690:H690"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23246,7 +25796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24975,161 +27525,355 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪镍(NI)连续</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>129470</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>129000</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>129480</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>128050</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>960</v>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>上期所</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>碳酸锂(LC)连续</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>153880</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>148940</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>153920</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>145300</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>5880</v>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>广期所</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>国内期货</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>美元/人民币(USDCNY)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>6.7927</v>
+      </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="6" t="n">
+        <v>6.7897</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>6.7786</v>
+      </c>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>CME氢氧化锂</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/29</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>国际期货</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>CME钴</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B46" s="9" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-    </row>
-    <row r="47">
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>CME氢氧化锂</t>
         </is>
       </c>
-      <c r="D47" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$47),"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$47)*(H$2:H$44),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" s="2" t="inlineStr">
+      <c r="D52" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$52),"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$52),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$52),"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$52),"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$49)=YEAR(TODAY()))*(MONTH(A$2:A$49)=MONTH(TODAY()))*(C$2:C$49=$C$52)*(H$2:H$49),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>CME钴</t>
         </is>
       </c>
-      <c r="D48" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$48),"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$48)*(H$2:H$44),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" s="2" t="inlineStr">
+      <c r="D53" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$53),"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$53),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$53),"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$53),"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$49)=YEAR(TODAY()))*(MONTH(A$2:A$49)=MONTH(TODAY()))*(C$2:C$49=$C$53)*(H$2:H$49),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>沪镍(NI)连续</t>
         </is>
       </c>
-      <c r="D49" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$49),"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$49)*(H$2:H$44),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" s="2" t="inlineStr">
+      <c r="D54" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$54),"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$54),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$54),"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$54),"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$49)=YEAR(TODAY()))*(MONTH(A$2:A$49)=MONTH(TODAY()))*(C$2:C$49=$C$54)*(H$2:H$49),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>碳酸锂(LC)连续</t>
         </is>
       </c>
-      <c r="D50" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$50),"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$50)*(H$2:H$44),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" s="2" t="inlineStr">
+      <c r="D55" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$55),"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$55),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$55),"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$55),"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$49)=YEAR(TODAY()))*(MONTH(A$2:A$49)=MONTH(TODAY()))*(C$2:C$49=$C$55)*(H$2:H$49),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>美元/人民币(USDCNY)</t>
         </is>
       </c>
-      <c r="D51" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IFERROR(AVERAGEIFS(F$2:F$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="10">
-        <f>IFERROR(AVERAGEIFS(G$2:G$44,A$2:A$44,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$44,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$44,$C$51),"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$44)=YEAR(TODAY()))*(MONTH(A$2:A$44)=MONTH(TODAY()))*(C$2:C$44=$C$51)*(H$2:H$44),"")</f>
+      <c r="D56" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$56),"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$56),"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="10">
+        <f>IFERROR(AVERAGEIFS(F$2:F$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$56),"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="10">
+        <f>IFERROR(AVERAGEIFS(G$2:G$49,A$2:A$49,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$49,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),C$2:C$49,$C$56),"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$49)=YEAR(TODAY()))*(MONTH(A$2:A$49)=MONTH(TODAY()))*(C$2:C$49=$C$56)*(H$2:H$49),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J44"/>
+  <autoFilter ref="A1:J49"/>
   <mergeCells count="1">
-    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A51:J51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -27626,7 +27626,7 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>6.7927</v>
+        <v>6.7923</v>
       </c>
       <c r="E47" s="5" t="n"/>
       <c r="F47" s="6" t="n">

--- a/金属价格日报.xlsx
+++ b/金属价格日报.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑粉计价" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$688</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'现货'!$A$1:$H$763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'期货'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H765"/>
+  <dimension ref="A1:H840"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -24042,1749 +24042,4299 @@
         </is>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B689" s="2" t="inlineStr">
+        <is>
+          <t>5系三元前驱体</t>
+        </is>
+      </c>
+      <c r="C689" s="3" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D689" s="4" t="n">
+        <v>103050</v>
+      </c>
+      <c r="E689" s="4" t="n">
+        <v>100550</v>
+      </c>
+      <c r="F689" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G689" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H689" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
     <row r="690">
-      <c r="A690" s="8" t="inlineStr">
+      <c r="A690" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B690" s="2" t="inlineStr">
+        <is>
+          <t>5系三元材料</t>
+        </is>
+      </c>
+      <c r="C690" s="3" t="n">
+        <v>181400</v>
+      </c>
+      <c r="D690" s="4" t="n">
+        <v>188100</v>
+      </c>
+      <c r="E690" s="4" t="n">
+        <v>184750</v>
+      </c>
+      <c r="F690" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G690" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H690" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B691" s="2" t="inlineStr">
+        <is>
+          <t>6系三元前驱体（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C691" s="3" t="n">
+        <v>90950</v>
+      </c>
+      <c r="D691" s="4" t="n">
+        <v>95550</v>
+      </c>
+      <c r="E691" s="4" t="n">
+        <v>93250</v>
+      </c>
+      <c r="F691" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G691" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H691" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>6系三元材料（单晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C692" s="3" t="n">
+        <v>183900</v>
+      </c>
+      <c r="D692" s="4" t="n">
+        <v>193400</v>
+      </c>
+      <c r="E692" s="4" t="n">
+        <v>188650</v>
+      </c>
+      <c r="F692" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G692" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H692" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B693" s="2" t="inlineStr">
+        <is>
+          <t>8系三元前驱体（多晶/动力型）</t>
+        </is>
+      </c>
+      <c r="C693" s="3" t="n">
+        <v>112450</v>
+      </c>
+      <c r="D693" s="4" t="n">
+        <v>118050</v>
+      </c>
+      <c r="E693" s="4" t="n">
+        <v>115250</v>
+      </c>
+      <c r="F693" s="4" t="n">
+        <v>-300</v>
+      </c>
+      <c r="G693" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H693" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B694" s="2" t="inlineStr">
+        <is>
+          <t>8系三元材料</t>
+        </is>
+      </c>
+      <c r="C694" s="3" t="n">
+        <v>207100</v>
+      </c>
+      <c r="D694" s="4" t="n">
+        <v>216700</v>
+      </c>
+      <c r="E694" s="4" t="n">
+        <v>211900</v>
+      </c>
+      <c r="F694" s="4" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G694" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H694" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>MHP系数（对SMM电池级硫酸镍指数）</t>
+        </is>
+      </c>
+      <c r="C695" s="7" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="D695" s="6" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="E695" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="F695" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G695" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H695" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B696" s="2" t="inlineStr">
+        <is>
+          <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C696" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D696" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="E696" s="6" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="F696" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G696" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H696" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B697" s="2" t="inlineStr">
+        <is>
+          <t>NCA三元材料</t>
+        </is>
+      </c>
+      <c r="C697" s="3" t="n">
+        <v>205700</v>
+      </c>
+      <c r="D697" s="4" t="n">
+        <v>213800</v>
+      </c>
+      <c r="E697" s="4" t="n">
+        <v>209750</v>
+      </c>
+      <c r="F697" s="4" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G697" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H697" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B698" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C698" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D698" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E698" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F698" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G698" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H698" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B699" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C699" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D699" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E699" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F699" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G699" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H699" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B700" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元极片粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C700" s="7" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="D700" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="E700" s="6" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="F700" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G700" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H700" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B701" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C701" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D701" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E701" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F701" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G701" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H701" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B702" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C702" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D702" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E702" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F702" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G702" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H702" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B703" s="2" t="inlineStr">
+        <is>
+          <t>SMM三元电池粉镍系数指数</t>
+        </is>
+      </c>
+      <c r="C703" s="7" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D703" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E703" s="6" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F703" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G703" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H703" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B704" s="2" t="inlineStr">
+        <is>
+          <t>SMM六氟磷酸锂指数</t>
+        </is>
+      </c>
+      <c r="C704" s="3" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D704" s="4" t="n">
+        <v>103292</v>
+      </c>
+      <c r="E704" s="4" t="n">
+        <v>101267</v>
+      </c>
+      <c r="F704" s="4" t="n">
+        <v>-730</v>
+      </c>
+      <c r="G704" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H704" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B705" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级氢氧化锂指数</t>
+        </is>
+      </c>
+      <c r="C705" s="3" t="n">
+        <v>142709</v>
+      </c>
+      <c r="D705" s="4" t="n">
+        <v>142709</v>
+      </c>
+      <c r="E705" s="4" t="n">
+        <v>142709</v>
+      </c>
+      <c r="F705" s="4" t="n">
+        <v>3954</v>
+      </c>
+      <c r="G705" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H705" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸锰指数</t>
+        </is>
+      </c>
+      <c r="C706" s="3" t="n">
+        <v>7684</v>
+      </c>
+      <c r="D706" s="4" t="n">
+        <v>7684</v>
+      </c>
+      <c r="E706" s="4" t="n">
+        <v>7684</v>
+      </c>
+      <c r="F706" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G706" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H706" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B707" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级硫酸镍指数</t>
+        </is>
+      </c>
+      <c r="C707" s="3" t="n">
+        <v>32352</v>
+      </c>
+      <c r="D707" s="4" t="n">
+        <v>32352</v>
+      </c>
+      <c r="E707" s="4" t="n">
+        <v>32352</v>
+      </c>
+      <c r="F707" s="4" t="n">
+        <v>-154</v>
+      </c>
+      <c r="G707" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H707" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B708" s="2" t="inlineStr">
+        <is>
+          <t>SMM电池级碳酸锂指数</t>
+        </is>
+      </c>
+      <c r="C708" s="3" t="n">
+        <v>156580</v>
+      </c>
+      <c r="D708" s="4" t="n">
+        <v>156580</v>
+      </c>
+      <c r="E708" s="4" t="n">
+        <v>156580</v>
+      </c>
+      <c r="F708" s="4" t="n">
+        <v>6689</v>
+      </c>
+      <c r="G708" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H708" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B709" s="2" t="inlineStr">
+        <is>
+          <t>SMM硫酸钴指数</t>
+        </is>
+      </c>
+      <c r="C709" s="3" t="n">
+        <v>85772</v>
+      </c>
+      <c r="D709" s="4" t="n">
+        <v>85772</v>
+      </c>
+      <c r="E709" s="4" t="n">
+        <v>85772</v>
+      </c>
+      <c r="F709" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G709" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H709" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B710" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂极片粉指数</t>
+        </is>
+      </c>
+      <c r="C710" s="3" t="n">
+        <v>6803</v>
+      </c>
+      <c r="D710" s="4" t="n">
+        <v>6803</v>
+      </c>
+      <c r="E710" s="4" t="n">
+        <v>6803</v>
+      </c>
+      <c r="F710" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G710" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H710" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B711" s="2" t="inlineStr">
+        <is>
+          <t>SMM磷酸铁锂电池粉指数</t>
+        </is>
+      </c>
+      <c r="C711" s="3" t="n">
+        <v>6461</v>
+      </c>
+      <c r="D711" s="4" t="n">
+        <v>6461</v>
+      </c>
+      <c r="E711" s="4" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F711" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G711" s="5" t="inlineStr">
+        <is>
+          <t>元/锂点</t>
+        </is>
+      </c>
+      <c r="H711" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B712" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C712" s="7" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="D712" s="6" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="E712" s="6" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="F712" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G712" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H712" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B713" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂极片粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C713" s="7" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="D713" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="E713" s="6" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="F713" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G713" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H713" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B714" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉钴系数指数</t>
+        </is>
+      </c>
+      <c r="C714" s="7" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="D714" s="6" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="E714" s="6" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="F714" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G714" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H714" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B715" s="2" t="inlineStr">
+        <is>
+          <t>SMM钴酸锂电池粉锂系数指数</t>
+        </is>
+      </c>
+      <c r="C715" s="7" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="D715" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="E715" s="6" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="F715" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G715" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H715" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B716" s="2" t="inlineStr">
+        <is>
+          <t>三元方壳锂电B品</t>
+        </is>
+      </c>
+      <c r="C716" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D716" s="6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E716" s="6" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="F716" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G716" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H716" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>六氟磷酸锂（国产）</t>
+        </is>
+      </c>
+      <c r="C717" s="3" t="n">
+        <v>102000</v>
+      </c>
+      <c r="D717" s="4" t="n">
+        <v>105000</v>
+      </c>
+      <c r="E717" s="4" t="n">
+        <v>103500</v>
+      </c>
+      <c r="F717" s="4" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="G717" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H717" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B718" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三钴</t>
+        </is>
+      </c>
+      <c r="C718" s="3" t="n">
+        <v>329000</v>
+      </c>
+      <c r="D718" s="4" t="n">
+        <v>341000</v>
+      </c>
+      <c r="E718" s="4" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F718" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G718" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H718" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B719" s="2" t="inlineStr">
+        <is>
+          <t>四氧化三锰（电池级）</t>
+        </is>
+      </c>
+      <c r="C719" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D719" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E719" s="4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F719" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G719" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H719" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B720" s="2" t="inlineStr">
+        <is>
+          <t>工业级氢氧化锂</t>
+        </is>
+      </c>
+      <c r="C720" s="3" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D720" s="4" t="n">
+        <v>134500</v>
+      </c>
+      <c r="E720" s="4" t="n">
+        <v>131250</v>
+      </c>
+      <c r="F720" s="4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G720" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H720" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B721" s="2" t="inlineStr">
+        <is>
+          <t>工业级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C721" s="3" t="n">
+        <v>147000</v>
+      </c>
+      <c r="D721" s="4" t="n">
+        <v>158000</v>
+      </c>
+      <c r="E721" s="4" t="n">
+        <v>152500</v>
+      </c>
+      <c r="F721" s="4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G721" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H721" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B722" s="2" t="inlineStr">
+        <is>
+          <t>工业级金属锂</t>
+        </is>
+      </c>
+      <c r="C722" s="3" t="n">
+        <v>1040000</v>
+      </c>
+      <c r="D722" s="4" t="n">
+        <v>1060000</v>
+      </c>
+      <c r="E722" s="4" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="F722" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G722" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H722" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B723" s="2" t="inlineStr">
+        <is>
+          <t>巴西锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C723" s="3" t="n">
+        <v>2170</v>
+      </c>
+      <c r="D723" s="4" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E723" s="4" t="n">
+        <v>2210</v>
+      </c>
+      <c r="F723" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G723" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H723" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B724" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂储能正极片</t>
+        </is>
+      </c>
+      <c r="C724" s="3" t="n">
+        <v>20500</v>
+      </c>
+      <c r="D724" s="4" t="n">
+        <v>23500</v>
+      </c>
+      <c r="E724" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F724" s="4" t="n">
+        <v>425</v>
+      </c>
+      <c r="G724" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H724" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B725" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂动力正极片</t>
+        </is>
+      </c>
+      <c r="C725" s="3" t="n">
+        <v>24300</v>
+      </c>
+      <c r="D725" s="4" t="n">
+        <v>28600</v>
+      </c>
+      <c r="E725" s="4" t="n">
+        <v>26450</v>
+      </c>
+      <c r="F725" s="4" t="n">
+        <v>525</v>
+      </c>
+      <c r="G725" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H725" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B726" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂软包电池</t>
+        </is>
+      </c>
+      <c r="C726" s="3" t="n">
+        <v>15300</v>
+      </c>
+      <c r="D726" s="4" t="n">
+        <v>16700</v>
+      </c>
+      <c r="E726" s="4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F726" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="G726" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H726" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B727" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂钢壳电池</t>
+        </is>
+      </c>
+      <c r="C727" s="3" t="n">
+        <v>9800</v>
+      </c>
+      <c r="D727" s="4" t="n">
+        <v>10700</v>
+      </c>
+      <c r="E727" s="4" t="n">
+        <v>10250</v>
+      </c>
+      <c r="F727" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G727" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H727" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>废旧磷酸铁锂铝壳电池</t>
+        </is>
+      </c>
+      <c r="C728" s="3" t="n">
+        <v>16600</v>
+      </c>
+      <c r="D728" s="4" t="n">
+        <v>17700</v>
+      </c>
+      <c r="E728" s="4" t="n">
+        <v>17150</v>
+      </c>
+      <c r="F728" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G728" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H728" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B729" s="2" t="inlineStr">
+        <is>
+          <t>方形磷酸铁锂电池B品</t>
+        </is>
+      </c>
+      <c r="C729" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D729" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E729" s="6" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F729" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G729" s="5" t="inlineStr">
+        <is>
+          <t>元/Ah</t>
+        </is>
+      </c>
+      <c r="H729" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B730" s="2" t="inlineStr">
+        <is>
+          <t>氧化亚镍</t>
+        </is>
+      </c>
+      <c r="C730" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D730" s="4" t="n">
+        <v>126000</v>
+      </c>
+      <c r="E730" s="4" t="n">
+        <v>122000</v>
+      </c>
+      <c r="F730" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G730" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H730" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B731" s="2" t="inlineStr">
+        <is>
+          <t>氧化钴</t>
+        </is>
+      </c>
+      <c r="C731" s="3" t="n">
+        <v>302000</v>
+      </c>
+      <c r="D731" s="4" t="n">
+        <v>315000</v>
+      </c>
+      <c r="E731" s="4" t="n">
+        <v>308500</v>
+      </c>
+      <c r="F731" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G731" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H731" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B732" s="2" t="inlineStr">
+        <is>
+          <t>氯化钴</t>
+        </is>
+      </c>
+      <c r="C732" s="3" t="n">
+        <v>104000</v>
+      </c>
+      <c r="D732" s="4" t="n">
+        <v>106500</v>
+      </c>
+      <c r="E732" s="4" t="n">
+        <v>105250</v>
+      </c>
+      <c r="F732" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G732" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H732" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B733" s="2" t="inlineStr">
+        <is>
+          <t>氯化镍NiCl₂·6H₂O</t>
+        </is>
+      </c>
+      <c r="C733" s="3" t="n">
+        <v>38500</v>
+      </c>
+      <c r="D733" s="4" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E733" s="4" t="n">
+        <v>39750</v>
+      </c>
+      <c r="F733" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G733" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H733" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B734" s="2" t="inlineStr">
+        <is>
+          <t>津巴布韦锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C734" s="3" t="n">
+        <v>2060</v>
+      </c>
+      <c r="D734" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E734" s="4" t="n">
+        <v>2130</v>
+      </c>
+      <c r="F734" s="4" t="n">
+        <v>-285</v>
+      </c>
+      <c r="G734" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H734" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B735" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚锂辉石精矿（CIF中国）现货</t>
+        </is>
+      </c>
+      <c r="C735" s="3" t="n">
+        <v>2190</v>
+      </c>
+      <c r="D735" s="4" t="n">
+        <v>2260</v>
+      </c>
+      <c r="E735" s="4" t="n">
+        <v>2225</v>
+      </c>
+      <c r="F735" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="G735" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H735" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B736" s="2" t="inlineStr">
+        <is>
+          <t>电池级无水氯化锂</t>
+        </is>
+      </c>
+      <c r="C736" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="D736" s="4" t="n">
+        <v>290</v>
+      </c>
+      <c r="E736" s="4" t="n">
+        <v>260</v>
+      </c>
+      <c r="F736" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G736" s="5" t="inlineStr">
+        <is>
+          <t>元/千克</t>
+        </is>
+      </c>
+      <c r="H736" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B737" s="2" t="inlineStr">
+        <is>
+          <t>电池级氟化锂</t>
+        </is>
+      </c>
+      <c r="C737" s="3" t="n">
+        <v>265000</v>
+      </c>
+      <c r="D737" s="4" t="n">
+        <v>273000</v>
+      </c>
+      <c r="E737" s="4" t="n">
+        <v>269000</v>
+      </c>
+      <c r="F737" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G737" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H737" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B738" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF中日韩)</t>
+        </is>
+      </c>
+      <c r="C738" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D738" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E738" s="6" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="F738" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G738" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H738" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C739" s="7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D739" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E739" s="6" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F739" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G739" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H739" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B740" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂(微粉）</t>
+        </is>
+      </c>
+      <c r="C740" s="3" t="n">
+        <v>144500</v>
+      </c>
+      <c r="D740" s="4" t="n">
+        <v>155000</v>
+      </c>
+      <c r="E740" s="4" t="n">
+        <v>149750</v>
+      </c>
+      <c r="F740" s="4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G740" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H740" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B741" s="2" t="inlineStr">
+        <is>
+          <t>电池级氢氧化锂（粗颗粒）</t>
+        </is>
+      </c>
+      <c r="C741" s="3" t="n">
+        <v>135500</v>
+      </c>
+      <c r="D741" s="4" t="n">
+        <v>152000</v>
+      </c>
+      <c r="E741" s="4" t="n">
+        <v>143750</v>
+      </c>
+      <c r="F741" s="4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G741" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H741" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B742" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸锰（出厂价）</t>
+        </is>
+      </c>
+      <c r="C742" s="3" t="n">
+        <v>7580</v>
+      </c>
+      <c r="D742" s="4" t="n">
+        <v>7800</v>
+      </c>
+      <c r="E742" s="4" t="n">
+        <v>7690</v>
+      </c>
+      <c r="F742" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G742" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H742" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B743" s="2" t="inlineStr">
+        <is>
+          <t>电池级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C743" s="3" t="n">
+        <v>32000</v>
+      </c>
+      <c r="D743" s="4" t="n">
+        <v>32400</v>
+      </c>
+      <c r="E743" s="4" t="n">
+        <v>32200</v>
+      </c>
+      <c r="F743" s="4" t="n">
+        <v>-160</v>
+      </c>
+      <c r="G743" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H743" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B744" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂</t>
+        </is>
+      </c>
+      <c r="C744" s="3" t="n">
+        <v>151000</v>
+      </c>
+      <c r="D744" s="4" t="n">
+        <v>162000</v>
+      </c>
+      <c r="E744" s="4" t="n">
+        <v>156500</v>
+      </c>
+      <c r="F744" s="4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="G744" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H744" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B745" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂(CIF韩国)</t>
+        </is>
+      </c>
+      <c r="C745" s="7" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D745" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E745" s="6" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="F745" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G745" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H745" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B746" s="2" t="inlineStr">
+        <is>
+          <t>电池级碳酸锂（CIF中日韩）</t>
+        </is>
+      </c>
+      <c r="C746" s="7" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D746" s="6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E746" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F746" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G746" s="5" t="inlineStr">
+        <is>
+          <t>美元/千克</t>
+        </is>
+      </c>
+      <c r="H746" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B747" s="2" t="inlineStr">
+        <is>
+          <t>电池级金属锂</t>
+        </is>
+      </c>
+      <c r="C747" s="3" t="n">
+        <v>1070000</v>
+      </c>
+      <c r="D747" s="4" t="n">
+        <v>1090000</v>
+      </c>
+      <c r="E747" s="4" t="n">
+        <v>1080000</v>
+      </c>
+      <c r="F747" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G747" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H747" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B748" s="2" t="inlineStr">
+        <is>
+          <t>电解钴</t>
+        </is>
+      </c>
+      <c r="C748" s="3" t="n">
+        <v>374000</v>
+      </c>
+      <c r="D748" s="4" t="n">
+        <v>385000</v>
+      </c>
+      <c r="E748" s="4" t="n">
+        <v>379500</v>
+      </c>
+      <c r="F748" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G748" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H748" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B749" s="2" t="inlineStr">
+        <is>
+          <t>电解钴（鹿特丹仓库）</t>
+        </is>
+      </c>
+      <c r="C749" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D749" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E749" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F749" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G749" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H749" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>电镀级硫酸镍</t>
+        </is>
+      </c>
+      <c r="C750" s="3" t="n">
+        <v>32500</v>
+      </c>
+      <c r="D750" s="4" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E750" s="4" t="n">
+        <v>34750</v>
+      </c>
+      <c r="F750" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G750" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H750" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B751" s="2" t="inlineStr">
+        <is>
+          <t>硫酸钴</t>
+        </is>
+      </c>
+      <c r="C751" s="3" t="n">
+        <v>85000</v>
+      </c>
+      <c r="D751" s="4" t="n">
+        <v>87000</v>
+      </c>
+      <c r="E751" s="4" t="n">
+        <v>86000</v>
+      </c>
+      <c r="F751" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G751" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H751" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B752" s="2" t="inlineStr">
+        <is>
+          <t>碳酸钴</t>
+        </is>
+      </c>
+      <c r="C752" s="3" t="n">
+        <v>208000</v>
+      </c>
+      <c r="D752" s="4" t="n">
+        <v>213000</v>
+      </c>
+      <c r="E752" s="4" t="n">
+        <v>210500</v>
+      </c>
+      <c r="F752" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G752" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H752" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B753" s="2" t="inlineStr">
+        <is>
+          <t>磷酸铁锂</t>
+        </is>
+      </c>
+      <c r="C753" s="3" t="n">
+        <v>56640</v>
+      </c>
+      <c r="D753" s="4" t="n">
+        <v>57340</v>
+      </c>
+      <c r="E753" s="4" t="n">
+        <v>56990</v>
+      </c>
+      <c r="F753" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="G753" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H753" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B754" s="2" t="inlineStr">
+        <is>
+          <t>磷酸锰铁锂</t>
+        </is>
+      </c>
+      <c r="C754" s="3" t="n">
+        <v>62500</v>
+      </c>
+      <c r="D754" s="4" t="n">
+        <v>67500</v>
+      </c>
+      <c r="E754" s="4" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F754" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G754" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H754" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B755" s="2" t="inlineStr">
+        <is>
+          <t>金属钴FOB</t>
+        </is>
+      </c>
+      <c r="C755" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D755" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E755" s="6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F755" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G755" s="5" t="inlineStr">
+        <is>
+          <t>美元/磅</t>
+        </is>
+      </c>
+      <c r="H755" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B756" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品中钴含量≥30%</t>
+        </is>
+      </c>
+      <c r="C756" s="3" t="n">
+        <v>26122</v>
+      </c>
+      <c r="D756" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="E756" s="4" t="n">
+        <v>26122</v>
+      </c>
+      <c r="F756" s="4" t="n">
+        <v>-661</v>
+      </c>
+      <c r="G756" s="5" t="inlineStr">
+        <is>
+          <t>元/金属吨</t>
+        </is>
+      </c>
+      <c r="H756" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B757" s="2" t="inlineStr">
+        <is>
+          <t>钴中间品原料计价系数（对SMM硫酸钴均价）</t>
+        </is>
+      </c>
+      <c r="C757" s="7" t="n">
+        <v>99</v>
+      </c>
+      <c r="D757" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E757" s="6" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F757" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G757" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H757" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B758" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂</t>
+        </is>
+      </c>
+      <c r="C758" s="3" t="n">
+        <v>373000</v>
+      </c>
+      <c r="D758" s="4" t="n">
+        <v>376000</v>
+      </c>
+      <c r="E758" s="4" t="n">
+        <v>374500</v>
+      </c>
+      <c r="F758" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G758" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H758" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B759" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂聚合物软包</t>
+        </is>
+      </c>
+      <c r="C759" s="3" t="n">
+        <v>96200</v>
+      </c>
+      <c r="D759" s="4" t="n">
+        <v>98500</v>
+      </c>
+      <c r="E759" s="4" t="n">
+        <v>97350</v>
+      </c>
+      <c r="F759" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G759" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H759" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B760" s="2" t="inlineStr">
+        <is>
+          <t>钴酸锂铝壳</t>
+        </is>
+      </c>
+      <c r="C760" s="3" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D760" s="4" t="n">
+        <v>90500</v>
+      </c>
+      <c r="E760" s="4" t="n">
+        <v>87250</v>
+      </c>
+      <c r="F760" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G760" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H760" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>锰酸锂圆柱钢壳</t>
+        </is>
+      </c>
+      <c r="C761" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D761" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="E761" s="4" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F761" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G761" s="5" t="inlineStr">
+        <is>
+          <t>元/吨</t>
+        </is>
+      </c>
+      <c r="H761" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B762" s="2" t="inlineStr">
+        <is>
+          <t>非洲硫酸锂(CIF中国)</t>
+        </is>
+      </c>
+      <c r="C762" s="3" t="n">
+        <v>7253</v>
+      </c>
+      <c r="D762" s="4" t="n">
+        <v>7848</v>
+      </c>
+      <c r="E762" s="4" t="n">
+        <v>7550.5</v>
+      </c>
+      <c r="F762" s="4" t="n">
+        <v>259</v>
+      </c>
+      <c r="G762" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H762" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2" t="inlineStr">
+        <is>
+          <t>2026/06/30</t>
+        </is>
+      </c>
+      <c r="B763" s="2" t="inlineStr">
+        <is>
+          <t>非洲锂辉石精矿（CIF中国）指数</t>
+        </is>
+      </c>
+      <c r="C763" s="3" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D763" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E763" s="4" t="n">
+        <v>2120</v>
+      </c>
+      <c r="F763" s="4" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G763" s="5" t="inlineStr">
+        <is>
+          <t>美元/吨</t>
+        </is>
+      </c>
+      <c r="H763" s="5" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="8" t="inlineStr">
         <is>
           <t>当月均价</t>
         </is>
       </c>
-      <c r="B690" s="9" t="n"/>
-      <c r="C690" s="9" t="n"/>
-      <c r="D690" s="9" t="n"/>
-      <c r="E690" s="9" t="n"/>
-      <c r="F690" s="9" t="n"/>
-      <c r="G690" s="9" t="n"/>
-      <c r="H690" s="9" t="n"/>
-    </row>
-    <row r="691">
-      <c r="B691" s="2" t="inlineStr">
+      <c r="B765" s="9" t="n"/>
+      <c r="C765" s="9" t="n"/>
+      <c r="D765" s="9" t="n"/>
+      <c r="E765" s="9" t="n"/>
+      <c r="F765" s="9" t="n"/>
+      <c r="G765" s="9" t="n"/>
+      <c r="H765" s="9" t="n"/>
+    </row>
+    <row r="766">
+      <c r="B766" s="2" t="inlineStr">
         <is>
           <t>5系三元前驱体</t>
         </is>
       </c>
-      <c r="C691" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$691),"")</f>
-        <v/>
-      </c>
-      <c r="D691" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$691),"")</f>
-        <v/>
-      </c>
-      <c r="E691" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$691),"")</f>
-        <v/>
-      </c>
-      <c r="F691" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$691)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="692">
-      <c r="B692" s="2" t="inlineStr">
+      <c r="C766" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$766),"")</f>
+        <v/>
+      </c>
+      <c r="D766" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$766),"")</f>
+        <v/>
+      </c>
+      <c r="E766" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$766),"")</f>
+        <v/>
+      </c>
+      <c r="F766" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$766)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="767">
+      <c r="B767" s="2" t="inlineStr">
         <is>
           <t>5系三元材料</t>
         </is>
       </c>
-      <c r="C692" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$692),"")</f>
-        <v/>
-      </c>
-      <c r="D692" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$692),"")</f>
-        <v/>
-      </c>
-      <c r="E692" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$692),"")</f>
-        <v/>
-      </c>
-      <c r="F692" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$692)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="693">
-      <c r="B693" s="2" t="inlineStr">
+      <c r="C767" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$767),"")</f>
+        <v/>
+      </c>
+      <c r="D767" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$767),"")</f>
+        <v/>
+      </c>
+      <c r="E767" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$767),"")</f>
+        <v/>
+      </c>
+      <c r="F767" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$767)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="768">
+      <c r="B768" s="2" t="inlineStr">
         <is>
           <t>6系三元前驱体（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C693" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$693),"")</f>
-        <v/>
-      </c>
-      <c r="D693" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$693),"")</f>
-        <v/>
-      </c>
-      <c r="E693" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$693),"")</f>
-        <v/>
-      </c>
-      <c r="F693" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$693)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="694">
-      <c r="B694" s="2" t="inlineStr">
+      <c r="C768" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$768),"")</f>
+        <v/>
+      </c>
+      <c r="D768" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$768),"")</f>
+        <v/>
+      </c>
+      <c r="E768" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$768),"")</f>
+        <v/>
+      </c>
+      <c r="F768" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$768)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="769">
+      <c r="B769" s="2" t="inlineStr">
         <is>
           <t>6系三元材料（单晶/动力型）</t>
         </is>
       </c>
-      <c r="C694" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$694),"")</f>
-        <v/>
-      </c>
-      <c r="D694" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$694),"")</f>
-        <v/>
-      </c>
-      <c r="E694" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$694),"")</f>
-        <v/>
-      </c>
-      <c r="F694" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$694)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="695">
-      <c r="B695" s="2" t="inlineStr">
+      <c r="C769" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$769),"")</f>
+        <v/>
+      </c>
+      <c r="D769" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$769),"")</f>
+        <v/>
+      </c>
+      <c r="E769" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$769),"")</f>
+        <v/>
+      </c>
+      <c r="F769" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$769)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="770">
+      <c r="B770" s="2" t="inlineStr">
         <is>
           <t>8系三元前驱体（多晶/动力型）</t>
         </is>
       </c>
-      <c r="C695" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$695),"")</f>
-        <v/>
-      </c>
-      <c r="D695" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$695),"")</f>
-        <v/>
-      </c>
-      <c r="E695" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$695),"")</f>
-        <v/>
-      </c>
-      <c r="F695" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$695)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="696">
-      <c r="B696" s="2" t="inlineStr">
+      <c r="C770" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$770),"")</f>
+        <v/>
+      </c>
+      <c r="D770" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$770),"")</f>
+        <v/>
+      </c>
+      <c r="E770" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$770),"")</f>
+        <v/>
+      </c>
+      <c r="F770" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$770)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="771">
+      <c r="B771" s="2" t="inlineStr">
         <is>
           <t>8系三元材料</t>
         </is>
       </c>
-      <c r="C696" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$696),"")</f>
-        <v/>
-      </c>
-      <c r="D696" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$696),"")</f>
-        <v/>
-      </c>
-      <c r="E696" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$696),"")</f>
-        <v/>
-      </c>
-      <c r="F696" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$696)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="697">
-      <c r="B697" s="2" t="inlineStr">
+      <c r="C771" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$771),"")</f>
+        <v/>
+      </c>
+      <c r="D771" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$771),"")</f>
+        <v/>
+      </c>
+      <c r="E771" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$771),"")</f>
+        <v/>
+      </c>
+      <c r="F771" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$771)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="772">
+      <c r="B772" s="2" t="inlineStr">
         <is>
           <t>MHP系数（对SMM电池级硫酸镍指数）</t>
         </is>
       </c>
-      <c r="C697" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$697),"")</f>
-        <v/>
-      </c>
-      <c r="D697" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$697),"")</f>
-        <v/>
-      </c>
-      <c r="E697" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$697),"")</f>
-        <v/>
-      </c>
-      <c r="F697" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$697)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="698">
-      <c r="B698" s="2" t="inlineStr">
+      <c r="C772" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$772),"")</f>
+        <v/>
+      </c>
+      <c r="D772" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$772),"")</f>
+        <v/>
+      </c>
+      <c r="E772" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$772),"")</f>
+        <v/>
+      </c>
+      <c r="F772" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$772)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="773">
+      <c r="B773" s="2" t="inlineStr">
         <is>
           <t>MHP钴元素计价系数（对SMM硫酸钴均价）</t>
         </is>
       </c>
-      <c r="C698" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$698),"")</f>
-        <v/>
-      </c>
-      <c r="D698" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$698),"")</f>
-        <v/>
-      </c>
-      <c r="E698" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$698),"")</f>
-        <v/>
-      </c>
-      <c r="F698" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$698)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="699">
-      <c r="B699" s="2" t="inlineStr">
+      <c r="C773" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$773),"")</f>
+        <v/>
+      </c>
+      <c r="D773" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$773),"")</f>
+        <v/>
+      </c>
+      <c r="E773" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$773),"")</f>
+        <v/>
+      </c>
+      <c r="F773" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$773)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="774">
+      <c r="B774" s="2" t="inlineStr">
         <is>
           <t>NCA三元材料</t>
         </is>
       </c>
-      <c r="C699" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$699),"")</f>
-        <v/>
-      </c>
-      <c r="D699" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$699),"")</f>
-        <v/>
-      </c>
-      <c r="E699" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$699),"")</f>
-        <v/>
-      </c>
-      <c r="F699" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$699)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="700">
-      <c r="B700" s="2" t="inlineStr">
+      <c r="C774" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$774),"")</f>
+        <v/>
+      </c>
+      <c r="D774" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$774),"")</f>
+        <v/>
+      </c>
+      <c r="E774" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$774),"")</f>
+        <v/>
+      </c>
+      <c r="F774" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$774)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="775">
+      <c r="B775" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C700" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$700),"")</f>
-        <v/>
-      </c>
-      <c r="D700" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$700),"")</f>
-        <v/>
-      </c>
-      <c r="E700" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$700),"")</f>
-        <v/>
-      </c>
-      <c r="F700" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$700)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="701">
-      <c r="B701" s="2" t="inlineStr">
+      <c r="C775" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$775),"")</f>
+        <v/>
+      </c>
+      <c r="D775" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$775),"")</f>
+        <v/>
+      </c>
+      <c r="E775" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$775),"")</f>
+        <v/>
+      </c>
+      <c r="F775" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$775)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="776">
+      <c r="B776" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C701" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$701),"")</f>
-        <v/>
-      </c>
-      <c r="D701" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$701),"")</f>
-        <v/>
-      </c>
-      <c r="E701" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$701),"")</f>
-        <v/>
-      </c>
-      <c r="F701" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$701)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="702">
-      <c r="B702" s="2" t="inlineStr">
+      <c r="C776" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$776),"")</f>
+        <v/>
+      </c>
+      <c r="D776" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$776),"")</f>
+        <v/>
+      </c>
+      <c r="E776" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$776),"")</f>
+        <v/>
+      </c>
+      <c r="F776" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$776)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="777">
+      <c r="B777" s="2" t="inlineStr">
         <is>
           <t>SMM三元极片粉镍系数指数</t>
         </is>
       </c>
-      <c r="C702" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$702),"")</f>
-        <v/>
-      </c>
-      <c r="D702" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$702),"")</f>
-        <v/>
-      </c>
-      <c r="E702" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$702),"")</f>
-        <v/>
-      </c>
-      <c r="F702" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$702)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="703">
-      <c r="B703" s="2" t="inlineStr">
+      <c r="C777" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$777),"")</f>
+        <v/>
+      </c>
+      <c r="D777" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$777),"")</f>
+        <v/>
+      </c>
+      <c r="E777" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$777),"")</f>
+        <v/>
+      </c>
+      <c r="F777" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$777)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="778">
+      <c r="B778" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C703" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$703),"")</f>
-        <v/>
-      </c>
-      <c r="D703" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$703),"")</f>
-        <v/>
-      </c>
-      <c r="E703" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$703),"")</f>
-        <v/>
-      </c>
-      <c r="F703" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$703)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="704">
-      <c r="B704" s="2" t="inlineStr">
+      <c r="C778" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$778),"")</f>
+        <v/>
+      </c>
+      <c r="D778" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$778),"")</f>
+        <v/>
+      </c>
+      <c r="E778" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$778),"")</f>
+        <v/>
+      </c>
+      <c r="F778" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$778)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="779">
+      <c r="B779" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C704" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$704),"")</f>
-        <v/>
-      </c>
-      <c r="D704" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$704),"")</f>
-        <v/>
-      </c>
-      <c r="E704" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$704),"")</f>
-        <v/>
-      </c>
-      <c r="F704" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$704)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="705">
-      <c r="B705" s="2" t="inlineStr">
+      <c r="C779" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$779),"")</f>
+        <v/>
+      </c>
+      <c r="D779" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$779),"")</f>
+        <v/>
+      </c>
+      <c r="E779" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$779),"")</f>
+        <v/>
+      </c>
+      <c r="F779" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$779)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="780">
+      <c r="B780" s="2" t="inlineStr">
         <is>
           <t>SMM三元电池粉镍系数指数</t>
         </is>
       </c>
-      <c r="C705" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$705),"")</f>
-        <v/>
-      </c>
-      <c r="D705" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$705),"")</f>
-        <v/>
-      </c>
-      <c r="E705" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$705),"")</f>
-        <v/>
-      </c>
-      <c r="F705" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$705)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="706">
-      <c r="B706" s="2" t="inlineStr">
+      <c r="C780" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$780),"")</f>
+        <v/>
+      </c>
+      <c r="D780" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$780),"")</f>
+        <v/>
+      </c>
+      <c r="E780" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$780),"")</f>
+        <v/>
+      </c>
+      <c r="F780" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$780)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="781">
+      <c r="B781" s="2" t="inlineStr">
         <is>
           <t>SMM六氟磷酸锂指数</t>
         </is>
       </c>
-      <c r="C706" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$706),"")</f>
-        <v/>
-      </c>
-      <c r="D706" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$706),"")</f>
-        <v/>
-      </c>
-      <c r="E706" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$706),"")</f>
-        <v/>
-      </c>
-      <c r="F706" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$706)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="707">
-      <c r="B707" s="2" t="inlineStr">
+      <c r="C781" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$781),"")</f>
+        <v/>
+      </c>
+      <c r="D781" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$781),"")</f>
+        <v/>
+      </c>
+      <c r="E781" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$781),"")</f>
+        <v/>
+      </c>
+      <c r="F781" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$781)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="782">
+      <c r="B782" s="2" t="inlineStr">
         <is>
           <t>SMM电池级氢氧化锂指数</t>
         </is>
       </c>
-      <c r="C707" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$707),"")</f>
-        <v/>
-      </c>
-      <c r="D707" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$707),"")</f>
-        <v/>
-      </c>
-      <c r="E707" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$707),"")</f>
-        <v/>
-      </c>
-      <c r="F707" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$707)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="708">
-      <c r="B708" s="2" t="inlineStr">
+      <c r="C782" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$782),"")</f>
+        <v/>
+      </c>
+      <c r="D782" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$782),"")</f>
+        <v/>
+      </c>
+      <c r="E782" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$782),"")</f>
+        <v/>
+      </c>
+      <c r="F782" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$782)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="783">
+      <c r="B783" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸锰指数</t>
         </is>
       </c>
-      <c r="C708" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$708),"")</f>
-        <v/>
-      </c>
-      <c r="D708" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$708),"")</f>
-        <v/>
-      </c>
-      <c r="E708" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$708),"")</f>
-        <v/>
-      </c>
-      <c r="F708" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$708)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="709">
-      <c r="B709" s="2" t="inlineStr">
+      <c r="C783" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$783),"")</f>
+        <v/>
+      </c>
+      <c r="D783" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$783),"")</f>
+        <v/>
+      </c>
+      <c r="E783" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$783),"")</f>
+        <v/>
+      </c>
+      <c r="F783" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$783)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="784">
+      <c r="B784" s="2" t="inlineStr">
         <is>
           <t>SMM电池级硫酸镍指数</t>
         </is>
       </c>
-      <c r="C709" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$709),"")</f>
-        <v/>
-      </c>
-      <c r="D709" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$709),"")</f>
-        <v/>
-      </c>
-      <c r="E709" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$709),"")</f>
-        <v/>
-      </c>
-      <c r="F709" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$709)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="710">
-      <c r="B710" s="2" t="inlineStr">
+      <c r="C784" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$784),"")</f>
+        <v/>
+      </c>
+      <c r="D784" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$784),"")</f>
+        <v/>
+      </c>
+      <c r="E784" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$784),"")</f>
+        <v/>
+      </c>
+      <c r="F784" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$784)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="785">
+      <c r="B785" s="2" t="inlineStr">
         <is>
           <t>SMM电池级碳酸锂指数</t>
         </is>
       </c>
-      <c r="C710" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$710),"")</f>
-        <v/>
-      </c>
-      <c r="D710" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$710),"")</f>
-        <v/>
-      </c>
-      <c r="E710" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$710),"")</f>
-        <v/>
-      </c>
-      <c r="F710" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$710)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="711">
-      <c r="B711" s="2" t="inlineStr">
+      <c r="C785" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$785),"")</f>
+        <v/>
+      </c>
+      <c r="D785" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$785),"")</f>
+        <v/>
+      </c>
+      <c r="E785" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$785),"")</f>
+        <v/>
+      </c>
+      <c r="F785" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$785)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="786">
+      <c r="B786" s="2" t="inlineStr">
         <is>
           <t>SMM硫酸钴指数</t>
         </is>
       </c>
-      <c r="C711" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$711),"")</f>
-        <v/>
-      </c>
-      <c r="D711" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$711),"")</f>
-        <v/>
-      </c>
-      <c r="E711" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$711),"")</f>
-        <v/>
-      </c>
-      <c r="F711" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$711)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="712">
-      <c r="B712" s="2" t="inlineStr">
+      <c r="C786" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$786),"")</f>
+        <v/>
+      </c>
+      <c r="D786" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$786),"")</f>
+        <v/>
+      </c>
+      <c r="E786" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$786),"")</f>
+        <v/>
+      </c>
+      <c r="F786" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$786)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="787">
+      <c r="B787" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂极片粉指数</t>
         </is>
       </c>
-      <c r="C712" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$712),"")</f>
-        <v/>
-      </c>
-      <c r="D712" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$712),"")</f>
-        <v/>
-      </c>
-      <c r="E712" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$712),"")</f>
-        <v/>
-      </c>
-      <c r="F712" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$712)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="713">
-      <c r="B713" s="2" t="inlineStr">
+      <c r="C787" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$787),"")</f>
+        <v/>
+      </c>
+      <c r="D787" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$787),"")</f>
+        <v/>
+      </c>
+      <c r="E787" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$787),"")</f>
+        <v/>
+      </c>
+      <c r="F787" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$787)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="788">
+      <c r="B788" s="2" t="inlineStr">
         <is>
           <t>SMM磷酸铁锂电池粉指数</t>
         </is>
       </c>
-      <c r="C713" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$713),"")</f>
-        <v/>
-      </c>
-      <c r="D713" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$713),"")</f>
-        <v/>
-      </c>
-      <c r="E713" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$713),"")</f>
-        <v/>
-      </c>
-      <c r="F713" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$713)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="714">
-      <c r="B714" s="2" t="inlineStr">
+      <c r="C788" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$788),"")</f>
+        <v/>
+      </c>
+      <c r="D788" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$788),"")</f>
+        <v/>
+      </c>
+      <c r="E788" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$788),"")</f>
+        <v/>
+      </c>
+      <c r="F788" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$788)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="789">
+      <c r="B789" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉钴系数指数</t>
         </is>
       </c>
-      <c r="C714" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$714),"")</f>
-        <v/>
-      </c>
-      <c r="D714" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$714),"")</f>
-        <v/>
-      </c>
-      <c r="E714" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$714),"")</f>
-        <v/>
-      </c>
-      <c r="F714" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$714)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="715">
-      <c r="B715" s="2" t="inlineStr">
+      <c r="C789" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$789),"")</f>
+        <v/>
+      </c>
+      <c r="D789" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$789),"")</f>
+        <v/>
+      </c>
+      <c r="E789" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$789),"")</f>
+        <v/>
+      </c>
+      <c r="F789" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$789)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="790">
+      <c r="B790" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂极片粉锂系数指数</t>
         </is>
       </c>
-      <c r="C715" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$715),"")</f>
-        <v/>
-      </c>
-      <c r="D715" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$715),"")</f>
-        <v/>
-      </c>
-      <c r="E715" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$715),"")</f>
-        <v/>
-      </c>
-      <c r="F715" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$715)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="716">
-      <c r="B716" s="2" t="inlineStr">
+      <c r="C790" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$790),"")</f>
+        <v/>
+      </c>
+      <c r="D790" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$790),"")</f>
+        <v/>
+      </c>
+      <c r="E790" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$790),"")</f>
+        <v/>
+      </c>
+      <c r="F790" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$790)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="791">
+      <c r="B791" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉钴系数指数</t>
         </is>
       </c>
-      <c r="C716" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$716),"")</f>
-        <v/>
-      </c>
-      <c r="D716" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$716),"")</f>
-        <v/>
-      </c>
-      <c r="E716" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$716),"")</f>
-        <v/>
-      </c>
-      <c r="F716" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$716)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="717">
-      <c r="B717" s="2" t="inlineStr">
+      <c r="C791" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$791),"")</f>
+        <v/>
+      </c>
+      <c r="D791" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$791),"")</f>
+        <v/>
+      </c>
+      <c r="E791" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$791),"")</f>
+        <v/>
+      </c>
+      <c r="F791" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$791)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="792">
+      <c r="B792" s="2" t="inlineStr">
         <is>
           <t>SMM钴酸锂电池粉锂系数指数</t>
         </is>
       </c>
-      <c r="C717" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$717),"")</f>
-        <v/>
-      </c>
-      <c r="D717" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$717),"")</f>
-        <v/>
-      </c>
-      <c r="E717" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$717),"")</f>
-        <v/>
-      </c>
-      <c r="F717" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$717)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="718">
-      <c r="B718" s="2" t="inlineStr">
+      <c r="C792" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$792),"")</f>
+        <v/>
+      </c>
+      <c r="D792" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$792),"")</f>
+        <v/>
+      </c>
+      <c r="E792" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$792),"")</f>
+        <v/>
+      </c>
+      <c r="F792" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$792)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="793">
+      <c r="B793" s="2" t="inlineStr">
         <is>
           <t>三元方壳锂电B品</t>
         </is>
       </c>
-      <c r="C718" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$718),"")</f>
-        <v/>
-      </c>
-      <c r="D718" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$718),"")</f>
-        <v/>
-      </c>
-      <c r="E718" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$718),"")</f>
-        <v/>
-      </c>
-      <c r="F718" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$718)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="719">
-      <c r="B719" s="2" t="inlineStr">
+      <c r="C793" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$793),"")</f>
+        <v/>
+      </c>
+      <c r="D793" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$793),"")</f>
+        <v/>
+      </c>
+      <c r="E793" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$793),"")</f>
+        <v/>
+      </c>
+      <c r="F793" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$793)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="794">
+      <c r="B794" s="2" t="inlineStr">
         <is>
           <t>六氟磷酸锂（国产）</t>
         </is>
       </c>
-      <c r="C719" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$719),"")</f>
-        <v/>
-      </c>
-      <c r="D719" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$719),"")</f>
-        <v/>
-      </c>
-      <c r="E719" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$719),"")</f>
-        <v/>
-      </c>
-      <c r="F719" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$719)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="720">
-      <c r="B720" s="2" t="inlineStr">
+      <c r="C794" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$794),"")</f>
+        <v/>
+      </c>
+      <c r="D794" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$794),"")</f>
+        <v/>
+      </c>
+      <c r="E794" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$794),"")</f>
+        <v/>
+      </c>
+      <c r="F794" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$794)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="795">
+      <c r="B795" s="2" t="inlineStr">
         <is>
           <t>四氧化三钴</t>
         </is>
       </c>
-      <c r="C720" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$720),"")</f>
-        <v/>
-      </c>
-      <c r="D720" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$720),"")</f>
-        <v/>
-      </c>
-      <c r="E720" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$720),"")</f>
-        <v/>
-      </c>
-      <c r="F720" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$720)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="721">
-      <c r="B721" s="2" t="inlineStr">
+      <c r="C795" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$795),"")</f>
+        <v/>
+      </c>
+      <c r="D795" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$795),"")</f>
+        <v/>
+      </c>
+      <c r="E795" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$795),"")</f>
+        <v/>
+      </c>
+      <c r="F795" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$795)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="796">
+      <c r="B796" s="2" t="inlineStr">
         <is>
           <t>四氧化三锰（电池级）</t>
         </is>
       </c>
-      <c r="C721" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$721),"")</f>
-        <v/>
-      </c>
-      <c r="D721" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$721),"")</f>
-        <v/>
-      </c>
-      <c r="E721" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$721),"")</f>
-        <v/>
-      </c>
-      <c r="F721" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$721)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="722">
-      <c r="B722" s="2" t="inlineStr">
+      <c r="C796" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$796),"")</f>
+        <v/>
+      </c>
+      <c r="D796" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$796),"")</f>
+        <v/>
+      </c>
+      <c r="E796" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$796),"")</f>
+        <v/>
+      </c>
+      <c r="F796" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$796)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="797">
+      <c r="B797" s="2" t="inlineStr">
         <is>
           <t>工业级氢氧化锂</t>
         </is>
       </c>
-      <c r="C722" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$722),"")</f>
-        <v/>
-      </c>
-      <c r="D722" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$722),"")</f>
-        <v/>
-      </c>
-      <c r="E722" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$722),"")</f>
-        <v/>
-      </c>
-      <c r="F722" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$722)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="723">
-      <c r="B723" s="2" t="inlineStr">
+      <c r="C797" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$797),"")</f>
+        <v/>
+      </c>
+      <c r="D797" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$797),"")</f>
+        <v/>
+      </c>
+      <c r="E797" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$797),"")</f>
+        <v/>
+      </c>
+      <c r="F797" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$797)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="798">
+      <c r="B798" s="2" t="inlineStr">
         <is>
           <t>工业级碳酸锂</t>
         </is>
       </c>
-      <c r="C723" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$723),"")</f>
-        <v/>
-      </c>
-      <c r="D723" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$723),"")</f>
-        <v/>
-      </c>
-      <c r="E723" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$723),"")</f>
-        <v/>
-      </c>
-      <c r="F723" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$723)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="724">
-      <c r="B724" s="2" t="inlineStr">
+      <c r="C798" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$798),"")</f>
+        <v/>
+      </c>
+      <c r="D798" s="10">
+        <f>IFERROR(AVERAGEIFS(D$2:D$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$798),"")</f>
+        <v/>
+      </c>
+      <c r="E798" s="10">
+        <f>IFERROR(AVERAGEIFS(E$2:E$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$763,$B$798),"")</f>
+        <v/>
+      </c>
+      <c r="F798" s="11">
+        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$763)=YEAR(TODAY()))*(MONTH(A$2:A$763)=MONTH(TODAY()))*(B$2:B$763=$B$798)*(F$2:F$763),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="799">
+      <c r="B799" s="2" t="inlineStr">
         <is>
           <t>工业级金属锂</t>
         </is>
       </c>
-      <c r="C724" s="10">
-        <f>IFERROR(AVERAGEIFS(C$2:C$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$724),"")</f>
-        <v/>
-      </c>
-      <c r="D724" s="10">
-        <f>IFERROR(AVERAGEIFS(D$2:D$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$724),"")</f>
-        <v/>
-      </c>
-      <c r="E724" s="10">
-        <f>IFERROR(AVERAGEIFS(E$2:E$688,A$2:A$688,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$688,"&lt;"&amp;DATE(YEAR(TODAY()),MONTH(TODAY())+1,1),B$2:B$688,$B$724),"")</f>
-        <v/>
-      </c>
-      <c r="F724" s="11">
-        <f>IFERROR(SUMPRODUCT((YEAR(A$2:A$688)=YEAR(TODAY()))*(MONTH(A$2:A$688)=MONTH(TODAY()))*(B$2:B$688=$B$724)*(F$2:F$688),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="725">
-      <c r="B725" s="2" t="inlineStr">
+      <c r="C799" s="10">
+        <f>IFERROR(AVERAGEIFS(C$2:C$763,A$2:A$763,"&gt;="&amp;DATE(YEAR(TODAY()),MONTH(TODAY()),1),A$2:A$763,"&lt;"